--- a/SAP_PPPI_ECC6_to_S4_Migration.xlsx
+++ b/SAP_PPPI_ECC6_to_S4_Migration.xlsx
@@ -15,8 +15,9 @@
     <sheet name="5. משאבים  מרכזי עבודה (Resourc" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="6. פק&quot;ע ייצור ומתכון בקרה (Proc" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="7. קונפיגורציה (Customizing)" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Cockpit מעקב מיגרציה" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="ER - Join Map" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="PP מול PP-PI" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="Cockpit מעקב מיגרציה" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="ER - Join Map" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'מסך ניווט מרכזי'!$A$1:$M$60</definedName>
@@ -27,6 +28,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'5. משאבים  מרכזי עבודה (Resourc'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'6. פק"ע ייצור ומתכון בקרה (Proc'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'7. קונפיגורציה (Customizing)'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="8">'PP מול PP-PI'!$A$1:$E$16</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -35,7 +37,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="44">
+  <fonts count="46">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -161,6 +163,29 @@
     <font>
       <name val="Segoe UI"/>
       <b val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E1E24"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="001E5A44"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <color rgb="009A5A23"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
@@ -243,12 +268,6 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001E5A44"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="Consolas"/>
       <b val="1"/>
       <color rgb="000B5394"/>
@@ -258,12 +277,6 @@
       <name val="Segoe UI"/>
       <b val="1"/>
       <color rgb="0064748B"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Segoe UI"/>
-      <b val="1"/>
-      <color rgb="001E1E24"/>
       <sz val="10"/>
     </font>
     <font>
@@ -465,62 +478,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="93">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="43" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="31" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="35" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -529,27 +542,27 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -625,7 +638,7 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -644,7 +657,7 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -663,36 +676,66 @@
     <xf numFmtId="0" fontId="20" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="34" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -702,13 +745,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="39" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1144,7 +1187,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T649"/>
+  <dimension ref="A1:T663"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1829,9 +1872,9 @@
         </is>
       </c>
       <c r="G13" s="1" t="n"/>
-      <c r="H13" s="24" t="inlineStr">
-        <is>
-          <t>◆ Cockpit מעקב מיגרציה</t>
+      <c r="H13" s="25" t="inlineStr">
+        <is>
+          <t>📚 PP מול PP-PI</t>
         </is>
       </c>
       <c r="I13" s="1" t="n"/>
@@ -1968,11 +2011,15 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="24" t="inlineStr">
         <is>
+          <t>◆ Cockpit מעקב מיגרציה</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
           <t>⇄ ER - Join Map</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="1" t="n"/>
       <c r="E16" s="1" t="n"/>
       <c r="F16" s="1" t="n"/>
       <c r="G16" s="1" t="n"/>
@@ -2021,7 +2068,7 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="26" t="n"/>
       <c r="C17" s="1" t="n"/>
-      <c r="D17" s="1" t="n"/>
+      <c r="D17" s="26" t="n"/>
       <c r="E17" s="1" t="n"/>
       <c r="F17" s="1" t="n"/>
       <c r="G17" s="1" t="n"/>
@@ -2591,7 +2638,7 @@
     <row r="28">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="30">
-        <f>IF(C25="","הקלד מונח וקבל תוצאות מיידיות...",IFERROR(_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6},$T$2:$T$649,$O$2:$O$649,$P$2:$P$649,$Q$2:$Q$649,$R$2:$R$649,$S$2:$S$649),(ISNUMBER(SEARCH(C25,$O$2:$O$649)))+(ISNUMBER(SEARCH(C25,$P$2:$P$649)))+(ISNUMBER(SEARCH(C25,$Q$2:$Q$649)))+(ISNUMBER(SEARCH(C25,$N$2:$N$649)))&gt;0),"לא נמצאו תוצאות"))</f>
+        <f>IF(C25="","הקלד מונח וקבל תוצאות מיידיות...",IFERROR(_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6},$T$2:$T$663,$O$2:$O$663,$P$2:$P$663,$Q$2:$Q$663,$R$2:$R$663,$S$2:$S$663),(ISNUMBER(SEARCH(C25,$O$2:$O$663)))+(ISNUMBER(SEARCH(C25,$P$2:$P$663)))+(ISNUMBER(SEARCH(C25,$Q$2:$Q$663)))+(ISNUMBER(SEARCH(C25,$N$2:$N$663)))&gt;0),"לא נמצאו תוצאות"))</f>
         <v/>
       </c>
       <c r="C28" s="1" t="n"/>
@@ -29867,23 +29914,27 @@
       <c r="M588" s="4" t="n"/>
       <c r="N588" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O588" s="6" t="inlineStr">
         <is>
-          <t>FROM MAKT JOIN MARA ON MAKT.MATNR = MARA.MATNR</t>
+          <t>סוג ייצור (Production type)</t>
         </is>
       </c>
       <c r="P588" s="4" t="inlineStr">
         <is>
-          <t>תיאורי חומר (טקסטים)</t>
-        </is>
-      </c>
-      <c r="Q588" s="4" t="inlineStr"/>
+          <t>ייצור בדיד / יחידות (Discrete)</t>
+        </is>
+      </c>
+      <c r="Q588" s="4" t="inlineStr">
+        <is>
+          <t>ייצור תהליכי / אצוות ונוזלים (Process)</t>
+        </is>
+      </c>
       <c r="R588" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S588" s="4" t="inlineStr">
@@ -29912,23 +29963,27 @@
       <c r="M589" s="4" t="n"/>
       <c r="N589" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O589" s="6" t="inlineStr">
         <is>
-          <t>FROM MARC JOIN MARA ON MARC.MATNR = MARA.MATNR</t>
+          <t>ענפים אופייניים (Industries)</t>
         </is>
       </c>
       <c r="P589" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מפעל</t>
-        </is>
-      </c>
-      <c r="Q589" s="4" t="inlineStr"/>
+          <t>רכב, אלקטרוניקה, מכונות, הרכבה</t>
+        </is>
+      </c>
+      <c r="Q589" s="4" t="inlineStr">
+        <is>
+          <t>מזון ומשקאות, כימיה, פארמה, קוסמטיקה</t>
+        </is>
+      </c>
       <c r="R589" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S589" s="4" t="inlineStr">
@@ -29957,23 +30012,27 @@
       <c r="M590" s="4" t="n"/>
       <c r="N590" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O590" s="6" t="inlineStr">
         <is>
-          <t>FROM MARD JOIN MARC ON MARD.MATNR = MARC.MATNR AND MARD.WERKS = MARC.WERKS</t>
+          <t>נתוני אב חומר (Material)</t>
         </is>
       </c>
       <c r="P590" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מחסן/מלאי</t>
-        </is>
-      </c>
-      <c r="Q590" s="4" t="inlineStr"/>
+          <t>חומר סטנדרטי (לרוב ללא אצווה)</t>
+        </is>
+      </c>
+      <c r="Q590" s="4" t="inlineStr">
+        <is>
+          <t>חומר מנוהל אצווה (Batch-managed) - חובה</t>
+        </is>
+      </c>
       <c r="R590" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S590" s="4" t="inlineStr">
@@ -30002,23 +30061,27 @@
       <c r="M591" s="4" t="n"/>
       <c r="N591" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O591" s="6" t="inlineStr">
         <is>
-          <t>FROM MARM JOIN MARA ON MARM.MATNR = MARA.MATNR</t>
+          <t>הוראת ייצור (Order)</t>
         </is>
       </c>
       <c r="P591" s="4" t="inlineStr">
         <is>
-          <t>המרות יחידות מידה חלופיות</t>
-        </is>
-      </c>
-      <c r="Q591" s="4" t="inlineStr"/>
+          <t>Production Order - CO01 / CO02 / CO03</t>
+        </is>
+      </c>
+      <c r="Q591" s="4" t="inlineStr">
+        <is>
+          <t>Process Order - COR1 / COR2 / COR3</t>
+        </is>
+      </c>
       <c r="R591" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S591" s="4" t="inlineStr">
@@ -30047,23 +30110,27 @@
       <c r="M592" s="4" t="n"/>
       <c r="N592" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O592" s="6" t="inlineStr">
         <is>
-          <t>FROM MEAN JOIN MARA ON MEAN.MATNR = MARA.MATNR</t>
+          <t>רשימת פעולות (Routing/Recipe)</t>
         </is>
       </c>
       <c r="P592" s="4" t="inlineStr">
         <is>
-          <t>ברקודים / EAN לחומר</t>
-        </is>
-      </c>
-      <c r="Q592" s="4" t="inlineStr"/>
+          <t>Routing - CA01 / CA02 / CA03</t>
+        </is>
+      </c>
+      <c r="Q592" s="4" t="inlineStr">
+        <is>
+          <t>Master Recipe (מתכון ייצור) - C201 / C202 / C203</t>
+        </is>
+      </c>
       <c r="R592" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S592" s="4" t="inlineStr">
@@ -30092,23 +30159,27 @@
       <c r="M593" s="4" t="n"/>
       <c r="N593" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O593" s="6" t="inlineStr">
         <is>
-          <t>FROM MBEW JOIN MARA ON MBEW.MATNR = MARA.MATNR</t>
+          <t>מבנה ביצוע (Execution structure)</t>
         </is>
       </c>
       <c r="P593" s="4" t="inlineStr">
         <is>
-          <t>הערכת חומר (Valuation)</t>
-        </is>
-      </c>
-      <c r="Q593" s="4" t="inlineStr"/>
+          <t>Operations (פעולות בלבד)</t>
+        </is>
+      </c>
+      <c r="Q593" s="4" t="inlineStr">
+        <is>
+          <t>Operations + Phases + Process Instructions (PI)</t>
+        </is>
+      </c>
       <c r="R593" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S593" s="4" t="inlineStr">
@@ -30137,23 +30208,27 @@
       <c r="M594" s="4" t="n"/>
       <c r="N594" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O594" s="6" t="inlineStr">
         <is>
-          <t>FROM MVKE JOIN MARA ON MVKE.MATNR = MARA.MATNR</t>
+          <t>משאבי ביצוע (Resources)</t>
         </is>
       </c>
       <c r="P594" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מכירות</t>
-        </is>
-      </c>
-      <c r="Q594" s="4" t="inlineStr"/>
+          <t>Work Center - CR01 / CR02 / CR03</t>
+        </is>
+      </c>
+      <c r="Q594" s="4" t="inlineStr">
+        <is>
+          <t>Resource - CRC1 / CRC2 / CRC3</t>
+        </is>
+      </c>
       <c r="R594" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S594" s="4" t="inlineStr">
@@ -30182,23 +30257,27 @@
       <c r="M595" s="4" t="n"/>
       <c r="N595" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O595" s="6" t="inlineStr">
         <is>
-          <t>FROM MLAN JOIN MARA ON MLAN.MATNR = MARA.MATNR</t>
+          <t>בקרת ביצוע (Shop-floor control)</t>
         </is>
       </c>
       <c r="P595" s="4" t="inlineStr">
         <is>
-          <t>נתוני מס לחומר (לפי מדינה)</t>
-        </is>
-      </c>
-      <c r="Q595" s="4" t="inlineStr"/>
+          <t>דיווח ביצוע (Confirmation) ידני/MES</t>
+        </is>
+      </c>
+      <c r="Q595" s="4" t="inlineStr">
+        <is>
+          <t>Control Recipe / PI Sheet / Process Messages</t>
+        </is>
+      </c>
       <c r="R595" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S595" s="4" t="inlineStr">
@@ -30227,23 +30306,27 @@
       <c r="M596" s="4" t="n"/>
       <c r="N596" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O596" s="6" t="inlineStr">
         <is>
-          <t>FROM MLGN JOIN MARA ON MLGN.MATNR = MARA.MATNR</t>
+          <t>מערכת מעקב (Monitoring cockpit)</t>
         </is>
       </c>
       <c r="P596" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מחסן (WM)</t>
-        </is>
-      </c>
-      <c r="Q596" s="4" t="inlineStr"/>
+          <t>COOIS (Order Information System)</t>
+        </is>
+      </c>
+      <c r="Q596" s="4" t="inlineStr">
+        <is>
+          <t>COIO (Process Order Information System) + PI Cockpit</t>
+        </is>
+      </c>
       <c r="R596" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S596" s="4" t="inlineStr">
@@ -30272,23 +30355,27 @@
       <c r="M597" s="4" t="n"/>
       <c r="N597" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O597" s="6" t="inlineStr">
         <is>
-          <t>FROM MLGT JOIN MLGN ON MLGT.MATNR = MLGN.MATNR AND MLGT.LGNUM = MLGN.LGNUM</t>
+          <t>עץ מוצר (BOM)</t>
         </is>
       </c>
       <c r="P597" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר לפי טיפוס אחסון</t>
-        </is>
-      </c>
-      <c r="Q597" s="4" t="inlineStr"/>
+          <t>Production BOM (STLAN=1)</t>
+        </is>
+      </c>
+      <c r="Q597" s="4" t="inlineStr">
+        <is>
+          <t>Recipe BOM + שיוך רכיב לפאזה (PLMZ)</t>
+        </is>
+      </c>
       <c r="R597" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S597" s="4" t="inlineStr">
@@ -30317,23 +30404,27 @@
       <c r="M598" s="4" t="n"/>
       <c r="N598" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O598" s="6" t="inlineStr">
         <is>
-          <t>FROM MDMA JOIN MARC ON MDMA.MATNR = MARC.MATNR AND MDMA.WERKS = MARC.WERKS</t>
+          <t>גרסת ייצור (Production Version)</t>
         </is>
       </c>
       <c r="P598" s="4" t="inlineStr">
         <is>
-          <t>אזורי MRP לחומר</t>
-        </is>
-      </c>
-      <c r="Q598" s="4" t="inlineStr"/>
+          <t>MKAL - מומלצת ב-ECC</t>
+        </is>
+      </c>
+      <c r="Q598" s="4" t="inlineStr">
+        <is>
+          <t>MKAL - חובה 100% ב-S/4HANA</t>
+        </is>
+      </c>
       <c r="R598" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S598" s="4" t="inlineStr">
@@ -30362,23 +30453,27 @@
       <c r="M599" s="4" t="n"/>
       <c r="N599" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O599" s="6" t="inlineStr">
         <is>
-          <t>FROM QMAT JOIN MARC ON QMAT.MATNR = MARC.MATNR AND QMAT.WERKS = MARC.WERKS</t>
+          <t>תכנון חומרים (Planning)</t>
         </is>
       </c>
       <c r="P599" s="4" t="inlineStr">
         <is>
-          <t>הגדרות בדיקת איכות לחומר</t>
-        </is>
-      </c>
-      <c r="Q599" s="4" t="inlineStr"/>
+          <t>MRP קלאסי - MD01 / NETCH</t>
+        </is>
+      </c>
+      <c r="Q599" s="4" t="inlineStr">
+        <is>
+          <t>MRP Live (HANA-optimized) - MD01N</t>
+        </is>
+      </c>
       <c r="R599" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S599" s="4" t="inlineStr">
@@ -30407,23 +30502,27 @@
       <c r="M600" s="4" t="n"/>
       <c r="N600" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O600" s="6" t="inlineStr">
         <is>
-          <t>FROM MCH1 JOIN MARA ON MCH1.MATNR = MARA.MATNR</t>
+          <t>ממשק חיצוני (IDoc/MES)</t>
         </is>
       </c>
       <c r="P600" s="4" t="inlineStr">
         <is>
-          <t>אצוות חומר (Batches)</t>
-        </is>
-      </c>
-      <c r="Q600" s="4" t="inlineStr"/>
+          <t>LOIPRO (Production Order)</t>
+        </is>
+      </c>
+      <c r="Q600" s="4" t="inlineStr">
+        <is>
+          <t>LOIPRO + PI Process Messages (PPCC1)</t>
+        </is>
+      </c>
       <c r="R600" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S600" s="4" t="inlineStr">
@@ -30452,23 +30551,27 @@
       <c r="M601" s="4" t="n"/>
       <c r="N601" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>PP/PP-PI</t>
         </is>
       </c>
       <c r="O601" s="6" t="inlineStr">
         <is>
-          <t>FROM MCHA JOIN MCH1 ON MCHA.MATNR = MCH1.MATNR AND MCHA.CHARG = MCH1.CHARG</t>
+          <t>עלות והערכה (Costing)</t>
         </is>
       </c>
       <c r="P601" s="4" t="inlineStr">
         <is>
-          <t>אצוות חומר ברמת מפעל</t>
-        </is>
-      </c>
-      <c r="Q601" s="4" t="inlineStr"/>
+          <t>Order settlement -&gt; CO</t>
+        </is>
+      </c>
+      <c r="Q601" s="4" t="inlineStr">
+        <is>
+          <t>Order settlement -&gt; Universal Journal (ACDOCA)</t>
+        </is>
+      </c>
       <c r="R601" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP מול PP-PI</t>
         </is>
       </c>
       <c r="S601" s="4" t="inlineStr">
@@ -30502,12 +30605,12 @@
       </c>
       <c r="O602" s="6" t="inlineStr">
         <is>
-          <t>FROM MARM JOIN T006 ON MARM.MEINH = T006.MSEHI</t>
+          <t>FROM MAKT JOIN MARA ON MAKT.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P602" s="4" t="inlineStr">
         <is>
-          <t>יחידות מידה (Customizing)</t>
+          <t>תיאורי חומר (טקסטים)</t>
         </is>
       </c>
       <c r="Q602" s="4" t="inlineStr"/>
@@ -30518,7 +30621,7 @@
       </c>
       <c r="S602" s="4" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="T602" s="7">
@@ -30547,12 +30650,12 @@
       </c>
       <c r="O603" s="6" t="inlineStr">
         <is>
-          <t>FROM MAST JOIN MARA ON MAST.MATNR = MARA.MATNR</t>
+          <t>FROM MARC JOIN MARA ON MARC.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P603" s="4" t="inlineStr">
         <is>
-          <t>קישור חומר לעץ מוצר</t>
+          <t>נתוני חומר ברמת מפעל</t>
         </is>
       </c>
       <c r="Q603" s="4" t="inlineStr"/>
@@ -30563,7 +30666,7 @@
       </c>
       <c r="S603" s="4" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="T603" s="7">
@@ -30592,12 +30695,12 @@
       </c>
       <c r="O604" s="6" t="inlineStr">
         <is>
-          <t>FROM STKO JOIN MAST ON STKO.STLNR = MAST.STLNR</t>
+          <t>FROM MARD JOIN MARC ON MARD.MATNR = MARC.MATNR AND MARD.WERKS = MARC.WERKS</t>
         </is>
       </c>
       <c r="P604" s="4" t="inlineStr">
         <is>
-          <t>כותרת עץ מוצר</t>
+          <t>נתוני חומר ברמת מחסן/מלאי</t>
         </is>
       </c>
       <c r="Q604" s="4" t="inlineStr"/>
@@ -30608,7 +30711,7 @@
       </c>
       <c r="S604" s="4" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="T604" s="7">
@@ -30637,12 +30740,12 @@
       </c>
       <c r="O605" s="6" t="inlineStr">
         <is>
-          <t>FROM STPO JOIN STKO ON STPO.STLNR = STKO.STLNR AND STPO.STLTY = STKO.STLTY</t>
+          <t>FROM MARM JOIN MARA ON MARM.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P605" s="4" t="inlineStr">
         <is>
-          <t>פריטי עץ מוצר (רכיבים)</t>
+          <t>המרות יחידות מידה חלופיות</t>
         </is>
       </c>
       <c r="Q605" s="4" t="inlineStr"/>
@@ -30653,7 +30756,7 @@
       </c>
       <c r="S605" s="4" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="T605" s="7">
@@ -30682,12 +30785,12 @@
       </c>
       <c r="O606" s="6" t="inlineStr">
         <is>
-          <t>FROM STAS JOIN STKO ON STAS.STLNR = STKO.STLNR</t>
+          <t>FROM MEAN JOIN MARA ON MEAN.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P606" s="4" t="inlineStr">
         <is>
-          <t>בחירת פריטי עץ מוצר</t>
+          <t>ברקודים / EAN לחומר</t>
         </is>
       </c>
       <c r="Q606" s="4" t="inlineStr"/>
@@ -30698,7 +30801,7 @@
       </c>
       <c r="S606" s="4" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="T606" s="7">
@@ -30727,12 +30830,12 @@
       </c>
       <c r="O607" s="6" t="inlineStr">
         <is>
-          <t>FROM STZU JOIN STKO ON STZU.STLNR = STKO.STLNR</t>
+          <t>FROM MBEW JOIN MARA ON MBEW.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P607" s="4" t="inlineStr">
         <is>
-          <t>טבלת היסטוריה/קישור לעץ מוצר</t>
+          <t>הערכת חומר (Valuation)</t>
         </is>
       </c>
       <c r="Q607" s="4" t="inlineStr"/>
@@ -30743,7 +30846,7 @@
       </c>
       <c r="S607" s="4" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="T607" s="7">
@@ -30772,12 +30875,12 @@
       </c>
       <c r="O608" s="6" t="inlineStr">
         <is>
-          <t>FROM STPU JOIN STPO ON STPU.STLKN = STPO.STLKN</t>
+          <t>FROM MVKE JOIN MARA ON MVKE.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P608" s="4" t="inlineStr">
         <is>
-          <t>טקסטים ארוכים לפריט עץ מוצר</t>
+          <t>נתוני חומר ברמת מכירות</t>
         </is>
       </c>
       <c r="Q608" s="4" t="inlineStr"/>
@@ -30788,7 +30891,7 @@
       </c>
       <c r="S608" s="4" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="T608" s="7">
@@ -30817,12 +30920,12 @@
       </c>
       <c r="O609" s="6" t="inlineStr">
         <is>
-          <t>FROM KDST JOIN MAST ON KDST.MATNR = MAST.MATNR</t>
+          <t>FROM MLAN JOIN MARA ON MLAN.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P609" s="4" t="inlineStr">
         <is>
-          <t>שימוש עץ מוצר בהזמנת לקוח</t>
+          <t>נתוני מס לחומר (לפי מדינה)</t>
         </is>
       </c>
       <c r="Q609" s="4" t="inlineStr"/>
@@ -30833,7 +30936,7 @@
       </c>
       <c r="S609" s="4" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="T609" s="7">
@@ -30862,12 +30965,12 @@
       </c>
       <c r="O610" s="6" t="inlineStr">
         <is>
-          <t>FROM PLKO JOIN MAPL ON PLKO.PLNTY = MAPL.PLNTY AND PLKO.PLNNR = MAPL.PLNNR</t>
+          <t>FROM MLGN JOIN MARA ON MLGN.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P610" s="4" t="inlineStr">
         <is>
-          <t>כותרת מתכון ייצור / רשימת פעולות</t>
+          <t>נתוני חומר ברמת מחסן (WM)</t>
         </is>
       </c>
       <c r="Q610" s="4" t="inlineStr"/>
@@ -30878,7 +30981,7 @@
       </c>
       <c r="S610" s="4" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="T610" s="7">
@@ -30907,12 +31010,12 @@
       </c>
       <c r="O611" s="6" t="inlineStr">
         <is>
-          <t>FROM PLPO JOIN PLAS ON PLPO.PLNTY = PLAS.PLNTY AND PLPO.PLNNR = PLAS.PLNNR AND PLPO.PLNKN = PLAS.PLNKN</t>
+          <t>FROM MLGT JOIN MLGN ON MLGT.MATNR = MLGN.MATNR AND MLGT.LGNUM = MLGN.LGNUM</t>
         </is>
       </c>
       <c r="P611" s="4" t="inlineStr">
         <is>
-          <t>פעולות/פאזות במתכון</t>
+          <t>נתוני חומר לפי טיפוס אחסון</t>
         </is>
       </c>
       <c r="Q611" s="4" t="inlineStr"/>
@@ -30923,7 +31026,7 @@
       </c>
       <c r="S611" s="4" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="T611" s="7">
@@ -30952,12 +31055,12 @@
       </c>
       <c r="O612" s="6" t="inlineStr">
         <is>
-          <t>FROM PLAS JOIN PLKO ON PLAS.PLNTY = PLKO.PLNTY AND PLAS.PLNNR = PLKO.PLNNR</t>
+          <t>FROM MDMA JOIN MARC ON MDMA.MATNR = MARC.MATNR AND MDMA.WERKS = MARC.WERKS</t>
         </is>
       </c>
       <c r="P612" s="4" t="inlineStr">
         <is>
-          <t>שיוך/בחירת פעולות לרשימה</t>
+          <t>אזורי MRP לחומר</t>
         </is>
       </c>
       <c r="Q612" s="4" t="inlineStr"/>
@@ -30968,7 +31071,7 @@
       </c>
       <c r="S612" s="4" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="T612" s="7">
@@ -30997,12 +31100,12 @@
       </c>
       <c r="O613" s="6" t="inlineStr">
         <is>
-          <t>FROM PLFL JOIN PLKO ON PLFL.PLNNR = PLKO.PLNNR</t>
+          <t>FROM QMAT JOIN MARC ON QMAT.MATNR = MARC.MATNR AND QMAT.WERKS = MARC.WERKS</t>
         </is>
       </c>
       <c r="P613" s="4" t="inlineStr">
         <is>
-          <t>רצפים במתכון</t>
+          <t>הגדרות בדיקת איכות לחומר</t>
         </is>
       </c>
       <c r="Q613" s="4" t="inlineStr"/>
@@ -31013,7 +31116,7 @@
       </c>
       <c r="S613" s="4" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="T613" s="7">
@@ -31042,12 +31145,12 @@
       </c>
       <c r="O614" s="6" t="inlineStr">
         <is>
-          <t>FROM PLMZ JOIN PLPO ON PLMZ.PLNKN = PLPO.PLNKN</t>
+          <t>FROM MCH1 JOIN MARA ON MCH1.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P614" s="4" t="inlineStr">
         <is>
-          <t>שיוך רכיבים לפעולות</t>
+          <t>אצוות חומר (Batches)</t>
         </is>
       </c>
       <c r="Q614" s="4" t="inlineStr"/>
@@ -31058,7 +31161,7 @@
       </c>
       <c r="S614" s="4" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="T614" s="7">
@@ -31087,12 +31190,12 @@
       </c>
       <c r="O615" s="6" t="inlineStr">
         <is>
-          <t>FROM PLMK JOIN PLPO ON PLMK.PLNKN = PLPO.PLNKN</t>
+          <t>FROM MCHA JOIN MCH1 ON MCHA.MATNR = MCH1.MATNR AND MCHA.CHARG = MCH1.CHARG</t>
         </is>
       </c>
       <c r="P615" s="4" t="inlineStr">
         <is>
-          <t>מאפייני בדיקה במתכון</t>
+          <t>אצוות חומר ברמת מפעל</t>
         </is>
       </c>
       <c r="Q615" s="4" t="inlineStr"/>
@@ -31103,7 +31206,7 @@
       </c>
       <c r="S615" s="4" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="T615" s="7">
@@ -31132,12 +31235,12 @@
       </c>
       <c r="O616" s="6" t="inlineStr">
         <is>
-          <t>FROM MAPL JOIN MARC ON MAPL.MATNR = MARC.MATNR AND MAPL.WERKS = MARC.WERKS</t>
+          <t>FROM MARM JOIN T006 ON MARM.MEINH = T006.MSEHI</t>
         </is>
       </c>
       <c r="P616" s="4" t="inlineStr">
         <is>
-          <t>שיוך חומר למתכון/רשימת פעולות</t>
+          <t>יחידות מידה (Customizing)</t>
         </is>
       </c>
       <c r="Q616" s="4" t="inlineStr"/>
@@ -31148,7 +31251,7 @@
       </c>
       <c r="S616" s="4" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="T616" s="7">
@@ -31177,12 +31280,12 @@
       </c>
       <c r="O617" s="6" t="inlineStr">
         <is>
-          <t>FROM FHMI JOIN PLPO ON FHMI.PLNKN = PLPO.PLNKN</t>
+          <t>FROM MAST JOIN MARA ON MAST.MATNR = MARA.MATNR</t>
         </is>
       </c>
       <c r="P617" s="4" t="inlineStr">
         <is>
-          <t>שיוך כלי עזר ייצור (PRT) לפעולה</t>
+          <t>קישור חומר לעץ מוצר</t>
         </is>
       </c>
       <c r="Q617" s="4" t="inlineStr"/>
@@ -31193,7 +31296,7 @@
       </c>
       <c r="S617" s="4" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="T617" s="7">
@@ -31222,12 +31325,12 @@
       </c>
       <c r="O618" s="6" t="inlineStr">
         <is>
-          <t>FROM PLZU JOIN PLKO ON PLZU.PLNNR = PLKO.PLNNR</t>
+          <t>FROM STKO JOIN MAST ON STKO.STLNR = MAST.STLNR</t>
         </is>
       </c>
       <c r="P618" s="4" t="inlineStr">
         <is>
-          <t>קישור היסטוריית רשימת פעולות</t>
+          <t>כותרת עץ מוצר</t>
         </is>
       </c>
       <c r="Q618" s="4" t="inlineStr"/>
@@ -31238,7 +31341,7 @@
       </c>
       <c r="S618" s="4" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="T618" s="7">
@@ -31267,12 +31370,12 @@
       </c>
       <c r="O619" s="6" t="inlineStr">
         <is>
-          <t>FROM PLPO JOIN TC60 ON PLPO.STEUS = TC60.STEUS</t>
+          <t>FROM STPO JOIN STKO ON STPO.STLNR = STKO.STLNR AND STPO.STLTY = STKO.STLTY</t>
         </is>
       </c>
       <c r="P619" s="4" t="inlineStr">
         <is>
-          <t>מאפייני הוראות תהליך (PI)</t>
+          <t>פריטי עץ מוצר (רכיבים)</t>
         </is>
       </c>
       <c r="Q619" s="4" t="inlineStr"/>
@@ -31283,7 +31386,7 @@
       </c>
       <c r="S619" s="4" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="T619" s="7">
@@ -31312,12 +31415,12 @@
       </c>
       <c r="O620" s="6" t="inlineStr">
         <is>
-          <t>FROM PLKO JOIN TCA01 ON PLKO.PROFIDNETZ = TCA01.PROFIDNETZ</t>
+          <t>FROM STAS JOIN STKO ON STAS.STLNR = STKO.STLNR</t>
         </is>
       </c>
       <c r="P620" s="4" t="inlineStr">
         <is>
-          <t>פרופיל רשימת פעולות (Customizing)</t>
+          <t>בחירת פריטי עץ מוצר</t>
         </is>
       </c>
       <c r="Q620" s="4" t="inlineStr"/>
@@ -31328,7 +31431,7 @@
       </c>
       <c r="S620" s="4" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="T620" s="7">
@@ -31357,12 +31460,12 @@
       </c>
       <c r="O621" s="6" t="inlineStr">
         <is>
-          <t>FROM MKAL JOIN MARC ON MKAL.MATNR = MARC.MATNR AND MKAL.WERKS = MARC.WERKS</t>
+          <t>FROM STZU JOIN STKO ON STZU.STLNR = STKO.STLNR</t>
         </is>
       </c>
       <c r="P621" s="4" t="inlineStr">
         <is>
-          <t>גרסאות ייצור לחומר</t>
+          <t>טבלת היסטוריה/קישור לעץ מוצר</t>
         </is>
       </c>
       <c r="Q621" s="4" t="inlineStr"/>
@@ -31373,7 +31476,7 @@
       </c>
       <c r="S621" s="4" t="inlineStr">
         <is>
-          <t>A36</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="T621" s="7">
@@ -31402,12 +31505,12 @@
       </c>
       <c r="O622" s="6" t="inlineStr">
         <is>
-          <t>FROM CRTX JOIN CRHD ON CRTX.OBJID = CRHD.OBJID AND CRTX.OBJTY = CRHD.OBJTY</t>
+          <t>FROM STPU JOIN STPO ON STPU.STLKN = STPO.STLKN</t>
         </is>
       </c>
       <c r="P622" s="4" t="inlineStr">
         <is>
-          <t>טקסטים של משאב</t>
+          <t>טקסטים ארוכים לפריט עץ מוצר</t>
         </is>
       </c>
       <c r="Q622" s="4" t="inlineStr"/>
@@ -31418,7 +31521,7 @@
       </c>
       <c r="S622" s="4" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="T622" s="7">
@@ -31447,12 +31550,12 @@
       </c>
       <c r="O623" s="6" t="inlineStr">
         <is>
-          <t>FROM CRCO JOIN CRHD ON CRCO.OBJID = CRHD.OBJID AND CRCO.OBJTY = CRHD.OBJTY</t>
+          <t>FROM KDST JOIN MAST ON KDST.MATNR = MAST.MATNR</t>
         </is>
       </c>
       <c r="P623" s="4" t="inlineStr">
         <is>
-          <t>שיוך משאב למרכז עלות</t>
+          <t>שימוש עץ מוצר בהזמנת לקוח</t>
         </is>
       </c>
       <c r="Q623" s="4" t="inlineStr"/>
@@ -31463,7 +31566,7 @@
       </c>
       <c r="S623" s="4" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="T623" s="7">
@@ -31492,12 +31595,12 @@
       </c>
       <c r="O624" s="6" t="inlineStr">
         <is>
-          <t>FROM CRCA JOIN CRHD ON CRCA.OBJID = CRHD.OBJID AND CRCA.OBJTY = CRHD.OBJTY</t>
+          <t>FROM PLKO JOIN MAPL ON PLKO.PLNTY = MAPL.PLNTY AND PLKO.PLNNR = MAPL.PLNNR</t>
         </is>
       </c>
       <c r="P624" s="4" t="inlineStr">
         <is>
-          <t>הקצאת קיבולת למשאב</t>
+          <t>כותרת מתכון ייצור / רשימת פעולות</t>
         </is>
       </c>
       <c r="Q624" s="4" t="inlineStr"/>
@@ -31508,7 +31611,7 @@
       </c>
       <c r="S624" s="4" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="T624" s="7">
@@ -31537,12 +31640,12 @@
       </c>
       <c r="O625" s="6" t="inlineStr">
         <is>
-          <t>FROM KAKO JOIN CRCA ON KAKO.KAPID = CRCA.KAPID</t>
+          <t>FROM PLPO JOIN PLAS ON PLPO.PLNTY = PLAS.PLNTY AND PLPO.PLNNR = PLAS.PLNNR AND PLPO.PLNKN = PLAS.PLNKN</t>
         </is>
       </c>
       <c r="P625" s="4" t="inlineStr">
         <is>
-          <t>כותרת קיבולת</t>
+          <t>פעולות/פאזות במתכון</t>
         </is>
       </c>
       <c r="Q625" s="4" t="inlineStr"/>
@@ -31553,7 +31656,7 @@
       </c>
       <c r="S625" s="4" t="inlineStr">
         <is>
-          <t>A40</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="T625" s="7">
@@ -31582,12 +31685,12 @@
       </c>
       <c r="O626" s="6" t="inlineStr">
         <is>
-          <t>FROM FHMI JOIN CRFH ON FHMI.FHMNR = CRFH.FHMNR</t>
+          <t>FROM PLAS JOIN PLKO ON PLAS.PLNTY = PLKO.PLNTY AND PLAS.PLNNR = PLKO.PLNNR</t>
         </is>
       </c>
       <c r="P626" s="4" t="inlineStr">
         <is>
-          <t>אב כלי עזר ייצור (PRT)</t>
+          <t>שיוך/בחירת פעולות לרשימה</t>
         </is>
       </c>
       <c r="Q626" s="4" t="inlineStr"/>
@@ -31598,7 +31701,7 @@
       </c>
       <c r="S626" s="4" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="T626" s="7">
@@ -31627,12 +31730,12 @@
       </c>
       <c r="O627" s="6" t="inlineStr">
         <is>
-          <t>FROM CRVD_A JOIN CRHD ON CRVD_A.OBJID = CRHD.OBJID</t>
+          <t>FROM PLFL JOIN PLKO ON PLFL.PLNNR = PLKO.PLNNR</t>
         </is>
       </c>
       <c r="P627" s="4" t="inlineStr">
         <is>
-          <t>ברירות מחדל למשאב (PI)</t>
+          <t>רצפים במתכון</t>
         </is>
       </c>
       <c r="Q627" s="4" t="inlineStr"/>
@@ -31643,7 +31746,7 @@
       </c>
       <c r="S627" s="4" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="T627" s="7">
@@ -31672,12 +31775,12 @@
       </c>
       <c r="O628" s="6" t="inlineStr">
         <is>
-          <t>FROM CSLA JOIN CRCO ON CSLA.LSTAR = CRCO.LSTAR</t>
+          <t>FROM PLMZ JOIN PLPO ON PLMZ.PLNKN = PLPO.PLNKN</t>
         </is>
       </c>
       <c r="P628" s="4" t="inlineStr">
         <is>
-          <t>סוגי פעילות למרכז עבודה</t>
+          <t>שיוך רכיבים לפעולות</t>
         </is>
       </c>
       <c r="Q628" s="4" t="inlineStr"/>
@@ -31688,7 +31791,7 @@
       </c>
       <c r="S628" s="4" t="inlineStr">
         <is>
-          <t>A43</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="T628" s="7">
@@ -31717,12 +31820,12 @@
       </c>
       <c r="O629" s="6" t="inlineStr">
         <is>
-          <t>FROM KAZT JOIN KAKO ON KAZT.KAPID = KAKO.KAPID</t>
+          <t>FROM PLMK JOIN PLPO ON PLMK.PLNKN = PLPO.PLNKN</t>
         </is>
       </c>
       <c r="P629" s="4" t="inlineStr">
         <is>
-          <t>מרווחי קיבולת זמינה</t>
+          <t>מאפייני בדיקה במתכון</t>
         </is>
       </c>
       <c r="Q629" s="4" t="inlineStr"/>
@@ -31733,7 +31836,7 @@
       </c>
       <c r="S629" s="4" t="inlineStr">
         <is>
-          <t>A44</t>
+          <t>A30</t>
         </is>
       </c>
       <c r="T629" s="7">
@@ -31762,12 +31865,12 @@
       </c>
       <c r="O630" s="6" t="inlineStr">
         <is>
-          <t>FROM AFKO JOIN AUFK ON AFKO.AUFNR = AUFK.AUFNR</t>
+          <t>FROM MAPL JOIN MARC ON MAPL.MATNR = MARC.MATNR AND MAPL.WERKS = MARC.WERKS</t>
         </is>
       </c>
       <c r="P630" s="4" t="inlineStr">
         <is>
-          <t>כותרת פקודת ייצור</t>
+          <t>שיוך חומר למתכון/רשימת פעולות</t>
         </is>
       </c>
       <c r="Q630" s="4" t="inlineStr"/>
@@ -31778,7 +31881,7 @@
       </c>
       <c r="S630" s="4" t="inlineStr">
         <is>
-          <t>A45</t>
+          <t>A31</t>
         </is>
       </c>
       <c r="T630" s="7">
@@ -31807,12 +31910,12 @@
       </c>
       <c r="O631" s="6" t="inlineStr">
         <is>
-          <t>FROM AFPO JOIN AFKO ON AFPO.AUFNR = AFKO.AUFNR</t>
+          <t>FROM FHMI JOIN PLPO ON FHMI.PLNKN = PLPO.PLNKN</t>
         </is>
       </c>
       <c r="P631" s="4" t="inlineStr">
         <is>
-          <t>פריט פקודת ייצור</t>
+          <t>שיוך כלי עזר ייצור (PRT) לפעולה</t>
         </is>
       </c>
       <c r="Q631" s="4" t="inlineStr"/>
@@ -31823,7 +31926,7 @@
       </c>
       <c r="S631" s="4" t="inlineStr">
         <is>
-          <t>A46</t>
+          <t>A32</t>
         </is>
       </c>
       <c r="T631" s="7">
@@ -31852,12 +31955,12 @@
       </c>
       <c r="O632" s="6" t="inlineStr">
         <is>
-          <t>FROM AFVC JOIN AFKO ON AFVC.AUFPL = AFKO.AUFPL</t>
+          <t>FROM PLZU JOIN PLKO ON PLZU.PLNNR = PLKO.PLNNR</t>
         </is>
       </c>
       <c r="P632" s="4" t="inlineStr">
         <is>
-          <t>פעולות פקודת הייצור</t>
+          <t>קישור היסטוריית רשימת פעולות</t>
         </is>
       </c>
       <c r="Q632" s="4" t="inlineStr"/>
@@ -31868,7 +31971,7 @@
       </c>
       <c r="S632" s="4" t="inlineStr">
         <is>
-          <t>A47</t>
+          <t>A33</t>
         </is>
       </c>
       <c r="T632" s="7">
@@ -31897,12 +32000,12 @@
       </c>
       <c r="O633" s="6" t="inlineStr">
         <is>
-          <t>FROM RESB JOIN AFKO ON RESB.AUFNR = AFKO.AUFNR</t>
+          <t>FROM PLPO JOIN TC60 ON PLPO.STEUS = TC60.STEUS</t>
         </is>
       </c>
       <c r="P633" s="4" t="inlineStr">
         <is>
-          <t>הזמנת רכיבים לפק"ע</t>
+          <t>מאפייני הוראות תהליך (PI)</t>
         </is>
       </c>
       <c r="Q633" s="4" t="inlineStr"/>
@@ -31913,7 +32016,7 @@
       </c>
       <c r="S633" s="4" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A34</t>
         </is>
       </c>
       <c r="T633" s="7">
@@ -31942,12 +32045,12 @@
       </c>
       <c r="O634" s="6" t="inlineStr">
         <is>
-          <t>FROM AFRU JOIN AFKO ON AFRU.AUFNR = AFKO.AUFNR</t>
+          <t>FROM PLKO JOIN TCA01 ON PLKO.PROFIDNETZ = TCA01.PROFIDNETZ</t>
         </is>
       </c>
       <c r="P634" s="4" t="inlineStr">
         <is>
-          <t>דיווחי ביצוע פק"ע</t>
+          <t>פרופיל רשימת פעולות (Customizing)</t>
         </is>
       </c>
       <c r="Q634" s="4" t="inlineStr"/>
@@ -31958,7 +32061,7 @@
       </c>
       <c r="S634" s="4" t="inlineStr">
         <is>
-          <t>A49</t>
+          <t>A35</t>
         </is>
       </c>
       <c r="T634" s="7">
@@ -31987,12 +32090,12 @@
       </c>
       <c r="O635" s="6" t="inlineStr">
         <is>
-          <t>FROM AFFH JOIN AFKO ON AFFH.AUFPL = AFKO.AUFPL</t>
+          <t>FROM MKAL JOIN MARC ON MKAL.MATNR = MARC.MATNR AND MKAL.WERKS = MARC.WERKS</t>
         </is>
       </c>
       <c r="P635" s="4" t="inlineStr">
         <is>
-          <t>שיוך PRT לפק"ע</t>
+          <t>גרסאות ייצור לחומר</t>
         </is>
       </c>
       <c r="Q635" s="4" t="inlineStr"/>
@@ -32003,7 +32106,7 @@
       </c>
       <c r="S635" s="4" t="inlineStr">
         <is>
-          <t>A50</t>
+          <t>A36</t>
         </is>
       </c>
       <c r="T635" s="7">
@@ -32032,12 +32135,12 @@
       </c>
       <c r="O636" s="6" t="inlineStr">
         <is>
-          <t>FROM AFFL JOIN AFKO ON AFFL.AUFPL = AFKO.AUFPL</t>
+          <t>FROM CRTX JOIN CRHD ON CRTX.OBJID = CRHD.OBJID AND CRTX.OBJTY = CRHD.OBJTY</t>
         </is>
       </c>
       <c r="P636" s="4" t="inlineStr">
         <is>
-          <t>רצפי פעולות בפק"ע</t>
+          <t>טקסטים של משאב</t>
         </is>
       </c>
       <c r="Q636" s="4" t="inlineStr"/>
@@ -32048,7 +32151,7 @@
       </c>
       <c r="S636" s="4" t="inlineStr">
         <is>
-          <t>A51</t>
+          <t>A37</t>
         </is>
       </c>
       <c r="T636" s="7">
@@ -32077,12 +32180,12 @@
       </c>
       <c r="O637" s="6" t="inlineStr">
         <is>
-          <t>FROM MARA JOIN T134 ON MARA.MTART = T134.MTART</t>
+          <t>FROM CRCO JOIN CRHD ON CRCO.OBJID = CRHD.OBJID AND CRCO.OBJTY = CRHD.OBJTY</t>
         </is>
       </c>
       <c r="P637" s="4" t="inlineStr">
         <is>
-          <t>סוגי חומר (Customizing)</t>
+          <t>שיוך משאב למרכז עלות</t>
         </is>
       </c>
       <c r="Q637" s="4" t="inlineStr"/>
@@ -32093,7 +32196,7 @@
       </c>
       <c r="S637" s="4" t="inlineStr">
         <is>
-          <t>A52</t>
+          <t>A38</t>
         </is>
       </c>
       <c r="T637" s="7">
@@ -32122,12 +32225,12 @@
       </c>
       <c r="O638" s="6" t="inlineStr">
         <is>
-          <t>FROM T134T JOIN T134 ON T134T.MTART = T134.MTART</t>
+          <t>FROM CRCA JOIN CRHD ON CRCA.OBJID = CRHD.OBJID AND CRCA.OBJTY = CRHD.OBJTY</t>
         </is>
       </c>
       <c r="P638" s="4" t="inlineStr">
         <is>
-          <t>טקסטים לסוגי חומר</t>
+          <t>הקצאת קיבולת למשאב</t>
         </is>
       </c>
       <c r="Q638" s="4" t="inlineStr"/>
@@ -32138,7 +32241,7 @@
       </c>
       <c r="S638" s="4" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>A39</t>
         </is>
       </c>
       <c r="T638" s="7">
@@ -32167,12 +32270,12 @@
       </c>
       <c r="O639" s="6" t="inlineStr">
         <is>
-          <t>FROM MARA JOIN T023 ON MARA.MATKL = T023.MATKL</t>
+          <t>FROM KAKO JOIN CRCA ON KAKO.KAPID = CRCA.KAPID</t>
         </is>
       </c>
       <c r="P639" s="4" t="inlineStr">
         <is>
-          <t>קבוצות חומר (Customizing)</t>
+          <t>כותרת קיבולת</t>
         </is>
       </c>
       <c r="Q639" s="4" t="inlineStr"/>
@@ -32183,7 +32286,7 @@
       </c>
       <c r="S639" s="4" t="inlineStr">
         <is>
-          <t>A54</t>
+          <t>A40</t>
         </is>
       </c>
       <c r="T639" s="7">
@@ -32212,12 +32315,12 @@
       </c>
       <c r="O640" s="6" t="inlineStr">
         <is>
-          <t>FROM T023T JOIN T023 ON T023T.MATKL = T023.MATKL</t>
+          <t>FROM FHMI JOIN CRFH ON FHMI.FHMNR = CRFH.FHMNR</t>
         </is>
       </c>
       <c r="P640" s="4" t="inlineStr">
         <is>
-          <t>טקסטים לקבוצות חומר</t>
+          <t>אב כלי עזר ייצור (PRT)</t>
         </is>
       </c>
       <c r="Q640" s="4" t="inlineStr"/>
@@ -32228,7 +32331,7 @@
       </c>
       <c r="S640" s="4" t="inlineStr">
         <is>
-          <t>A55</t>
+          <t>A41</t>
         </is>
       </c>
       <c r="T640" s="7">
@@ -32257,12 +32360,12 @@
       </c>
       <c r="O641" s="6" t="inlineStr">
         <is>
-          <t>FROM AUFK JOIN T399X ON AUFK.WERKS = T399X.WERKS AND AUFK.AUART = T399X.AUART</t>
+          <t>FROM CRVD_A JOIN CRHD ON CRVD_A.OBJID = CRHD.OBJID</t>
         </is>
       </c>
       <c r="P641" s="4" t="inlineStr">
         <is>
-          <t>פרמטרי בקרת ייצור למפעל</t>
+          <t>ברירות מחדל למשאב (PI)</t>
         </is>
       </c>
       <c r="Q641" s="4" t="inlineStr"/>
@@ -32273,7 +32376,7 @@
       </c>
       <c r="S641" s="4" t="inlineStr">
         <is>
-          <t>A56</t>
+          <t>A42</t>
         </is>
       </c>
       <c r="T641" s="7">
@@ -32302,12 +32405,12 @@
       </c>
       <c r="O642" s="6" t="inlineStr">
         <is>
-          <t>FROM T399X JOIN TCK03 ON T399X.KLVARP = TCK03.KLVAR</t>
+          <t>FROM CSLA JOIN CRCO ON CSLA.LSTAR = CRCO.LSTAR</t>
         </is>
       </c>
       <c r="P642" s="4" t="inlineStr">
         <is>
-          <t>וריאנט תמחיר (Costing Variant)</t>
+          <t>סוגי פעילות למרכז עבודה</t>
         </is>
       </c>
       <c r="Q642" s="4" t="inlineStr"/>
@@ -32318,7 +32421,7 @@
       </c>
       <c r="S642" s="4" t="inlineStr">
         <is>
-          <t>A57</t>
+          <t>A43</t>
         </is>
       </c>
       <c r="T642" s="7">
@@ -32347,12 +32450,12 @@
       </c>
       <c r="O643" s="6" t="inlineStr">
         <is>
-          <t>FROM MARC JOIN T438M ON MARC.DISMM = T438M.DISMM</t>
+          <t>FROM KAZT JOIN KAKO ON KAZT.KAPID = KAKO.KAPID</t>
         </is>
       </c>
       <c r="P643" s="4" t="inlineStr">
         <is>
-          <t>פרמטרי MRP לחומר/מפעל</t>
+          <t>מרווחי קיבולת זמינה</t>
         </is>
       </c>
       <c r="Q643" s="4" t="inlineStr"/>
@@ -32363,7 +32466,7 @@
       </c>
       <c r="S643" s="4" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>A44</t>
         </is>
       </c>
       <c r="T643" s="7">
@@ -32392,12 +32495,12 @@
       </c>
       <c r="O644" s="6" t="inlineStr">
         <is>
-          <t>FROM AUFK JOIN T003O ON AUFK.AUART = T003O.AUART</t>
+          <t>FROM AFKO JOIN AUFK ON AFKO.AUFNR = AUFK.AUFNR</t>
         </is>
       </c>
       <c r="P644" s="4" t="inlineStr">
         <is>
-          <t>סוגי פקודת ייצור (Process Order Types)</t>
+          <t>כותרת פקודת ייצור</t>
         </is>
       </c>
       <c r="Q644" s="4" t="inlineStr"/>
@@ -32408,7 +32511,7 @@
       </c>
       <c r="S644" s="4" t="inlineStr">
         <is>
-          <t>A59</t>
+          <t>A45</t>
         </is>
       </c>
       <c r="T644" s="7">
@@ -32437,12 +32540,12 @@
       </c>
       <c r="O645" s="6" t="inlineStr">
         <is>
-          <t>FROM TCO01 JOIN T003O ON TCO01.AUART = T003O.AUART</t>
+          <t>FROM AFPO JOIN AFKO ON AFPO.AUFNR = AFKO.AUFNR</t>
         </is>
       </c>
       <c r="P645" s="4" t="inlineStr">
         <is>
-          <t>פרמטרים תלויי סוג פק"ע (Order Profile)</t>
+          <t>פריט פקודת ייצור</t>
         </is>
       </c>
       <c r="Q645" s="4" t="inlineStr"/>
@@ -32453,7 +32556,7 @@
       </c>
       <c r="S645" s="4" t="inlineStr">
         <is>
-          <t>A60</t>
+          <t>A46</t>
         </is>
       </c>
       <c r="T645" s="7">
@@ -32482,12 +32585,12 @@
       </c>
       <c r="O646" s="6" t="inlineStr">
         <is>
-          <t>FROM JEST JOIN TJ30 ON JEST.STAT = TJ30.ESTAT</t>
+          <t>FROM AFVC JOIN AFKO ON AFVC.AUFPL = AFKO.AUFPL</t>
         </is>
       </c>
       <c r="P646" s="4" t="inlineStr">
         <is>
-          <t>סטטוסי משתמש בפרופיל (User Status)</t>
+          <t>פעולות פקודת הייצור</t>
         </is>
       </c>
       <c r="Q646" s="4" t="inlineStr"/>
@@ -32498,7 +32601,7 @@
       </c>
       <c r="S646" s="4" t="inlineStr">
         <is>
-          <t>A61</t>
+          <t>A47</t>
         </is>
       </c>
       <c r="T646" s="7">
@@ -32527,12 +32630,12 @@
       </c>
       <c r="O647" s="6" t="inlineStr">
         <is>
-          <t>FROM TJ30T JOIN TJ30 ON TJ30T.STSMA = TJ30.STSMA AND TJ30T.ESTAT = TJ30.ESTAT</t>
+          <t>FROM RESB JOIN AFKO ON RESB.AUFNR = AFKO.AUFNR</t>
         </is>
       </c>
       <c r="P647" s="4" t="inlineStr">
         <is>
-          <t>טקסטים לסטטוסי משתמש</t>
+          <t>הזמנת רכיבים לפק"ע</t>
         </is>
       </c>
       <c r="Q647" s="4" t="inlineStr"/>
@@ -32543,7 +32646,7 @@
       </c>
       <c r="S647" s="4" t="inlineStr">
         <is>
-          <t>A62</t>
+          <t>A48</t>
         </is>
       </c>
       <c r="T647" s="7">
@@ -32572,12 +32675,12 @@
       </c>
       <c r="O648" s="6" t="inlineStr">
         <is>
-          <t>FROM EKKO JOIN BUT000 ON EKKO.LIFNR = BUT000.PARTNER</t>
+          <t>FROM AFRU JOIN AFKO ON AFRU.AUFNR = AFKO.AUFNR</t>
         </is>
       </c>
       <c r="P648" s="4" t="inlineStr">
         <is>
-          <t>שותף עסקי (BP - השפעת מעבר S/4)</t>
+          <t>דיווחי ביצוע פק"ע</t>
         </is>
       </c>
       <c r="Q648" s="4" t="inlineStr"/>
@@ -32588,7 +32691,7 @@
       </c>
       <c r="S648" s="4" t="inlineStr">
         <is>
-          <t>A63</t>
+          <t>A49</t>
         </is>
       </c>
       <c r="T648" s="7">
@@ -32617,12 +32720,12 @@
       </c>
       <c r="O649" s="6" t="inlineStr">
         <is>
-          <t>FROM PLPO JOIN TC22 ON PLPO.STEUS = TC22.STEUS</t>
+          <t>FROM AFFH JOIN AFKO ON AFFH.AUFPL = AFKO.AUFPL</t>
         </is>
       </c>
       <c r="P649" s="4" t="inlineStr">
         <is>
-          <t>מפתחות בקרת תהליך/פעולה (PI Control)</t>
+          <t>שיוך PRT לפק"ע</t>
         </is>
       </c>
       <c r="Q649" s="4" t="inlineStr"/>
@@ -32633,7 +32736,7 @@
       </c>
       <c r="S649" s="4" t="inlineStr">
         <is>
-          <t>A64</t>
+          <t>A50</t>
         </is>
       </c>
       <c r="T649" s="7">
@@ -32641,8 +32744,638 @@
         <v/>
       </c>
     </row>
+    <row r="650">
+      <c r="A650" s="4" t="n"/>
+      <c r="B650" s="4" t="n"/>
+      <c r="C650" s="4" t="n"/>
+      <c r="D650" s="4" t="n"/>
+      <c r="E650" s="4" t="n"/>
+      <c r="F650" s="4" t="n"/>
+      <c r="G650" s="4" t="n"/>
+      <c r="H650" s="4" t="n"/>
+      <c r="I650" s="4" t="n"/>
+      <c r="J650" s="4" t="n"/>
+      <c r="K650" s="4" t="n"/>
+      <c r="L650" s="4" t="n"/>
+      <c r="M650" s="4" t="n"/>
+      <c r="N650" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O650" s="6" t="inlineStr">
+        <is>
+          <t>FROM AFFL JOIN AFKO ON AFFL.AUFPL = AFKO.AUFPL</t>
+        </is>
+      </c>
+      <c r="P650" s="4" t="inlineStr">
+        <is>
+          <t>רצפי פעולות בפק"ע</t>
+        </is>
+      </c>
+      <c r="Q650" s="4" t="inlineStr"/>
+      <c r="R650" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S650" s="4" t="inlineStr">
+        <is>
+          <t>A51</t>
+        </is>
+      </c>
+      <c r="T650" s="7">
+        <f>HYPERLINK("#'"&amp;R650&amp;"'!"&amp;S650,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="651">
+      <c r="A651" s="4" t="n"/>
+      <c r="B651" s="4" t="n"/>
+      <c r="C651" s="4" t="n"/>
+      <c r="D651" s="4" t="n"/>
+      <c r="E651" s="4" t="n"/>
+      <c r="F651" s="4" t="n"/>
+      <c r="G651" s="4" t="n"/>
+      <c r="H651" s="4" t="n"/>
+      <c r="I651" s="4" t="n"/>
+      <c r="J651" s="4" t="n"/>
+      <c r="K651" s="4" t="n"/>
+      <c r="L651" s="4" t="n"/>
+      <c r="M651" s="4" t="n"/>
+      <c r="N651" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O651" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARA JOIN T134 ON MARA.MTART = T134.MTART</t>
+        </is>
+      </c>
+      <c r="P651" s="4" t="inlineStr">
+        <is>
+          <t>סוגי חומר (Customizing)</t>
+        </is>
+      </c>
+      <c r="Q651" s="4" t="inlineStr"/>
+      <c r="R651" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S651" s="4" t="inlineStr">
+        <is>
+          <t>A52</t>
+        </is>
+      </c>
+      <c r="T651" s="7">
+        <f>HYPERLINK("#'"&amp;R651&amp;"'!"&amp;S651,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="652">
+      <c r="A652" s="4" t="n"/>
+      <c r="B652" s="4" t="n"/>
+      <c r="C652" s="4" t="n"/>
+      <c r="D652" s="4" t="n"/>
+      <c r="E652" s="4" t="n"/>
+      <c r="F652" s="4" t="n"/>
+      <c r="G652" s="4" t="n"/>
+      <c r="H652" s="4" t="n"/>
+      <c r="I652" s="4" t="n"/>
+      <c r="J652" s="4" t="n"/>
+      <c r="K652" s="4" t="n"/>
+      <c r="L652" s="4" t="n"/>
+      <c r="M652" s="4" t="n"/>
+      <c r="N652" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O652" s="6" t="inlineStr">
+        <is>
+          <t>FROM T134T JOIN T134 ON T134T.MTART = T134.MTART</t>
+        </is>
+      </c>
+      <c r="P652" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים לסוגי חומר</t>
+        </is>
+      </c>
+      <c r="Q652" s="4" t="inlineStr"/>
+      <c r="R652" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S652" s="4" t="inlineStr">
+        <is>
+          <t>A53</t>
+        </is>
+      </c>
+      <c r="T652" s="7">
+        <f>HYPERLINK("#'"&amp;R652&amp;"'!"&amp;S652,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="653">
+      <c r="A653" s="4" t="n"/>
+      <c r="B653" s="4" t="n"/>
+      <c r="C653" s="4" t="n"/>
+      <c r="D653" s="4" t="n"/>
+      <c r="E653" s="4" t="n"/>
+      <c r="F653" s="4" t="n"/>
+      <c r="G653" s="4" t="n"/>
+      <c r="H653" s="4" t="n"/>
+      <c r="I653" s="4" t="n"/>
+      <c r="J653" s="4" t="n"/>
+      <c r="K653" s="4" t="n"/>
+      <c r="L653" s="4" t="n"/>
+      <c r="M653" s="4" t="n"/>
+      <c r="N653" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O653" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARA JOIN T023 ON MARA.MATKL = T023.MATKL</t>
+        </is>
+      </c>
+      <c r="P653" s="4" t="inlineStr">
+        <is>
+          <t>קבוצות חומר (Customizing)</t>
+        </is>
+      </c>
+      <c r="Q653" s="4" t="inlineStr"/>
+      <c r="R653" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S653" s="4" t="inlineStr">
+        <is>
+          <t>A54</t>
+        </is>
+      </c>
+      <c r="T653" s="7">
+        <f>HYPERLINK("#'"&amp;R653&amp;"'!"&amp;S653,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="654">
+      <c r="A654" s="4" t="n"/>
+      <c r="B654" s="4" t="n"/>
+      <c r="C654" s="4" t="n"/>
+      <c r="D654" s="4" t="n"/>
+      <c r="E654" s="4" t="n"/>
+      <c r="F654" s="4" t="n"/>
+      <c r="G654" s="4" t="n"/>
+      <c r="H654" s="4" t="n"/>
+      <c r="I654" s="4" t="n"/>
+      <c r="J654" s="4" t="n"/>
+      <c r="K654" s="4" t="n"/>
+      <c r="L654" s="4" t="n"/>
+      <c r="M654" s="4" t="n"/>
+      <c r="N654" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O654" s="6" t="inlineStr">
+        <is>
+          <t>FROM T023T JOIN T023 ON T023T.MATKL = T023.MATKL</t>
+        </is>
+      </c>
+      <c r="P654" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים לקבוצות חומר</t>
+        </is>
+      </c>
+      <c r="Q654" s="4" t="inlineStr"/>
+      <c r="R654" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S654" s="4" t="inlineStr">
+        <is>
+          <t>A55</t>
+        </is>
+      </c>
+      <c r="T654" s="7">
+        <f>HYPERLINK("#'"&amp;R654&amp;"'!"&amp;S654,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="655">
+      <c r="A655" s="4" t="n"/>
+      <c r="B655" s="4" t="n"/>
+      <c r="C655" s="4" t="n"/>
+      <c r="D655" s="4" t="n"/>
+      <c r="E655" s="4" t="n"/>
+      <c r="F655" s="4" t="n"/>
+      <c r="G655" s="4" t="n"/>
+      <c r="H655" s="4" t="n"/>
+      <c r="I655" s="4" t="n"/>
+      <c r="J655" s="4" t="n"/>
+      <c r="K655" s="4" t="n"/>
+      <c r="L655" s="4" t="n"/>
+      <c r="M655" s="4" t="n"/>
+      <c r="N655" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O655" s="6" t="inlineStr">
+        <is>
+          <t>FROM AUFK JOIN T399X ON AUFK.WERKS = T399X.WERKS AND AUFK.AUART = T399X.AUART</t>
+        </is>
+      </c>
+      <c r="P655" s="4" t="inlineStr">
+        <is>
+          <t>פרמטרי בקרת ייצור למפעל</t>
+        </is>
+      </c>
+      <c r="Q655" s="4" t="inlineStr"/>
+      <c r="R655" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S655" s="4" t="inlineStr">
+        <is>
+          <t>A56</t>
+        </is>
+      </c>
+      <c r="T655" s="7">
+        <f>HYPERLINK("#'"&amp;R655&amp;"'!"&amp;S655,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="656">
+      <c r="A656" s="4" t="n"/>
+      <c r="B656" s="4" t="n"/>
+      <c r="C656" s="4" t="n"/>
+      <c r="D656" s="4" t="n"/>
+      <c r="E656" s="4" t="n"/>
+      <c r="F656" s="4" t="n"/>
+      <c r="G656" s="4" t="n"/>
+      <c r="H656" s="4" t="n"/>
+      <c r="I656" s="4" t="n"/>
+      <c r="J656" s="4" t="n"/>
+      <c r="K656" s="4" t="n"/>
+      <c r="L656" s="4" t="n"/>
+      <c r="M656" s="4" t="n"/>
+      <c r="N656" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O656" s="6" t="inlineStr">
+        <is>
+          <t>FROM T399X JOIN TCK03 ON T399X.KLVARP = TCK03.KLVAR</t>
+        </is>
+      </c>
+      <c r="P656" s="4" t="inlineStr">
+        <is>
+          <t>וריאנט תמחיר (Costing Variant)</t>
+        </is>
+      </c>
+      <c r="Q656" s="4" t="inlineStr"/>
+      <c r="R656" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S656" s="4" t="inlineStr">
+        <is>
+          <t>A57</t>
+        </is>
+      </c>
+      <c r="T656" s="7">
+        <f>HYPERLINK("#'"&amp;R656&amp;"'!"&amp;S656,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="657">
+      <c r="A657" s="4" t="n"/>
+      <c r="B657" s="4" t="n"/>
+      <c r="C657" s="4" t="n"/>
+      <c r="D657" s="4" t="n"/>
+      <c r="E657" s="4" t="n"/>
+      <c r="F657" s="4" t="n"/>
+      <c r="G657" s="4" t="n"/>
+      <c r="H657" s="4" t="n"/>
+      <c r="I657" s="4" t="n"/>
+      <c r="J657" s="4" t="n"/>
+      <c r="K657" s="4" t="n"/>
+      <c r="L657" s="4" t="n"/>
+      <c r="M657" s="4" t="n"/>
+      <c r="N657" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O657" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARC JOIN T438M ON MARC.DISMM = T438M.DISMM</t>
+        </is>
+      </c>
+      <c r="P657" s="4" t="inlineStr">
+        <is>
+          <t>פרמטרי MRP לחומר/מפעל</t>
+        </is>
+      </c>
+      <c r="Q657" s="4" t="inlineStr"/>
+      <c r="R657" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S657" s="4" t="inlineStr">
+        <is>
+          <t>A58</t>
+        </is>
+      </c>
+      <c r="T657" s="7">
+        <f>HYPERLINK("#'"&amp;R657&amp;"'!"&amp;S657,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="658">
+      <c r="A658" s="4" t="n"/>
+      <c r="B658" s="4" t="n"/>
+      <c r="C658" s="4" t="n"/>
+      <c r="D658" s="4" t="n"/>
+      <c r="E658" s="4" t="n"/>
+      <c r="F658" s="4" t="n"/>
+      <c r="G658" s="4" t="n"/>
+      <c r="H658" s="4" t="n"/>
+      <c r="I658" s="4" t="n"/>
+      <c r="J658" s="4" t="n"/>
+      <c r="K658" s="4" t="n"/>
+      <c r="L658" s="4" t="n"/>
+      <c r="M658" s="4" t="n"/>
+      <c r="N658" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O658" s="6" t="inlineStr">
+        <is>
+          <t>FROM AUFK JOIN T003O ON AUFK.AUART = T003O.AUART</t>
+        </is>
+      </c>
+      <c r="P658" s="4" t="inlineStr">
+        <is>
+          <t>סוגי פקודת ייצור (Process Order Types)</t>
+        </is>
+      </c>
+      <c r="Q658" s="4" t="inlineStr"/>
+      <c r="R658" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S658" s="4" t="inlineStr">
+        <is>
+          <t>A59</t>
+        </is>
+      </c>
+      <c r="T658" s="7">
+        <f>HYPERLINK("#'"&amp;R658&amp;"'!"&amp;S658,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="659">
+      <c r="A659" s="4" t="n"/>
+      <c r="B659" s="4" t="n"/>
+      <c r="C659" s="4" t="n"/>
+      <c r="D659" s="4" t="n"/>
+      <c r="E659" s="4" t="n"/>
+      <c r="F659" s="4" t="n"/>
+      <c r="G659" s="4" t="n"/>
+      <c r="H659" s="4" t="n"/>
+      <c r="I659" s="4" t="n"/>
+      <c r="J659" s="4" t="n"/>
+      <c r="K659" s="4" t="n"/>
+      <c r="L659" s="4" t="n"/>
+      <c r="M659" s="4" t="n"/>
+      <c r="N659" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O659" s="6" t="inlineStr">
+        <is>
+          <t>FROM TCO01 JOIN T003O ON TCO01.AUART = T003O.AUART</t>
+        </is>
+      </c>
+      <c r="P659" s="4" t="inlineStr">
+        <is>
+          <t>פרמטרים תלויי סוג פק"ע (Order Profile)</t>
+        </is>
+      </c>
+      <c r="Q659" s="4" t="inlineStr"/>
+      <c r="R659" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S659" s="4" t="inlineStr">
+        <is>
+          <t>A60</t>
+        </is>
+      </c>
+      <c r="T659" s="7">
+        <f>HYPERLINK("#'"&amp;R659&amp;"'!"&amp;S659,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="660">
+      <c r="A660" s="4" t="n"/>
+      <c r="B660" s="4" t="n"/>
+      <c r="C660" s="4" t="n"/>
+      <c r="D660" s="4" t="n"/>
+      <c r="E660" s="4" t="n"/>
+      <c r="F660" s="4" t="n"/>
+      <c r="G660" s="4" t="n"/>
+      <c r="H660" s="4" t="n"/>
+      <c r="I660" s="4" t="n"/>
+      <c r="J660" s="4" t="n"/>
+      <c r="K660" s="4" t="n"/>
+      <c r="L660" s="4" t="n"/>
+      <c r="M660" s="4" t="n"/>
+      <c r="N660" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O660" s="6" t="inlineStr">
+        <is>
+          <t>FROM JEST JOIN TJ30 ON JEST.STAT = TJ30.ESTAT</t>
+        </is>
+      </c>
+      <c r="P660" s="4" t="inlineStr">
+        <is>
+          <t>סטטוסי משתמש בפרופיל (User Status)</t>
+        </is>
+      </c>
+      <c r="Q660" s="4" t="inlineStr"/>
+      <c r="R660" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S660" s="4" t="inlineStr">
+        <is>
+          <t>A61</t>
+        </is>
+      </c>
+      <c r="T660" s="7">
+        <f>HYPERLINK("#'"&amp;R660&amp;"'!"&amp;S660,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="661">
+      <c r="A661" s="4" t="n"/>
+      <c r="B661" s="4" t="n"/>
+      <c r="C661" s="4" t="n"/>
+      <c r="D661" s="4" t="n"/>
+      <c r="E661" s="4" t="n"/>
+      <c r="F661" s="4" t="n"/>
+      <c r="G661" s="4" t="n"/>
+      <c r="H661" s="4" t="n"/>
+      <c r="I661" s="4" t="n"/>
+      <c r="J661" s="4" t="n"/>
+      <c r="K661" s="4" t="n"/>
+      <c r="L661" s="4" t="n"/>
+      <c r="M661" s="4" t="n"/>
+      <c r="N661" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O661" s="6" t="inlineStr">
+        <is>
+          <t>FROM TJ30T JOIN TJ30 ON TJ30T.STSMA = TJ30.STSMA AND TJ30T.ESTAT = TJ30.ESTAT</t>
+        </is>
+      </c>
+      <c r="P661" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים לסטטוסי משתמש</t>
+        </is>
+      </c>
+      <c r="Q661" s="4" t="inlineStr"/>
+      <c r="R661" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S661" s="4" t="inlineStr">
+        <is>
+          <t>A62</t>
+        </is>
+      </c>
+      <c r="T661" s="7">
+        <f>HYPERLINK("#'"&amp;R661&amp;"'!"&amp;S661,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="662">
+      <c r="A662" s="4" t="n"/>
+      <c r="B662" s="4" t="n"/>
+      <c r="C662" s="4" t="n"/>
+      <c r="D662" s="4" t="n"/>
+      <c r="E662" s="4" t="n"/>
+      <c r="F662" s="4" t="n"/>
+      <c r="G662" s="4" t="n"/>
+      <c r="H662" s="4" t="n"/>
+      <c r="I662" s="4" t="n"/>
+      <c r="J662" s="4" t="n"/>
+      <c r="K662" s="4" t="n"/>
+      <c r="L662" s="4" t="n"/>
+      <c r="M662" s="4" t="n"/>
+      <c r="N662" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O662" s="6" t="inlineStr">
+        <is>
+          <t>FROM EKKO JOIN BUT000 ON EKKO.LIFNR = BUT000.PARTNER</t>
+        </is>
+      </c>
+      <c r="P662" s="4" t="inlineStr">
+        <is>
+          <t>שותף עסקי (BP - השפעת מעבר S/4)</t>
+        </is>
+      </c>
+      <c r="Q662" s="4" t="inlineStr"/>
+      <c r="R662" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S662" s="4" t="inlineStr">
+        <is>
+          <t>A63</t>
+        </is>
+      </c>
+      <c r="T662" s="7">
+        <f>HYPERLINK("#'"&amp;R662&amp;"'!"&amp;S662,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="663">
+      <c r="A663" s="4" t="n"/>
+      <c r="B663" s="4" t="n"/>
+      <c r="C663" s="4" t="n"/>
+      <c r="D663" s="4" t="n"/>
+      <c r="E663" s="4" t="n"/>
+      <c r="F663" s="4" t="n"/>
+      <c r="G663" s="4" t="n"/>
+      <c r="H663" s="4" t="n"/>
+      <c r="I663" s="4" t="n"/>
+      <c r="J663" s="4" t="n"/>
+      <c r="K663" s="4" t="n"/>
+      <c r="L663" s="4" t="n"/>
+      <c r="M663" s="4" t="n"/>
+      <c r="N663" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O663" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLPO JOIN TC22 ON PLPO.STEUS = TC22.STEUS</t>
+        </is>
+      </c>
+      <c r="P663" s="4" t="inlineStr">
+        <is>
+          <t>מפתחות בקרת תהליך/פעולה (PI Control)</t>
+        </is>
+      </c>
+      <c r="Q663" s="4" t="inlineStr"/>
+      <c r="R663" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S663" s="4" t="inlineStr">
+        <is>
+          <t>A64</t>
+        </is>
+      </c>
+      <c r="T663" s="7">
+        <f>HYPERLINK("#'"&amp;R663&amp;"'!"&amp;S663,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="18">
     <mergeCell ref="F13:F14"/>
     <mergeCell ref="J2:M3"/>
     <mergeCell ref="D10:D11"/>
@@ -32654,6 +33387,7 @@
     <mergeCell ref="D13:D14"/>
     <mergeCell ref="B56:H59"/>
     <mergeCell ref="B2:H2"/>
+    <mergeCell ref="D16:D17"/>
     <mergeCell ref="B16:B17"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="B10:B11"/>
@@ -32671,6 +33405,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F13" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -32691,6 +33426,2555 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:L72"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>◄ חזרה למסך הראשי</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="n"/>
+      <c r="C1" s="34" t="inlineStr">
+        <is>
+          <t>Cockpit מעקב מיגרציה  -  PP-PI Migration Tracking (Project NEO)</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+      <c r="H1" s="4" t="n"/>
+      <c r="I1" s="4" t="n"/>
+      <c r="J1" s="4" t="n"/>
+      <c r="K1" s="4" t="n"/>
+      <c r="L1" s="4" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="9" t="inlineStr">
+        <is>
+          <t>KPI &amp; Summary  -  סיכום חי (COUNTIF; בסיס מוכן לגרף נייטיב ב-2 קליקים)</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="n"/>
+      <c r="D2" s="4" t="n"/>
+      <c r="E2" s="4" t="n"/>
+      <c r="F2" s="4" t="n"/>
+      <c r="G2" s="4" t="n"/>
+      <c r="H2" s="4" t="n"/>
+      <c r="I2" s="4" t="n"/>
+      <c r="J2" s="4" t="n"/>
+      <c r="K2" s="84" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="L2" s="84" t="inlineStr">
+        <is>
+          <t>Count</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="10">
+        <f>COUNTA($C$8:$C$72)</f>
+        <v/>
+      </c>
+      <c r="C3" s="11">
+        <f>COUNTIF($D$8:$D$72,"Done")</f>
+        <v/>
+      </c>
+      <c r="D3" s="12">
+        <f>COUNTIF($D$8:$D$72,"Tested")</f>
+        <v/>
+      </c>
+      <c r="E3" s="13">
+        <f>COUNTIF($D$8:$D$72,"In analysis")+COUNTIF($D$8:$D$72,"In conversion")</f>
+        <v/>
+      </c>
+      <c r="F3" s="14">
+        <f>COUNTIF($D$8:$D$72,"Not started")</f>
+        <v/>
+      </c>
+      <c r="G3" s="15">
+        <f>IFERROR(COUNTIF($D$8:$D$72,"Done")/COUNTA($C$8:$C$72),0)</f>
+        <v/>
+      </c>
+      <c r="H3" s="4" t="n"/>
+      <c r="I3" s="4" t="n"/>
+      <c r="J3" s="4" t="n"/>
+      <c r="K3" s="85" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="L3" s="86">
+        <f>COUNTIF($D$8:$D$72,$K3)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="n"/>
+      <c r="B4" s="87" t="inlineStr">
+        <is>
+          <t>סה"כ</t>
+        </is>
+      </c>
+      <c r="C4" s="88" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="D4" s="89" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
+      <c r="E4" s="90" t="inlineStr">
+        <is>
+          <t>In Progress</t>
+        </is>
+      </c>
+      <c r="F4" s="91" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="G4" s="92" t="inlineStr">
+        <is>
+          <t>% Done</t>
+        </is>
+      </c>
+      <c r="H4" s="4" t="n"/>
+      <c r="I4" s="4" t="n"/>
+      <c r="J4" s="4" t="n"/>
+      <c r="K4" s="93" t="inlineStr">
+        <is>
+          <t>In analysis</t>
+        </is>
+      </c>
+      <c r="L4" s="86">
+        <f>COUNTIF($D$8:$D$72,$K4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="n"/>
+      <c r="B5" s="4" t="n"/>
+      <c r="C5" s="4" t="n"/>
+      <c r="D5" s="4" t="n"/>
+      <c r="E5" s="4" t="n"/>
+      <c r="F5" s="4" t="n"/>
+      <c r="G5" s="4" t="n"/>
+      <c r="H5" s="4" t="n"/>
+      <c r="I5" s="4" t="n"/>
+      <c r="J5" s="4" t="n"/>
+      <c r="K5" s="94" t="inlineStr">
+        <is>
+          <t>In conversion</t>
+        </is>
+      </c>
+      <c r="L5" s="86">
+        <f>COUNTIF($D$8:$D$72,$K5)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="n"/>
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
+      <c r="F6" s="4" t="n"/>
+      <c r="G6" s="4" t="n"/>
+      <c r="H6" s="4" t="n"/>
+      <c r="I6" s="4" t="n"/>
+      <c r="J6" s="4" t="n"/>
+      <c r="K6" s="95" t="inlineStr">
+        <is>
+          <t>Tested</t>
+        </is>
+      </c>
+      <c r="L6" s="86">
+        <f>COUNTIF($D$8:$D$72,$K6)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7" ht="26" customHeight="1">
+      <c r="A7" s="73" t="inlineStr">
+        <is>
+          <t>מס' (#)</t>
+        </is>
+      </c>
+      <c r="B7" s="73" t="inlineStr">
+        <is>
+          <t>מודול / נושא</t>
+        </is>
+      </c>
+      <c r="C7" s="73" t="inlineStr">
+        <is>
+          <t>טבלה</t>
+        </is>
+      </c>
+      <c r="D7" s="73" t="inlineStr">
+        <is>
+          <t>סטטוס מעבר (Status)</t>
+        </is>
+      </c>
+      <c r="E7" s="73" t="inlineStr">
+        <is>
+          <t>קישור</t>
+        </is>
+      </c>
+      <c r="F7" s="73" t="inlineStr">
+        <is>
+          <t>תיאור</t>
+        </is>
+      </c>
+      <c r="G7" s="4" t="n"/>
+      <c r="H7" s="4" t="n"/>
+      <c r="I7" s="4" t="n"/>
+      <c r="J7" s="4" t="n"/>
+      <c r="K7" s="96" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="L7" s="86">
+        <f>COUNTIF($D$8:$D$72,$K7)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="50" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>MARA</t>
+        </is>
+      </c>
+      <c r="D8" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E8" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A22","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F8" s="53" t="inlineStr">
+        <is>
+          <t>נתוני אב חומר כלליים</t>
+        </is>
+      </c>
+      <c r="G8" s="4" t="n"/>
+      <c r="H8" s="4" t="n"/>
+      <c r="I8" s="4" t="n"/>
+      <c r="J8" s="4" t="n"/>
+      <c r="K8" s="4" t="n"/>
+      <c r="L8" s="4" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C9" s="60" t="inlineStr">
+        <is>
+          <t>MAKT</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E9" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A32","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F9" s="64" t="inlineStr">
+        <is>
+          <t>תיאורי חומר (טקסטים)</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="n"/>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="n"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="50" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C10" s="49" t="inlineStr">
+        <is>
+          <t>MARC</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E10" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A38","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F10" s="53" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מפעל</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="n"/>
+      <c r="H10" s="4" t="n"/>
+      <c r="I10" s="4" t="n"/>
+      <c r="J10" s="4" t="n"/>
+      <c r="K10" s="4" t="n"/>
+      <c r="L10" s="4" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="61" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C11" s="60" t="inlineStr">
+        <is>
+          <t>MARD</t>
+        </is>
+      </c>
+      <c r="D11" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E11" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A48","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F11" s="64" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מחסן/מלאי</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="n"/>
+      <c r="H11" s="4" t="n"/>
+      <c r="I11" s="4" t="n"/>
+      <c r="J11" s="4" t="n"/>
+      <c r="K11" s="4" t="n"/>
+      <c r="L11" s="4" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C12" s="49" t="inlineStr">
+        <is>
+          <t>MARM</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E12" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A55","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F12" s="53" t="inlineStr">
+        <is>
+          <t>המרות יחידות מידה חלופיות</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="n"/>
+      <c r="H12" s="4" t="n"/>
+      <c r="I12" s="4" t="n"/>
+      <c r="J12" s="4" t="n"/>
+      <c r="K12" s="4" t="n"/>
+      <c r="L12" s="4" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="61" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C13" s="60" t="inlineStr">
+        <is>
+          <t>MEAN</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E13" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A63","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F13" s="64" t="inlineStr">
+        <is>
+          <t>ברקודים / EAN לחומר</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="n"/>
+      <c r="H13" s="4" t="n"/>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="n"/>
+      <c r="K13" s="4" t="n"/>
+      <c r="L13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="50" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C14" s="49" t="inlineStr">
+        <is>
+          <t>MBEW</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E14" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A70","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F14" s="53" t="inlineStr">
+        <is>
+          <t>הערכת חומר (Valuation)</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n"/>
+      <c r="H14" s="4" t="n"/>
+      <c r="I14" s="4" t="n"/>
+      <c r="J14" s="4" t="n"/>
+      <c r="K14" s="4" t="n"/>
+      <c r="L14" s="4" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="61" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C15" s="60" t="inlineStr">
+        <is>
+          <t>MVKE</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E15" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A78","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F15" s="64" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מכירות</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="n"/>
+      <c r="H15" s="4" t="n"/>
+      <c r="I15" s="4" t="n"/>
+      <c r="J15" s="4" t="n"/>
+      <c r="K15" s="4" t="n"/>
+      <c r="L15" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="50" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C16" s="49" t="inlineStr">
+        <is>
+          <t>MLAN</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E16" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A84","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F16" s="53" t="inlineStr">
+        <is>
+          <t>נתוני מס לחומר (לפי מדינה)</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="n"/>
+      <c r="H16" s="4" t="n"/>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="n"/>
+      <c r="K16" s="4" t="n"/>
+      <c r="L16" s="4" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="61" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C17" s="60" t="inlineStr">
+        <is>
+          <t>MLGN</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E17" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A89","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F17" s="64" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מחסן (WM)</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="n"/>
+      <c r="H17" s="4" t="n"/>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="n"/>
+      <c r="K17" s="4" t="n"/>
+      <c r="L17" s="4" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="50" t="n">
+        <v>11</v>
+      </c>
+      <c r="B18" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C18" s="49" t="inlineStr">
+        <is>
+          <t>MLGT</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E18" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A95","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F18" s="53" t="inlineStr">
+        <is>
+          <t>נתוני חומר לפי טיפוס אחסון</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="n"/>
+      <c r="H18" s="4" t="n"/>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="n"/>
+      <c r="K18" s="4" t="n"/>
+      <c r="L18" s="4" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="61" t="n">
+        <v>12</v>
+      </c>
+      <c r="B19" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C19" s="60" t="inlineStr">
+        <is>
+          <t>MDMA</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E19" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A101","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F19" s="64" t="inlineStr">
+        <is>
+          <t>אזורי MRP לחומר</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="n"/>
+      <c r="H19" s="4" t="n"/>
+      <c r="I19" s="4" t="n"/>
+      <c r="J19" s="4" t="n"/>
+      <c r="K19" s="4" t="n"/>
+      <c r="L19" s="4" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="B20" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C20" s="49" t="inlineStr">
+        <is>
+          <t>QMAT</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E20" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A107","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F20" s="53" t="inlineStr">
+        <is>
+          <t>הגדרות בדיקת איכות לחומר</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="n"/>
+      <c r="H20" s="4" t="n"/>
+      <c r="I20" s="4" t="n"/>
+      <c r="J20" s="4" t="n"/>
+      <c r="K20" s="4" t="n"/>
+      <c r="L20" s="4" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="61" t="n">
+        <v>14</v>
+      </c>
+      <c r="B21" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C21" s="60" t="inlineStr">
+        <is>
+          <t>MCH1</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E21" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A113","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F21" s="64" t="inlineStr">
+        <is>
+          <t>אצוות חומר (Batches)</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="50" t="n">
+        <v>15</v>
+      </c>
+      <c r="B22" s="53" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C22" s="49" t="inlineStr">
+        <is>
+          <t>MCHA</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E22" s="97">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A122","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F22" s="53" t="inlineStr">
+        <is>
+          <t>אצוות חומר ברמת מפעל</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="61" t="n">
+        <v>16</v>
+      </c>
+      <c r="B23" s="64" t="inlineStr">
+        <is>
+          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
+        </is>
+      </c>
+      <c r="C23" s="60" t="inlineStr">
+        <is>
+          <t>T006</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E23" s="98">
+        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A128","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F23" s="64" t="inlineStr">
+        <is>
+          <t>יחידות מידה (Customizing)</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="50" t="n">
+        <v>17</v>
+      </c>
+      <c r="B24" s="53" t="inlineStr">
+        <is>
+          <t>2. עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C24" s="49" t="inlineStr">
+        <is>
+          <t>MAST</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E24" s="97">
+        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A21","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F24" s="53" t="inlineStr">
+        <is>
+          <t>קישור חומר לעץ מוצר</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="61" t="n">
+        <v>18</v>
+      </c>
+      <c r="B25" s="64" t="inlineStr">
+        <is>
+          <t>2. עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C25" s="60" t="inlineStr">
+        <is>
+          <t>STKO</t>
+        </is>
+      </c>
+      <c r="D25" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E25" s="98">
+        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A28","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F25" s="64" t="inlineStr">
+        <is>
+          <t>כותרת עץ מוצר</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="50" t="n">
+        <v>19</v>
+      </c>
+      <c r="B26" s="53" t="inlineStr">
+        <is>
+          <t>2. עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C26" s="49" t="inlineStr">
+        <is>
+          <t>STPO</t>
+        </is>
+      </c>
+      <c r="D26" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E26" s="97">
+        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A36","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F26" s="53" t="inlineStr">
+        <is>
+          <t>פריטי עץ מוצר (רכיבים)</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="61" t="n">
+        <v>20</v>
+      </c>
+      <c r="B27" s="64" t="inlineStr">
+        <is>
+          <t>2. עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C27" s="60" t="inlineStr">
+        <is>
+          <t>STAS</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E27" s="98">
+        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A47","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F27" s="64" t="inlineStr">
+        <is>
+          <t>בחירת פריטי עץ מוצר</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="50" t="n">
+        <v>21</v>
+      </c>
+      <c r="B28" s="53" t="inlineStr">
+        <is>
+          <t>2. עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C28" s="49" t="inlineStr">
+        <is>
+          <t>STZU</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E28" s="97">
+        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A54","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F28" s="53" t="inlineStr">
+        <is>
+          <t>טבלת היסטוריה/קישור לעץ מוצר</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="61" t="n">
+        <v>22</v>
+      </c>
+      <c r="B29" s="64" t="inlineStr">
+        <is>
+          <t>2. עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C29" s="60" t="inlineStr">
+        <is>
+          <t>STPU</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E29" s="98">
+        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A60","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F29" s="64" t="inlineStr">
+        <is>
+          <t>טקסטים ארוכים לפריט עץ מוצר</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="n"/>
+      <c r="H29" s="4" t="n"/>
+      <c r="I29" s="4" t="n"/>
+      <c r="J29" s="4" t="n"/>
+      <c r="K29" s="4" t="n"/>
+      <c r="L29" s="4" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="50" t="n">
+        <v>23</v>
+      </c>
+      <c r="B30" s="53" t="inlineStr">
+        <is>
+          <t>2. עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C30" s="49" t="inlineStr">
+        <is>
+          <t>KDST</t>
+        </is>
+      </c>
+      <c r="D30" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E30" s="97">
+        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A65","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F30" s="53" t="inlineStr">
+        <is>
+          <t>שימוש עץ מוצר בהזמנת לקוח</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="61" t="n">
+        <v>24</v>
+      </c>
+      <c r="B31" s="64" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C31" s="60" t="inlineStr">
+        <is>
+          <t>PLKO</t>
+        </is>
+      </c>
+      <c r="D31" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E31" s="98">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A21","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F31" s="64" t="inlineStr">
+        <is>
+          <t>כותרת מתכון ייצור / רשימת פעולות</t>
+        </is>
+      </c>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="50" t="n">
+        <v>25</v>
+      </c>
+      <c r="B32" s="53" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C32" s="49" t="inlineStr">
+        <is>
+          <t>PLPO</t>
+        </is>
+      </c>
+      <c r="D32" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E32" s="97">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A30","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F32" s="53" t="inlineStr">
+        <is>
+          <t>פעולות/פאזות במתכון</t>
+        </is>
+      </c>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="61" t="n">
+        <v>26</v>
+      </c>
+      <c r="B33" s="64" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C33" s="60" t="inlineStr">
+        <is>
+          <t>PLAS</t>
+        </is>
+      </c>
+      <c r="D33" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E33" s="98">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A41","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F33" s="64" t="inlineStr">
+        <is>
+          <t>שיוך/בחירת פעולות לרשימה</t>
+        </is>
+      </c>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="50" t="n">
+        <v>27</v>
+      </c>
+      <c r="B34" s="53" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C34" s="49" t="inlineStr">
+        <is>
+          <t>PLFL</t>
+        </is>
+      </c>
+      <c r="D34" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E34" s="97">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A49","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F34" s="53" t="inlineStr">
+        <is>
+          <t>רצפים במתכון</t>
+        </is>
+      </c>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="61" t="n">
+        <v>28</v>
+      </c>
+      <c r="B35" s="64" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C35" s="60" t="inlineStr">
+        <is>
+          <t>PLMZ</t>
+        </is>
+      </c>
+      <c r="D35" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E35" s="98">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A55","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F35" s="64" t="inlineStr">
+        <is>
+          <t>שיוך רכיבים לפעולות</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="50" t="n">
+        <v>29</v>
+      </c>
+      <c r="B36" s="53" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C36" s="49" t="inlineStr">
+        <is>
+          <t>PLMK</t>
+        </is>
+      </c>
+      <c r="D36" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E36" s="97">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A62","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F36" s="53" t="inlineStr">
+        <is>
+          <t>מאפייני בדיקה במתכון</t>
+        </is>
+      </c>
+      <c r="G36" s="4" t="n"/>
+      <c r="H36" s="4" t="n"/>
+      <c r="I36" s="4" t="n"/>
+      <c r="J36" s="4" t="n"/>
+      <c r="K36" s="4" t="n"/>
+      <c r="L36" s="4" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="61" t="n">
+        <v>30</v>
+      </c>
+      <c r="B37" s="64" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C37" s="60" t="inlineStr">
+        <is>
+          <t>MAPL</t>
+        </is>
+      </c>
+      <c r="D37" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E37" s="98">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A70","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F37" s="64" t="inlineStr">
+        <is>
+          <t>שיוך חומר למתכון/רשימת פעולות</t>
+        </is>
+      </c>
+      <c r="G37" s="4" t="n"/>
+      <c r="H37" s="4" t="n"/>
+      <c r="I37" s="4" t="n"/>
+      <c r="J37" s="4" t="n"/>
+      <c r="K37" s="4" t="n"/>
+      <c r="L37" s="4" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="50" t="n">
+        <v>31</v>
+      </c>
+      <c r="B38" s="53" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C38" s="49" t="inlineStr">
+        <is>
+          <t>FHMI</t>
+        </is>
+      </c>
+      <c r="D38" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E38" s="97">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A77","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F38" s="53" t="inlineStr">
+        <is>
+          <t>שיוך כלי עזר ייצור (PRT) לפעולה</t>
+        </is>
+      </c>
+      <c r="G38" s="4" t="n"/>
+      <c r="H38" s="4" t="n"/>
+      <c r="I38" s="4" t="n"/>
+      <c r="J38" s="4" t="n"/>
+      <c r="K38" s="4" t="n"/>
+      <c r="L38" s="4" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="61" t="n">
+        <v>32</v>
+      </c>
+      <c r="B39" s="64" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C39" s="60" t="inlineStr">
+        <is>
+          <t>PLZU</t>
+        </is>
+      </c>
+      <c r="D39" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E39" s="98">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A83","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F39" s="64" t="inlineStr">
+        <is>
+          <t>קישור היסטוריית רשימת פעולות</t>
+        </is>
+      </c>
+      <c r="G39" s="4" t="n"/>
+      <c r="H39" s="4" t="n"/>
+      <c r="I39" s="4" t="n"/>
+      <c r="J39" s="4" t="n"/>
+      <c r="K39" s="4" t="n"/>
+      <c r="L39" s="4" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="50" t="n">
+        <v>33</v>
+      </c>
+      <c r="B40" s="53" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C40" s="49" t="inlineStr">
+        <is>
+          <t>TC60</t>
+        </is>
+      </c>
+      <c r="D40" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E40" s="97">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A88","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F40" s="53" t="inlineStr">
+        <is>
+          <t>מאפייני הוראות תהליך (PI)</t>
+        </is>
+      </c>
+      <c r="G40" s="4" t="n"/>
+      <c r="H40" s="4" t="n"/>
+      <c r="I40" s="4" t="n"/>
+      <c r="J40" s="4" t="n"/>
+      <c r="K40" s="4" t="n"/>
+      <c r="L40" s="4" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="61" t="n">
+        <v>34</v>
+      </c>
+      <c r="B41" s="64" t="inlineStr">
+        <is>
+          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
+        </is>
+      </c>
+      <c r="C41" s="60" t="inlineStr">
+        <is>
+          <t>TCA01</t>
+        </is>
+      </c>
+      <c r="D41" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E41" s="98">
+        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A93","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F41" s="64" t="inlineStr">
+        <is>
+          <t>פרופיל רשימת פעולות (Customizing)</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n"/>
+      <c r="H41" s="4" t="n"/>
+      <c r="I41" s="4" t="n"/>
+      <c r="J41" s="4" t="n"/>
+      <c r="K41" s="4" t="n"/>
+      <c r="L41" s="4" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="50" t="n">
+        <v>35</v>
+      </c>
+      <c r="B42" s="53" t="inlineStr">
+        <is>
+          <t>4. גרסאות ייצור (Production Versions - חובה ב-S/4)</t>
+        </is>
+      </c>
+      <c r="C42" s="49" t="inlineStr">
+        <is>
+          <t>MKAL</t>
+        </is>
+      </c>
+      <c r="D42" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E42" s="97">
+        <f>HYPERLINK("#'"&amp;"4. גרסאות ייצור (Production Ver"&amp;"'!A19","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F42" s="53" t="inlineStr">
+        <is>
+          <t>גרסאות ייצור לחומר</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n"/>
+      <c r="H42" s="4" t="n"/>
+      <c r="I42" s="4" t="n"/>
+      <c r="J42" s="4" t="n"/>
+      <c r="K42" s="4" t="n"/>
+      <c r="L42" s="4" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="61" t="n">
+        <v>36</v>
+      </c>
+      <c r="B43" s="64" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C43" s="60" t="inlineStr">
+        <is>
+          <t>CRHD</t>
+        </is>
+      </c>
+      <c r="D43" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E43" s="98">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A20","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F43" s="64" t="inlineStr">
+        <is>
+          <t>כותרת משאב / מרכז עבודה</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n"/>
+      <c r="H43" s="4" t="n"/>
+      <c r="I43" s="4" t="n"/>
+      <c r="J43" s="4" t="n"/>
+      <c r="K43" s="4" t="n"/>
+      <c r="L43" s="4" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="50" t="n">
+        <v>37</v>
+      </c>
+      <c r="B44" s="53" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C44" s="49" t="inlineStr">
+        <is>
+          <t>CRTX</t>
+        </is>
+      </c>
+      <c r="D44" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E44" s="97">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A29","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F44" s="53" t="inlineStr">
+        <is>
+          <t>טקסטים של משאב</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n"/>
+      <c r="H44" s="4" t="n"/>
+      <c r="I44" s="4" t="n"/>
+      <c r="J44" s="4" t="n"/>
+      <c r="K44" s="4" t="n"/>
+      <c r="L44" s="4" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="61" t="n">
+        <v>38</v>
+      </c>
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C45" s="60" t="inlineStr">
+        <is>
+          <t>CRCO</t>
+        </is>
+      </c>
+      <c r="D45" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E45" s="98">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A35","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F45" s="64" t="inlineStr">
+        <is>
+          <t>שיוך משאב למרכז עלות</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n"/>
+      <c r="H45" s="4" t="n"/>
+      <c r="I45" s="4" t="n"/>
+      <c r="J45" s="4" t="n"/>
+      <c r="K45" s="4" t="n"/>
+      <c r="L45" s="4" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="50" t="n">
+        <v>39</v>
+      </c>
+      <c r="B46" s="53" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C46" s="49" t="inlineStr">
+        <is>
+          <t>CRCA</t>
+        </is>
+      </c>
+      <c r="D46" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E46" s="97">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A43","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F46" s="53" t="inlineStr">
+        <is>
+          <t>הקצאת קיבולת למשאב</t>
+        </is>
+      </c>
+      <c r="G46" s="4" t="n"/>
+      <c r="H46" s="4" t="n"/>
+      <c r="I46" s="4" t="n"/>
+      <c r="J46" s="4" t="n"/>
+      <c r="K46" s="4" t="n"/>
+      <c r="L46" s="4" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="61" t="n">
+        <v>40</v>
+      </c>
+      <c r="B47" s="64" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C47" s="60" t="inlineStr">
+        <is>
+          <t>KAKO</t>
+        </is>
+      </c>
+      <c r="D47" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E47" s="98">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A49","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F47" s="64" t="inlineStr">
+        <is>
+          <t>כותרת קיבולת</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n"/>
+      <c r="H47" s="4" t="n"/>
+      <c r="I47" s="4" t="n"/>
+      <c r="J47" s="4" t="n"/>
+      <c r="K47" s="4" t="n"/>
+      <c r="L47" s="4" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="50" t="n">
+        <v>41</v>
+      </c>
+      <c r="B48" s="53" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C48" s="49" t="inlineStr">
+        <is>
+          <t>CRFH</t>
+        </is>
+      </c>
+      <c r="D48" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E48" s="97">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A55","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F48" s="53" t="inlineStr">
+        <is>
+          <t>אב כלי עזר ייצור (PRT)</t>
+        </is>
+      </c>
+      <c r="G48" s="4" t="n"/>
+      <c r="H48" s="4" t="n"/>
+      <c r="I48" s="4" t="n"/>
+      <c r="J48" s="4" t="n"/>
+      <c r="K48" s="4" t="n"/>
+      <c r="L48" s="4" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="61" t="n">
+        <v>42</v>
+      </c>
+      <c r="B49" s="64" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C49" s="60" t="inlineStr">
+        <is>
+          <t>CRVD_A</t>
+        </is>
+      </c>
+      <c r="D49" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E49" s="98">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A61","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F49" s="64" t="inlineStr">
+        <is>
+          <t>ברירות מחדל למשאב (PI)</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n"/>
+      <c r="H49" s="4" t="n"/>
+      <c r="I49" s="4" t="n"/>
+      <c r="J49" s="4" t="n"/>
+      <c r="K49" s="4" t="n"/>
+      <c r="L49" s="4" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="50" t="n">
+        <v>43</v>
+      </c>
+      <c r="B50" s="53" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C50" s="49" t="inlineStr">
+        <is>
+          <t>CSLA</t>
+        </is>
+      </c>
+      <c r="D50" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E50" s="97">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A66","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F50" s="53" t="inlineStr">
+        <is>
+          <t>סוגי פעילות למרכז עבודה</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n"/>
+      <c r="H50" s="4" t="n"/>
+      <c r="I50" s="4" t="n"/>
+      <c r="J50" s="4" t="n"/>
+      <c r="K50" s="4" t="n"/>
+      <c r="L50" s="4" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="61" t="n">
+        <v>44</v>
+      </c>
+      <c r="B51" s="64" t="inlineStr">
+        <is>
+          <t>5. משאבים / מרכזי עבודה (Resources)</t>
+        </is>
+      </c>
+      <c r="C51" s="60" t="inlineStr">
+        <is>
+          <t>KAZT</t>
+        </is>
+      </c>
+      <c r="D51" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E51" s="98">
+        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A71","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F51" s="64" t="inlineStr">
+        <is>
+          <t>מרווחי קיבולת זמינה</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n"/>
+      <c r="H51" s="4" t="n"/>
+      <c r="I51" s="4" t="n"/>
+      <c r="J51" s="4" t="n"/>
+      <c r="K51" s="4" t="n"/>
+      <c r="L51" s="4" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="50" t="n">
+        <v>45</v>
+      </c>
+      <c r="B52" s="53" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C52" s="49" t="inlineStr">
+        <is>
+          <t>AUFK</t>
+        </is>
+      </c>
+      <c r="D52" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E52" s="97">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A22","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F52" s="53" t="inlineStr">
+        <is>
+          <t>נתוני אב של פקודת ייצור</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n"/>
+      <c r="H52" s="4" t="n"/>
+      <c r="I52" s="4" t="n"/>
+      <c r="J52" s="4" t="n"/>
+      <c r="K52" s="4" t="n"/>
+      <c r="L52" s="4" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="61" t="n">
+        <v>46</v>
+      </c>
+      <c r="B53" s="64" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C53" s="60" t="inlineStr">
+        <is>
+          <t>AFKO</t>
+        </is>
+      </c>
+      <c r="D53" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E53" s="98">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A29","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F53" s="64" t="inlineStr">
+        <is>
+          <t>כותרת פקודת ייצור</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n"/>
+      <c r="H53" s="4" t="n"/>
+      <c r="I53" s="4" t="n"/>
+      <c r="J53" s="4" t="n"/>
+      <c r="K53" s="4" t="n"/>
+      <c r="L53" s="4" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="50" t="n">
+        <v>47</v>
+      </c>
+      <c r="B54" s="53" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C54" s="49" t="inlineStr">
+        <is>
+          <t>AFPO</t>
+        </is>
+      </c>
+      <c r="D54" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E54" s="97">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A37","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F54" s="53" t="inlineStr">
+        <is>
+          <t>פריט פקודת ייצור</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n"/>
+      <c r="H54" s="4" t="n"/>
+      <c r="I54" s="4" t="n"/>
+      <c r="J54" s="4" t="n"/>
+      <c r="K54" s="4" t="n"/>
+      <c r="L54" s="4" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="61" t="n">
+        <v>48</v>
+      </c>
+      <c r="B55" s="64" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C55" s="60" t="inlineStr">
+        <is>
+          <t>AFVC</t>
+        </is>
+      </c>
+      <c r="D55" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E55" s="98">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A44","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F55" s="64" t="inlineStr">
+        <is>
+          <t>פעולות פקודת הייצור</t>
+        </is>
+      </c>
+      <c r="G55" s="4" t="n"/>
+      <c r="H55" s="4" t="n"/>
+      <c r="I55" s="4" t="n"/>
+      <c r="J55" s="4" t="n"/>
+      <c r="K55" s="4" t="n"/>
+      <c r="L55" s="4" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B56" s="53" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C56" s="49" t="inlineStr">
+        <is>
+          <t>RESB</t>
+        </is>
+      </c>
+      <c r="D56" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E56" s="97">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A52","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F56" s="53" t="inlineStr">
+        <is>
+          <t>הזמנת רכיבים לפק"ע</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n"/>
+      <c r="H56" s="4" t="n"/>
+      <c r="I56" s="4" t="n"/>
+      <c r="J56" s="4" t="n"/>
+      <c r="K56" s="4" t="n"/>
+      <c r="L56" s="4" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="61" t="n">
+        <v>50</v>
+      </c>
+      <c r="B57" s="64" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C57" s="60" t="inlineStr">
+        <is>
+          <t>AFRU</t>
+        </is>
+      </c>
+      <c r="D57" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E57" s="98">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A60","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F57" s="64" t="inlineStr">
+        <is>
+          <t>דיווחי ביצוע פק"ע</t>
+        </is>
+      </c>
+      <c r="G57" s="4" t="n"/>
+      <c r="H57" s="4" t="n"/>
+      <c r="I57" s="4" t="n"/>
+      <c r="J57" s="4" t="n"/>
+      <c r="K57" s="4" t="n"/>
+      <c r="L57" s="4" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="50" t="n">
+        <v>51</v>
+      </c>
+      <c r="B58" s="53" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C58" s="49" t="inlineStr">
+        <is>
+          <t>AFFH</t>
+        </is>
+      </c>
+      <c r="D58" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E58" s="97">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A67","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F58" s="53" t="inlineStr">
+        <is>
+          <t>שיוך PRT לפק"ע</t>
+        </is>
+      </c>
+      <c r="G58" s="4" t="n"/>
+      <c r="H58" s="4" t="n"/>
+      <c r="I58" s="4" t="n"/>
+      <c r="J58" s="4" t="n"/>
+      <c r="K58" s="4" t="n"/>
+      <c r="L58" s="4" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="61" t="n">
+        <v>52</v>
+      </c>
+      <c r="B59" s="64" t="inlineStr">
+        <is>
+          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
+        </is>
+      </c>
+      <c r="C59" s="60" t="inlineStr">
+        <is>
+          <t>AFFL</t>
+        </is>
+      </c>
+      <c r="D59" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E59" s="98">
+        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A72","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F59" s="64" t="inlineStr">
+        <is>
+          <t>רצפי פעולות בפק"ע</t>
+        </is>
+      </c>
+      <c r="G59" s="4" t="n"/>
+      <c r="H59" s="4" t="n"/>
+      <c r="I59" s="4" t="n"/>
+      <c r="J59" s="4" t="n"/>
+      <c r="K59" s="4" t="n"/>
+      <c r="L59" s="4" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="50" t="n">
+        <v>53</v>
+      </c>
+      <c r="B60" s="53" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C60" s="49" t="inlineStr">
+        <is>
+          <t>T134</t>
+        </is>
+      </c>
+      <c r="D60" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E60" s="97">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A22","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F60" s="53" t="inlineStr">
+        <is>
+          <t>סוגי חומר (Customizing)</t>
+        </is>
+      </c>
+      <c r="G60" s="4" t="n"/>
+      <c r="H60" s="4" t="n"/>
+      <c r="I60" s="4" t="n"/>
+      <c r="J60" s="4" t="n"/>
+      <c r="K60" s="4" t="n"/>
+      <c r="L60" s="4" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="61" t="n">
+        <v>54</v>
+      </c>
+      <c r="B61" s="64" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C61" s="60" t="inlineStr">
+        <is>
+          <t>T134T</t>
+        </is>
+      </c>
+      <c r="D61" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E61" s="98">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A27","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F61" s="64" t="inlineStr">
+        <is>
+          <t>טקסטים לסוגי חומר</t>
+        </is>
+      </c>
+      <c r="G61" s="4" t="n"/>
+      <c r="H61" s="4" t="n"/>
+      <c r="I61" s="4" t="n"/>
+      <c r="J61" s="4" t="n"/>
+      <c r="K61" s="4" t="n"/>
+      <c r="L61" s="4" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="50" t="n">
+        <v>55</v>
+      </c>
+      <c r="B62" s="53" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C62" s="49" t="inlineStr">
+        <is>
+          <t>T023</t>
+        </is>
+      </c>
+      <c r="D62" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E62" s="97">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A32","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F62" s="53" t="inlineStr">
+        <is>
+          <t>קבוצות חומר (Customizing)</t>
+        </is>
+      </c>
+      <c r="G62" s="4" t="n"/>
+      <c r="H62" s="4" t="n"/>
+      <c r="I62" s="4" t="n"/>
+      <c r="J62" s="4" t="n"/>
+      <c r="K62" s="4" t="n"/>
+      <c r="L62" s="4" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="61" t="n">
+        <v>56</v>
+      </c>
+      <c r="B63" s="64" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C63" s="60" t="inlineStr">
+        <is>
+          <t>T023T</t>
+        </is>
+      </c>
+      <c r="D63" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E63" s="98">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A36","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F63" s="64" t="inlineStr">
+        <is>
+          <t>טקסטים לקבוצות חומר</t>
+        </is>
+      </c>
+      <c r="G63" s="4" t="n"/>
+      <c r="H63" s="4" t="n"/>
+      <c r="I63" s="4" t="n"/>
+      <c r="J63" s="4" t="n"/>
+      <c r="K63" s="4" t="n"/>
+      <c r="L63" s="4" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="50" t="n">
+        <v>57</v>
+      </c>
+      <c r="B64" s="53" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C64" s="49" t="inlineStr">
+        <is>
+          <t>T399X</t>
+        </is>
+      </c>
+      <c r="D64" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E64" s="97">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A41","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F64" s="53" t="inlineStr">
+        <is>
+          <t>פרמטרי בקרת ייצור למפעל</t>
+        </is>
+      </c>
+      <c r="G64" s="4" t="n"/>
+      <c r="H64" s="4" t="n"/>
+      <c r="I64" s="4" t="n"/>
+      <c r="J64" s="4" t="n"/>
+      <c r="K64" s="4" t="n"/>
+      <c r="L64" s="4" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="61" t="n">
+        <v>58</v>
+      </c>
+      <c r="B65" s="64" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C65" s="60" t="inlineStr">
+        <is>
+          <t>TCK03</t>
+        </is>
+      </c>
+      <c r="D65" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E65" s="98">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A47","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F65" s="64" t="inlineStr">
+        <is>
+          <t>וריאנט תמחיר (Costing Variant)</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="n"/>
+      <c r="H65" s="4" t="n"/>
+      <c r="I65" s="4" t="n"/>
+      <c r="J65" s="4" t="n"/>
+      <c r="K65" s="4" t="n"/>
+      <c r="L65" s="4" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="50" t="n">
+        <v>59</v>
+      </c>
+      <c r="B66" s="53" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C66" s="49" t="inlineStr">
+        <is>
+          <t>T438M</t>
+        </is>
+      </c>
+      <c r="D66" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E66" s="97">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A52","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F66" s="53" t="inlineStr">
+        <is>
+          <t>פרמטרי MRP לחומר/מפעל</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="n"/>
+      <c r="H66" s="4" t="n"/>
+      <c r="I66" s="4" t="n"/>
+      <c r="J66" s="4" t="n"/>
+      <c r="K66" s="4" t="n"/>
+      <c r="L66" s="4" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B67" s="64" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C67" s="60" t="inlineStr">
+        <is>
+          <t>T003O</t>
+        </is>
+      </c>
+      <c r="D67" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E67" s="98">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A56","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F67" s="64" t="inlineStr">
+        <is>
+          <t>סוגי פקודת ייצור (Process Order Types)</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="n"/>
+      <c r="H67" s="4" t="n"/>
+      <c r="I67" s="4" t="n"/>
+      <c r="J67" s="4" t="n"/>
+      <c r="K67" s="4" t="n"/>
+      <c r="L67" s="4" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="50" t="n">
+        <v>61</v>
+      </c>
+      <c r="B68" s="53" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C68" s="49" t="inlineStr">
+        <is>
+          <t>TCO01</t>
+        </is>
+      </c>
+      <c r="D68" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E68" s="97">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A62","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F68" s="53" t="inlineStr">
+        <is>
+          <t>פרמטרים תלויי סוג פק"ע (Order Profile)</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="n"/>
+      <c r="H68" s="4" t="n"/>
+      <c r="I68" s="4" t="n"/>
+      <c r="J68" s="4" t="n"/>
+      <c r="K68" s="4" t="n"/>
+      <c r="L68" s="4" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="61" t="n">
+        <v>62</v>
+      </c>
+      <c r="B69" s="64" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C69" s="60" t="inlineStr">
+        <is>
+          <t>TJ30</t>
+        </is>
+      </c>
+      <c r="D69" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E69" s="98">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A68","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F69" s="64" t="inlineStr">
+        <is>
+          <t>סטטוסי משתמש בפרופיל (User Status)</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="n"/>
+      <c r="H69" s="4" t="n"/>
+      <c r="I69" s="4" t="n"/>
+      <c r="J69" s="4" t="n"/>
+      <c r="K69" s="4" t="n"/>
+      <c r="L69" s="4" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="50" t="n">
+        <v>63</v>
+      </c>
+      <c r="B70" s="53" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C70" s="49" t="inlineStr">
+        <is>
+          <t>TJ30T</t>
+        </is>
+      </c>
+      <c r="D70" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E70" s="97">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A74","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F70" s="53" t="inlineStr">
+        <is>
+          <t>טקסטים לסטטוסי משתמש</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="n"/>
+      <c r="H70" s="4" t="n"/>
+      <c r="I70" s="4" t="n"/>
+      <c r="J70" s="4" t="n"/>
+      <c r="K70" s="4" t="n"/>
+      <c r="L70" s="4" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="61" t="n">
+        <v>64</v>
+      </c>
+      <c r="B71" s="64" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C71" s="60" t="inlineStr">
+        <is>
+          <t>BUT000</t>
+        </is>
+      </c>
+      <c r="D71" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E71" s="98">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A81","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F71" s="64" t="inlineStr">
+        <is>
+          <t>שותף עסקי (BP - השפעת מעבר S/4)</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="n"/>
+      <c r="H71" s="4" t="n"/>
+      <c r="I71" s="4" t="n"/>
+      <c r="J71" s="4" t="n"/>
+      <c r="K71" s="4" t="n"/>
+      <c r="L71" s="4" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="50" t="n">
+        <v>65</v>
+      </c>
+      <c r="B72" s="53" t="inlineStr">
+        <is>
+          <t>7. קונפיגורציה (Customizing)</t>
+        </is>
+      </c>
+      <c r="C72" s="49" t="inlineStr">
+        <is>
+          <t>TC22</t>
+        </is>
+      </c>
+      <c r="D72" s="51" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="E72" s="97">
+        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A88","➜ פתח")</f>
+        <v/>
+      </c>
+      <c r="F72" s="53" t="inlineStr">
+        <is>
+          <t>מפתחות בקרת תהליך/פעולה (PI Control)</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="n"/>
+      <c r="H72" s="4" t="n"/>
+      <c r="I72" s="4" t="n"/>
+      <c r="J72" s="4" t="n"/>
+      <c r="K72" s="4" t="n"/>
+      <c r="L72" s="4" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="D8:D72">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"Not started"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"In analysis"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"In conversion"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
+      <formula>"Tested"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
+      <formula>"Done"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="D8:D72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"Not started,In analysis,In conversion,Tested,Done"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+  </hyperlinks>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D62027"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -32715,22 +35999,22 @@
       <c r="D1" s="4" t="n"/>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="85" t="inlineStr">
+      <c r="A2" s="73" t="inlineStr">
         <is>
           <t>מס' (#)</t>
         </is>
       </c>
-      <c r="B2" s="85" t="inlineStr">
+      <c r="B2" s="73" t="inlineStr">
         <is>
           <t>טבלה (Child)</t>
         </is>
       </c>
-      <c r="C2" s="85" t="inlineStr">
+      <c r="C2" s="73" t="inlineStr">
         <is>
           <t>JOIN ON (SQL / CDS Views Syntax)</t>
         </is>
       </c>
-      <c r="D2" s="85" t="inlineStr">
+      <c r="D2" s="73" t="inlineStr">
         <is>
           <t>תיאור</t>
         </is>
@@ -32740,12 +36024,12 @@
       <c r="A3" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="89" t="inlineStr">
+      <c r="B3" s="99" t="inlineStr">
         <is>
           <t>MAKT</t>
         </is>
       </c>
-      <c r="C3" s="90" t="inlineStr">
+      <c r="C3" s="100" t="inlineStr">
         <is>
           <t>FROM MAKT JOIN MARA ON MAKT.MATNR = MARA.MATNR</t>
         </is>
@@ -32760,12 +36044,12 @@
       <c r="A4" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="91" t="inlineStr">
+      <c r="B4" s="101" t="inlineStr">
         <is>
           <t>MARC</t>
         </is>
       </c>
-      <c r="C4" s="92" t="inlineStr">
+      <c r="C4" s="102" t="inlineStr">
         <is>
           <t>FROM MARC JOIN MARA ON MARC.MATNR = MARA.MATNR</t>
         </is>
@@ -32780,12 +36064,12 @@
       <c r="A5" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="89" t="inlineStr">
+      <c r="B5" s="99" t="inlineStr">
         <is>
           <t>MARD</t>
         </is>
       </c>
-      <c r="C5" s="90" t="inlineStr">
+      <c r="C5" s="100" t="inlineStr">
         <is>
           <t>FROM MARD JOIN MARC ON MARD.MATNR = MARC.MATNR AND MARD.WERKS = MARC.WERKS</t>
         </is>
@@ -32800,12 +36084,12 @@
       <c r="A6" s="58" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="91" t="inlineStr">
+      <c r="B6" s="101" t="inlineStr">
         <is>
           <t>MARM</t>
         </is>
       </c>
-      <c r="C6" s="92" t="inlineStr">
+      <c r="C6" s="102" t="inlineStr">
         <is>
           <t>FROM MARM JOIN MARA ON MARM.MATNR = MARA.MATNR</t>
         </is>
@@ -32820,12 +36104,12 @@
       <c r="A7" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="89" t="inlineStr">
+      <c r="B7" s="99" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
       </c>
-      <c r="C7" s="90" t="inlineStr">
+      <c r="C7" s="100" t="inlineStr">
         <is>
           <t>FROM MEAN JOIN MARA ON MEAN.MATNR = MARA.MATNR</t>
         </is>
@@ -32840,12 +36124,12 @@
       <c r="A8" s="58" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="91" t="inlineStr">
+      <c r="B8" s="101" t="inlineStr">
         <is>
           <t>MBEW</t>
         </is>
       </c>
-      <c r="C8" s="92" t="inlineStr">
+      <c r="C8" s="102" t="inlineStr">
         <is>
           <t>FROM MBEW JOIN MARA ON MBEW.MATNR = MARA.MATNR</t>
         </is>
@@ -32860,12 +36144,12 @@
       <c r="A9" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="89" t="inlineStr">
+      <c r="B9" s="99" t="inlineStr">
         <is>
           <t>MVKE</t>
         </is>
       </c>
-      <c r="C9" s="90" t="inlineStr">
+      <c r="C9" s="100" t="inlineStr">
         <is>
           <t>FROM MVKE JOIN MARA ON MVKE.MATNR = MARA.MATNR</t>
         </is>
@@ -32880,12 +36164,12 @@
       <c r="A10" s="58" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="91" t="inlineStr">
+      <c r="B10" s="101" t="inlineStr">
         <is>
           <t>MLAN</t>
         </is>
       </c>
-      <c r="C10" s="92" t="inlineStr">
+      <c r="C10" s="102" t="inlineStr">
         <is>
           <t>FROM MLAN JOIN MARA ON MLAN.MATNR = MARA.MATNR</t>
         </is>
@@ -32900,12 +36184,12 @@
       <c r="A11" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="89" t="inlineStr">
+      <c r="B11" s="99" t="inlineStr">
         <is>
           <t>MLGN</t>
         </is>
       </c>
-      <c r="C11" s="90" t="inlineStr">
+      <c r="C11" s="100" t="inlineStr">
         <is>
           <t>FROM MLGN JOIN MARA ON MLGN.MATNR = MARA.MATNR</t>
         </is>
@@ -32920,12 +36204,12 @@
       <c r="A12" s="58" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="91" t="inlineStr">
+      <c r="B12" s="101" t="inlineStr">
         <is>
           <t>MLGT</t>
         </is>
       </c>
-      <c r="C12" s="92" t="inlineStr">
+      <c r="C12" s="102" t="inlineStr">
         <is>
           <t>FROM MLGT JOIN MLGN ON MLGT.MATNR = MLGN.MATNR AND MLGT.LGNUM = MLGN.LGNUM</t>
         </is>
@@ -32940,12 +36224,12 @@
       <c r="A13" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="89" t="inlineStr">
+      <c r="B13" s="99" t="inlineStr">
         <is>
           <t>MDMA</t>
         </is>
       </c>
-      <c r="C13" s="90" t="inlineStr">
+      <c r="C13" s="100" t="inlineStr">
         <is>
           <t>FROM MDMA JOIN MARC ON MDMA.MATNR = MARC.MATNR AND MDMA.WERKS = MARC.WERKS</t>
         </is>
@@ -32960,12 +36244,12 @@
       <c r="A14" s="58" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="91" t="inlineStr">
+      <c r="B14" s="101" t="inlineStr">
         <is>
           <t>QMAT</t>
         </is>
       </c>
-      <c r="C14" s="92" t="inlineStr">
+      <c r="C14" s="102" t="inlineStr">
         <is>
           <t>FROM QMAT JOIN MARC ON QMAT.MATNR = MARC.MATNR AND QMAT.WERKS = MARC.WERKS</t>
         </is>
@@ -32980,12 +36264,12 @@
       <c r="A15" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="89" t="inlineStr">
+      <c r="B15" s="99" t="inlineStr">
         <is>
           <t>MCH1</t>
         </is>
       </c>
-      <c r="C15" s="90" t="inlineStr">
+      <c r="C15" s="100" t="inlineStr">
         <is>
           <t>FROM MCH1 JOIN MARA ON MCH1.MATNR = MARA.MATNR</t>
         </is>
@@ -33000,12 +36284,12 @@
       <c r="A16" s="58" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="91" t="inlineStr">
+      <c r="B16" s="101" t="inlineStr">
         <is>
           <t>MCHA</t>
         </is>
       </c>
-      <c r="C16" s="92" t="inlineStr">
+      <c r="C16" s="102" t="inlineStr">
         <is>
           <t>FROM MCHA JOIN MCH1 ON MCHA.MATNR = MCH1.MATNR AND MCHA.CHARG = MCH1.CHARG</t>
         </is>
@@ -33020,12 +36304,12 @@
       <c r="A17" s="47" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="89" t="inlineStr">
+      <c r="B17" s="99" t="inlineStr">
         <is>
           <t>T006</t>
         </is>
       </c>
-      <c r="C17" s="90" t="inlineStr">
+      <c r="C17" s="100" t="inlineStr">
         <is>
           <t>FROM MARM JOIN T006 ON MARM.MEINH = T006.MSEHI</t>
         </is>
@@ -33040,12 +36324,12 @@
       <c r="A18" s="58" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="91" t="inlineStr">
+      <c r="B18" s="101" t="inlineStr">
         <is>
           <t>MAST</t>
         </is>
       </c>
-      <c r="C18" s="92" t="inlineStr">
+      <c r="C18" s="102" t="inlineStr">
         <is>
           <t>FROM MAST JOIN MARA ON MAST.MATNR = MARA.MATNR</t>
         </is>
@@ -33060,12 +36344,12 @@
       <c r="A19" s="47" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="89" t="inlineStr">
+      <c r="B19" s="99" t="inlineStr">
         <is>
           <t>STKO</t>
         </is>
       </c>
-      <c r="C19" s="90" t="inlineStr">
+      <c r="C19" s="100" t="inlineStr">
         <is>
           <t>FROM STKO JOIN MAST ON STKO.STLNR = MAST.STLNR</t>
         </is>
@@ -33080,12 +36364,12 @@
       <c r="A20" s="58" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="91" t="inlineStr">
+      <c r="B20" s="101" t="inlineStr">
         <is>
           <t>STPO</t>
         </is>
       </c>
-      <c r="C20" s="92" t="inlineStr">
+      <c r="C20" s="102" t="inlineStr">
         <is>
           <t>FROM STPO JOIN STKO ON STPO.STLNR = STKO.STLNR AND STPO.STLTY = STKO.STLTY</t>
         </is>
@@ -33100,12 +36384,12 @@
       <c r="A21" s="47" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="89" t="inlineStr">
+      <c r="B21" s="99" t="inlineStr">
         <is>
           <t>STAS</t>
         </is>
       </c>
-      <c r="C21" s="90" t="inlineStr">
+      <c r="C21" s="100" t="inlineStr">
         <is>
           <t>FROM STAS JOIN STKO ON STAS.STLNR = STKO.STLNR</t>
         </is>
@@ -33120,12 +36404,12 @@
       <c r="A22" s="58" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="91" t="inlineStr">
+      <c r="B22" s="101" t="inlineStr">
         <is>
           <t>STZU</t>
         </is>
       </c>
-      <c r="C22" s="92" t="inlineStr">
+      <c r="C22" s="102" t="inlineStr">
         <is>
           <t>FROM STZU JOIN STKO ON STZU.STLNR = STKO.STLNR</t>
         </is>
@@ -33140,12 +36424,12 @@
       <c r="A23" s="47" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="89" t="inlineStr">
+      <c r="B23" s="99" t="inlineStr">
         <is>
           <t>STPU</t>
         </is>
       </c>
-      <c r="C23" s="90" t="inlineStr">
+      <c r="C23" s="100" t="inlineStr">
         <is>
           <t>FROM STPU JOIN STPO ON STPU.STLKN = STPO.STLKN</t>
         </is>
@@ -33160,12 +36444,12 @@
       <c r="A24" s="58" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="91" t="inlineStr">
+      <c r="B24" s="101" t="inlineStr">
         <is>
           <t>KDST</t>
         </is>
       </c>
-      <c r="C24" s="92" t="inlineStr">
+      <c r="C24" s="102" t="inlineStr">
         <is>
           <t>FROM KDST JOIN MAST ON KDST.MATNR = MAST.MATNR</t>
         </is>
@@ -33180,12 +36464,12 @@
       <c r="A25" s="47" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="89" t="inlineStr">
+      <c r="B25" s="99" t="inlineStr">
         <is>
           <t>PLKO</t>
         </is>
       </c>
-      <c r="C25" s="90" t="inlineStr">
+      <c r="C25" s="100" t="inlineStr">
         <is>
           <t>FROM PLKO JOIN MAPL ON PLKO.PLNTY = MAPL.PLNTY AND PLKO.PLNNR = MAPL.PLNNR</t>
         </is>
@@ -33200,12 +36484,12 @@
       <c r="A26" s="58" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="91" t="inlineStr">
+      <c r="B26" s="101" t="inlineStr">
         <is>
           <t>PLPO</t>
         </is>
       </c>
-      <c r="C26" s="92" t="inlineStr">
+      <c r="C26" s="102" t="inlineStr">
         <is>
           <t>FROM PLPO JOIN PLAS ON PLPO.PLNTY = PLAS.PLNTY AND PLPO.PLNNR = PLAS.PLNNR AND PLPO.PLNKN = PLAS.PLNKN</t>
         </is>
@@ -33220,12 +36504,12 @@
       <c r="A27" s="47" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="89" t="inlineStr">
+      <c r="B27" s="99" t="inlineStr">
         <is>
           <t>PLAS</t>
         </is>
       </c>
-      <c r="C27" s="90" t="inlineStr">
+      <c r="C27" s="100" t="inlineStr">
         <is>
           <t>FROM PLAS JOIN PLKO ON PLAS.PLNTY = PLKO.PLNTY AND PLAS.PLNNR = PLKO.PLNNR</t>
         </is>
@@ -33240,12 +36524,12 @@
       <c r="A28" s="58" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="91" t="inlineStr">
+      <c r="B28" s="101" t="inlineStr">
         <is>
           <t>PLFL</t>
         </is>
       </c>
-      <c r="C28" s="92" t="inlineStr">
+      <c r="C28" s="102" t="inlineStr">
         <is>
           <t>FROM PLFL JOIN PLKO ON PLFL.PLNNR = PLKO.PLNNR</t>
         </is>
@@ -33260,12 +36544,12 @@
       <c r="A29" s="47" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="89" t="inlineStr">
+      <c r="B29" s="99" t="inlineStr">
         <is>
           <t>PLMZ</t>
         </is>
       </c>
-      <c r="C29" s="90" t="inlineStr">
+      <c r="C29" s="100" t="inlineStr">
         <is>
           <t>FROM PLMZ JOIN PLPO ON PLMZ.PLNKN = PLPO.PLNKN</t>
         </is>
@@ -33280,12 +36564,12 @@
       <c r="A30" s="58" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="91" t="inlineStr">
+      <c r="B30" s="101" t="inlineStr">
         <is>
           <t>PLMK</t>
         </is>
       </c>
-      <c r="C30" s="92" t="inlineStr">
+      <c r="C30" s="102" t="inlineStr">
         <is>
           <t>FROM PLMK JOIN PLPO ON PLMK.PLNKN = PLPO.PLNKN</t>
         </is>
@@ -33300,12 +36584,12 @@
       <c r="A31" s="47" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="89" t="inlineStr">
+      <c r="B31" s="99" t="inlineStr">
         <is>
           <t>MAPL</t>
         </is>
       </c>
-      <c r="C31" s="90" t="inlineStr">
+      <c r="C31" s="100" t="inlineStr">
         <is>
           <t>FROM MAPL JOIN MARC ON MAPL.MATNR = MARC.MATNR AND MAPL.WERKS = MARC.WERKS</t>
         </is>
@@ -33320,12 +36604,12 @@
       <c r="A32" s="58" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="91" t="inlineStr">
+      <c r="B32" s="101" t="inlineStr">
         <is>
           <t>FHMI</t>
         </is>
       </c>
-      <c r="C32" s="92" t="inlineStr">
+      <c r="C32" s="102" t="inlineStr">
         <is>
           <t>FROM FHMI JOIN PLPO ON FHMI.PLNKN = PLPO.PLNKN</t>
         </is>
@@ -33340,12 +36624,12 @@
       <c r="A33" s="47" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="89" t="inlineStr">
+      <c r="B33" s="99" t="inlineStr">
         <is>
           <t>PLZU</t>
         </is>
       </c>
-      <c r="C33" s="90" t="inlineStr">
+      <c r="C33" s="100" t="inlineStr">
         <is>
           <t>FROM PLZU JOIN PLKO ON PLZU.PLNNR = PLKO.PLNNR</t>
         </is>
@@ -33360,12 +36644,12 @@
       <c r="A34" s="58" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="91" t="inlineStr">
+      <c r="B34" s="101" t="inlineStr">
         <is>
           <t>TC60</t>
         </is>
       </c>
-      <c r="C34" s="92" t="inlineStr">
+      <c r="C34" s="102" t="inlineStr">
         <is>
           <t>FROM PLPO JOIN TC60 ON PLPO.STEUS = TC60.STEUS</t>
         </is>
@@ -33380,12 +36664,12 @@
       <c r="A35" s="47" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="89" t="inlineStr">
+      <c r="B35" s="99" t="inlineStr">
         <is>
           <t>TCA01</t>
         </is>
       </c>
-      <c r="C35" s="90" t="inlineStr">
+      <c r="C35" s="100" t="inlineStr">
         <is>
           <t>FROM PLKO JOIN TCA01 ON PLKO.PROFIDNETZ = TCA01.PROFIDNETZ</t>
         </is>
@@ -33400,12 +36684,12 @@
       <c r="A36" s="58" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="91" t="inlineStr">
+      <c r="B36" s="101" t="inlineStr">
         <is>
           <t>MKAL</t>
         </is>
       </c>
-      <c r="C36" s="92" t="inlineStr">
+      <c r="C36" s="102" t="inlineStr">
         <is>
           <t>FROM MKAL JOIN MARC ON MKAL.MATNR = MARC.MATNR AND MKAL.WERKS = MARC.WERKS</t>
         </is>
@@ -33420,12 +36704,12 @@
       <c r="A37" s="47" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="89" t="inlineStr">
+      <c r="B37" s="99" t="inlineStr">
         <is>
           <t>CRTX</t>
         </is>
       </c>
-      <c r="C37" s="90" t="inlineStr">
+      <c r="C37" s="100" t="inlineStr">
         <is>
           <t>FROM CRTX JOIN CRHD ON CRTX.OBJID = CRHD.OBJID AND CRTX.OBJTY = CRHD.OBJTY</t>
         </is>
@@ -33440,12 +36724,12 @@
       <c r="A38" s="58" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="91" t="inlineStr">
+      <c r="B38" s="101" t="inlineStr">
         <is>
           <t>CRCO</t>
         </is>
       </c>
-      <c r="C38" s="92" t="inlineStr">
+      <c r="C38" s="102" t="inlineStr">
         <is>
           <t>FROM CRCO JOIN CRHD ON CRCO.OBJID = CRHD.OBJID AND CRCO.OBJTY = CRHD.OBJTY</t>
         </is>
@@ -33460,12 +36744,12 @@
       <c r="A39" s="47" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="89" t="inlineStr">
+      <c r="B39" s="99" t="inlineStr">
         <is>
           <t>CRCA</t>
         </is>
       </c>
-      <c r="C39" s="90" t="inlineStr">
+      <c r="C39" s="100" t="inlineStr">
         <is>
           <t>FROM CRCA JOIN CRHD ON CRCA.OBJID = CRHD.OBJID AND CRCA.OBJTY = CRHD.OBJTY</t>
         </is>
@@ -33480,12 +36764,12 @@
       <c r="A40" s="58" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="91" t="inlineStr">
+      <c r="B40" s="101" t="inlineStr">
         <is>
           <t>KAKO</t>
         </is>
       </c>
-      <c r="C40" s="92" t="inlineStr">
+      <c r="C40" s="102" t="inlineStr">
         <is>
           <t>FROM KAKO JOIN CRCA ON KAKO.KAPID = CRCA.KAPID</t>
         </is>
@@ -33500,12 +36784,12 @@
       <c r="A41" s="47" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="89" t="inlineStr">
+      <c r="B41" s="99" t="inlineStr">
         <is>
           <t>CRFH</t>
         </is>
       </c>
-      <c r="C41" s="90" t="inlineStr">
+      <c r="C41" s="100" t="inlineStr">
         <is>
           <t>FROM FHMI JOIN CRFH ON FHMI.FHMNR = CRFH.FHMNR</t>
         </is>
@@ -33520,12 +36804,12 @@
       <c r="A42" s="58" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="91" t="inlineStr">
+      <c r="B42" s="101" t="inlineStr">
         <is>
           <t>CRVD_A</t>
         </is>
       </c>
-      <c r="C42" s="92" t="inlineStr">
+      <c r="C42" s="102" t="inlineStr">
         <is>
           <t>FROM CRVD_A JOIN CRHD ON CRVD_A.OBJID = CRHD.OBJID</t>
         </is>
@@ -33540,12 +36824,12 @@
       <c r="A43" s="47" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="89" t="inlineStr">
+      <c r="B43" s="99" t="inlineStr">
         <is>
           <t>CSLA</t>
         </is>
       </c>
-      <c r="C43" s="90" t="inlineStr">
+      <c r="C43" s="100" t="inlineStr">
         <is>
           <t>FROM CSLA JOIN CRCO ON CSLA.LSTAR = CRCO.LSTAR</t>
         </is>
@@ -33560,12 +36844,12 @@
       <c r="A44" s="58" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="91" t="inlineStr">
+      <c r="B44" s="101" t="inlineStr">
         <is>
           <t>KAZT</t>
         </is>
       </c>
-      <c r="C44" s="92" t="inlineStr">
+      <c r="C44" s="102" t="inlineStr">
         <is>
           <t>FROM KAZT JOIN KAKO ON KAZT.KAPID = KAKO.KAPID</t>
         </is>
@@ -33580,12 +36864,12 @@
       <c r="A45" s="47" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="89" t="inlineStr">
+      <c r="B45" s="99" t="inlineStr">
         <is>
           <t>AFKO</t>
         </is>
       </c>
-      <c r="C45" s="90" t="inlineStr">
+      <c r="C45" s="100" t="inlineStr">
         <is>
           <t>FROM AFKO JOIN AUFK ON AFKO.AUFNR = AUFK.AUFNR</t>
         </is>
@@ -33600,12 +36884,12 @@
       <c r="A46" s="58" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="91" t="inlineStr">
+      <c r="B46" s="101" t="inlineStr">
         <is>
           <t>AFPO</t>
         </is>
       </c>
-      <c r="C46" s="92" t="inlineStr">
+      <c r="C46" s="102" t="inlineStr">
         <is>
           <t>FROM AFPO JOIN AFKO ON AFPO.AUFNR = AFKO.AUFNR</t>
         </is>
@@ -33620,12 +36904,12 @@
       <c r="A47" s="47" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="89" t="inlineStr">
+      <c r="B47" s="99" t="inlineStr">
         <is>
           <t>AFVC</t>
         </is>
       </c>
-      <c r="C47" s="90" t="inlineStr">
+      <c r="C47" s="100" t="inlineStr">
         <is>
           <t>FROM AFVC JOIN AFKO ON AFVC.AUFPL = AFKO.AUFPL</t>
         </is>
@@ -33640,12 +36924,12 @@
       <c r="A48" s="58" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="91" t="inlineStr">
+      <c r="B48" s="101" t="inlineStr">
         <is>
           <t>RESB</t>
         </is>
       </c>
-      <c r="C48" s="92" t="inlineStr">
+      <c r="C48" s="102" t="inlineStr">
         <is>
           <t>FROM RESB JOIN AFKO ON RESB.AUFNR = AFKO.AUFNR</t>
         </is>
@@ -33660,12 +36944,12 @@
       <c r="A49" s="47" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="89" t="inlineStr">
+      <c r="B49" s="99" t="inlineStr">
         <is>
           <t>AFRU</t>
         </is>
       </c>
-      <c r="C49" s="90" t="inlineStr">
+      <c r="C49" s="100" t="inlineStr">
         <is>
           <t>FROM AFRU JOIN AFKO ON AFRU.AUFNR = AFKO.AUFNR</t>
         </is>
@@ -33680,12 +36964,12 @@
       <c r="A50" s="58" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="91" t="inlineStr">
+      <c r="B50" s="101" t="inlineStr">
         <is>
           <t>AFFH</t>
         </is>
       </c>
-      <c r="C50" s="92" t="inlineStr">
+      <c r="C50" s="102" t="inlineStr">
         <is>
           <t>FROM AFFH JOIN AFKO ON AFFH.AUFPL = AFKO.AUFPL</t>
         </is>
@@ -33700,12 +36984,12 @@
       <c r="A51" s="47" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="89" t="inlineStr">
+      <c r="B51" s="99" t="inlineStr">
         <is>
           <t>AFFL</t>
         </is>
       </c>
-      <c r="C51" s="90" t="inlineStr">
+      <c r="C51" s="100" t="inlineStr">
         <is>
           <t>FROM AFFL JOIN AFKO ON AFFL.AUFPL = AFKO.AUFPL</t>
         </is>
@@ -33720,12 +37004,12 @@
       <c r="A52" s="58" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="91" t="inlineStr">
+      <c r="B52" s="101" t="inlineStr">
         <is>
           <t>T134</t>
         </is>
       </c>
-      <c r="C52" s="92" t="inlineStr">
+      <c r="C52" s="102" t="inlineStr">
         <is>
           <t>FROM MARA JOIN T134 ON MARA.MTART = T134.MTART</t>
         </is>
@@ -33740,12 +37024,12 @@
       <c r="A53" s="47" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="89" t="inlineStr">
+      <c r="B53" s="99" t="inlineStr">
         <is>
           <t>T134T</t>
         </is>
       </c>
-      <c r="C53" s="90" t="inlineStr">
+      <c r="C53" s="100" t="inlineStr">
         <is>
           <t>FROM T134T JOIN T134 ON T134T.MTART = T134.MTART</t>
         </is>
@@ -33760,12 +37044,12 @@
       <c r="A54" s="58" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="91" t="inlineStr">
+      <c r="B54" s="101" t="inlineStr">
         <is>
           <t>T023</t>
         </is>
       </c>
-      <c r="C54" s="92" t="inlineStr">
+      <c r="C54" s="102" t="inlineStr">
         <is>
           <t>FROM MARA JOIN T023 ON MARA.MATKL = T023.MATKL</t>
         </is>
@@ -33780,12 +37064,12 @@
       <c r="A55" s="47" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="89" t="inlineStr">
+      <c r="B55" s="99" t="inlineStr">
         <is>
           <t>T023T</t>
         </is>
       </c>
-      <c r="C55" s="90" t="inlineStr">
+      <c r="C55" s="100" t="inlineStr">
         <is>
           <t>FROM T023T JOIN T023 ON T023T.MATKL = T023.MATKL</t>
         </is>
@@ -33800,12 +37084,12 @@
       <c r="A56" s="58" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="91" t="inlineStr">
+      <c r="B56" s="101" t="inlineStr">
         <is>
           <t>T399X</t>
         </is>
       </c>
-      <c r="C56" s="92" t="inlineStr">
+      <c r="C56" s="102" t="inlineStr">
         <is>
           <t>FROM AUFK JOIN T399X ON AUFK.WERKS = T399X.WERKS AND AUFK.AUART = T399X.AUART</t>
         </is>
@@ -33820,12 +37104,12 @@
       <c r="A57" s="47" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="89" t="inlineStr">
+      <c r="B57" s="99" t="inlineStr">
         <is>
           <t>TCK03</t>
         </is>
       </c>
-      <c r="C57" s="90" t="inlineStr">
+      <c r="C57" s="100" t="inlineStr">
         <is>
           <t>FROM T399X JOIN TCK03 ON T399X.KLVARP = TCK03.KLVAR</t>
         </is>
@@ -33840,12 +37124,12 @@
       <c r="A58" s="58" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="91" t="inlineStr">
+      <c r="B58" s="101" t="inlineStr">
         <is>
           <t>T438M</t>
         </is>
       </c>
-      <c r="C58" s="92" t="inlineStr">
+      <c r="C58" s="102" t="inlineStr">
         <is>
           <t>FROM MARC JOIN T438M ON MARC.DISMM = T438M.DISMM</t>
         </is>
@@ -33860,12 +37144,12 @@
       <c r="A59" s="47" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="89" t="inlineStr">
+      <c r="B59" s="99" t="inlineStr">
         <is>
           <t>T003O</t>
         </is>
       </c>
-      <c r="C59" s="90" t="inlineStr">
+      <c r="C59" s="100" t="inlineStr">
         <is>
           <t>FROM AUFK JOIN T003O ON AUFK.AUART = T003O.AUART</t>
         </is>
@@ -33880,12 +37164,12 @@
       <c r="A60" s="58" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="91" t="inlineStr">
+      <c r="B60" s="101" t="inlineStr">
         <is>
           <t>TCO01</t>
         </is>
       </c>
-      <c r="C60" s="92" t="inlineStr">
+      <c r="C60" s="102" t="inlineStr">
         <is>
           <t>FROM TCO01 JOIN T003O ON TCO01.AUART = T003O.AUART</t>
         </is>
@@ -33900,12 +37184,12 @@
       <c r="A61" s="47" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="89" t="inlineStr">
+      <c r="B61" s="99" t="inlineStr">
         <is>
           <t>TJ30</t>
         </is>
       </c>
-      <c r="C61" s="90" t="inlineStr">
+      <c r="C61" s="100" t="inlineStr">
         <is>
           <t>FROM JEST JOIN TJ30 ON JEST.STAT = TJ30.ESTAT</t>
         </is>
@@ -33920,12 +37204,12 @@
       <c r="A62" s="58" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="91" t="inlineStr">
+      <c r="B62" s="101" t="inlineStr">
         <is>
           <t>TJ30T</t>
         </is>
       </c>
-      <c r="C62" s="92" t="inlineStr">
+      <c r="C62" s="102" t="inlineStr">
         <is>
           <t>FROM TJ30T JOIN TJ30 ON TJ30T.STSMA = TJ30.STSMA AND TJ30T.ESTAT = TJ30.ESTAT</t>
         </is>
@@ -33940,12 +37224,12 @@
       <c r="A63" s="47" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="89" t="inlineStr">
+      <c r="B63" s="99" t="inlineStr">
         <is>
           <t>BUT000</t>
         </is>
       </c>
-      <c r="C63" s="90" t="inlineStr">
+      <c r="C63" s="100" t="inlineStr">
         <is>
           <t>FROM EKKO JOIN BUT000 ON EKKO.LIFNR = BUT000.PARTNER</t>
         </is>
@@ -33960,12 +37244,12 @@
       <c r="A64" s="58" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="91" t="inlineStr">
+      <c r="B64" s="101" t="inlineStr">
         <is>
           <t>TC22</t>
         </is>
       </c>
-      <c r="C64" s="92" t="inlineStr">
+      <c r="C64" s="102" t="inlineStr">
         <is>
           <t>FROM PLPO JOIN TC22 ON PLPO.STEUS = TC22.STEUS</t>
         </is>
@@ -54341,21 +57625,18 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="00D62027"/>
+    <tabColor rgb="008A9EA7"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L72"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="15" customWidth="1" min="11" max="11"/>
-    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -54367,2522 +57648,407 @@
       <c r="B1" s="33" t="n"/>
       <c r="C1" s="34" t="inlineStr">
         <is>
-          <t>Cockpit מעקב מיגרציה  -  PP-PI Migration Tracking (Project NEO)</t>
+          <t>SAP PP (Discrete) מול SAP PP-PI (Process) - שכבת חינוך ארגונית  ·  CBC NEO</t>
         </is>
       </c>
       <c r="D1" s="4" t="n"/>
       <c r="E1" s="4" t="n"/>
-      <c r="F1" s="4" t="n"/>
-      <c r="G1" s="4" t="n"/>
-      <c r="H1" s="4" t="n"/>
-      <c r="I1" s="4" t="n"/>
-      <c r="J1" s="4" t="n"/>
-      <c r="K1" s="4" t="n"/>
-      <c r="L1" s="4" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="n"/>
-      <c r="B2" s="9" t="inlineStr">
-        <is>
-          <t>KPI &amp; Summary  -  סיכום חי (COUNTIF; בסיס מוכן לגרף נייטיב ב-2 קליקים)</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="73" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="L2" s="73" t="inlineStr">
-        <is>
-          <t>Count</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="4" t="n"/>
-      <c r="B3" s="10">
-        <f>COUNTA($C$8:$C$72)</f>
-        <v/>
-      </c>
-      <c r="C3" s="11">
-        <f>COUNTIF($D$8:$D$72,"Done")</f>
-        <v/>
-      </c>
-      <c r="D3" s="12">
-        <f>COUNTIF($D$8:$D$72,"Tested")</f>
-        <v/>
-      </c>
-      <c r="E3" s="13">
-        <f>COUNTIF($D$8:$D$72,"In analysis")+COUNTIF($D$8:$D$72,"In conversion")</f>
-        <v/>
-      </c>
-      <c r="F3" s="14">
-        <f>COUNTIF($D$8:$D$72,"Not started")</f>
-        <v/>
-      </c>
-      <c r="G3" s="15">
-        <f>IFERROR(COUNTIF($D$8:$D$72,"Done")/COUNTA($C$8:$C$72),0)</f>
-        <v/>
-      </c>
-      <c r="H3" s="4" t="n"/>
-      <c r="I3" s="4" t="n"/>
-      <c r="J3" s="4" t="n"/>
-      <c r="K3" s="74" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="L3" s="75">
-        <f>COUNTIF($D$8:$D$72,$K3)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="n"/>
-      <c r="B4" s="76" t="inlineStr">
-        <is>
-          <t>סה"כ</t>
-        </is>
-      </c>
-      <c r="C4" s="77" t="inlineStr">
-        <is>
-          <t>Done</t>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="73" t="inlineStr">
+        <is>
+          <t>מס' (#)</t>
+        </is>
+      </c>
+      <c r="B2" s="73" t="inlineStr">
+        <is>
+          <t>היבט (Aspect)</t>
+        </is>
+      </c>
+      <c r="C2" s="73" t="inlineStr">
+        <is>
+          <t>SAP PP - ייצור בדיד (Discrete)</t>
+        </is>
+      </c>
+      <c r="D2" s="74" t="inlineStr">
+        <is>
+          <t>SAP PP-PI - ייצור תהליכי (Process)</t>
+        </is>
+      </c>
+      <c r="E2" s="73" t="inlineStr">
+        <is>
+          <t>הערת CBC / S/4HANA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="46" customHeight="1">
+      <c r="A3" s="75" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="76" t="inlineStr">
+        <is>
+          <t>סוג ייצור (Production type)</t>
+        </is>
+      </c>
+      <c r="C3" s="77" t="inlineStr">
+        <is>
+          <t>ייצור בדיד / יחידות (Discrete)</t>
+        </is>
+      </c>
+      <c r="D3" s="78" t="inlineStr">
+        <is>
+          <t>ייצור תהליכי / אצוות ונוזלים (Process)</t>
+        </is>
+      </c>
+      <c r="E3" s="79" t="inlineStr">
+        <is>
+          <t>CBC: ייצור משקאות הוא תהליכי מובהק - PP-PI הוא המודול הנכון (לא PP בדיד).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="46" customHeight="1">
+      <c r="A4" s="80" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="81" t="inlineStr">
+        <is>
+          <t>ענפים אופייניים (Industries)</t>
+        </is>
+      </c>
+      <c r="C4" s="82" t="inlineStr">
+        <is>
+          <t>רכב, אלקטרוניקה, מכונות, הרכבה</t>
         </is>
       </c>
       <c r="D4" s="78" t="inlineStr">
         <is>
-          <t>Tested</t>
-        </is>
-      </c>
-      <c r="E4" s="79" t="inlineStr">
-        <is>
-          <t>In Progress</t>
-        </is>
-      </c>
-      <c r="F4" s="80" t="inlineStr">
-        <is>
-          <t>Open</t>
-        </is>
-      </c>
-      <c r="G4" s="81" t="inlineStr">
-        <is>
-          <t>% Done</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="n"/>
-      <c r="I4" s="4" t="n"/>
-      <c r="J4" s="4" t="n"/>
-      <c r="K4" s="82" t="inlineStr">
-        <is>
-          <t>In analysis</t>
-        </is>
-      </c>
-      <c r="L4" s="75">
-        <f>COUNTIF($D$8:$D$72,$K4)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="n"/>
-      <c r="B5" s="4" t="n"/>
-      <c r="C5" s="4" t="n"/>
-      <c r="D5" s="4" t="n"/>
-      <c r="E5" s="4" t="n"/>
-      <c r="F5" s="4" t="n"/>
-      <c r="G5" s="4" t="n"/>
-      <c r="H5" s="4" t="n"/>
-      <c r="I5" s="4" t="n"/>
-      <c r="J5" s="4" t="n"/>
-      <c r="K5" s="83" t="inlineStr">
-        <is>
-          <t>In conversion</t>
-        </is>
-      </c>
-      <c r="L5" s="75">
-        <f>COUNTIF($D$8:$D$72,$K5)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="n"/>
-      <c r="B6" s="4" t="n"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-      <c r="F6" s="4" t="n"/>
-      <c r="G6" s="4" t="n"/>
-      <c r="H6" s="4" t="n"/>
-      <c r="I6" s="4" t="n"/>
-      <c r="J6" s="4" t="n"/>
-      <c r="K6" s="84" t="inlineStr">
-        <is>
-          <t>Tested</t>
-        </is>
-      </c>
-      <c r="L6" s="75">
-        <f>COUNTIF($D$8:$D$72,$K6)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7" ht="26" customHeight="1">
-      <c r="A7" s="85" t="inlineStr">
-        <is>
-          <t>מס' (#)</t>
-        </is>
-      </c>
-      <c r="B7" s="85" t="inlineStr">
-        <is>
-          <t>מודול / נושא</t>
-        </is>
-      </c>
-      <c r="C7" s="85" t="inlineStr">
-        <is>
-          <t>טבלה</t>
-        </is>
-      </c>
-      <c r="D7" s="85" t="inlineStr">
-        <is>
-          <t>סטטוס מעבר (Status)</t>
-        </is>
-      </c>
-      <c r="E7" s="85" t="inlineStr">
-        <is>
-          <t>קישור</t>
-        </is>
-      </c>
-      <c r="F7" s="85" t="inlineStr">
-        <is>
-          <t>תיאור</t>
-        </is>
-      </c>
-      <c r="G7" s="4" t="n"/>
-      <c r="H7" s="4" t="n"/>
-      <c r="I7" s="4" t="n"/>
-      <c r="J7" s="4" t="n"/>
-      <c r="K7" s="86" t="inlineStr">
-        <is>
-          <t>Done</t>
-        </is>
-      </c>
-      <c r="L7" s="75">
-        <f>COUNTIF($D$8:$D$72,$K7)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="50" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C8" s="49" t="inlineStr">
-        <is>
-          <t>MARA</t>
-        </is>
-      </c>
-      <c r="D8" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E8" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A22","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F8" s="53" t="inlineStr">
-        <is>
-          <t>נתוני אב חומר כלליים</t>
-        </is>
-      </c>
-      <c r="G8" s="4" t="n"/>
-      <c r="H8" s="4" t="n"/>
-      <c r="I8" s="4" t="n"/>
-      <c r="J8" s="4" t="n"/>
-      <c r="K8" s="4" t="n"/>
-      <c r="L8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C9" s="60" t="inlineStr">
-        <is>
-          <t>MAKT</t>
-        </is>
-      </c>
-      <c r="D9" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E9" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A32","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F9" s="64" t="inlineStr">
-        <is>
-          <t>תיאורי חומר (טקסטים)</t>
-        </is>
-      </c>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="50" t="n">
+          <t>מזון ומשקאות, כימיה, פארמה, קוסמטיקה</t>
+        </is>
+      </c>
+      <c r="E4" s="83" t="inlineStr">
+        <is>
+          <t>CBC (Coca-Cola) נמצא בליבת ה-Process Industries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="46" customHeight="1">
+      <c r="A5" s="75" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C10" s="49" t="inlineStr">
-        <is>
-          <t>MARC</t>
-        </is>
-      </c>
-      <c r="D10" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E10" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A38","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F10" s="53" t="inlineStr">
-        <is>
-          <t>נתוני חומר ברמת מפעל</t>
-        </is>
-      </c>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="61" t="n">
+      <c r="B5" s="76" t="inlineStr">
+        <is>
+          <t>נתוני אב חומר (Material)</t>
+        </is>
+      </c>
+      <c r="C5" s="77" t="inlineStr">
+        <is>
+          <t>חומר סטנדרטי (לרוב ללא אצווה)</t>
+        </is>
+      </c>
+      <c r="D5" s="78" t="inlineStr">
+        <is>
+          <t>חומר מנוהל אצווה (Batch-managed) - חובה</t>
+        </is>
+      </c>
+      <c r="E5" s="79" t="inlineStr">
+        <is>
+          <t>כל תרכיז/מוצר ב-CBC מנוהל אצווה לניהול BBD/תפוגה ומעקב Track&amp;Trace.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="46" customHeight="1">
+      <c r="A6" s="80" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C11" s="60" t="inlineStr">
-        <is>
-          <t>MARD</t>
-        </is>
-      </c>
-      <c r="D11" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E11" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A48","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F11" s="64" t="inlineStr">
-        <is>
-          <t>נתוני חומר ברמת מחסן/מלאי</t>
-        </is>
-      </c>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="50" t="n">
+      <c r="B6" s="81" t="inlineStr">
+        <is>
+          <t>הוראת ייצור (Order)</t>
+        </is>
+      </c>
+      <c r="C6" s="82" t="inlineStr">
+        <is>
+          <t>Production Order - CO01 / CO02 / CO03</t>
+        </is>
+      </c>
+      <c r="D6" s="78" t="inlineStr">
+        <is>
+          <t>Process Order - COR1 / COR2 / COR3</t>
+        </is>
+      </c>
+      <c r="E6" s="83" t="inlineStr">
+        <is>
+          <t>שחרור Process Order מפעיל Control Recipe ו-IDoc LOIPRO ל-MES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="46" customHeight="1">
+      <c r="A7" s="75" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C12" s="49" t="inlineStr">
-        <is>
-          <t>MARM</t>
-        </is>
-      </c>
-      <c r="D12" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E12" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A55","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F12" s="53" t="inlineStr">
-        <is>
-          <t>המרות יחידות מידה חלופיות</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="61" t="n">
+      <c r="B7" s="76" t="inlineStr">
+        <is>
+          <t>רשימת פעולות (Routing/Recipe)</t>
+        </is>
+      </c>
+      <c r="C7" s="77" t="inlineStr">
+        <is>
+          <t>Routing - CA01 / CA02 / CA03</t>
+        </is>
+      </c>
+      <c r="D7" s="78" t="inlineStr">
+        <is>
+          <t>Master Recipe (מתכון ייצור) - C201 / C202 / C203</t>
+        </is>
+      </c>
+      <c r="E7" s="79" t="inlineStr">
+        <is>
+          <t>המתכון כולל נוסחה (Formula), פאזות והוראות תהליך - לא רק פעולות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="46" customHeight="1">
+      <c r="A8" s="80" t="n">
         <v>6</v>
       </c>
-      <c r="B13" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C13" s="60" t="inlineStr">
-        <is>
-          <t>MEAN</t>
-        </is>
-      </c>
-      <c r="D13" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E13" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A63","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F13" s="64" t="inlineStr">
-        <is>
-          <t>ברקודים / EAN לחומר</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="50" t="n">
+      <c r="B8" s="81" t="inlineStr">
+        <is>
+          <t>מבנה ביצוע (Execution structure)</t>
+        </is>
+      </c>
+      <c r="C8" s="82" t="inlineStr">
+        <is>
+          <t>Operations (פעולות בלבד)</t>
+        </is>
+      </c>
+      <c r="D8" s="78" t="inlineStr">
+        <is>
+          <t>Operations + Phases + Process Instructions (PI)</t>
+        </is>
+      </c>
+      <c r="E8" s="83" t="inlineStr">
+        <is>
+          <t>הפאזות (ערבול/פסטור/מילוי) שולחות הוראות לבקרי הקו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="46" customHeight="1">
+      <c r="A9" s="75" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C14" s="49" t="inlineStr">
-        <is>
-          <t>MBEW</t>
-        </is>
-      </c>
-      <c r="D14" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E14" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A70","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F14" s="53" t="inlineStr">
-        <is>
-          <t>הערכת חומר (Valuation)</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="61" t="n">
+      <c r="B9" s="76" t="inlineStr">
+        <is>
+          <t>משאבי ביצוע (Resources)</t>
+        </is>
+      </c>
+      <c r="C9" s="77" t="inlineStr">
+        <is>
+          <t>Work Center - CR01 / CR02 / CR03</t>
+        </is>
+      </c>
+      <c r="D9" s="78" t="inlineStr">
+        <is>
+          <t>Resource - CRC1 / CRC2 / CRC3</t>
+        </is>
+      </c>
+      <c r="E9" s="79" t="inlineStr">
+        <is>
+          <t>אותו מודל טכני (CRHD) אך ה-Resource נושא ערכי PI וברירות מחדל לתהליך.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="46" customHeight="1">
+      <c r="A10" s="80" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C15" s="60" t="inlineStr">
-        <is>
-          <t>MVKE</t>
-        </is>
-      </c>
-      <c r="D15" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E15" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A78","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F15" s="64" t="inlineStr">
-        <is>
-          <t>נתוני חומר ברמת מכירות</t>
-        </is>
-      </c>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="50" t="n">
+      <c r="B10" s="81" t="inlineStr">
+        <is>
+          <t>בקרת ביצוע (Shop-floor control)</t>
+        </is>
+      </c>
+      <c r="C10" s="82" t="inlineStr">
+        <is>
+          <t>דיווח ביצוע (Confirmation) ידני/MES</t>
+        </is>
+      </c>
+      <c r="D10" s="78" t="inlineStr">
+        <is>
+          <t>Control Recipe / PI Sheet / Process Messages</t>
+        </is>
+      </c>
+      <c r="E10" s="83" t="inlineStr">
+        <is>
+          <t>PP-PI מתממשק ל-Zetes/Daymax דרך הודעות תהליך (PI Messages) ו-IDoc.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="75" t="n">
         <v>9</v>
       </c>
-      <c r="B16" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C16" s="49" t="inlineStr">
-        <is>
-          <t>MLAN</t>
-        </is>
-      </c>
-      <c r="D16" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E16" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A84","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F16" s="53" t="inlineStr">
-        <is>
-          <t>נתוני מס לחומר (לפי מדינה)</t>
-        </is>
-      </c>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="61" t="n">
+      <c r="B11" s="76" t="inlineStr">
+        <is>
+          <t>מערכת מעקב (Monitoring cockpit)</t>
+        </is>
+      </c>
+      <c r="C11" s="77" t="inlineStr">
+        <is>
+          <t>COOIS (Order Information System)</t>
+        </is>
+      </c>
+      <c r="D11" s="78" t="inlineStr">
+        <is>
+          <t>COIO (Process Order Information System) + PI Cockpit</t>
+        </is>
+      </c>
+      <c r="E11" s="79" t="inlineStr">
+        <is>
+          <t>COIO הוא לוח המעקב התפעולי המרכזי של CBC.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="80" t="n">
         <v>10</v>
       </c>
-      <c r="B17" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C17" s="60" t="inlineStr">
-        <is>
-          <t>MLGN</t>
-        </is>
-      </c>
-      <c r="D17" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E17" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A89","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F17" s="64" t="inlineStr">
-        <is>
-          <t>נתוני חומר ברמת מחסן (WM)</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="n"/>
-      <c r="H17" s="4" t="n"/>
-      <c r="I17" s="4" t="n"/>
-      <c r="J17" s="4" t="n"/>
-      <c r="K17" s="4" t="n"/>
-      <c r="L17" s="4" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="50" t="n">
+      <c r="B12" s="81" t="inlineStr">
+        <is>
+          <t>עץ מוצר (BOM)</t>
+        </is>
+      </c>
+      <c r="C12" s="82" t="inlineStr">
+        <is>
+          <t>Production BOM (STLAN=1)</t>
+        </is>
+      </c>
+      <c r="D12" s="78" t="inlineStr">
+        <is>
+          <t>Recipe BOM + שיוך רכיב לפאזה (PLMZ)</t>
+        </is>
+      </c>
+      <c r="E12" s="83" t="inlineStr">
+        <is>
+          <t>ב-PP-PI כל חומר גלם משויך לפאזה הספציפית שבה הוא נצרך.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="75" t="n">
         <v>11</v>
       </c>
-      <c r="B18" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C18" s="49" t="inlineStr">
-        <is>
-          <t>MLGT</t>
-        </is>
-      </c>
-      <c r="D18" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E18" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A95","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F18" s="53" t="inlineStr">
-        <is>
-          <t>נתוני חומר לפי טיפוס אחסון</t>
-        </is>
-      </c>
-      <c r="G18" s="4" t="n"/>
-      <c r="H18" s="4" t="n"/>
-      <c r="I18" s="4" t="n"/>
-      <c r="J18" s="4" t="n"/>
-      <c r="K18" s="4" t="n"/>
-      <c r="L18" s="4" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="61" t="n">
+      <c r="B13" s="76" t="inlineStr">
+        <is>
+          <t>גרסת ייצור (Production Version)</t>
+        </is>
+      </c>
+      <c r="C13" s="77" t="inlineStr">
+        <is>
+          <t>MKAL - מומלצת ב-ECC</t>
+        </is>
+      </c>
+      <c r="D13" s="78" t="inlineStr">
+        <is>
+          <t>MKAL - חובה 100% ב-S/4HANA</t>
+        </is>
+      </c>
+      <c r="E13" s="79" t="inlineStr">
+        <is>
+          <t>ב-S/4 ה-VERID נועל את הקישור המדויק מתכון&lt;-&gt;BOM חלופי לכל ביצוע.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="80" t="n">
         <v>12</v>
       </c>
-      <c r="B19" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C19" s="60" t="inlineStr">
-        <is>
-          <t>MDMA</t>
-        </is>
-      </c>
-      <c r="D19" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E19" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A101","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F19" s="64" t="inlineStr">
-        <is>
-          <t>אזורי MRP לחומר</t>
-        </is>
-      </c>
-      <c r="G19" s="4" t="n"/>
-      <c r="H19" s="4" t="n"/>
-      <c r="I19" s="4" t="n"/>
-      <c r="J19" s="4" t="n"/>
-      <c r="K19" s="4" t="n"/>
-      <c r="L19" s="4" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="50" t="n">
+      <c r="B14" s="81" t="inlineStr">
+        <is>
+          <t>תכנון חומרים (Planning)</t>
+        </is>
+      </c>
+      <c r="C14" s="82" t="inlineStr">
+        <is>
+          <t>MRP קלאסי - MD01 / NETCH</t>
+        </is>
+      </c>
+      <c r="D14" s="78" t="inlineStr">
+        <is>
+          <t>MRP Live (HANA-optimized) - MD01N</t>
+        </is>
+      </c>
+      <c r="E14" s="83" t="inlineStr">
+        <is>
+          <t>ב-S/4 ריצות ה-MRP הקלאסיות מוחלפות ב-MRP Live שרץ ישירות על HANA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="75" t="n">
         <v>13</v>
       </c>
-      <c r="B20" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C20" s="49" t="inlineStr">
-        <is>
-          <t>QMAT</t>
-        </is>
-      </c>
-      <c r="D20" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E20" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A107","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F20" s="53" t="inlineStr">
-        <is>
-          <t>הגדרות בדיקת איכות לחומר</t>
-        </is>
-      </c>
-      <c r="G20" s="4" t="n"/>
-      <c r="H20" s="4" t="n"/>
-      <c r="I20" s="4" t="n"/>
-      <c r="J20" s="4" t="n"/>
-      <c r="K20" s="4" t="n"/>
-      <c r="L20" s="4" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="61" t="n">
+      <c r="B15" s="76" t="inlineStr">
+        <is>
+          <t>ממשק חיצוני (IDoc/MES)</t>
+        </is>
+      </c>
+      <c r="C15" s="77" t="inlineStr">
+        <is>
+          <t>LOIPRO (Production Order)</t>
+        </is>
+      </c>
+      <c r="D15" s="78" t="inlineStr">
+        <is>
+          <t>LOIPRO + PI Process Messages (PPCC1)</t>
+        </is>
+      </c>
+      <c r="E15" s="79" t="inlineStr">
+        <is>
+          <t>סנכרון דו-כיווני בין SAP לבין מערכות הלוגיסטיקה/אוטומציה (Zetes/Daymax).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="80" t="n">
         <v>14</v>
       </c>
-      <c r="B21" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C21" s="60" t="inlineStr">
-        <is>
-          <t>MCH1</t>
-        </is>
-      </c>
-      <c r="D21" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E21" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A113","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F21" s="64" t="inlineStr">
-        <is>
-          <t>אצוות חומר (Batches)</t>
-        </is>
-      </c>
-      <c r="G21" s="4" t="n"/>
-      <c r="H21" s="4" t="n"/>
-      <c r="I21" s="4" t="n"/>
-      <c r="J21" s="4" t="n"/>
-      <c r="K21" s="4" t="n"/>
-      <c r="L21" s="4" t="n"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="50" t="n">
-        <v>15</v>
-      </c>
-      <c r="B22" s="53" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C22" s="49" t="inlineStr">
-        <is>
-          <t>MCHA</t>
-        </is>
-      </c>
-      <c r="D22" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E22" s="87">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A122","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F22" s="53" t="inlineStr">
-        <is>
-          <t>אצוות חומר ברמת מפעל</t>
-        </is>
-      </c>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="61" t="n">
-        <v>16</v>
-      </c>
-      <c r="B23" s="64" t="inlineStr">
-        <is>
-          <t>1. נתוני אב חומר ויחידות מידה (Material &amp; UoM)</t>
-        </is>
-      </c>
-      <c r="C23" s="60" t="inlineStr">
-        <is>
-          <t>T006</t>
-        </is>
-      </c>
-      <c r="D23" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E23" s="88">
-        <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A128","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F23" s="64" t="inlineStr">
-        <is>
-          <t>יחידות מידה (Customizing)</t>
-        </is>
-      </c>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="50" t="n">
-        <v>17</v>
-      </c>
-      <c r="B24" s="53" t="inlineStr">
-        <is>
-          <t>2. עץ מוצר (BOM)</t>
-        </is>
-      </c>
-      <c r="C24" s="49" t="inlineStr">
-        <is>
-          <t>MAST</t>
-        </is>
-      </c>
-      <c r="D24" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E24" s="87">
-        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A21","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F24" s="53" t="inlineStr">
-        <is>
-          <t>קישור חומר לעץ מוצר</t>
-        </is>
-      </c>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="61" t="n">
-        <v>18</v>
-      </c>
-      <c r="B25" s="64" t="inlineStr">
-        <is>
-          <t>2. עץ מוצר (BOM)</t>
-        </is>
-      </c>
-      <c r="C25" s="60" t="inlineStr">
-        <is>
-          <t>STKO</t>
-        </is>
-      </c>
-      <c r="D25" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E25" s="88">
-        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A28","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F25" s="64" t="inlineStr">
-        <is>
-          <t>כותרת עץ מוצר</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="50" t="n">
-        <v>19</v>
-      </c>
-      <c r="B26" s="53" t="inlineStr">
-        <is>
-          <t>2. עץ מוצר (BOM)</t>
-        </is>
-      </c>
-      <c r="C26" s="49" t="inlineStr">
-        <is>
-          <t>STPO</t>
-        </is>
-      </c>
-      <c r="D26" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E26" s="87">
-        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A36","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F26" s="53" t="inlineStr">
-        <is>
-          <t>פריטי עץ מוצר (רכיבים)</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n"/>
-      <c r="H26" s="4" t="n"/>
-      <c r="I26" s="4" t="n"/>
-      <c r="J26" s="4" t="n"/>
-      <c r="K26" s="4" t="n"/>
-      <c r="L26" s="4" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="61" t="n">
-        <v>20</v>
-      </c>
-      <c r="B27" s="64" t="inlineStr">
-        <is>
-          <t>2. עץ מוצר (BOM)</t>
-        </is>
-      </c>
-      <c r="C27" s="60" t="inlineStr">
-        <is>
-          <t>STAS</t>
-        </is>
-      </c>
-      <c r="D27" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E27" s="88">
-        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A47","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F27" s="64" t="inlineStr">
-        <is>
-          <t>בחירת פריטי עץ מוצר</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="50" t="n">
-        <v>21</v>
-      </c>
-      <c r="B28" s="53" t="inlineStr">
-        <is>
-          <t>2. עץ מוצר (BOM)</t>
-        </is>
-      </c>
-      <c r="C28" s="49" t="inlineStr">
-        <is>
-          <t>STZU</t>
-        </is>
-      </c>
-      <c r="D28" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E28" s="87">
-        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A54","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F28" s="53" t="inlineStr">
-        <is>
-          <t>טבלת היסטוריה/קישור לעץ מוצר</t>
-        </is>
-      </c>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="61" t="n">
-        <v>22</v>
-      </c>
-      <c r="B29" s="64" t="inlineStr">
-        <is>
-          <t>2. עץ מוצר (BOM)</t>
-        </is>
-      </c>
-      <c r="C29" s="60" t="inlineStr">
-        <is>
-          <t>STPU</t>
-        </is>
-      </c>
-      <c r="D29" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E29" s="88">
-        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A60","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F29" s="64" t="inlineStr">
-        <is>
-          <t>טקסטים ארוכים לפריט עץ מוצר</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n"/>
-      <c r="H29" s="4" t="n"/>
-      <c r="I29" s="4" t="n"/>
-      <c r="J29" s="4" t="n"/>
-      <c r="K29" s="4" t="n"/>
-      <c r="L29" s="4" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="50" t="n">
-        <v>23</v>
-      </c>
-      <c r="B30" s="53" t="inlineStr">
-        <is>
-          <t>2. עץ מוצר (BOM)</t>
-        </is>
-      </c>
-      <c r="C30" s="49" t="inlineStr">
-        <is>
-          <t>KDST</t>
-        </is>
-      </c>
-      <c r="D30" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E30" s="87">
-        <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A65","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F30" s="53" t="inlineStr">
-        <is>
-          <t>שימוש עץ מוצר בהזמנת לקוח</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="n"/>
-      <c r="H30" s="4" t="n"/>
-      <c r="I30" s="4" t="n"/>
-      <c r="J30" s="4" t="n"/>
-      <c r="K30" s="4" t="n"/>
-      <c r="L30" s="4" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="61" t="n">
-        <v>24</v>
-      </c>
-      <c r="B31" s="64" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C31" s="60" t="inlineStr">
-        <is>
-          <t>PLKO</t>
-        </is>
-      </c>
-      <c r="D31" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E31" s="88">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A21","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F31" s="64" t="inlineStr">
-        <is>
-          <t>כותרת מתכון ייצור / רשימת פעולות</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="n"/>
-      <c r="H31" s="4" t="n"/>
-      <c r="I31" s="4" t="n"/>
-      <c r="J31" s="4" t="n"/>
-      <c r="K31" s="4" t="n"/>
-      <c r="L31" s="4" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="50" t="n">
-        <v>25</v>
-      </c>
-      <c r="B32" s="53" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C32" s="49" t="inlineStr">
-        <is>
-          <t>PLPO</t>
-        </is>
-      </c>
-      <c r="D32" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E32" s="87">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A30","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F32" s="53" t="inlineStr">
-        <is>
-          <t>פעולות/פאזות במתכון</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="n"/>
-      <c r="H32" s="4" t="n"/>
-      <c r="I32" s="4" t="n"/>
-      <c r="J32" s="4" t="n"/>
-      <c r="K32" s="4" t="n"/>
-      <c r="L32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="61" t="n">
-        <v>26</v>
-      </c>
-      <c r="B33" s="64" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C33" s="60" t="inlineStr">
-        <is>
-          <t>PLAS</t>
-        </is>
-      </c>
-      <c r="D33" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E33" s="88">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A41","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F33" s="64" t="inlineStr">
-        <is>
-          <t>שיוך/בחירת פעולות לרשימה</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n"/>
-      <c r="H33" s="4" t="n"/>
-      <c r="I33" s="4" t="n"/>
-      <c r="J33" s="4" t="n"/>
-      <c r="K33" s="4" t="n"/>
-      <c r="L33" s="4" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="50" t="n">
-        <v>27</v>
-      </c>
-      <c r="B34" s="53" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C34" s="49" t="inlineStr">
-        <is>
-          <t>PLFL</t>
-        </is>
-      </c>
-      <c r="D34" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E34" s="87">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A49","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F34" s="53" t="inlineStr">
-        <is>
-          <t>רצפים במתכון</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="n"/>
-      <c r="H34" s="4" t="n"/>
-      <c r="I34" s="4" t="n"/>
-      <c r="J34" s="4" t="n"/>
-      <c r="K34" s="4" t="n"/>
-      <c r="L34" s="4" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="61" t="n">
-        <v>28</v>
-      </c>
-      <c r="B35" s="64" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C35" s="60" t="inlineStr">
-        <is>
-          <t>PLMZ</t>
-        </is>
-      </c>
-      <c r="D35" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E35" s="88">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A55","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F35" s="64" t="inlineStr">
-        <is>
-          <t>שיוך רכיבים לפעולות</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="n"/>
-      <c r="H35" s="4" t="n"/>
-      <c r="I35" s="4" t="n"/>
-      <c r="J35" s="4" t="n"/>
-      <c r="K35" s="4" t="n"/>
-      <c r="L35" s="4" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="50" t="n">
-        <v>29</v>
-      </c>
-      <c r="B36" s="53" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C36" s="49" t="inlineStr">
-        <is>
-          <t>PLMK</t>
-        </is>
-      </c>
-      <c r="D36" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E36" s="87">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A62","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F36" s="53" t="inlineStr">
-        <is>
-          <t>מאפייני בדיקה במתכון</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="n"/>
-      <c r="H36" s="4" t="n"/>
-      <c r="I36" s="4" t="n"/>
-      <c r="J36" s="4" t="n"/>
-      <c r="K36" s="4" t="n"/>
-      <c r="L36" s="4" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="61" t="n">
-        <v>30</v>
-      </c>
-      <c r="B37" s="64" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C37" s="60" t="inlineStr">
-        <is>
-          <t>MAPL</t>
-        </is>
-      </c>
-      <c r="D37" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E37" s="88">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A70","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F37" s="64" t="inlineStr">
-        <is>
-          <t>שיוך חומר למתכון/רשימת פעולות</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="n"/>
-      <c r="H37" s="4" t="n"/>
-      <c r="I37" s="4" t="n"/>
-      <c r="J37" s="4" t="n"/>
-      <c r="K37" s="4" t="n"/>
-      <c r="L37" s="4" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="50" t="n">
-        <v>31</v>
-      </c>
-      <c r="B38" s="53" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C38" s="49" t="inlineStr">
-        <is>
-          <t>FHMI</t>
-        </is>
-      </c>
-      <c r="D38" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E38" s="87">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A77","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F38" s="53" t="inlineStr">
-        <is>
-          <t>שיוך כלי עזר ייצור (PRT) לפעולה</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="n"/>
-      <c r="H38" s="4" t="n"/>
-      <c r="I38" s="4" t="n"/>
-      <c r="J38" s="4" t="n"/>
-      <c r="K38" s="4" t="n"/>
-      <c r="L38" s="4" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="61" t="n">
-        <v>32</v>
-      </c>
-      <c r="B39" s="64" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C39" s="60" t="inlineStr">
-        <is>
-          <t>PLZU</t>
-        </is>
-      </c>
-      <c r="D39" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E39" s="88">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A83","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F39" s="64" t="inlineStr">
-        <is>
-          <t>קישור היסטוריית רשימת פעולות</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="n"/>
-      <c r="H39" s="4" t="n"/>
-      <c r="I39" s="4" t="n"/>
-      <c r="J39" s="4" t="n"/>
-      <c r="K39" s="4" t="n"/>
-      <c r="L39" s="4" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="50" t="n">
-        <v>33</v>
-      </c>
-      <c r="B40" s="53" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C40" s="49" t="inlineStr">
-        <is>
-          <t>TC60</t>
-        </is>
-      </c>
-      <c r="D40" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E40" s="87">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A88","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F40" s="53" t="inlineStr">
-        <is>
-          <t>מאפייני הוראות תהליך (PI)</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="n"/>
-      <c r="H40" s="4" t="n"/>
-      <c r="I40" s="4" t="n"/>
-      <c r="J40" s="4" t="n"/>
-      <c r="K40" s="4" t="n"/>
-      <c r="L40" s="4" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="61" t="n">
-        <v>34</v>
-      </c>
-      <c r="B41" s="64" t="inlineStr">
-        <is>
-          <t>3. מתכון ייצור ופעולות (Master Recipe)</t>
-        </is>
-      </c>
-      <c r="C41" s="60" t="inlineStr">
-        <is>
-          <t>TCA01</t>
-        </is>
-      </c>
-      <c r="D41" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E41" s="88">
-        <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A93","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F41" s="64" t="inlineStr">
-        <is>
-          <t>פרופיל רשימת פעולות (Customizing)</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="n"/>
-      <c r="H41" s="4" t="n"/>
-      <c r="I41" s="4" t="n"/>
-      <c r="J41" s="4" t="n"/>
-      <c r="K41" s="4" t="n"/>
-      <c r="L41" s="4" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="50" t="n">
-        <v>35</v>
-      </c>
-      <c r="B42" s="53" t="inlineStr">
-        <is>
-          <t>4. גרסאות ייצור (Production Versions - חובה ב-S/4)</t>
-        </is>
-      </c>
-      <c r="C42" s="49" t="inlineStr">
-        <is>
-          <t>MKAL</t>
-        </is>
-      </c>
-      <c r="D42" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E42" s="87">
-        <f>HYPERLINK("#'"&amp;"4. גרסאות ייצור (Production Ver"&amp;"'!A19","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F42" s="53" t="inlineStr">
-        <is>
-          <t>גרסאות ייצור לחומר</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="n"/>
-      <c r="H42" s="4" t="n"/>
-      <c r="I42" s="4" t="n"/>
-      <c r="J42" s="4" t="n"/>
-      <c r="K42" s="4" t="n"/>
-      <c r="L42" s="4" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="61" t="n">
-        <v>36</v>
-      </c>
-      <c r="B43" s="64" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C43" s="60" t="inlineStr">
-        <is>
-          <t>CRHD</t>
-        </is>
-      </c>
-      <c r="D43" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E43" s="88">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A20","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F43" s="64" t="inlineStr">
-        <is>
-          <t>כותרת משאב / מרכז עבודה</t>
-        </is>
-      </c>
-      <c r="G43" s="4" t="n"/>
-      <c r="H43" s="4" t="n"/>
-      <c r="I43" s="4" t="n"/>
-      <c r="J43" s="4" t="n"/>
-      <c r="K43" s="4" t="n"/>
-      <c r="L43" s="4" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="50" t="n">
-        <v>37</v>
-      </c>
-      <c r="B44" s="53" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C44" s="49" t="inlineStr">
-        <is>
-          <t>CRTX</t>
-        </is>
-      </c>
-      <c r="D44" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E44" s="87">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A29","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F44" s="53" t="inlineStr">
-        <is>
-          <t>טקסטים של משאב</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="n"/>
-      <c r="H44" s="4" t="n"/>
-      <c r="I44" s="4" t="n"/>
-      <c r="J44" s="4" t="n"/>
-      <c r="K44" s="4" t="n"/>
-      <c r="L44" s="4" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="61" t="n">
-        <v>38</v>
-      </c>
-      <c r="B45" s="64" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C45" s="60" t="inlineStr">
-        <is>
-          <t>CRCO</t>
-        </is>
-      </c>
-      <c r="D45" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E45" s="88">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A35","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F45" s="64" t="inlineStr">
-        <is>
-          <t>שיוך משאב למרכז עלות</t>
-        </is>
-      </c>
-      <c r="G45" s="4" t="n"/>
-      <c r="H45" s="4" t="n"/>
-      <c r="I45" s="4" t="n"/>
-      <c r="J45" s="4" t="n"/>
-      <c r="K45" s="4" t="n"/>
-      <c r="L45" s="4" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="50" t="n">
-        <v>39</v>
-      </c>
-      <c r="B46" s="53" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C46" s="49" t="inlineStr">
-        <is>
-          <t>CRCA</t>
-        </is>
-      </c>
-      <c r="D46" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E46" s="87">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A43","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F46" s="53" t="inlineStr">
-        <is>
-          <t>הקצאת קיבולת למשאב</t>
-        </is>
-      </c>
-      <c r="G46" s="4" t="n"/>
-      <c r="H46" s="4" t="n"/>
-      <c r="I46" s="4" t="n"/>
-      <c r="J46" s="4" t="n"/>
-      <c r="K46" s="4" t="n"/>
-      <c r="L46" s="4" t="n"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="61" t="n">
-        <v>40</v>
-      </c>
-      <c r="B47" s="64" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C47" s="60" t="inlineStr">
-        <is>
-          <t>KAKO</t>
-        </is>
-      </c>
-      <c r="D47" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E47" s="88">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A49","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F47" s="64" t="inlineStr">
-        <is>
-          <t>כותרת קיבולת</t>
-        </is>
-      </c>
-      <c r="G47" s="4" t="n"/>
-      <c r="H47" s="4" t="n"/>
-      <c r="I47" s="4" t="n"/>
-      <c r="J47" s="4" t="n"/>
-      <c r="K47" s="4" t="n"/>
-      <c r="L47" s="4" t="n"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="50" t="n">
-        <v>41</v>
-      </c>
-      <c r="B48" s="53" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C48" s="49" t="inlineStr">
-        <is>
-          <t>CRFH</t>
-        </is>
-      </c>
-      <c r="D48" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E48" s="87">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A55","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F48" s="53" t="inlineStr">
-        <is>
-          <t>אב כלי עזר ייצור (PRT)</t>
-        </is>
-      </c>
-      <c r="G48" s="4" t="n"/>
-      <c r="H48" s="4" t="n"/>
-      <c r="I48" s="4" t="n"/>
-      <c r="J48" s="4" t="n"/>
-      <c r="K48" s="4" t="n"/>
-      <c r="L48" s="4" t="n"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="61" t="n">
-        <v>42</v>
-      </c>
-      <c r="B49" s="64" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C49" s="60" t="inlineStr">
-        <is>
-          <t>CRVD_A</t>
-        </is>
-      </c>
-      <c r="D49" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E49" s="88">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A61","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F49" s="64" t="inlineStr">
-        <is>
-          <t>ברירות מחדל למשאב (PI)</t>
-        </is>
-      </c>
-      <c r="G49" s="4" t="n"/>
-      <c r="H49" s="4" t="n"/>
-      <c r="I49" s="4" t="n"/>
-      <c r="J49" s="4" t="n"/>
-      <c r="K49" s="4" t="n"/>
-      <c r="L49" s="4" t="n"/>
-    </row>
-    <row r="50">
-      <c r="A50" s="50" t="n">
-        <v>43</v>
-      </c>
-      <c r="B50" s="53" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C50" s="49" t="inlineStr">
-        <is>
-          <t>CSLA</t>
-        </is>
-      </c>
-      <c r="D50" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E50" s="87">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A66","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F50" s="53" t="inlineStr">
-        <is>
-          <t>סוגי פעילות למרכז עבודה</t>
-        </is>
-      </c>
-      <c r="G50" s="4" t="n"/>
-      <c r="H50" s="4" t="n"/>
-      <c r="I50" s="4" t="n"/>
-      <c r="J50" s="4" t="n"/>
-      <c r="K50" s="4" t="n"/>
-      <c r="L50" s="4" t="n"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="61" t="n">
-        <v>44</v>
-      </c>
-      <c r="B51" s="64" t="inlineStr">
-        <is>
-          <t>5. משאבים / מרכזי עבודה (Resources)</t>
-        </is>
-      </c>
-      <c r="C51" s="60" t="inlineStr">
-        <is>
-          <t>KAZT</t>
-        </is>
-      </c>
-      <c r="D51" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E51" s="88">
-        <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A71","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F51" s="64" t="inlineStr">
-        <is>
-          <t>מרווחי קיבולת זמינה</t>
-        </is>
-      </c>
-      <c r="G51" s="4" t="n"/>
-      <c r="H51" s="4" t="n"/>
-      <c r="I51" s="4" t="n"/>
-      <c r="J51" s="4" t="n"/>
-      <c r="K51" s="4" t="n"/>
-      <c r="L51" s="4" t="n"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="50" t="n">
-        <v>45</v>
-      </c>
-      <c r="B52" s="53" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C52" s="49" t="inlineStr">
-        <is>
-          <t>AUFK</t>
-        </is>
-      </c>
-      <c r="D52" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E52" s="87">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A22","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F52" s="53" t="inlineStr">
-        <is>
-          <t>נתוני אב של פקודת ייצור</t>
-        </is>
-      </c>
-      <c r="G52" s="4" t="n"/>
-      <c r="H52" s="4" t="n"/>
-      <c r="I52" s="4" t="n"/>
-      <c r="J52" s="4" t="n"/>
-      <c r="K52" s="4" t="n"/>
-      <c r="L52" s="4" t="n"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="61" t="n">
-        <v>46</v>
-      </c>
-      <c r="B53" s="64" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C53" s="60" t="inlineStr">
-        <is>
-          <t>AFKO</t>
-        </is>
-      </c>
-      <c r="D53" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E53" s="88">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A29","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F53" s="64" t="inlineStr">
-        <is>
-          <t>כותרת פקודת ייצור</t>
-        </is>
-      </c>
-      <c r="G53" s="4" t="n"/>
-      <c r="H53" s="4" t="n"/>
-      <c r="I53" s="4" t="n"/>
-      <c r="J53" s="4" t="n"/>
-      <c r="K53" s="4" t="n"/>
-      <c r="L53" s="4" t="n"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="50" t="n">
-        <v>47</v>
-      </c>
-      <c r="B54" s="53" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C54" s="49" t="inlineStr">
-        <is>
-          <t>AFPO</t>
-        </is>
-      </c>
-      <c r="D54" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E54" s="87">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A37","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F54" s="53" t="inlineStr">
-        <is>
-          <t>פריט פקודת ייצור</t>
-        </is>
-      </c>
-      <c r="G54" s="4" t="n"/>
-      <c r="H54" s="4" t="n"/>
-      <c r="I54" s="4" t="n"/>
-      <c r="J54" s="4" t="n"/>
-      <c r="K54" s="4" t="n"/>
-      <c r="L54" s="4" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="61" t="n">
-        <v>48</v>
-      </c>
-      <c r="B55" s="64" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C55" s="60" t="inlineStr">
-        <is>
-          <t>AFVC</t>
-        </is>
-      </c>
-      <c r="D55" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E55" s="88">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A44","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F55" s="64" t="inlineStr">
-        <is>
-          <t>פעולות פקודת הייצור</t>
-        </is>
-      </c>
-      <c r="G55" s="4" t="n"/>
-      <c r="H55" s="4" t="n"/>
-      <c r="I55" s="4" t="n"/>
-      <c r="J55" s="4" t="n"/>
-      <c r="K55" s="4" t="n"/>
-      <c r="L55" s="4" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B56" s="53" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C56" s="49" t="inlineStr">
-        <is>
-          <t>RESB</t>
-        </is>
-      </c>
-      <c r="D56" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E56" s="87">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A52","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F56" s="53" t="inlineStr">
-        <is>
-          <t>הזמנת רכיבים לפק"ע</t>
-        </is>
-      </c>
-      <c r="G56" s="4" t="n"/>
-      <c r="H56" s="4" t="n"/>
-      <c r="I56" s="4" t="n"/>
-      <c r="J56" s="4" t="n"/>
-      <c r="K56" s="4" t="n"/>
-      <c r="L56" s="4" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="61" t="n">
-        <v>50</v>
-      </c>
-      <c r="B57" s="64" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C57" s="60" t="inlineStr">
-        <is>
-          <t>AFRU</t>
-        </is>
-      </c>
-      <c r="D57" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E57" s="88">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A60","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F57" s="64" t="inlineStr">
-        <is>
-          <t>דיווחי ביצוע פק"ע</t>
-        </is>
-      </c>
-      <c r="G57" s="4" t="n"/>
-      <c r="H57" s="4" t="n"/>
-      <c r="I57" s="4" t="n"/>
-      <c r="J57" s="4" t="n"/>
-      <c r="K57" s="4" t="n"/>
-      <c r="L57" s="4" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="50" t="n">
-        <v>51</v>
-      </c>
-      <c r="B58" s="53" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C58" s="49" t="inlineStr">
-        <is>
-          <t>AFFH</t>
-        </is>
-      </c>
-      <c r="D58" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E58" s="87">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A67","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F58" s="53" t="inlineStr">
-        <is>
-          <t>שיוך PRT לפק"ע</t>
-        </is>
-      </c>
-      <c r="G58" s="4" t="n"/>
-      <c r="H58" s="4" t="n"/>
-      <c r="I58" s="4" t="n"/>
-      <c r="J58" s="4" t="n"/>
-      <c r="K58" s="4" t="n"/>
-      <c r="L58" s="4" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="61" t="n">
-        <v>52</v>
-      </c>
-      <c r="B59" s="64" t="inlineStr">
-        <is>
-          <t>6. פק"ע ייצור ומתכון בקרה (Process Order)</t>
-        </is>
-      </c>
-      <c r="C59" s="60" t="inlineStr">
-        <is>
-          <t>AFFL</t>
-        </is>
-      </c>
-      <c r="D59" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E59" s="88">
-        <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A72","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F59" s="64" t="inlineStr">
-        <is>
-          <t>רצפי פעולות בפק"ע</t>
-        </is>
-      </c>
-      <c r="G59" s="4" t="n"/>
-      <c r="H59" s="4" t="n"/>
-      <c r="I59" s="4" t="n"/>
-      <c r="J59" s="4" t="n"/>
-      <c r="K59" s="4" t="n"/>
-      <c r="L59" s="4" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="50" t="n">
-        <v>53</v>
-      </c>
-      <c r="B60" s="53" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C60" s="49" t="inlineStr">
-        <is>
-          <t>T134</t>
-        </is>
-      </c>
-      <c r="D60" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E60" s="87">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A22","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F60" s="53" t="inlineStr">
-        <is>
-          <t>סוגי חומר (Customizing)</t>
-        </is>
-      </c>
-      <c r="G60" s="4" t="n"/>
-      <c r="H60" s="4" t="n"/>
-      <c r="I60" s="4" t="n"/>
-      <c r="J60" s="4" t="n"/>
-      <c r="K60" s="4" t="n"/>
-      <c r="L60" s="4" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" s="61" t="n">
-        <v>54</v>
-      </c>
-      <c r="B61" s="64" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C61" s="60" t="inlineStr">
-        <is>
-          <t>T134T</t>
-        </is>
-      </c>
-      <c r="D61" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E61" s="88">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A27","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F61" s="64" t="inlineStr">
-        <is>
-          <t>טקסטים לסוגי חומר</t>
-        </is>
-      </c>
-      <c r="G61" s="4" t="n"/>
-      <c r="H61" s="4" t="n"/>
-      <c r="I61" s="4" t="n"/>
-      <c r="J61" s="4" t="n"/>
-      <c r="K61" s="4" t="n"/>
-      <c r="L61" s="4" t="n"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="50" t="n">
-        <v>55</v>
-      </c>
-      <c r="B62" s="53" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C62" s="49" t="inlineStr">
-        <is>
-          <t>T023</t>
-        </is>
-      </c>
-      <c r="D62" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E62" s="87">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A32","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F62" s="53" t="inlineStr">
-        <is>
-          <t>קבוצות חומר (Customizing)</t>
-        </is>
-      </c>
-      <c r="G62" s="4" t="n"/>
-      <c r="H62" s="4" t="n"/>
-      <c r="I62" s="4" t="n"/>
-      <c r="J62" s="4" t="n"/>
-      <c r="K62" s="4" t="n"/>
-      <c r="L62" s="4" t="n"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="61" t="n">
-        <v>56</v>
-      </c>
-      <c r="B63" s="64" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C63" s="60" t="inlineStr">
-        <is>
-          <t>T023T</t>
-        </is>
-      </c>
-      <c r="D63" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E63" s="88">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A36","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F63" s="64" t="inlineStr">
-        <is>
-          <t>טקסטים לקבוצות חומר</t>
-        </is>
-      </c>
-      <c r="G63" s="4" t="n"/>
-      <c r="H63" s="4" t="n"/>
-      <c r="I63" s="4" t="n"/>
-      <c r="J63" s="4" t="n"/>
-      <c r="K63" s="4" t="n"/>
-      <c r="L63" s="4" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="50" t="n">
-        <v>57</v>
-      </c>
-      <c r="B64" s="53" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C64" s="49" t="inlineStr">
-        <is>
-          <t>T399X</t>
-        </is>
-      </c>
-      <c r="D64" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E64" s="87">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A41","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F64" s="53" t="inlineStr">
-        <is>
-          <t>פרמטרי בקרת ייצור למפעל</t>
-        </is>
-      </c>
-      <c r="G64" s="4" t="n"/>
-      <c r="H64" s="4" t="n"/>
-      <c r="I64" s="4" t="n"/>
-      <c r="J64" s="4" t="n"/>
-      <c r="K64" s="4" t="n"/>
-      <c r="L64" s="4" t="n"/>
-    </row>
-    <row r="65">
-      <c r="A65" s="61" t="n">
-        <v>58</v>
-      </c>
-      <c r="B65" s="64" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C65" s="60" t="inlineStr">
-        <is>
-          <t>TCK03</t>
-        </is>
-      </c>
-      <c r="D65" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E65" s="88">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A47","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F65" s="64" t="inlineStr">
-        <is>
-          <t>וריאנט תמחיר (Costing Variant)</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="n"/>
-      <c r="H65" s="4" t="n"/>
-      <c r="I65" s="4" t="n"/>
-      <c r="J65" s="4" t="n"/>
-      <c r="K65" s="4" t="n"/>
-      <c r="L65" s="4" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" s="50" t="n">
-        <v>59</v>
-      </c>
-      <c r="B66" s="53" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C66" s="49" t="inlineStr">
-        <is>
-          <t>T438M</t>
-        </is>
-      </c>
-      <c r="D66" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E66" s="87">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A52","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F66" s="53" t="inlineStr">
-        <is>
-          <t>פרמטרי MRP לחומר/מפעל</t>
-        </is>
-      </c>
-      <c r="G66" s="4" t="n"/>
-      <c r="H66" s="4" t="n"/>
-      <c r="I66" s="4" t="n"/>
-      <c r="J66" s="4" t="n"/>
-      <c r="K66" s="4" t="n"/>
-      <c r="L66" s="4" t="n"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B67" s="64" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C67" s="60" t="inlineStr">
-        <is>
-          <t>T003O</t>
-        </is>
-      </c>
-      <c r="D67" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E67" s="88">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A56","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F67" s="64" t="inlineStr">
-        <is>
-          <t>סוגי פקודת ייצור (Process Order Types)</t>
-        </is>
-      </c>
-      <c r="G67" s="4" t="n"/>
-      <c r="H67" s="4" t="n"/>
-      <c r="I67" s="4" t="n"/>
-      <c r="J67" s="4" t="n"/>
-      <c r="K67" s="4" t="n"/>
-      <c r="L67" s="4" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" s="50" t="n">
-        <v>61</v>
-      </c>
-      <c r="B68" s="53" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C68" s="49" t="inlineStr">
-        <is>
-          <t>TCO01</t>
-        </is>
-      </c>
-      <c r="D68" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E68" s="87">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A62","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F68" s="53" t="inlineStr">
-        <is>
-          <t>פרמטרים תלויי סוג פק"ע (Order Profile)</t>
-        </is>
-      </c>
-      <c r="G68" s="4" t="n"/>
-      <c r="H68" s="4" t="n"/>
-      <c r="I68" s="4" t="n"/>
-      <c r="J68" s="4" t="n"/>
-      <c r="K68" s="4" t="n"/>
-      <c r="L68" s="4" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" s="61" t="n">
-        <v>62</v>
-      </c>
-      <c r="B69" s="64" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C69" s="60" t="inlineStr">
-        <is>
-          <t>TJ30</t>
-        </is>
-      </c>
-      <c r="D69" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E69" s="88">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A68","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F69" s="64" t="inlineStr">
-        <is>
-          <t>סטטוסי משתמש בפרופיל (User Status)</t>
-        </is>
-      </c>
-      <c r="G69" s="4" t="n"/>
-      <c r="H69" s="4" t="n"/>
-      <c r="I69" s="4" t="n"/>
-      <c r="J69" s="4" t="n"/>
-      <c r="K69" s="4" t="n"/>
-      <c r="L69" s="4" t="n"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="50" t="n">
-        <v>63</v>
-      </c>
-      <c r="B70" s="53" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C70" s="49" t="inlineStr">
-        <is>
-          <t>TJ30T</t>
-        </is>
-      </c>
-      <c r="D70" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E70" s="87">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A74","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F70" s="53" t="inlineStr">
-        <is>
-          <t>טקסטים לסטטוסי משתמש</t>
-        </is>
-      </c>
-      <c r="G70" s="4" t="n"/>
-      <c r="H70" s="4" t="n"/>
-      <c r="I70" s="4" t="n"/>
-      <c r="J70" s="4" t="n"/>
-      <c r="K70" s="4" t="n"/>
-      <c r="L70" s="4" t="n"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="61" t="n">
-        <v>64</v>
-      </c>
-      <c r="B71" s="64" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C71" s="60" t="inlineStr">
-        <is>
-          <t>BUT000</t>
-        </is>
-      </c>
-      <c r="D71" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E71" s="88">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A81","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F71" s="64" t="inlineStr">
-        <is>
-          <t>שותף עסקי (BP - השפעת מעבר S/4)</t>
-        </is>
-      </c>
-      <c r="G71" s="4" t="n"/>
-      <c r="H71" s="4" t="n"/>
-      <c r="I71" s="4" t="n"/>
-      <c r="J71" s="4" t="n"/>
-      <c r="K71" s="4" t="n"/>
-      <c r="L71" s="4" t="n"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="50" t="n">
-        <v>65</v>
-      </c>
-      <c r="B72" s="53" t="inlineStr">
-        <is>
-          <t>7. קונפיגורציה (Customizing)</t>
-        </is>
-      </c>
-      <c r="C72" s="49" t="inlineStr">
-        <is>
-          <t>TC22</t>
-        </is>
-      </c>
-      <c r="D72" s="51" t="inlineStr">
-        <is>
-          <t>Not started</t>
-        </is>
-      </c>
-      <c r="E72" s="87">
-        <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A88","➜ פתח")</f>
-        <v/>
-      </c>
-      <c r="F72" s="53" t="inlineStr">
-        <is>
-          <t>מפתחות בקרת תהליך/פעולה (PI Control)</t>
-        </is>
-      </c>
-      <c r="G72" s="4" t="n"/>
-      <c r="H72" s="4" t="n"/>
-      <c r="I72" s="4" t="n"/>
-      <c r="J72" s="4" t="n"/>
-      <c r="K72" s="4" t="n"/>
-      <c r="L72" s="4" t="n"/>
+      <c r="B16" s="81" t="inlineStr">
+        <is>
+          <t>עלות והערכה (Costing)</t>
+        </is>
+      </c>
+      <c r="C16" s="82" t="inlineStr">
+        <is>
+          <t>Order settlement -&gt; CO</t>
+        </is>
+      </c>
+      <c r="D16" s="78" t="inlineStr">
+        <is>
+          <t>Order settlement -&gt; Universal Journal (ACDOCA)</t>
+        </is>
+      </c>
+      <c r="E16" s="83" t="inlineStr">
+        <is>
+          <t>ב-S/4 Material Ledger חובה; עלויות הפק"ע זורמות ל-ACDOCA.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="C1:F1"/>
+  <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="A1:B1"/>
   </mergeCells>
-  <conditionalFormatting sqref="D8:D72">
-    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
-      <formula>"Not started"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
-      <formula>"In analysis"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
-      <formula>"In conversion"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="4" operator="equal" dxfId="3">
-      <formula>"Tested"</formula>
-    </cfRule>
-    <cfRule type="cellIs" priority="5" operator="equal" dxfId="4">
-      <formula>"Done"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation sqref="D8:D72" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"Not started,In analysis,In conversion,Tested,Done"</formula1>
-    </dataValidation>
-  </dataValidations>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
   </hyperlinks>
+  <printOptions gridLines="0"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Segoe UI,Bold"&amp;11&amp;K1E1E24Project NEO  |  SAP PP vs PP-PI  -  Education Layer</oddHeader>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;8&amp;K6B7280CBC NEO - PP vs PP-PI - Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/SAP_PPPI_ECC6_to_S4_Migration.xlsx
+++ b/SAP_PPPI_ECC6_to_S4_Migration.xlsx
@@ -1266,7 +1266,7 @@
       <c r="A2" s="1" t="n"/>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>CBC ISRAEL  |  SAP PP-PI  -  מסך ניווט מרכזי</t>
+          <t>CBC ISRAEL  |  SAP PP-PI Migration Blueprint Portal</t>
         </is>
       </c>
       <c r="C2" s="4" t="n"/>
@@ -1324,7 +1324,7 @@
       <c r="A3" s="1" t="n"/>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Project NEO  -  Production Planning for Process Industries  |  ECC 6.0 ➜ S/4HANA</t>
+          <t>Project NEO  -  Migration Cockpit + Blueprint מאוחדים  |  PP-PI  ECC 6.0 ➜ S/4HANA</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -1422,7 +1422,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="9" t="inlineStr">
         <is>
-          <t>סיכום התקדמות מיגרציה (KPI - חי מה-Cockpit)</t>
+          <t>🚀 Migration Cockpit - מצב פריסה חי (KPI מתעדכן מ-Cockpit; עדכן סטטוס בלשונית Cockpit, פתח Blueprint בלשוניות הזרמים)</t>
         </is>
       </c>
       <c r="C5" s="4" t="n"/>

--- a/SAP_PPPI_ECC6_to_S4_Migration.xlsx
+++ b/SAP_PPPI_ECC6_to_S4_Migration.xlsx
@@ -16,8 +16,10 @@
     <sheet name="6. פק&quot;ע ייצור ומתכון בקרה (Proc" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="7. קונפיגורציה (Customizing)" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="PP מול PP-PI" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Cockpit מעקב מיגרציה" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="ER - Join Map" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="PP_PPPI_Tcodes" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="SAP_Maint_Tools" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Cockpit מעקב מיגרציה" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="ER - Join Map" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'מסך ניווט מרכזי'!$A$1:$M$60</definedName>
@@ -29,6 +31,8 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="6">'6. פק"ע ייצור ומתכון בקרה (Proc'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="7">'7. קונפיגורציה (Customizing)'!$1:$2</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="8">'PP מול PP-PI'!$A$1:$E$16</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="9">'PP_PPPI_Tcodes'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="10">'SAP_Maint_Tools'!$1:$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -37,7 +41,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="46">
+  <fonts count="47">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -182,6 +186,12 @@
       <name val="Segoe UI"/>
       <color rgb="009A5A23"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="Segoe UI"/>
+      <b val="1"/>
+      <color rgb="009A5A23"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Segoe UI"/>
@@ -478,62 +488,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="105">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="32" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="35" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="9" fontId="36" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -545,24 +555,24 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -641,7 +651,7 @@
     <xf numFmtId="0" fontId="12" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -660,7 +670,7 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="45" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -715,32 +725,56 @@
     <xf numFmtId="0" fontId="24" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="32" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="38" fillId="8" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="14" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="38" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="13" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="23" fillId="12" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -751,13 +785,13 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="40" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1193,7 +1227,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T924"/>
+  <dimension ref="A1:T996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2017,19 +2051,27 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="24" t="inlineStr">
         <is>
+          <t>🛠 PP_PPPI_Tcodes</t>
+        </is>
+      </c>
+      <c r="C16" s="1" t="n"/>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>⚙ SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="E16" s="1" t="n"/>
+      <c r="F16" s="24" t="inlineStr">
+        <is>
           <t>◆ Cockpit מעקב מיגרציה</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n"/>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="G16" s="1" t="n"/>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>⇄ ER - Join Map</t>
         </is>
       </c>
-      <c r="E16" s="1" t="n"/>
-      <c r="F16" s="1" t="n"/>
-      <c r="G16" s="1" t="n"/>
-      <c r="H16" s="1" t="n"/>
       <c r="I16" s="1" t="n"/>
       <c r="J16" s="1" t="n"/>
       <c r="K16" s="1" t="n"/>
@@ -2076,9 +2118,9 @@
       <c r="C17" s="1" t="n"/>
       <c r="D17" s="26" t="n"/>
       <c r="E17" s="1" t="n"/>
-      <c r="F17" s="1" t="n"/>
+      <c r="F17" s="26" t="n"/>
       <c r="G17" s="1" t="n"/>
-      <c r="H17" s="1" t="n"/>
+      <c r="H17" s="26" t="n"/>
       <c r="I17" s="1" t="n"/>
       <c r="J17" s="1" t="n"/>
       <c r="K17" s="1" t="n"/>
@@ -2644,7 +2686,7 @@
     <row r="28">
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="30">
-        <f>IF(C25="","הקלד מונח וקבל תוצאות מיידיות...",IFERROR(_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6},$T$2:$T$924,$O$2:$O$924,$P$2:$P$924,$Q$2:$Q$924,$R$2:$R$924,$S$2:$S$924),(ISNUMBER(SEARCH(C25,$O$2:$O$924)))+(ISNUMBER(SEARCH(C25,$P$2:$P$924)))+(ISNUMBER(SEARCH(C25,$Q$2:$Q$924)))+(ISNUMBER(SEARCH(C25,$N$2:$N$924)))&gt;0),"לא נמצאו תוצאות"))</f>
+        <f>IF(C25="","הקלד מונח וקבל תוצאות מיידיות...",IFERROR(_xlfn._xlws.FILTER(CHOOSE({1,2,3,4,5,6},$T$2:$T$996,$O$2:$O$996,$P$2:$P$996,$Q$2:$Q$996,$R$2:$R$996,$S$2:$S$996),(ISNUMBER(SEARCH(C25,$O$2:$O$996)))+(ISNUMBER(SEARCH(C25,$P$2:$P$996)))+(ISNUMBER(SEARCH(C25,$Q$2:$Q$996)))+(ISNUMBER(SEARCH(C25,$N$2:$N$996)))&gt;0),"לא נמצאו תוצאות"))</f>
         <v/>
       </c>
       <c r="C28" s="1" t="n"/>
@@ -43248,23 +43290,27 @@
       <c r="M860" s="4" t="n"/>
       <c r="N860" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O860" s="6" t="inlineStr">
         <is>
-          <t>FROM MAKT JOIN MARA ON MAKT.MATNR = MARA.MATNR</t>
+          <t>CS01 / CS02 / CS03</t>
         </is>
       </c>
       <c r="P860" s="4" t="inlineStr">
         <is>
-          <t>תיאורי חומר (טקסטים)</t>
-        </is>
-      </c>
-      <c r="Q860" s="4" t="inlineStr"/>
+          <t>יצירה / שינוי / תצוגה של עץ מוצר חומר (Material BOM). הליבה להגדרת מבנה הרכיבים של כל מוצר CBC - תרכיז, סוכר, CO2, חומרי אריזה - כולל כמויות, יחידות ופחת רכיב (1%). מקור הפיצוץ לכל פק"ע.</t>
+        </is>
+      </c>
+      <c r="Q860" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R860" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S860" s="4" t="inlineStr">
@@ -43293,28 +43339,32 @@
       <c r="M861" s="4" t="n"/>
       <c r="N861" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O861" s="6" t="inlineStr">
         <is>
-          <t>FROM MARC JOIN MARA ON MARC.MATNR = MARA.MATNR</t>
+          <t>F1743 / F1813</t>
         </is>
       </c>
       <c r="P861" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מפעל</t>
-        </is>
-      </c>
-      <c r="Q861" s="4" t="inlineStr"/>
+          <t>Maintain Bill of Material / Manage Material BOMs</t>
+        </is>
+      </c>
+      <c r="Q861" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R861" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S861" s="4" t="inlineStr">
         <is>
-          <t>A4</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="T861" s="7">
@@ -43338,28 +43388,32 @@
       <c r="M862" s="4" t="n"/>
       <c r="N862" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O862" s="6" t="inlineStr">
         <is>
-          <t>FROM MARD JOIN MARC ON MARD.MATNR = MARC.MATNR AND MARD.WERKS = MARC.WERKS</t>
+          <t>CS11</t>
         </is>
       </c>
       <c r="P862" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מחסן/מלאי</t>
-        </is>
-      </c>
-      <c r="Q862" s="4" t="inlineStr"/>
+          <t>פיצוץ עץ מוצר רב-רמתי (Multilevel BOM Explosion) - מציג את כל רמות ההיררכיה של הרכיבים מהמוצר המוגמר ועד חומרי הגלם. כלי ניתוח מרכזי לתכנון חומרים ולבדיקת עלות מוצר ב-CBC.</t>
+        </is>
+      </c>
+      <c r="Q862" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R862" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S862" s="4" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="T862" s="7">
@@ -43383,28 +43437,32 @@
       <c r="M863" s="4" t="n"/>
       <c r="N863" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O863" s="6" t="inlineStr">
         <is>
-          <t>FROM MARM JOIN MARA ON MARM.MATNR = MARA.MATNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P863" s="4" t="inlineStr">
         <is>
-          <t>המרות יחידות מידה חלופיות</t>
-        </is>
-      </c>
-      <c r="Q863" s="4" t="inlineStr"/>
+          <t>Display Bill of Material (multilevel)</t>
+        </is>
+      </c>
+      <c r="Q863" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R863" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S863" s="4" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="T863" s="7">
@@ -43428,28 +43486,32 @@
       <c r="M864" s="4" t="n"/>
       <c r="N864" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O864" s="6" t="inlineStr">
         <is>
-          <t>FROM MEAN JOIN MARA ON MEAN.MATNR = MARA.MATNR</t>
+          <t>CS12</t>
         </is>
       </c>
       <c r="P864" s="4" t="inlineStr">
         <is>
-          <t>ברקודים / EAN לחומר</t>
-        </is>
-      </c>
-      <c r="Q864" s="4" t="inlineStr"/>
+          <t>פיצוץ עץ מוצר רב-רמתי מלא (כל הרמות בו-זמנית) עם כמויות מצטברות. משמש להפקת רשימת חומרים מלאה (Total BOM) לתמחיר ולרכש מרוכז.</t>
+        </is>
+      </c>
+      <c r="Q864" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R864" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S864" s="4" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="T864" s="7">
@@ -43473,28 +43535,32 @@
       <c r="M865" s="4" t="n"/>
       <c r="N865" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O865" s="6" t="inlineStr">
         <is>
-          <t>FROM MBEW JOIN MARA ON MBEW.MATNR = MARA.MATNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P865" s="4" t="inlineStr">
         <is>
-          <t>הערכת חומר (Valuation)</t>
-        </is>
-      </c>
-      <c r="Q865" s="4" t="inlineStr"/>
+          <t>Display Bill of Material (multilevel)</t>
+        </is>
+      </c>
+      <c r="Q865" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R865" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S865" s="4" t="inlineStr">
         <is>
-          <t>A8</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="T865" s="7">
@@ -43518,28 +43584,32 @@
       <c r="M866" s="4" t="n"/>
       <c r="N866" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O866" s="6" t="inlineStr">
         <is>
-          <t>FROM MVKE JOIN MARA ON MVKE.MATNR = MARA.MATNR</t>
+          <t>CS13</t>
         </is>
       </c>
       <c r="P866" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מכירות</t>
-        </is>
-      </c>
-      <c r="Q866" s="4" t="inlineStr"/>
+          <t>פיצוץ עץ מוצר מסוכם (Summarized BOM) - מאחד רכיבים זהים החוזרים במספר רמות לשורה אחת עם כמות כוללת. חיוני לרכש ולתכנון חומר גלם משותף (סוכר/CO2) בין מוצרים.</t>
+        </is>
+      </c>
+      <c r="Q866" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R866" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S866" s="4" t="inlineStr">
         <is>
-          <t>A9</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="T866" s="7">
@@ -43563,28 +43633,32 @@
       <c r="M867" s="4" t="n"/>
       <c r="N867" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O867" s="6" t="inlineStr">
         <is>
-          <t>FROM MLAN JOIN MARA ON MLAN.MATNR = MARA.MATNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P867" s="4" t="inlineStr">
         <is>
-          <t>נתוני מס לחומר (לפי מדינה)</t>
-        </is>
-      </c>
-      <c r="Q867" s="4" t="inlineStr"/>
+          <t>Display Bill of Material (multilevel)</t>
+        </is>
+      </c>
+      <c r="Q867" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R867" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S867" s="4" t="inlineStr">
         <is>
-          <t>A10</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="T867" s="7">
@@ -43608,28 +43682,32 @@
       <c r="M868" s="4" t="n"/>
       <c r="N868" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O868" s="6" t="inlineStr">
         <is>
-          <t>FROM MLGN JOIN MARA ON MLGN.MATNR = MARA.MATNR</t>
+          <t>CS14</t>
         </is>
       </c>
       <c r="P868" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר ברמת מחסן (WM)</t>
-        </is>
-      </c>
-      <c r="Q868" s="4" t="inlineStr"/>
+          <t>השוואת עצי מוצר (BOM Comparison) - משווה שני עצי מוצר (או שתי חלופות/גרסאות) ומסמן הבדלים ברכיבים ובכמויות. קריטי לאימות שינויי מתכון מאושרים ב-CBC לפני העברה לייצור.</t>
+        </is>
+      </c>
+      <c r="Q868" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R868" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S868" s="4" t="inlineStr">
         <is>
-          <t>A11</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="T868" s="7">
@@ -43653,28 +43731,32 @@
       <c r="M869" s="4" t="n"/>
       <c r="N869" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O869" s="6" t="inlineStr">
         <is>
-          <t>FROM MLGT JOIN MLGN ON MLGT.MATNR = MLGN.MATNR AND MLGT.LGNUM = MLGN.LGNUM</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P869" s="4" t="inlineStr">
         <is>
-          <t>נתוני חומר לפי טיפוס אחסון</t>
-        </is>
-      </c>
-      <c r="Q869" s="4" t="inlineStr"/>
+          <t>Compare Bill of Materials</t>
+        </is>
+      </c>
+      <c r="Q869" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R869" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S869" s="4" t="inlineStr">
         <is>
-          <t>A12</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="T869" s="7">
@@ -43698,28 +43780,32 @@
       <c r="M870" s="4" t="n"/>
       <c r="N870" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O870" s="6" t="inlineStr">
         <is>
-          <t>FROM MDMA JOIN MARC ON MDMA.MATNR = MARC.MATNR AND MDMA.WERKS = MARC.WERKS</t>
+          <t>CS15</t>
         </is>
       </c>
       <c r="P870" s="4" t="inlineStr">
         <is>
-          <t>אזורי MRP לחומר</t>
-        </is>
-      </c>
-      <c r="Q870" s="4" t="inlineStr"/>
+          <t>רשימת 'היכן בשימוש' (Where-Used List) - מציג בכל אילו עצי מוצר/מוצרים משמש רכיב נתון. חיוני לניתוח השפעה (Impact Analysis) בעת החלפת חומר גלם/ספק או ריקול אצווה.</t>
+        </is>
+      </c>
+      <c r="Q870" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R870" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S870" s="4" t="inlineStr">
         <is>
-          <t>A13</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="T870" s="7">
@@ -43743,28 +43829,32 @@
       <c r="M871" s="4" t="n"/>
       <c r="N871" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O871" s="6" t="inlineStr">
         <is>
-          <t>FROM QMAT JOIN MARC ON QMAT.MATNR = MARC.MATNR AND QMAT.WERKS = MARC.WERKS</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P871" s="4" t="inlineStr">
         <is>
-          <t>הגדרות בדיקת איכות לחומר</t>
-        </is>
-      </c>
-      <c r="Q871" s="4" t="inlineStr"/>
+          <t>Where-Used List - Material</t>
+        </is>
+      </c>
+      <c r="Q871" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R871" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S871" s="4" t="inlineStr">
         <is>
-          <t>A14</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="T871" s="7">
@@ -43788,28 +43878,32 @@
       <c r="M872" s="4" t="n"/>
       <c r="N872" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O872" s="6" t="inlineStr">
         <is>
-          <t>FROM MCH1 JOIN MARA ON MCH1.MATNR = MARA.MATNR</t>
+          <t>CO24</t>
         </is>
       </c>
       <c r="P872" s="4" t="inlineStr">
         <is>
-          <t>אצוות חומר (Batches)</t>
-        </is>
-      </c>
-      <c r="Q872" s="4" t="inlineStr"/>
+          <t>מידע חוסרים (Missing Parts Info System) - מציג רכיבים חסרים לפק"ע שלא ניתן לפלוט (מלאי לא מספיק). כלי תפעולי לזיהוי עיכובי ייצור בקו ב-CBC לפני שחרור.</t>
+        </is>
+      </c>
+      <c r="Q872" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R872" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S872" s="4" t="inlineStr">
         <is>
-          <t>A15</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="T872" s="7">
@@ -43833,28 +43927,32 @@
       <c r="M873" s="4" t="n"/>
       <c r="N873" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O873" s="6" t="inlineStr">
         <is>
-          <t>FROM MCHA JOIN MCH1 ON MCHA.MATNR = MCH1.MATNR AND MCHA.CHARG = MCH1.CHARG</t>
+          <t>F0251</t>
         </is>
       </c>
       <c r="P873" s="4" t="inlineStr">
         <is>
-          <t>אצוות חומר ברמת מפעל</t>
-        </is>
-      </c>
-      <c r="Q873" s="4" t="inlineStr"/>
+          <t>Monitor Material Coverage - Net Segments</t>
+        </is>
+      </c>
+      <c r="Q873" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R873" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S873" s="4" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="T873" s="7">
@@ -43878,28 +43976,32 @@
       <c r="M874" s="4" t="n"/>
       <c r="N874" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O874" s="6" t="inlineStr">
         <is>
-          <t>FROM MARM JOIN T006 ON MARM.MEINH = T006.MSEHI</t>
+          <t>CO46</t>
         </is>
       </c>
       <c r="P874" s="4" t="inlineStr">
         <is>
-          <t>יחידות מידה (Customizing)</t>
-        </is>
-      </c>
-      <c r="Q874" s="4" t="inlineStr"/>
+          <t>דוח התקדמות פק"ע (Order Progress Report) - מציג את מצב הפק"ע, הפעולות, הרכיבים והדיווחים במבט אחד. כלי מעקב לתפעול לבקרת קצב ייצור והשלמת אצוות.</t>
+        </is>
+      </c>
+      <c r="Q874" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R874" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S874" s="4" t="inlineStr">
         <is>
-          <t>A17</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="T874" s="7">
@@ -43923,28 +44025,32 @@
       <c r="M875" s="4" t="n"/>
       <c r="N875" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O875" s="6" t="inlineStr">
         <is>
-          <t>FROM MAST JOIN MARA ON MAST.MATNR = MARA.MATNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P875" s="4" t="inlineStr">
         <is>
-          <t>קישור חומר לעץ מוצר</t>
-        </is>
-      </c>
-      <c r="Q875" s="4" t="inlineStr"/>
+          <t>Production Order/Process Order Progress</t>
+        </is>
+      </c>
+      <c r="Q875" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R875" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S875" s="4" t="inlineStr">
         <is>
-          <t>A18</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="T875" s="7">
@@ -43968,28 +44074,32 @@
       <c r="M876" s="4" t="n"/>
       <c r="N876" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O876" s="6" t="inlineStr">
         <is>
-          <t>FROM STKO JOIN MAST ON STKO.STLNR = MAST.STLNR</t>
+          <t>COOIS</t>
         </is>
       </c>
       <c r="P876" s="4" t="inlineStr">
         <is>
-          <t>כותרת עץ מוצר</t>
-        </is>
-      </c>
-      <c r="Q876" s="4" t="inlineStr"/>
+          <t>מערכת מידע פקודות ייצור (Production Order Information System) - דוח מרכזי לסינון, צפייה ועיבוד המוני של פקודות ייצור בדידות (Discrete) לפי סטטוס, חומר, מועד ועוד.</t>
+        </is>
+      </c>
+      <c r="Q876" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R876" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S876" s="4" t="inlineStr">
         <is>
-          <t>A19</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="T876" s="7">
@@ -44013,28 +44123,32 @@
       <c r="M877" s="4" t="n"/>
       <c r="N877" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O877" s="6" t="inlineStr">
         <is>
-          <t>FROM STPO JOIN STKO ON STPO.STLNR = STKO.STLNR AND STPO.STLTY = STKO.STLTY</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P877" s="4" t="inlineStr">
         <is>
-          <t>פריטי עץ מוצר (רכיבים)</t>
-        </is>
-      </c>
-      <c r="Q877" s="4" t="inlineStr"/>
+          <t>Manage Production Orders</t>
+        </is>
+      </c>
+      <c r="Q877" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R877" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S877" s="4" t="inlineStr">
         <is>
-          <t>A20</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="T877" s="7">
@@ -44058,28 +44172,32 @@
       <c r="M878" s="4" t="n"/>
       <c r="N878" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O878" s="6" t="inlineStr">
         <is>
-          <t>FROM STAS JOIN STKO ON STAS.STLNR = STKO.STLNR</t>
+          <t>COOISPI</t>
         </is>
       </c>
       <c r="P878" s="4" t="inlineStr">
         <is>
-          <t>בחירת פריטי עץ מוצר</t>
-        </is>
-      </c>
-      <c r="Q878" s="4" t="inlineStr"/>
+          <t>מערכת מידע פקודות תהליך (Process Order Information System) - המקבילה של COOIS לפק"ע תהליכיות (Process Orders). הדוח התפעולי המרכזי של CBC לסינון ועיבוד המוני של פק"ע ייצור משקאות.</t>
+        </is>
+      </c>
+      <c r="Q878" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R878" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S878" s="4" t="inlineStr">
         <is>
-          <t>A21</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="T878" s="7">
@@ -44103,28 +44221,32 @@
       <c r="M879" s="4" t="n"/>
       <c r="N879" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O879" s="6" t="inlineStr">
         <is>
-          <t>FROM STZU JOIN STKO ON STZU.STLNR = STKO.STLNR</t>
+          <t>F4512</t>
         </is>
       </c>
       <c r="P879" s="4" t="inlineStr">
         <is>
-          <t>טבלת היסטוריה/קישור לעץ מוצר</t>
-        </is>
-      </c>
-      <c r="Q879" s="4" t="inlineStr"/>
+          <t>Manage Process Orders</t>
+        </is>
+      </c>
+      <c r="Q879" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R879" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S879" s="4" t="inlineStr">
         <is>
-          <t>A22</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="T879" s="7">
@@ -44148,28 +44270,32 @@
       <c r="M880" s="4" t="n"/>
       <c r="N880" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O880" s="6" t="inlineStr">
         <is>
-          <t>FROM STPU JOIN STPO ON STPU.STLKN = STPO.STLKN</t>
+          <t>COIO</t>
         </is>
       </c>
       <c r="P880" s="4" t="inlineStr">
         <is>
-          <t>טקסטים ארוכים לפריט עץ מוצר</t>
-        </is>
-      </c>
-      <c r="Q880" s="4" t="inlineStr"/>
+          <t>לוח מעקב פקודות (Order Tracking Cockpit / Process Order Cockpit) - מסך תפעולי מאוחד למעקב אחר פק"ע התהליך, סטטוסים, חומרים ודיווחים. לב המעקב התפעולי של מנהל הקו ב-CBC.</t>
+        </is>
+      </c>
+      <c r="Q880" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R880" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S880" s="4" t="inlineStr">
         <is>
-          <t>A23</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="T880" s="7">
@@ -44193,28 +44319,32 @@
       <c r="M881" s="4" t="n"/>
       <c r="N881" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O881" s="6" t="inlineStr">
         <is>
-          <t>FROM KDST JOIN MAST ON KDST.MATNR = MAST.MATNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P881" s="4" t="inlineStr">
         <is>
-          <t>שימוש עץ מוצר בהזמנת לקוח</t>
-        </is>
-      </c>
-      <c r="Q881" s="4" t="inlineStr"/>
+          <t>Process Order Cockpit / Operator Dashboard</t>
+        </is>
+      </c>
+      <c r="Q881" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R881" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S881" s="4" t="inlineStr">
         <is>
-          <t>A24</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="T881" s="7">
@@ -44238,28 +44368,32 @@
       <c r="M882" s="4" t="n"/>
       <c r="N882" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O882" s="6" t="inlineStr">
         <is>
-          <t>FROM PLKO JOIN MAPL ON PLKO.PLNTY = MAPL.PLNTY AND PLKO.PLNNR = MAPL.PLNNR</t>
+          <t>COR1 / COR2 / COR3</t>
         </is>
       </c>
       <c r="P882" s="4" t="inlineStr">
         <is>
-          <t>כותרת מתכון ייצור / רשימת פעולות</t>
-        </is>
-      </c>
-      <c r="Q882" s="4" t="inlineStr"/>
+          <t>יצירה / שינוי / תצוגה של פקודת ייצור תהליכית (Process Order) - ליבת ביצוע הייצור ב-CBC. שחרור הפק"ע (REL) מייצר Control Recipe ושולח הוראות תהליך (IDoc LOIPRO) לקו/MES.</t>
+        </is>
+      </c>
+      <c r="Q882" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R882" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S882" s="4" t="inlineStr">
         <is>
-          <t>A25</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="T882" s="7">
@@ -44283,28 +44417,32 @@
       <c r="M883" s="4" t="n"/>
       <c r="N883" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O883" s="6" t="inlineStr">
         <is>
-          <t>FROM PLPO JOIN PLAS ON PLPO.PLNTY = PLAS.PLNTY AND PLPO.PLNNR = PLAS.PLNNR AND PLPO.PLNKN = PLAS.PLNKN</t>
+          <t>F4512</t>
         </is>
       </c>
       <c r="P883" s="4" t="inlineStr">
         <is>
-          <t>פעולות/פאזות במתכון</t>
-        </is>
-      </c>
-      <c r="Q883" s="4" t="inlineStr"/>
+          <t>Create / Manage Process Orders</t>
+        </is>
+      </c>
+      <c r="Q883" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R883" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S883" s="4" t="inlineStr">
         <is>
-          <t>A26</t>
+          <t>A14</t>
         </is>
       </c>
       <c r="T883" s="7">
@@ -44328,28 +44466,32 @@
       <c r="M884" s="4" t="n"/>
       <c r="N884" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O884" s="6" t="inlineStr">
         <is>
-          <t>FROM PLAS JOIN PLKO ON PLAS.PLNTY = PLKO.PLNTY AND PLAS.PLNNR = PLKO.PLNNR</t>
+          <t>CO01 / CO02 / CO03</t>
         </is>
       </c>
       <c r="P884" s="4" t="inlineStr">
         <is>
-          <t>שיוך/בחירת פעולות לרשימה</t>
-        </is>
-      </c>
-      <c r="Q884" s="4" t="inlineStr"/>
+          <t>יצירה / שינוי / תצוגה של פקודת ייצור בדידה (Discrete Production Order). משמש בייצור בדיד (לא משקאות) - מובא כאן לצורך הבחנה מ-PP-PI; ב-CBC הליבה היא Process Orders.</t>
+        </is>
+      </c>
+      <c r="Q884" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R884" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S884" s="4" t="inlineStr">
         <is>
-          <t>A27</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="T884" s="7">
@@ -44373,28 +44515,32 @@
       <c r="M885" s="4" t="n"/>
       <c r="N885" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O885" s="6" t="inlineStr">
         <is>
-          <t>FROM PLFL JOIN PLKO ON PLFL.PLNNR = PLKO.PLNNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P885" s="4" t="inlineStr">
         <is>
-          <t>רצפים במתכון</t>
-        </is>
-      </c>
-      <c r="Q885" s="4" t="inlineStr"/>
+          <t>Create / Manage Production Orders</t>
+        </is>
+      </c>
+      <c r="Q885" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R885" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S885" s="4" t="inlineStr">
         <is>
-          <t>A28</t>
+          <t>A15</t>
         </is>
       </c>
       <c r="T885" s="7">
@@ -44418,28 +44564,32 @@
       <c r="M886" s="4" t="n"/>
       <c r="N886" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O886" s="6" t="inlineStr">
         <is>
-          <t>FROM PLMZ JOIN PLPO ON PLMZ.PLNKN = PLPO.PLNKN</t>
+          <t>C201 / C202 / C203</t>
         </is>
       </c>
       <c r="P886" s="4" t="inlineStr">
         <is>
-          <t>שיוך רכיבים לפעולות</t>
-        </is>
-      </c>
-      <c r="Q886" s="4" t="inlineStr"/>
+          <t>יצירה / שינוי / תצוגה של מתכון ייצור (Master Recipe) - הגדרת הנוסחה, הפאזות, ההוראות וערכי התקן. כל משקה ב-CBC מיוצר לפי מתכון מאושר; שינוי דורש ניהול שינויים הנדסי (ECM).</t>
+        </is>
+      </c>
+      <c r="Q886" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R886" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S886" s="4" t="inlineStr">
         <is>
-          <t>A29</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="T886" s="7">
@@ -44463,28 +44613,32 @@
       <c r="M887" s="4" t="n"/>
       <c r="N887" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O887" s="6" t="inlineStr">
         <is>
-          <t>FROM PLMK JOIN PLPO ON PLMK.PLNKN = PLPO.PLNKN</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P887" s="4" t="inlineStr">
         <is>
-          <t>מאפייני בדיקה במתכון</t>
-        </is>
-      </c>
-      <c r="Q887" s="4" t="inlineStr"/>
+          <t>Manage Master Recipes</t>
+        </is>
+      </c>
+      <c r="Q887" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R887" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S887" s="4" t="inlineStr">
         <is>
-          <t>A30</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="T887" s="7">
@@ -44508,28 +44662,32 @@
       <c r="M888" s="4" t="n"/>
       <c r="N888" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O888" s="6" t="inlineStr">
         <is>
-          <t>FROM MAPL JOIN MARC ON MAPL.MATNR = MARC.MATNR AND MAPL.WERKS = MARC.WERKS</t>
+          <t>CA01 / CA02 / CA03</t>
         </is>
       </c>
       <c r="P888" s="4" t="inlineStr">
         <is>
-          <t>שיוך חומר למתכון/רשימת פעולות</t>
-        </is>
-      </c>
-      <c r="Q888" s="4" t="inlineStr"/>
+          <t>יצירה / שינוי / תצוגה של רשימת פעולות (Routing) לייצור בדיד. המקבילה הבדידה של מתכון ה-PP-PI; מובא להבחנה - ב-CBC משתמשים ב-Master Recipe ולא ב-Routing.</t>
+        </is>
+      </c>
+      <c r="Q888" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R888" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S888" s="4" t="inlineStr">
         <is>
-          <t>A31</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="T888" s="7">
@@ -44553,28 +44711,32 @@
       <c r="M889" s="4" t="n"/>
       <c r="N889" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O889" s="6" t="inlineStr">
         <is>
-          <t>FROM FHMI JOIN PLPO ON FHMI.PLNKN = PLPO.PLNKN</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P889" s="4" t="inlineStr">
         <is>
-          <t>שיוך כלי עזר ייצור (PRT) לפעולה</t>
-        </is>
-      </c>
-      <c r="Q889" s="4" t="inlineStr"/>
+          <t>Manage Routings</t>
+        </is>
+      </c>
+      <c r="Q889" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R889" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S889" s="4" t="inlineStr">
         <is>
-          <t>A32</t>
+          <t>A17</t>
         </is>
       </c>
       <c r="T889" s="7">
@@ -44598,28 +44760,32 @@
       <c r="M890" s="4" t="n"/>
       <c r="N890" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O890" s="6" t="inlineStr">
         <is>
-          <t>FROM PLZU JOIN PLKO ON PLZU.PLNNR = PLKO.PLNNR</t>
+          <t>C223</t>
         </is>
       </c>
       <c r="P890" s="4" t="inlineStr">
         <is>
-          <t>קישור היסטוריית רשימת פעולות</t>
-        </is>
-      </c>
-      <c r="Q890" s="4" t="inlineStr"/>
+          <t>ניהול גרסאות ייצור (Production Versions) - מקשר חומר -&gt; עץ מוצר חלופי + מתכון + קו ייצור. ב-S/4HANA חובה מוחלטת לכל ביצוע ייצור; ב-CBC כל שילוב מוצר/קו = גרסה.</t>
+        </is>
+      </c>
+      <c r="Q890" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R890" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S890" s="4" t="inlineStr">
         <is>
-          <t>A33</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="T890" s="7">
@@ -44643,28 +44809,32 @@
       <c r="M891" s="4" t="n"/>
       <c r="N891" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O891" s="6" t="inlineStr">
         <is>
-          <t>FROM PLPO JOIN TC60 ON PLPO.STEUS = TC60.STEUS</t>
+          <t>F2703</t>
         </is>
       </c>
       <c r="P891" s="4" t="inlineStr">
         <is>
-          <t>מאפייני הוראות תהליך (PI)</t>
-        </is>
-      </c>
-      <c r="Q891" s="4" t="inlineStr"/>
+          <t>Manage Production Versions</t>
+        </is>
+      </c>
+      <c r="Q891" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R891" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S891" s="4" t="inlineStr">
         <is>
-          <t>A34</t>
+          <t>A18</t>
         </is>
       </c>
       <c r="T891" s="7">
@@ -44688,28 +44858,32 @@
       <c r="M892" s="4" t="n"/>
       <c r="N892" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O892" s="6" t="inlineStr">
         <is>
-          <t>FROM PLKO JOIN TCA01 ON PLKO.PROFIDNETZ = TCA01.PROFIDNETZ</t>
+          <t>CO11N</t>
         </is>
       </c>
       <c r="P892" s="4" t="inlineStr">
         <is>
-          <t>פרופיל רשימת פעולות (Customizing)</t>
-        </is>
-      </c>
-      <c r="Q892" s="4" t="inlineStr"/>
+          <t>דיווח ביצוע לפעולה בייצור בדיד (Time Ticket Confirmation). מובא להבחנה; ב-CBC הדיווח התהליכי מתבצע דרך COR6N/CORK והודעות תהליך מהקו.</t>
+        </is>
+      </c>
+      <c r="Q892" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R892" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S892" s="4" t="inlineStr">
         <is>
-          <t>A35</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="T892" s="7">
@@ -44733,28 +44907,32 @@
       <c r="M893" s="4" t="n"/>
       <c r="N893" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O893" s="6" t="inlineStr">
         <is>
-          <t>FROM MKAL JOIN MARC ON MKAL.MATNR = MARC.MATNR AND MKAL.WERKS = MARC.WERKS</t>
+          <t>F3372</t>
         </is>
       </c>
       <c r="P893" s="4" t="inlineStr">
         <is>
-          <t>גרסאות ייצור לחומר</t>
-        </is>
-      </c>
-      <c r="Q893" s="4" t="inlineStr"/>
+          <t>Confirm Production Operation</t>
+        </is>
+      </c>
+      <c r="Q893" s="4" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
       <c r="R893" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S893" s="4" t="inlineStr">
         <is>
-          <t>A36</t>
+          <t>A19</t>
         </is>
       </c>
       <c r="T893" s="7">
@@ -44778,28 +44956,32 @@
       <c r="M894" s="4" t="n"/>
       <c r="N894" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O894" s="6" t="inlineStr">
         <is>
-          <t>FROM CRTX JOIN CRHD ON CRTX.OBJID = CRHD.OBJID AND CRTX.OBJTY = CRHD.OBJTY</t>
+          <t>COR6N</t>
         </is>
       </c>
       <c r="P894" s="4" t="inlineStr">
         <is>
-          <t>טקסטים של משאב</t>
-        </is>
-      </c>
-      <c r="Q894" s="4" t="inlineStr"/>
+          <t>דיווח ביצוע לפאזת פק"ע תהליכית (Process Order Phase Confirmation) - דיווח כמות שיוצרה, פחת וזמני מכונה/אדם לפאזה. מקור הנתונים מהקו (PI Sheet/MES) ובסיס לעלות ולניתוח פחת מול 1% היעד.</t>
+        </is>
+      </c>
+      <c r="Q894" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R894" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S894" s="4" t="inlineStr">
         <is>
-          <t>A37</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="T894" s="7">
@@ -44823,28 +45005,32 @@
       <c r="M895" s="4" t="n"/>
       <c r="N895" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O895" s="6" t="inlineStr">
         <is>
-          <t>FROM CRCO JOIN CRHD ON CRCO.OBJID = CRHD.OBJID AND CRCO.OBJTY = CRHD.OBJTY</t>
+          <t>F3372</t>
         </is>
       </c>
       <c r="P895" s="4" t="inlineStr">
         <is>
-          <t>שיוך משאב למרכז עלות</t>
-        </is>
-      </c>
-      <c r="Q895" s="4" t="inlineStr"/>
+          <t>Confirm Process Order / Operation</t>
+        </is>
+      </c>
+      <c r="Q895" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R895" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S895" s="4" t="inlineStr">
         <is>
-          <t>A38</t>
+          <t>A20</t>
         </is>
       </c>
       <c r="T895" s="7">
@@ -44868,28 +45054,32 @@
       <c r="M896" s="4" t="n"/>
       <c r="N896" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O896" s="6" t="inlineStr">
         <is>
-          <t>FROM CRCA JOIN CRHD ON CRCA.OBJID = CRHD.OBJID AND CRCA.OBJTY = CRHD.OBJTY</t>
+          <t>MD04</t>
         </is>
       </c>
       <c r="P896" s="4" t="inlineStr">
         <is>
-          <t>הקצאת קיבולת למשאב</t>
-        </is>
-      </c>
-      <c r="Q896" s="4" t="inlineStr"/>
+          <t>רשימת מלאי/דרישות (Stock / Requirements List) - המסך התפעולי המרכזי לתכנון: מציג מלאי, דרישות, פק"ע, הזמנות רכש וגרעונות לחומר. מנהל החומר ב-CBC עובד מולו יומית.</t>
+        </is>
+      </c>
+      <c r="Q896" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R896" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S896" s="4" t="inlineStr">
         <is>
-          <t>A39</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="T896" s="7">
@@ -44913,28 +45103,32 @@
       <c r="M897" s="4" t="n"/>
       <c r="N897" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O897" s="6" t="inlineStr">
         <is>
-          <t>FROM KAKO JOIN CRCA ON KAKO.KAPID = CRCA.KAPID</t>
+          <t>F0251</t>
         </is>
       </c>
       <c r="P897" s="4" t="inlineStr">
         <is>
-          <t>כותרת קיבולת</t>
-        </is>
-      </c>
-      <c r="Q897" s="4" t="inlineStr"/>
+          <t>Monitor Material Coverage - Net Segments</t>
+        </is>
+      </c>
+      <c r="Q897" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R897" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S897" s="4" t="inlineStr">
         <is>
-          <t>A40</t>
+          <t>A21</t>
         </is>
       </c>
       <c r="T897" s="7">
@@ -44958,28 +45152,32 @@
       <c r="M898" s="4" t="n"/>
       <c r="N898" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O898" s="6" t="inlineStr">
         <is>
-          <t>FROM FHMI JOIN CRFH ON FHMI.FHMNR = CRFH.FHMNR</t>
+          <t>MD01 / MD01N</t>
         </is>
       </c>
       <c r="P898" s="4" t="inlineStr">
         <is>
-          <t>אב כלי עזר ייצור (PRT)</t>
-        </is>
-      </c>
-      <c r="Q898" s="4" t="inlineStr"/>
+          <t>הרצת תכנון חומרים (MRP / MRP Live). MD01N היא הגרסה החדשה הרצה ישירות על HANA (MRP Live) - מתכננת חומרי גלם, מוצרי ביניים וייצור ומייצרת פק"ע/הזמנות רכש מתוכננות.</t>
+        </is>
+      </c>
+      <c r="Q898" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R898" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S898" s="4" t="inlineStr">
         <is>
-          <t>A41</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="T898" s="7">
@@ -45003,28 +45201,32 @@
       <c r="M899" s="4" t="n"/>
       <c r="N899" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O899" s="6" t="inlineStr">
         <is>
-          <t>FROM CRVD_A JOIN CRHD ON CRVD_A.OBJID = CRHD.OBJID</t>
+          <t>F2101</t>
         </is>
       </c>
       <c r="P899" s="4" t="inlineStr">
         <is>
-          <t>ברירות מחדל למשאב (PI)</t>
-        </is>
-      </c>
-      <c r="Q899" s="4" t="inlineStr"/>
+          <t>Schedule MRP Runs / Monitor Material Requirements</t>
+        </is>
+      </c>
+      <c r="Q899" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R899" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S899" s="4" t="inlineStr">
         <is>
-          <t>A42</t>
+          <t>A22</t>
         </is>
       </c>
       <c r="T899" s="7">
@@ -45048,28 +45250,32 @@
       <c r="M900" s="4" t="n"/>
       <c r="N900" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O900" s="6" t="inlineStr">
         <is>
-          <t>FROM CSLA JOIN CRCO ON CSLA.LSTAR = CRCO.LSTAR</t>
+          <t>COGI</t>
         </is>
       </c>
       <c r="P900" s="4" t="inlineStr">
         <is>
-          <t>סוגי פעילות למרכז עבודה</t>
-        </is>
-      </c>
-      <c r="Q900" s="4" t="inlineStr"/>
+          <t>עיבוד תנועות מלאי שגויות (Postprocessing of Faulty Goods Movements) - מטפל בפליטות/קליטות אוטומטיות שנכשלו (Backflush). קריטי בייצור משקאות: כשל בפליטת חומר גלם אוטומטית מהקו חייב טיפול מיידי כדי לא לעצור דיווח.</t>
+        </is>
+      </c>
+      <c r="Q900" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R900" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S900" s="4" t="inlineStr">
         <is>
-          <t>A43</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="T900" s="7">
@@ -45093,28 +45299,32 @@
       <c r="M901" s="4" t="n"/>
       <c r="N901" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O901" s="6" t="inlineStr">
         <is>
-          <t>FROM KAZT JOIN KAKO ON KAZT.KAPID = KAKO.KAPID</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P901" s="4" t="inlineStr">
         <is>
-          <t>מרווחי קיבולת זמינה</t>
-        </is>
-      </c>
-      <c r="Q901" s="4" t="inlineStr"/>
+          <t>Manage Material Documents / Clear Faulty Movements</t>
+        </is>
+      </c>
+      <c r="Q901" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R901" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S901" s="4" t="inlineStr">
         <is>
-          <t>A44</t>
+          <t>A23</t>
         </is>
       </c>
       <c r="T901" s="7">
@@ -45138,28 +45348,32 @@
       <c r="M902" s="4" t="n"/>
       <c r="N902" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O902" s="6" t="inlineStr">
         <is>
-          <t>FROM AFKO JOIN AUFK ON AFKO.AUFNR = AUFK.AUFNR</t>
+          <t>CM01 / CM07</t>
         </is>
       </c>
       <c r="P902" s="4" t="inlineStr">
         <is>
-          <t>כותרת פקודת ייצור</t>
-        </is>
-      </c>
-      <c r="Q902" s="4" t="inlineStr"/>
+          <t>הערכת עומסי קיבולת (Capacity Load / Evaluation) - מציג את העומס מול הזמינות של קווי הייצור/המשאבים. כלי לזיהוי צווארי בקבוק ולתזמון ייצור משקאות יעיל ב-CBC.</t>
+        </is>
+      </c>
+      <c r="Q902" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R902" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S902" s="4" t="inlineStr">
         <is>
-          <t>A45</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="T902" s="7">
@@ -45183,28 +45397,32 @@
       <c r="M903" s="4" t="n"/>
       <c r="N903" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O903" s="6" t="inlineStr">
         <is>
-          <t>FROM AFPO JOIN AFKO ON AFPO.AUFNR = AFKO.AUFNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P903" s="4" t="inlineStr">
         <is>
-          <t>פריט פקודת ייצור</t>
-        </is>
-      </c>
-      <c r="Q903" s="4" t="inlineStr"/>
+          <t>Capacity Scheduling Board / Monitor Capacity Utilisation</t>
+        </is>
+      </c>
+      <c r="Q903" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R903" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S903" s="4" t="inlineStr">
         <is>
-          <t>A46</t>
+          <t>A24</t>
         </is>
       </c>
       <c r="T903" s="7">
@@ -45228,28 +45446,32 @@
       <c r="M904" s="4" t="n"/>
       <c r="N904" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O904" s="6" t="inlineStr">
         <is>
-          <t>FROM AFVC JOIN AFKO ON AFVC.AUFPL = AFKO.AUFPL</t>
+          <t>COHV / COHVPI</t>
         </is>
       </c>
       <c r="P904" s="4" t="inlineStr">
         <is>
-          <t>פעולות פקודת הייצור</t>
-        </is>
-      </c>
-      <c r="Q904" s="4" t="inlineStr"/>
+          <t>עיבוד המוני של פקודות (Mass Processing) - מאפשר שחרור, הדפסה, דיווח או ביטול של מאות פק"ע בו-זמנית. חיוני לתפעול יומי של עשרות פק"ע ייצור ב-CBC.</t>
+        </is>
+      </c>
+      <c r="Q904" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R904" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S904" s="4" t="inlineStr">
         <is>
-          <t>A47</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="T904" s="7">
@@ -45273,28 +45495,32 @@
       <c r="M905" s="4" t="n"/>
       <c r="N905" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O905" s="6" t="inlineStr">
         <is>
-          <t>FROM RESB JOIN AFKO ON RESB.AUFNR = AFKO.AUFNR</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P905" s="4" t="inlineStr">
         <is>
-          <t>הזמנת רכיבים לפק"ע</t>
-        </is>
-      </c>
-      <c r="Q905" s="4" t="inlineStr"/>
+          <t>Mass Processing - Orders</t>
+        </is>
+      </c>
+      <c r="Q905" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R905" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S905" s="4" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>A25</t>
         </is>
       </c>
       <c r="T905" s="7">
@@ -45318,28 +45544,32 @@
       <c r="M906" s="4" t="n"/>
       <c r="N906" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O906" s="6" t="inlineStr">
         <is>
-          <t>FROM AFRU JOIN AFKO ON AFRU.AUFNR = AFKO.AUFNR</t>
+          <t>CORK / CORT</t>
         </is>
       </c>
       <c r="P906" s="4" t="inlineStr">
         <is>
-          <t>דיווחי ביצוע פק"ע</t>
-        </is>
-      </c>
-      <c r="Q906" s="4" t="inlineStr"/>
+          <t>השלמה ובקרה של פק"ע תהליך: CORK = דיווח השלמת פק"ע; CORT = מוניטור מתכוני בקרה (Control Recipe Monitor). CORT מנהל את שליחת הוראות התהליך לקו/MES ומעקב סטטוס המסירה (Zetes/Daymax).</t>
+        </is>
+      </c>
+      <c r="Q906" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R906" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S906" s="4" t="inlineStr">
         <is>
-          <t>A49</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="T906" s="7">
@@ -45363,28 +45593,32 @@
       <c r="M907" s="4" t="n"/>
       <c r="N907" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O907" s="6" t="inlineStr">
         <is>
-          <t>FROM AFFH JOIN AFKO ON AFFH.AUFPL = AFKO.AUFPL</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P907" s="4" t="inlineStr">
         <is>
-          <t>שיוך PRT לפק"ע</t>
-        </is>
-      </c>
-      <c r="Q907" s="4" t="inlineStr"/>
+          <t>Confirm Process Order / Control Recipe Monitor</t>
+        </is>
+      </c>
+      <c r="Q907" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R907" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S907" s="4" t="inlineStr">
         <is>
-          <t>A50</t>
+          <t>A26</t>
         </is>
       </c>
       <c r="T907" s="7">
@@ -45408,28 +45642,32 @@
       <c r="M908" s="4" t="n"/>
       <c r="N908" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O908" s="6" t="inlineStr">
         <is>
-          <t>FROM AFFL JOIN AFKO ON AFFL.AUFPL = AFKO.AUFPL</t>
+          <t>CO53</t>
         </is>
       </c>
       <c r="P908" s="4" t="inlineStr">
         <is>
-          <t>רצפי פעולות בפק"ע</t>
-        </is>
-      </c>
-      <c r="Q908" s="4" t="inlineStr"/>
+          <t>רשימת עבודה למתכוני בקרה / גיליון PI (Control Recipe / PI Sheet Worklist) - מציג למפעיל הקו את הוראות התהליך לביצוע ולתיעוד (ערכים נמדדים, אישורים). הממשק הישיר בין SAP לאוטומציית הקו ב-CBC.</t>
+        </is>
+      </c>
+      <c r="Q908" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R908" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S908" s="4" t="inlineStr">
         <is>
-          <t>A51</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="T908" s="7">
@@ -45453,28 +45691,32 @@
       <c r="M909" s="4" t="n"/>
       <c r="N909" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O909" s="6" t="inlineStr">
         <is>
-          <t>FROM MARA JOIN T134 ON MARA.MTART = T134.MTART</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P909" s="4" t="inlineStr">
         <is>
-          <t>סוגי חומר (Customizing)</t>
-        </is>
-      </c>
-      <c r="Q909" s="4" t="inlineStr"/>
+          <t>Process Operator Dashboard / Digital Mfg</t>
+        </is>
+      </c>
+      <c r="Q909" s="4" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
       <c r="R909" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S909" s="4" t="inlineStr">
         <is>
-          <t>A52</t>
+          <t>A27</t>
         </is>
       </c>
       <c r="T909" s="7">
@@ -45498,28 +45740,32 @@
       <c r="M910" s="4" t="n"/>
       <c r="N910" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O910" s="6" t="inlineStr">
         <is>
-          <t>FROM T134T JOIN T134 ON T134T.MTART = T134.MTART</t>
+          <t>MB1A / MIGO</t>
         </is>
       </c>
       <c r="P910" s="4" t="inlineStr">
         <is>
-          <t>טקסטים לסוגי חומר</t>
-        </is>
-      </c>
-      <c r="Q910" s="4" t="inlineStr"/>
+          <t>תנועות מלאי: MB1A = פליטת חומר (261) לפק"ע; MIGO = תנועת מלאי כללית (פליטה/קליטה). פליטת חומרי גלם וקליטת מוצר מוגמר ב-CBC, מסונכרן עם מסופי Zetes.</t>
+        </is>
+      </c>
+      <c r="Q910" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R910" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S910" s="4" t="inlineStr">
         <is>
-          <t>A53</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="T910" s="7">
@@ -45543,28 +45789,32 @@
       <c r="M911" s="4" t="n"/>
       <c r="N911" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O911" s="6" t="inlineStr">
         <is>
-          <t>FROM MARA JOIN T023 ON MARA.MATKL = T023.MATKL</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P911" s="4" t="inlineStr">
         <is>
-          <t>קבוצות חומר (Customizing)</t>
-        </is>
-      </c>
-      <c r="Q911" s="4" t="inlineStr"/>
+          <t>Post Goods Movement</t>
+        </is>
+      </c>
+      <c r="Q911" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R911" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S911" s="4" t="inlineStr">
         <is>
-          <t>A54</t>
+          <t>A28</t>
         </is>
       </c>
       <c r="T911" s="7">
@@ -45588,28 +45838,32 @@
       <c r="M912" s="4" t="n"/>
       <c r="N912" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>T-code</t>
         </is>
       </c>
       <c r="O912" s="6" t="inlineStr">
         <is>
-          <t>FROM T023T JOIN T023 ON T023T.MATKL = T023.MATKL</t>
+          <t>MB31</t>
         </is>
       </c>
       <c r="P912" s="4" t="inlineStr">
         <is>
-          <t>טקסטים לקבוצות חומר</t>
-        </is>
-      </c>
-      <c r="Q912" s="4" t="inlineStr"/>
+          <t>קליטת סחורה לפק"ע (Goods Receipt for Order, תנועה 101) - קליטת המוצר המוגמר/ביניים שיוצר למלאי, כולל אצווה ותאריך תפוגה. נקודת סיום הייצור והעברה ללוגיסטיקה.</t>
+        </is>
+      </c>
+      <c r="Q912" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R912" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S912" s="4" t="inlineStr">
         <is>
-          <t>A55</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="T912" s="7">
@@ -45633,28 +45887,32 @@
       <c r="M913" s="4" t="n"/>
       <c r="N913" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Fiori</t>
         </is>
       </c>
       <c r="O913" s="6" t="inlineStr">
         <is>
-          <t>FROM AUFK JOIN T399X ON AUFK.WERKS = T399X.WERKS AND AUFK.AUART = T399X.AUART</t>
+          <t>(אמת ID)</t>
         </is>
       </c>
       <c r="P913" s="4" t="inlineStr">
         <is>
-          <t>פרמטרי בקרת ייצור למפעל</t>
-        </is>
-      </c>
-      <c r="Q913" s="4" t="inlineStr"/>
+          <t>Post Goods Receipt for Production</t>
+        </is>
+      </c>
+      <c r="Q913" s="4" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
       <c r="R913" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>PP_PPPI_Tcodes</t>
         </is>
       </c>
       <c r="S913" s="4" t="inlineStr">
         <is>
-          <t>A56</t>
+          <t>A29</t>
         </is>
       </c>
       <c r="T913" s="7">
@@ -45678,28 +45936,28 @@
       <c r="M914" s="4" t="n"/>
       <c r="N914" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O914" s="6" t="inlineStr">
         <is>
-          <t>FROM T399X JOIN TCK03 ON T399X.KLVARP = TCK03.KLVAR</t>
+          <t>SPRO</t>
         </is>
       </c>
       <c r="P914" s="4" t="inlineStr">
         <is>
-          <t>וריאנט תמחיר (Costing Variant)</t>
+          <t>מרכז ה-Customizing (IMG) - הגדרת כל הקונפיגורציה של SAP: מבנה ארגוני, סוגי פק"ע, פרופילי סטטוס, פרמטרי MRP, ממשקים ועוד. כלי העבודה המרכזי של המיישם ב-Project NEO.</t>
         </is>
       </c>
       <c r="Q914" s="4" t="inlineStr"/>
       <c r="R914" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S914" s="4" t="inlineStr">
         <is>
-          <t>A57</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="T914" s="7">
@@ -45723,28 +45981,28 @@
       <c r="M915" s="4" t="n"/>
       <c r="N915" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O915" s="6" t="inlineStr">
         <is>
-          <t>FROM MARC JOIN T438M ON MARC.DISMM = T438M.DISMM</t>
+          <t>SU01</t>
         </is>
       </c>
       <c r="P915" s="4" t="inlineStr">
         <is>
-          <t>פרמטרי MRP לחומר/מפעל</t>
+          <t>תחזוקת משתמשים - יצירה/שינוי/נעילה של משתמשי SAP, הקצאת תפקידים, פרופילים, פרמטרים וסיסמאות. בסיס לאבטחת המערכת ולהרשאות בפרויקט.</t>
         </is>
       </c>
       <c r="Q915" s="4" t="inlineStr"/>
       <c r="R915" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S915" s="4" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>A4</t>
         </is>
       </c>
       <c r="T915" s="7">
@@ -45768,28 +46026,28 @@
       <c r="M916" s="4" t="n"/>
       <c r="N916" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O916" s="6" t="inlineStr">
         <is>
-          <t>FROM AUFK JOIN T003O ON AUFK.AUART = T003O.AUART</t>
+          <t>PFCG</t>
         </is>
       </c>
       <c r="P916" s="4" t="inlineStr">
         <is>
-          <t>סוגי פקודת ייצור (Process Order Types)</t>
+          <t>תחזוקת תפקידים והרשאות (Role Maintenance) - בניית תפקידים (Roles), אובייקטי הרשאה, תפריטים והקצאת אפליקציות. הליבה לאבטחת הגישה לטרנזקציות ולאפליקציות Fiori.</t>
         </is>
       </c>
       <c r="Q916" s="4" t="inlineStr"/>
       <c r="R916" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S916" s="4" t="inlineStr">
         <is>
-          <t>A59</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="T916" s="7">
@@ -45813,28 +46071,28 @@
       <c r="M917" s="4" t="n"/>
       <c r="N917" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O917" s="6" t="inlineStr">
         <is>
-          <t>FROM TCO01 JOIN T003O ON TCO01.AUART = T003O.AUART</t>
+          <t>SE37</t>
         </is>
       </c>
       <c r="P917" s="4" t="inlineStr">
         <is>
-          <t>פרמטרים תלויי סוג פק"ע (Order Profile)</t>
+          <t>Function Builder - יצירה ובדיקה של מודולי פונקציה ו-BAPIs. כלי הליבה של ABAP לבדיקת ממשקים (BAPI_MATERIAL_SAVEDATA, BAPI_PROCORD_CREATE) ולפיתוח אינטגרציות.</t>
         </is>
       </c>
       <c r="Q917" s="4" t="inlineStr"/>
       <c r="R917" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S917" s="4" t="inlineStr">
         <is>
-          <t>A60</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="T917" s="7">
@@ -45858,28 +46116,28 @@
       <c r="M918" s="4" t="n"/>
       <c r="N918" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O918" s="6" t="inlineStr">
         <is>
-          <t>FROM JEST JOIN TJ30 ON JEST.STAT = TJ30.ESTAT</t>
+          <t>SE38 / SA38</t>
         </is>
       </c>
       <c r="P918" s="4" t="inlineStr">
         <is>
-          <t>סטטוסי משתמש בפרופיל (User Status)</t>
+          <t>ABAP Editor (SE38) והרצת דוחות (SA38) - כתיבה, עריכה והרצה של תוכניות ABAP ודוחות סטנדרטיים (RMMG2000, RCC22300). כלי מרכזי לדיווח ולתחזוקה.</t>
         </is>
       </c>
       <c r="Q918" s="4" t="inlineStr"/>
       <c r="R918" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S918" s="4" t="inlineStr">
         <is>
-          <t>A61</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="T918" s="7">
@@ -45903,28 +46161,28 @@
       <c r="M919" s="4" t="n"/>
       <c r="N919" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O919" s="6" t="inlineStr">
         <is>
-          <t>FROM TJ30T JOIN TJ30 ON TJ30T.STSMA = TJ30.STSMA AND TJ30T.ESTAT = TJ30.ESTAT</t>
+          <t>SE11 / SE16 / SE16N</t>
         </is>
       </c>
       <c r="P919" s="4" t="inlineStr">
         <is>
-          <t>טקסטים לסטטוסי משתמש</t>
+          <t>מילון הנתונים (Data Dictionary) ועיון בתוכן טבלאות. SE11 = הגדרת טבלאות/Views/Structures; SE16/SE16N = דפדפן תוכן הטבלאות (MARA, MKAL, AFKO). חיוני לבדיקת מבנה ונתונים בפרויקט.</t>
         </is>
       </c>
       <c r="Q919" s="4" t="inlineStr"/>
       <c r="R919" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S919" s="4" t="inlineStr">
         <is>
-          <t>A62</t>
+          <t>A8</t>
         </is>
       </c>
       <c r="T919" s="7">
@@ -45948,28 +46206,28 @@
       <c r="M920" s="4" t="n"/>
       <c r="N920" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O920" s="6" t="inlineStr">
         <is>
-          <t>FROM EKKO JOIN BUT000 ON EKKO.LIFNR = BUT000.PARTNER</t>
+          <t>SM30 / SM31</t>
         </is>
       </c>
       <c r="P920" s="4" t="inlineStr">
         <is>
-          <t>שותף עסקי (BP - השפעת מעבר S/4)</t>
+          <t>תחזוקת תצוגות טבלה (Table View Maintenance) - עדכון ידני של טבלאות קונפיגורציה (T003O, TCO01, T399X) ללא SPRO. כלי מהיר למיישם לעדכון פרמטרים.</t>
         </is>
       </c>
       <c r="Q920" s="4" t="inlineStr"/>
       <c r="R920" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S920" s="4" t="inlineStr">
         <is>
-          <t>A63</t>
+          <t>A9</t>
         </is>
       </c>
       <c r="T920" s="7">
@@ -45993,28 +46251,28 @@
       <c r="M921" s="4" t="n"/>
       <c r="N921" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O921" s="6" t="inlineStr">
         <is>
-          <t>FROM PLPO JOIN TC22 ON PLPO.STEUS = TC22.STEUS</t>
+          <t>SM37</t>
         </is>
       </c>
       <c r="P921" s="4" t="inlineStr">
         <is>
-          <t>מפתחות בקרת תהליך/פעולה (PI Control)</t>
+          <t>מוניטור משימות רקע (Background Job Monitor) - מעקב, תזמון וניתוח של ג'obs ברקע (הרצות MRP, יצירת IDocs, עיבוד המוני). חיוני לתפעול אצוות לילה ב-CBC.</t>
         </is>
       </c>
       <c r="Q921" s="4" t="inlineStr"/>
       <c r="R921" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S921" s="4" t="inlineStr">
         <is>
-          <t>A64</t>
+          <t>A10</t>
         </is>
       </c>
       <c r="T921" s="7">
@@ -46038,28 +46296,28 @@
       <c r="M922" s="4" t="n"/>
       <c r="N922" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O922" s="6" t="inlineStr">
         <is>
-          <t>FROM JEST JOIN AUFK ON JEST.OBJNR = AUFK.OBJNR</t>
+          <t>ST22</t>
         </is>
       </c>
       <c r="P922" s="4" t="inlineStr">
         <is>
-          <t>סטטוס אובייקט - מכונת מצבים של הפק"ע</t>
+          <t>ניתוח קריסות ABAP (Dump Analysis) - מציג שגיאות ריצה (Short Dumps) עם stack trace וניתוח שורש. כלי הדיבוג הראשון לכל תקלת תוכנית או ממשק.</t>
         </is>
       </c>
       <c r="Q922" s="4" t="inlineStr"/>
       <c r="R922" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S922" s="4" t="inlineStr">
         <is>
-          <t>A65</t>
+          <t>A11</t>
         </is>
       </c>
       <c r="T922" s="7">
@@ -46083,28 +46341,28 @@
       <c r="M923" s="4" t="n"/>
       <c r="N923" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O923" s="6" t="inlineStr">
         <is>
-          <t>FROM JSTO JOIN AUFK ON JSTO.OBJNR = AUFK.OBJNR</t>
+          <t>SM04 / AL08</t>
         </is>
       </c>
       <c r="P923" s="4" t="inlineStr">
         <is>
-          <t>כותרת אובייקט סטטוס + פרופיל</t>
+          <t>מוניטור משתמשים מחוברים (User Monitor) - SM04 = משתמשים בשרת נוכחי; AL08 = כל המשתמשים בכל השרתים. לבקרת עומס, ניתוק תהליכים ופתרון נעילות.</t>
         </is>
       </c>
       <c r="Q923" s="4" t="inlineStr"/>
       <c r="R923" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S923" s="4" t="inlineStr">
         <is>
-          <t>A66</t>
+          <t>A12</t>
         </is>
       </c>
       <c r="T923" s="7">
@@ -46128,28 +46386,28 @@
       <c r="M924" s="4" t="n"/>
       <c r="N924" s="4" t="inlineStr">
         <is>
-          <t>Join</t>
+          <t>Tool</t>
         </is>
       </c>
       <c r="O924" s="6" t="inlineStr">
         <is>
-          <t>FROM JEST JOIN TJ02T ON JEST.STAT = TJ02T.ISTAT</t>
+          <t>WE02 / WE05 / WE19</t>
         </is>
       </c>
       <c r="P924" s="4" t="inlineStr">
         <is>
-          <t>טקסטים של סטטוסי מערכת (CRTE/REL/CNF/TECO)</t>
+          <t>מוניטור IDocs - WE02/WE05 = צפייה וניתוח IDocs נכנסים/יוצאים (MATMAS, LOIPRO) וסטטוסים; WE19 = כלי בדיקה (test tool). הליבה לפתרון תקלות בממשקים ל-Zetes ו-Daymax.</t>
         </is>
       </c>
       <c r="Q924" s="4" t="inlineStr"/>
       <c r="R924" s="4" t="inlineStr">
         <is>
-          <t>ER - Join Map</t>
+          <t>SAP_Maint_Tools</t>
         </is>
       </c>
       <c r="S924" s="4" t="inlineStr">
         <is>
-          <t>A67</t>
+          <t>A13</t>
         </is>
       </c>
       <c r="T924" s="7">
@@ -46157,25 +46415,3267 @@
         <v/>
       </c>
     </row>
+    <row r="925">
+      <c r="A925" s="4" t="n"/>
+      <c r="B925" s="4" t="n"/>
+      <c r="C925" s="4" t="n"/>
+      <c r="D925" s="4" t="n"/>
+      <c r="E925" s="4" t="n"/>
+      <c r="F925" s="4" t="n"/>
+      <c r="G925" s="4" t="n"/>
+      <c r="H925" s="4" t="n"/>
+      <c r="I925" s="4" t="n"/>
+      <c r="J925" s="4" t="n"/>
+      <c r="K925" s="4" t="n"/>
+      <c r="L925" s="4" t="n"/>
+      <c r="M925" s="4" t="n"/>
+      <c r="N925" s="4" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="O925" s="6" t="inlineStr">
+        <is>
+          <t>WE20 / WE21</t>
+        </is>
+      </c>
+      <c r="P925" s="4" t="inlineStr">
+        <is>
+          <t>פרופילי שותפים ויציאות (Partner Profiles &amp; Ports) - WE20 = הגדרת פרופיל שותף (אילו IDocs נשלחים/מתקבלים לכל שותף); WE21 = הגדרת פורטים (tRFC/File). מגדיר את צינור התקשורת ל-Zetes/Daymax.</t>
+        </is>
+      </c>
+      <c r="Q925" s="4" t="inlineStr"/>
+      <c r="R925" s="4" t="inlineStr">
+        <is>
+          <t>SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="S925" s="4" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="T925" s="7">
+        <f>HYPERLINK("#'"&amp;R925&amp;"'!"&amp;S925,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" s="4" t="n"/>
+      <c r="B926" s="4" t="n"/>
+      <c r="C926" s="4" t="n"/>
+      <c r="D926" s="4" t="n"/>
+      <c r="E926" s="4" t="n"/>
+      <c r="F926" s="4" t="n"/>
+      <c r="G926" s="4" t="n"/>
+      <c r="H926" s="4" t="n"/>
+      <c r="I926" s="4" t="n"/>
+      <c r="J926" s="4" t="n"/>
+      <c r="K926" s="4" t="n"/>
+      <c r="L926" s="4" t="n"/>
+      <c r="M926" s="4" t="n"/>
+      <c r="N926" s="4" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="O926" s="6" t="inlineStr">
+        <is>
+          <t>BD64</t>
+        </is>
+      </c>
+      <c r="P926" s="4" t="inlineStr">
+        <is>
+          <t>מודל הפצה (Distribution Model / ALE) - הגדרת אילו הודעות (Message Types) מופצות בין מערכות SAP/חיצוניות. בסיס ה-ALE לתשתית ה-IDoc של המפעל.</t>
+        </is>
+      </c>
+      <c r="Q926" s="4" t="inlineStr"/>
+      <c r="R926" s="4" t="inlineStr">
+        <is>
+          <t>SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="S926" s="4" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="T926" s="7">
+        <f>HYPERLINK("#'"&amp;R926&amp;"'!"&amp;S926,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" s="4" t="n"/>
+      <c r="B927" s="4" t="n"/>
+      <c r="C927" s="4" t="n"/>
+      <c r="D927" s="4" t="n"/>
+      <c r="E927" s="4" t="n"/>
+      <c r="F927" s="4" t="n"/>
+      <c r="G927" s="4" t="n"/>
+      <c r="H927" s="4" t="n"/>
+      <c r="I927" s="4" t="n"/>
+      <c r="J927" s="4" t="n"/>
+      <c r="K927" s="4" t="n"/>
+      <c r="L927" s="4" t="n"/>
+      <c r="M927" s="4" t="n"/>
+      <c r="N927" s="4" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="O927" s="6" t="inlineStr">
+        <is>
+          <t>SMQ1 / SMQ2</t>
+        </is>
+      </c>
+      <c r="P927" s="4" t="inlineStr">
+        <is>
+          <t>מוניטור תורים (qRFC Queues) - SMQ1 = תור יוצא (outbound); SMQ2 = תור נכנס (inbound). מעקב וטיפול בהודעות תקועות בתקשורת אסינכרונית בין SAP למערכות (CIF/MES).</t>
+        </is>
+      </c>
+      <c r="Q927" s="4" t="inlineStr"/>
+      <c r="R927" s="4" t="inlineStr">
+        <is>
+          <t>SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="S927" s="4" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="T927" s="7">
+        <f>HYPERLINK("#'"&amp;R927&amp;"'!"&amp;S927,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" s="4" t="n"/>
+      <c r="B928" s="4" t="n"/>
+      <c r="C928" s="4" t="n"/>
+      <c r="D928" s="4" t="n"/>
+      <c r="E928" s="4" t="n"/>
+      <c r="F928" s="4" t="n"/>
+      <c r="G928" s="4" t="n"/>
+      <c r="H928" s="4" t="n"/>
+      <c r="I928" s="4" t="n"/>
+      <c r="J928" s="4" t="n"/>
+      <c r="K928" s="4" t="n"/>
+      <c r="L928" s="4" t="n"/>
+      <c r="M928" s="4" t="n"/>
+      <c r="N928" s="4" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="O928" s="6" t="inlineStr">
+        <is>
+          <t>STMS / SE09 / SE10</t>
+        </is>
+      </c>
+      <c r="P928" s="4" t="inlineStr">
+        <is>
+          <t>ניהול תעבורה (Transport Management) - STMS = נוף התעבורה והעברת בקשות בין סביבות (DEV-&gt;QA-&gt;PRD); SE09/SE10 = ארגון בקשות התעבורה. ליבת ה-Change Management של הפרויקט.</t>
+        </is>
+      </c>
+      <c r="Q928" s="4" t="inlineStr"/>
+      <c r="R928" s="4" t="inlineStr">
+        <is>
+          <t>SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="S928" s="4" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="T928" s="7">
+        <f>HYPERLINK("#'"&amp;R928&amp;"'!"&amp;S928,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" s="4" t="n"/>
+      <c r="B929" s="4" t="n"/>
+      <c r="C929" s="4" t="n"/>
+      <c r="D929" s="4" t="n"/>
+      <c r="E929" s="4" t="n"/>
+      <c r="F929" s="4" t="n"/>
+      <c r="G929" s="4" t="n"/>
+      <c r="H929" s="4" t="n"/>
+      <c r="I929" s="4" t="n"/>
+      <c r="J929" s="4" t="n"/>
+      <c r="K929" s="4" t="n"/>
+      <c r="L929" s="4" t="n"/>
+      <c r="M929" s="4" t="n"/>
+      <c r="N929" s="4" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="O929" s="6" t="inlineStr">
+        <is>
+          <t>ST05 / SAT</t>
+        </is>
+      </c>
+      <c r="P929" s="4" t="inlineStr">
+        <is>
+          <t>כלי Trace וביצועים - ST05 = SQL/RFC/Buffer trace לניתוח ביצועי שאילתות וממשקים; SAT = ניתוח זמן ריצה (Runtime Analysis). חיוני לאופטימיזציה של דוחות וממשקים כבדים.</t>
+        </is>
+      </c>
+      <c r="Q929" s="4" t="inlineStr"/>
+      <c r="R929" s="4" t="inlineStr">
+        <is>
+          <t>SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="S929" s="4" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="T929" s="7">
+        <f>HYPERLINK("#'"&amp;R929&amp;"'!"&amp;S929,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" s="4" t="n"/>
+      <c r="B930" s="4" t="n"/>
+      <c r="C930" s="4" t="n"/>
+      <c r="D930" s="4" t="n"/>
+      <c r="E930" s="4" t="n"/>
+      <c r="F930" s="4" t="n"/>
+      <c r="G930" s="4" t="n"/>
+      <c r="H930" s="4" t="n"/>
+      <c r="I930" s="4" t="n"/>
+      <c r="J930" s="4" t="n"/>
+      <c r="K930" s="4" t="n"/>
+      <c r="L930" s="4" t="n"/>
+      <c r="M930" s="4" t="n"/>
+      <c r="N930" s="4" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="O930" s="6" t="inlineStr">
+        <is>
+          <t>SLG1</t>
+        </is>
+      </c>
+      <c r="P930" s="4" t="inlineStr">
+        <is>
+          <t>יומן יישום (Application Log) - מציג הודעות, אזהרות ושגיאות שתוכניות/ממשקים רשמו (לדוגמה כשלי המרת BP, שגיאות MRP). כלי מעקב מרכזי לאבחון תהליכים ברקע.</t>
+        </is>
+      </c>
+      <c r="Q930" s="4" t="inlineStr"/>
+      <c r="R930" s="4" t="inlineStr">
+        <is>
+          <t>SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="S930" s="4" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="T930" s="7">
+        <f>HYPERLINK("#'"&amp;R930&amp;"'!"&amp;S930,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" s="4" t="n"/>
+      <c r="B931" s="4" t="n"/>
+      <c r="C931" s="4" t="n"/>
+      <c r="D931" s="4" t="n"/>
+      <c r="E931" s="4" t="n"/>
+      <c r="F931" s="4" t="n"/>
+      <c r="G931" s="4" t="n"/>
+      <c r="H931" s="4" t="n"/>
+      <c r="I931" s="4" t="n"/>
+      <c r="J931" s="4" t="n"/>
+      <c r="K931" s="4" t="n"/>
+      <c r="L931" s="4" t="n"/>
+      <c r="M931" s="4" t="n"/>
+      <c r="N931" s="4" t="inlineStr">
+        <is>
+          <t>Tool</t>
+        </is>
+      </c>
+      <c r="O931" s="6" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
+      <c r="P931" s="4" t="inlineStr">
+        <is>
+          <t>שותף עסקי (Business Partner) - נקודת הכניסה היחידה לניהול לקוחות/ספקים ב-S/4HANA (מחליף XK01/MK01/XD01). ניהול תפקידים (Roles), קבוצות וכתובות. קריטי לספקי חומרי הגלם של CBC.</t>
+        </is>
+      </c>
+      <c r="Q931" s="4" t="inlineStr"/>
+      <c r="R931" s="4" t="inlineStr">
+        <is>
+          <t>SAP_Maint_Tools</t>
+        </is>
+      </c>
+      <c r="S931" s="4" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="T931" s="7">
+        <f>HYPERLINK("#'"&amp;R931&amp;"'!"&amp;S931,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" s="4" t="n"/>
+      <c r="B932" s="4" t="n"/>
+      <c r="C932" s="4" t="n"/>
+      <c r="D932" s="4" t="n"/>
+      <c r="E932" s="4" t="n"/>
+      <c r="F932" s="4" t="n"/>
+      <c r="G932" s="4" t="n"/>
+      <c r="H932" s="4" t="n"/>
+      <c r="I932" s="4" t="n"/>
+      <c r="J932" s="4" t="n"/>
+      <c r="K932" s="4" t="n"/>
+      <c r="L932" s="4" t="n"/>
+      <c r="M932" s="4" t="n"/>
+      <c r="N932" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O932" s="6" t="inlineStr">
+        <is>
+          <t>FROM MAKT JOIN MARA ON MAKT.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P932" s="4" t="inlineStr">
+        <is>
+          <t>תיאורי חומר (טקסטים)</t>
+        </is>
+      </c>
+      <c r="Q932" s="4" t="inlineStr"/>
+      <c r="R932" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S932" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="T932" s="7">
+        <f>HYPERLINK("#'"&amp;R932&amp;"'!"&amp;S932,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" s="4" t="n"/>
+      <c r="B933" s="4" t="n"/>
+      <c r="C933" s="4" t="n"/>
+      <c r="D933" s="4" t="n"/>
+      <c r="E933" s="4" t="n"/>
+      <c r="F933" s="4" t="n"/>
+      <c r="G933" s="4" t="n"/>
+      <c r="H933" s="4" t="n"/>
+      <c r="I933" s="4" t="n"/>
+      <c r="J933" s="4" t="n"/>
+      <c r="K933" s="4" t="n"/>
+      <c r="L933" s="4" t="n"/>
+      <c r="M933" s="4" t="n"/>
+      <c r="N933" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O933" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARC JOIN MARA ON MARC.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P933" s="4" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מפעל</t>
+        </is>
+      </c>
+      <c r="Q933" s="4" t="inlineStr"/>
+      <c r="R933" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S933" s="4" t="inlineStr">
+        <is>
+          <t>A4</t>
+        </is>
+      </c>
+      <c r="T933" s="7">
+        <f>HYPERLINK("#'"&amp;R933&amp;"'!"&amp;S933,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" s="4" t="n"/>
+      <c r="B934" s="4" t="n"/>
+      <c r="C934" s="4" t="n"/>
+      <c r="D934" s="4" t="n"/>
+      <c r="E934" s="4" t="n"/>
+      <c r="F934" s="4" t="n"/>
+      <c r="G934" s="4" t="n"/>
+      <c r="H934" s="4" t="n"/>
+      <c r="I934" s="4" t="n"/>
+      <c r="J934" s="4" t="n"/>
+      <c r="K934" s="4" t="n"/>
+      <c r="L934" s="4" t="n"/>
+      <c r="M934" s="4" t="n"/>
+      <c r="N934" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O934" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARD JOIN MARC ON MARD.MATNR = MARC.MATNR AND MARD.WERKS = MARC.WERKS</t>
+        </is>
+      </c>
+      <c r="P934" s="4" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מחסן/מלאי</t>
+        </is>
+      </c>
+      <c r="Q934" s="4" t="inlineStr"/>
+      <c r="R934" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S934" s="4" t="inlineStr">
+        <is>
+          <t>A5</t>
+        </is>
+      </c>
+      <c r="T934" s="7">
+        <f>HYPERLINK("#'"&amp;R934&amp;"'!"&amp;S934,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" s="4" t="n"/>
+      <c r="B935" s="4" t="n"/>
+      <c r="C935" s="4" t="n"/>
+      <c r="D935" s="4" t="n"/>
+      <c r="E935" s="4" t="n"/>
+      <c r="F935" s="4" t="n"/>
+      <c r="G935" s="4" t="n"/>
+      <c r="H935" s="4" t="n"/>
+      <c r="I935" s="4" t="n"/>
+      <c r="J935" s="4" t="n"/>
+      <c r="K935" s="4" t="n"/>
+      <c r="L935" s="4" t="n"/>
+      <c r="M935" s="4" t="n"/>
+      <c r="N935" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O935" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARM JOIN MARA ON MARM.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P935" s="4" t="inlineStr">
+        <is>
+          <t>המרות יחידות מידה חלופיות</t>
+        </is>
+      </c>
+      <c r="Q935" s="4" t="inlineStr"/>
+      <c r="R935" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S935" s="4" t="inlineStr">
+        <is>
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="T935" s="7">
+        <f>HYPERLINK("#'"&amp;R935&amp;"'!"&amp;S935,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" s="4" t="n"/>
+      <c r="B936" s="4" t="n"/>
+      <c r="C936" s="4" t="n"/>
+      <c r="D936" s="4" t="n"/>
+      <c r="E936" s="4" t="n"/>
+      <c r="F936" s="4" t="n"/>
+      <c r="G936" s="4" t="n"/>
+      <c r="H936" s="4" t="n"/>
+      <c r="I936" s="4" t="n"/>
+      <c r="J936" s="4" t="n"/>
+      <c r="K936" s="4" t="n"/>
+      <c r="L936" s="4" t="n"/>
+      <c r="M936" s="4" t="n"/>
+      <c r="N936" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O936" s="6" t="inlineStr">
+        <is>
+          <t>FROM MEAN JOIN MARA ON MEAN.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P936" s="4" t="inlineStr">
+        <is>
+          <t>ברקודים / EAN לחומר</t>
+        </is>
+      </c>
+      <c r="Q936" s="4" t="inlineStr"/>
+      <c r="R936" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S936" s="4" t="inlineStr">
+        <is>
+          <t>A7</t>
+        </is>
+      </c>
+      <c r="T936" s="7">
+        <f>HYPERLINK("#'"&amp;R936&amp;"'!"&amp;S936,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" s="4" t="n"/>
+      <c r="B937" s="4" t="n"/>
+      <c r="C937" s="4" t="n"/>
+      <c r="D937" s="4" t="n"/>
+      <c r="E937" s="4" t="n"/>
+      <c r="F937" s="4" t="n"/>
+      <c r="G937" s="4" t="n"/>
+      <c r="H937" s="4" t="n"/>
+      <c r="I937" s="4" t="n"/>
+      <c r="J937" s="4" t="n"/>
+      <c r="K937" s="4" t="n"/>
+      <c r="L937" s="4" t="n"/>
+      <c r="M937" s="4" t="n"/>
+      <c r="N937" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O937" s="6" t="inlineStr">
+        <is>
+          <t>FROM MBEW JOIN MARA ON MBEW.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P937" s="4" t="inlineStr">
+        <is>
+          <t>הערכת חומר (Valuation)</t>
+        </is>
+      </c>
+      <c r="Q937" s="4" t="inlineStr"/>
+      <c r="R937" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S937" s="4" t="inlineStr">
+        <is>
+          <t>A8</t>
+        </is>
+      </c>
+      <c r="T937" s="7">
+        <f>HYPERLINK("#'"&amp;R937&amp;"'!"&amp;S937,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" s="4" t="n"/>
+      <c r="B938" s="4" t="n"/>
+      <c r="C938" s="4" t="n"/>
+      <c r="D938" s="4" t="n"/>
+      <c r="E938" s="4" t="n"/>
+      <c r="F938" s="4" t="n"/>
+      <c r="G938" s="4" t="n"/>
+      <c r="H938" s="4" t="n"/>
+      <c r="I938" s="4" t="n"/>
+      <c r="J938" s="4" t="n"/>
+      <c r="K938" s="4" t="n"/>
+      <c r="L938" s="4" t="n"/>
+      <c r="M938" s="4" t="n"/>
+      <c r="N938" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O938" s="6" t="inlineStr">
+        <is>
+          <t>FROM MVKE JOIN MARA ON MVKE.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P938" s="4" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מכירות</t>
+        </is>
+      </c>
+      <c r="Q938" s="4" t="inlineStr"/>
+      <c r="R938" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S938" s="4" t="inlineStr">
+        <is>
+          <t>A9</t>
+        </is>
+      </c>
+      <c r="T938" s="7">
+        <f>HYPERLINK("#'"&amp;R938&amp;"'!"&amp;S938,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" s="4" t="n"/>
+      <c r="B939" s="4" t="n"/>
+      <c r="C939" s="4" t="n"/>
+      <c r="D939" s="4" t="n"/>
+      <c r="E939" s="4" t="n"/>
+      <c r="F939" s="4" t="n"/>
+      <c r="G939" s="4" t="n"/>
+      <c r="H939" s="4" t="n"/>
+      <c r="I939" s="4" t="n"/>
+      <c r="J939" s="4" t="n"/>
+      <c r="K939" s="4" t="n"/>
+      <c r="L939" s="4" t="n"/>
+      <c r="M939" s="4" t="n"/>
+      <c r="N939" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O939" s="6" t="inlineStr">
+        <is>
+          <t>FROM MLAN JOIN MARA ON MLAN.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P939" s="4" t="inlineStr">
+        <is>
+          <t>נתוני מס לחומר (לפי מדינה)</t>
+        </is>
+      </c>
+      <c r="Q939" s="4" t="inlineStr"/>
+      <c r="R939" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S939" s="4" t="inlineStr">
+        <is>
+          <t>A10</t>
+        </is>
+      </c>
+      <c r="T939" s="7">
+        <f>HYPERLINK("#'"&amp;R939&amp;"'!"&amp;S939,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" s="4" t="n"/>
+      <c r="B940" s="4" t="n"/>
+      <c r="C940" s="4" t="n"/>
+      <c r="D940" s="4" t="n"/>
+      <c r="E940" s="4" t="n"/>
+      <c r="F940" s="4" t="n"/>
+      <c r="G940" s="4" t="n"/>
+      <c r="H940" s="4" t="n"/>
+      <c r="I940" s="4" t="n"/>
+      <c r="J940" s="4" t="n"/>
+      <c r="K940" s="4" t="n"/>
+      <c r="L940" s="4" t="n"/>
+      <c r="M940" s="4" t="n"/>
+      <c r="N940" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O940" s="6" t="inlineStr">
+        <is>
+          <t>FROM MLGN JOIN MARA ON MLGN.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P940" s="4" t="inlineStr">
+        <is>
+          <t>נתוני חומר ברמת מחסן (WM)</t>
+        </is>
+      </c>
+      <c r="Q940" s="4" t="inlineStr"/>
+      <c r="R940" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S940" s="4" t="inlineStr">
+        <is>
+          <t>A11</t>
+        </is>
+      </c>
+      <c r="T940" s="7">
+        <f>HYPERLINK("#'"&amp;R940&amp;"'!"&amp;S940,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" s="4" t="n"/>
+      <c r="B941" s="4" t="n"/>
+      <c r="C941" s="4" t="n"/>
+      <c r="D941" s="4" t="n"/>
+      <c r="E941" s="4" t="n"/>
+      <c r="F941" s="4" t="n"/>
+      <c r="G941" s="4" t="n"/>
+      <c r="H941" s="4" t="n"/>
+      <c r="I941" s="4" t="n"/>
+      <c r="J941" s="4" t="n"/>
+      <c r="K941" s="4" t="n"/>
+      <c r="L941" s="4" t="n"/>
+      <c r="M941" s="4" t="n"/>
+      <c r="N941" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O941" s="6" t="inlineStr">
+        <is>
+          <t>FROM MLGT JOIN MLGN ON MLGT.MATNR = MLGN.MATNR AND MLGT.LGNUM = MLGN.LGNUM</t>
+        </is>
+      </c>
+      <c r="P941" s="4" t="inlineStr">
+        <is>
+          <t>נתוני חומר לפי טיפוס אחסון</t>
+        </is>
+      </c>
+      <c r="Q941" s="4" t="inlineStr"/>
+      <c r="R941" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S941" s="4" t="inlineStr">
+        <is>
+          <t>A12</t>
+        </is>
+      </c>
+      <c r="T941" s="7">
+        <f>HYPERLINK("#'"&amp;R941&amp;"'!"&amp;S941,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" s="4" t="n"/>
+      <c r="B942" s="4" t="n"/>
+      <c r="C942" s="4" t="n"/>
+      <c r="D942" s="4" t="n"/>
+      <c r="E942" s="4" t="n"/>
+      <c r="F942" s="4" t="n"/>
+      <c r="G942" s="4" t="n"/>
+      <c r="H942" s="4" t="n"/>
+      <c r="I942" s="4" t="n"/>
+      <c r="J942" s="4" t="n"/>
+      <c r="K942" s="4" t="n"/>
+      <c r="L942" s="4" t="n"/>
+      <c r="M942" s="4" t="n"/>
+      <c r="N942" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O942" s="6" t="inlineStr">
+        <is>
+          <t>FROM MDMA JOIN MARC ON MDMA.MATNR = MARC.MATNR AND MDMA.WERKS = MARC.WERKS</t>
+        </is>
+      </c>
+      <c r="P942" s="4" t="inlineStr">
+        <is>
+          <t>אזורי MRP לחומר</t>
+        </is>
+      </c>
+      <c r="Q942" s="4" t="inlineStr"/>
+      <c r="R942" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S942" s="4" t="inlineStr">
+        <is>
+          <t>A13</t>
+        </is>
+      </c>
+      <c r="T942" s="7">
+        <f>HYPERLINK("#'"&amp;R942&amp;"'!"&amp;S942,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" s="4" t="n"/>
+      <c r="B943" s="4" t="n"/>
+      <c r="C943" s="4" t="n"/>
+      <c r="D943" s="4" t="n"/>
+      <c r="E943" s="4" t="n"/>
+      <c r="F943" s="4" t="n"/>
+      <c r="G943" s="4" t="n"/>
+      <c r="H943" s="4" t="n"/>
+      <c r="I943" s="4" t="n"/>
+      <c r="J943" s="4" t="n"/>
+      <c r="K943" s="4" t="n"/>
+      <c r="L943" s="4" t="n"/>
+      <c r="M943" s="4" t="n"/>
+      <c r="N943" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O943" s="6" t="inlineStr">
+        <is>
+          <t>FROM QMAT JOIN MARC ON QMAT.MATNR = MARC.MATNR AND QMAT.WERKS = MARC.WERKS</t>
+        </is>
+      </c>
+      <c r="P943" s="4" t="inlineStr">
+        <is>
+          <t>הגדרות בדיקת איכות לחומר</t>
+        </is>
+      </c>
+      <c r="Q943" s="4" t="inlineStr"/>
+      <c r="R943" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S943" s="4" t="inlineStr">
+        <is>
+          <t>A14</t>
+        </is>
+      </c>
+      <c r="T943" s="7">
+        <f>HYPERLINK("#'"&amp;R943&amp;"'!"&amp;S943,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" s="4" t="n"/>
+      <c r="B944" s="4" t="n"/>
+      <c r="C944" s="4" t="n"/>
+      <c r="D944" s="4" t="n"/>
+      <c r="E944" s="4" t="n"/>
+      <c r="F944" s="4" t="n"/>
+      <c r="G944" s="4" t="n"/>
+      <c r="H944" s="4" t="n"/>
+      <c r="I944" s="4" t="n"/>
+      <c r="J944" s="4" t="n"/>
+      <c r="K944" s="4" t="n"/>
+      <c r="L944" s="4" t="n"/>
+      <c r="M944" s="4" t="n"/>
+      <c r="N944" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O944" s="6" t="inlineStr">
+        <is>
+          <t>FROM MCH1 JOIN MARA ON MCH1.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P944" s="4" t="inlineStr">
+        <is>
+          <t>אצוות חומר (Batches)</t>
+        </is>
+      </c>
+      <c r="Q944" s="4" t="inlineStr"/>
+      <c r="R944" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S944" s="4" t="inlineStr">
+        <is>
+          <t>A15</t>
+        </is>
+      </c>
+      <c r="T944" s="7">
+        <f>HYPERLINK("#'"&amp;R944&amp;"'!"&amp;S944,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" s="4" t="n"/>
+      <c r="B945" s="4" t="n"/>
+      <c r="C945" s="4" t="n"/>
+      <c r="D945" s="4" t="n"/>
+      <c r="E945" s="4" t="n"/>
+      <c r="F945" s="4" t="n"/>
+      <c r="G945" s="4" t="n"/>
+      <c r="H945" s="4" t="n"/>
+      <c r="I945" s="4" t="n"/>
+      <c r="J945" s="4" t="n"/>
+      <c r="K945" s="4" t="n"/>
+      <c r="L945" s="4" t="n"/>
+      <c r="M945" s="4" t="n"/>
+      <c r="N945" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O945" s="6" t="inlineStr">
+        <is>
+          <t>FROM MCHA JOIN MCH1 ON MCHA.MATNR = MCH1.MATNR AND MCHA.CHARG = MCH1.CHARG</t>
+        </is>
+      </c>
+      <c r="P945" s="4" t="inlineStr">
+        <is>
+          <t>אצוות חומר ברמת מפעל</t>
+        </is>
+      </c>
+      <c r="Q945" s="4" t="inlineStr"/>
+      <c r="R945" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S945" s="4" t="inlineStr">
+        <is>
+          <t>A16</t>
+        </is>
+      </c>
+      <c r="T945" s="7">
+        <f>HYPERLINK("#'"&amp;R945&amp;"'!"&amp;S945,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" s="4" t="n"/>
+      <c r="B946" s="4" t="n"/>
+      <c r="C946" s="4" t="n"/>
+      <c r="D946" s="4" t="n"/>
+      <c r="E946" s="4" t="n"/>
+      <c r="F946" s="4" t="n"/>
+      <c r="G946" s="4" t="n"/>
+      <c r="H946" s="4" t="n"/>
+      <c r="I946" s="4" t="n"/>
+      <c r="J946" s="4" t="n"/>
+      <c r="K946" s="4" t="n"/>
+      <c r="L946" s="4" t="n"/>
+      <c r="M946" s="4" t="n"/>
+      <c r="N946" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O946" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARM JOIN T006 ON MARM.MEINH = T006.MSEHI</t>
+        </is>
+      </c>
+      <c r="P946" s="4" t="inlineStr">
+        <is>
+          <t>יחידות מידה (Customizing)</t>
+        </is>
+      </c>
+      <c r="Q946" s="4" t="inlineStr"/>
+      <c r="R946" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S946" s="4" t="inlineStr">
+        <is>
+          <t>A17</t>
+        </is>
+      </c>
+      <c r="T946" s="7">
+        <f>HYPERLINK("#'"&amp;R946&amp;"'!"&amp;S946,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" s="4" t="n"/>
+      <c r="B947" s="4" t="n"/>
+      <c r="C947" s="4" t="n"/>
+      <c r="D947" s="4" t="n"/>
+      <c r="E947" s="4" t="n"/>
+      <c r="F947" s="4" t="n"/>
+      <c r="G947" s="4" t="n"/>
+      <c r="H947" s="4" t="n"/>
+      <c r="I947" s="4" t="n"/>
+      <c r="J947" s="4" t="n"/>
+      <c r="K947" s="4" t="n"/>
+      <c r="L947" s="4" t="n"/>
+      <c r="M947" s="4" t="n"/>
+      <c r="N947" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O947" s="6" t="inlineStr">
+        <is>
+          <t>FROM MAST JOIN MARA ON MAST.MATNR = MARA.MATNR</t>
+        </is>
+      </c>
+      <c r="P947" s="4" t="inlineStr">
+        <is>
+          <t>קישור חומר לעץ מוצר</t>
+        </is>
+      </c>
+      <c r="Q947" s="4" t="inlineStr"/>
+      <c r="R947" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S947" s="4" t="inlineStr">
+        <is>
+          <t>A18</t>
+        </is>
+      </c>
+      <c r="T947" s="7">
+        <f>HYPERLINK("#'"&amp;R947&amp;"'!"&amp;S947,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" s="4" t="n"/>
+      <c r="B948" s="4" t="n"/>
+      <c r="C948" s="4" t="n"/>
+      <c r="D948" s="4" t="n"/>
+      <c r="E948" s="4" t="n"/>
+      <c r="F948" s="4" t="n"/>
+      <c r="G948" s="4" t="n"/>
+      <c r="H948" s="4" t="n"/>
+      <c r="I948" s="4" t="n"/>
+      <c r="J948" s="4" t="n"/>
+      <c r="K948" s="4" t="n"/>
+      <c r="L948" s="4" t="n"/>
+      <c r="M948" s="4" t="n"/>
+      <c r="N948" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O948" s="6" t="inlineStr">
+        <is>
+          <t>FROM STKO JOIN MAST ON STKO.STLNR = MAST.STLNR</t>
+        </is>
+      </c>
+      <c r="P948" s="4" t="inlineStr">
+        <is>
+          <t>כותרת עץ מוצר</t>
+        </is>
+      </c>
+      <c r="Q948" s="4" t="inlineStr"/>
+      <c r="R948" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S948" s="4" t="inlineStr">
+        <is>
+          <t>A19</t>
+        </is>
+      </c>
+      <c r="T948" s="7">
+        <f>HYPERLINK("#'"&amp;R948&amp;"'!"&amp;S948,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" s="4" t="n"/>
+      <c r="B949" s="4" t="n"/>
+      <c r="C949" s="4" t="n"/>
+      <c r="D949" s="4" t="n"/>
+      <c r="E949" s="4" t="n"/>
+      <c r="F949" s="4" t="n"/>
+      <c r="G949" s="4" t="n"/>
+      <c r="H949" s="4" t="n"/>
+      <c r="I949" s="4" t="n"/>
+      <c r="J949" s="4" t="n"/>
+      <c r="K949" s="4" t="n"/>
+      <c r="L949" s="4" t="n"/>
+      <c r="M949" s="4" t="n"/>
+      <c r="N949" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O949" s="6" t="inlineStr">
+        <is>
+          <t>FROM STPO JOIN STKO ON STPO.STLNR = STKO.STLNR AND STPO.STLTY = STKO.STLTY</t>
+        </is>
+      </c>
+      <c r="P949" s="4" t="inlineStr">
+        <is>
+          <t>פריטי עץ מוצר (רכיבים)</t>
+        </is>
+      </c>
+      <c r="Q949" s="4" t="inlineStr"/>
+      <c r="R949" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S949" s="4" t="inlineStr">
+        <is>
+          <t>A20</t>
+        </is>
+      </c>
+      <c r="T949" s="7">
+        <f>HYPERLINK("#'"&amp;R949&amp;"'!"&amp;S949,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" s="4" t="n"/>
+      <c r="B950" s="4" t="n"/>
+      <c r="C950" s="4" t="n"/>
+      <c r="D950" s="4" t="n"/>
+      <c r="E950" s="4" t="n"/>
+      <c r="F950" s="4" t="n"/>
+      <c r="G950" s="4" t="n"/>
+      <c r="H950" s="4" t="n"/>
+      <c r="I950" s="4" t="n"/>
+      <c r="J950" s="4" t="n"/>
+      <c r="K950" s="4" t="n"/>
+      <c r="L950" s="4" t="n"/>
+      <c r="M950" s="4" t="n"/>
+      <c r="N950" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O950" s="6" t="inlineStr">
+        <is>
+          <t>FROM STAS JOIN STKO ON STAS.STLNR = STKO.STLNR</t>
+        </is>
+      </c>
+      <c r="P950" s="4" t="inlineStr">
+        <is>
+          <t>בחירת פריטי עץ מוצר</t>
+        </is>
+      </c>
+      <c r="Q950" s="4" t="inlineStr"/>
+      <c r="R950" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S950" s="4" t="inlineStr">
+        <is>
+          <t>A21</t>
+        </is>
+      </c>
+      <c r="T950" s="7">
+        <f>HYPERLINK("#'"&amp;R950&amp;"'!"&amp;S950,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" s="4" t="n"/>
+      <c r="B951" s="4" t="n"/>
+      <c r="C951" s="4" t="n"/>
+      <c r="D951" s="4" t="n"/>
+      <c r="E951" s="4" t="n"/>
+      <c r="F951" s="4" t="n"/>
+      <c r="G951" s="4" t="n"/>
+      <c r="H951" s="4" t="n"/>
+      <c r="I951" s="4" t="n"/>
+      <c r="J951" s="4" t="n"/>
+      <c r="K951" s="4" t="n"/>
+      <c r="L951" s="4" t="n"/>
+      <c r="M951" s="4" t="n"/>
+      <c r="N951" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O951" s="6" t="inlineStr">
+        <is>
+          <t>FROM STZU JOIN STKO ON STZU.STLNR = STKO.STLNR</t>
+        </is>
+      </c>
+      <c r="P951" s="4" t="inlineStr">
+        <is>
+          <t>טבלת היסטוריה/קישור לעץ מוצר</t>
+        </is>
+      </c>
+      <c r="Q951" s="4" t="inlineStr"/>
+      <c r="R951" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S951" s="4" t="inlineStr">
+        <is>
+          <t>A22</t>
+        </is>
+      </c>
+      <c r="T951" s="7">
+        <f>HYPERLINK("#'"&amp;R951&amp;"'!"&amp;S951,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" s="4" t="n"/>
+      <c r="B952" s="4" t="n"/>
+      <c r="C952" s="4" t="n"/>
+      <c r="D952" s="4" t="n"/>
+      <c r="E952" s="4" t="n"/>
+      <c r="F952" s="4" t="n"/>
+      <c r="G952" s="4" t="n"/>
+      <c r="H952" s="4" t="n"/>
+      <c r="I952" s="4" t="n"/>
+      <c r="J952" s="4" t="n"/>
+      <c r="K952" s="4" t="n"/>
+      <c r="L952" s="4" t="n"/>
+      <c r="M952" s="4" t="n"/>
+      <c r="N952" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O952" s="6" t="inlineStr">
+        <is>
+          <t>FROM STPU JOIN STPO ON STPU.STLKN = STPO.STLKN</t>
+        </is>
+      </c>
+      <c r="P952" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים ארוכים לפריט עץ מוצר</t>
+        </is>
+      </c>
+      <c r="Q952" s="4" t="inlineStr"/>
+      <c r="R952" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S952" s="4" t="inlineStr">
+        <is>
+          <t>A23</t>
+        </is>
+      </c>
+      <c r="T952" s="7">
+        <f>HYPERLINK("#'"&amp;R952&amp;"'!"&amp;S952,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" s="4" t="n"/>
+      <c r="B953" s="4" t="n"/>
+      <c r="C953" s="4" t="n"/>
+      <c r="D953" s="4" t="n"/>
+      <c r="E953" s="4" t="n"/>
+      <c r="F953" s="4" t="n"/>
+      <c r="G953" s="4" t="n"/>
+      <c r="H953" s="4" t="n"/>
+      <c r="I953" s="4" t="n"/>
+      <c r="J953" s="4" t="n"/>
+      <c r="K953" s="4" t="n"/>
+      <c r="L953" s="4" t="n"/>
+      <c r="M953" s="4" t="n"/>
+      <c r="N953" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O953" s="6" t="inlineStr">
+        <is>
+          <t>FROM KDST JOIN MAST ON KDST.MATNR = MAST.MATNR</t>
+        </is>
+      </c>
+      <c r="P953" s="4" t="inlineStr">
+        <is>
+          <t>שימוש עץ מוצר בהזמנת לקוח</t>
+        </is>
+      </c>
+      <c r="Q953" s="4" t="inlineStr"/>
+      <c r="R953" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S953" s="4" t="inlineStr">
+        <is>
+          <t>A24</t>
+        </is>
+      </c>
+      <c r="T953" s="7">
+        <f>HYPERLINK("#'"&amp;R953&amp;"'!"&amp;S953,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" s="4" t="n"/>
+      <c r="B954" s="4" t="n"/>
+      <c r="C954" s="4" t="n"/>
+      <c r="D954" s="4" t="n"/>
+      <c r="E954" s="4" t="n"/>
+      <c r="F954" s="4" t="n"/>
+      <c r="G954" s="4" t="n"/>
+      <c r="H954" s="4" t="n"/>
+      <c r="I954" s="4" t="n"/>
+      <c r="J954" s="4" t="n"/>
+      <c r="K954" s="4" t="n"/>
+      <c r="L954" s="4" t="n"/>
+      <c r="M954" s="4" t="n"/>
+      <c r="N954" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O954" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLKO JOIN MAPL ON PLKO.PLNTY = MAPL.PLNTY AND PLKO.PLNNR = MAPL.PLNNR</t>
+        </is>
+      </c>
+      <c r="P954" s="4" t="inlineStr">
+        <is>
+          <t>כותרת מתכון ייצור / רשימת פעולות</t>
+        </is>
+      </c>
+      <c r="Q954" s="4" t="inlineStr"/>
+      <c r="R954" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S954" s="4" t="inlineStr">
+        <is>
+          <t>A25</t>
+        </is>
+      </c>
+      <c r="T954" s="7">
+        <f>HYPERLINK("#'"&amp;R954&amp;"'!"&amp;S954,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" s="4" t="n"/>
+      <c r="B955" s="4" t="n"/>
+      <c r="C955" s="4" t="n"/>
+      <c r="D955" s="4" t="n"/>
+      <c r="E955" s="4" t="n"/>
+      <c r="F955" s="4" t="n"/>
+      <c r="G955" s="4" t="n"/>
+      <c r="H955" s="4" t="n"/>
+      <c r="I955" s="4" t="n"/>
+      <c r="J955" s="4" t="n"/>
+      <c r="K955" s="4" t="n"/>
+      <c r="L955" s="4" t="n"/>
+      <c r="M955" s="4" t="n"/>
+      <c r="N955" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O955" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLPO JOIN PLAS ON PLPO.PLNTY = PLAS.PLNTY AND PLPO.PLNNR = PLAS.PLNNR AND PLPO.PLNKN = PLAS.PLNKN</t>
+        </is>
+      </c>
+      <c r="P955" s="4" t="inlineStr">
+        <is>
+          <t>פעולות/פאזות במתכון</t>
+        </is>
+      </c>
+      <c r="Q955" s="4" t="inlineStr"/>
+      <c r="R955" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S955" s="4" t="inlineStr">
+        <is>
+          <t>A26</t>
+        </is>
+      </c>
+      <c r="T955" s="7">
+        <f>HYPERLINK("#'"&amp;R955&amp;"'!"&amp;S955,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" s="4" t="n"/>
+      <c r="B956" s="4" t="n"/>
+      <c r="C956" s="4" t="n"/>
+      <c r="D956" s="4" t="n"/>
+      <c r="E956" s="4" t="n"/>
+      <c r="F956" s="4" t="n"/>
+      <c r="G956" s="4" t="n"/>
+      <c r="H956" s="4" t="n"/>
+      <c r="I956" s="4" t="n"/>
+      <c r="J956" s="4" t="n"/>
+      <c r="K956" s="4" t="n"/>
+      <c r="L956" s="4" t="n"/>
+      <c r="M956" s="4" t="n"/>
+      <c r="N956" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O956" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLAS JOIN PLKO ON PLAS.PLNTY = PLKO.PLNTY AND PLAS.PLNNR = PLKO.PLNNR</t>
+        </is>
+      </c>
+      <c r="P956" s="4" t="inlineStr">
+        <is>
+          <t>שיוך/בחירת פעולות לרשימה</t>
+        </is>
+      </c>
+      <c r="Q956" s="4" t="inlineStr"/>
+      <c r="R956" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S956" s="4" t="inlineStr">
+        <is>
+          <t>A27</t>
+        </is>
+      </c>
+      <c r="T956" s="7">
+        <f>HYPERLINK("#'"&amp;R956&amp;"'!"&amp;S956,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" s="4" t="n"/>
+      <c r="B957" s="4" t="n"/>
+      <c r="C957" s="4" t="n"/>
+      <c r="D957" s="4" t="n"/>
+      <c r="E957" s="4" t="n"/>
+      <c r="F957" s="4" t="n"/>
+      <c r="G957" s="4" t="n"/>
+      <c r="H957" s="4" t="n"/>
+      <c r="I957" s="4" t="n"/>
+      <c r="J957" s="4" t="n"/>
+      <c r="K957" s="4" t="n"/>
+      <c r="L957" s="4" t="n"/>
+      <c r="M957" s="4" t="n"/>
+      <c r="N957" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O957" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLFL JOIN PLKO ON PLFL.PLNNR = PLKO.PLNNR</t>
+        </is>
+      </c>
+      <c r="P957" s="4" t="inlineStr">
+        <is>
+          <t>רצפים במתכון</t>
+        </is>
+      </c>
+      <c r="Q957" s="4" t="inlineStr"/>
+      <c r="R957" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S957" s="4" t="inlineStr">
+        <is>
+          <t>A28</t>
+        </is>
+      </c>
+      <c r="T957" s="7">
+        <f>HYPERLINK("#'"&amp;R957&amp;"'!"&amp;S957,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" s="4" t="n"/>
+      <c r="B958" s="4" t="n"/>
+      <c r="C958" s="4" t="n"/>
+      <c r="D958" s="4" t="n"/>
+      <c r="E958" s="4" t="n"/>
+      <c r="F958" s="4" t="n"/>
+      <c r="G958" s="4" t="n"/>
+      <c r="H958" s="4" t="n"/>
+      <c r="I958" s="4" t="n"/>
+      <c r="J958" s="4" t="n"/>
+      <c r="K958" s="4" t="n"/>
+      <c r="L958" s="4" t="n"/>
+      <c r="M958" s="4" t="n"/>
+      <c r="N958" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O958" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLMZ JOIN PLPO ON PLMZ.PLNKN = PLPO.PLNKN</t>
+        </is>
+      </c>
+      <c r="P958" s="4" t="inlineStr">
+        <is>
+          <t>שיוך רכיבים לפעולות</t>
+        </is>
+      </c>
+      <c r="Q958" s="4" t="inlineStr"/>
+      <c r="R958" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S958" s="4" t="inlineStr">
+        <is>
+          <t>A29</t>
+        </is>
+      </c>
+      <c r="T958" s="7">
+        <f>HYPERLINK("#'"&amp;R958&amp;"'!"&amp;S958,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" s="4" t="n"/>
+      <c r="B959" s="4" t="n"/>
+      <c r="C959" s="4" t="n"/>
+      <c r="D959" s="4" t="n"/>
+      <c r="E959" s="4" t="n"/>
+      <c r="F959" s="4" t="n"/>
+      <c r="G959" s="4" t="n"/>
+      <c r="H959" s="4" t="n"/>
+      <c r="I959" s="4" t="n"/>
+      <c r="J959" s="4" t="n"/>
+      <c r="K959" s="4" t="n"/>
+      <c r="L959" s="4" t="n"/>
+      <c r="M959" s="4" t="n"/>
+      <c r="N959" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O959" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLMK JOIN PLPO ON PLMK.PLNKN = PLPO.PLNKN</t>
+        </is>
+      </c>
+      <c r="P959" s="4" t="inlineStr">
+        <is>
+          <t>מאפייני בדיקה במתכון</t>
+        </is>
+      </c>
+      <c r="Q959" s="4" t="inlineStr"/>
+      <c r="R959" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S959" s="4" t="inlineStr">
+        <is>
+          <t>A30</t>
+        </is>
+      </c>
+      <c r="T959" s="7">
+        <f>HYPERLINK("#'"&amp;R959&amp;"'!"&amp;S959,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" s="4" t="n"/>
+      <c r="B960" s="4" t="n"/>
+      <c r="C960" s="4" t="n"/>
+      <c r="D960" s="4" t="n"/>
+      <c r="E960" s="4" t="n"/>
+      <c r="F960" s="4" t="n"/>
+      <c r="G960" s="4" t="n"/>
+      <c r="H960" s="4" t="n"/>
+      <c r="I960" s="4" t="n"/>
+      <c r="J960" s="4" t="n"/>
+      <c r="K960" s="4" t="n"/>
+      <c r="L960" s="4" t="n"/>
+      <c r="M960" s="4" t="n"/>
+      <c r="N960" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O960" s="6" t="inlineStr">
+        <is>
+          <t>FROM MAPL JOIN MARC ON MAPL.MATNR = MARC.MATNR AND MAPL.WERKS = MARC.WERKS</t>
+        </is>
+      </c>
+      <c r="P960" s="4" t="inlineStr">
+        <is>
+          <t>שיוך חומר למתכון/רשימת פעולות</t>
+        </is>
+      </c>
+      <c r="Q960" s="4" t="inlineStr"/>
+      <c r="R960" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S960" s="4" t="inlineStr">
+        <is>
+          <t>A31</t>
+        </is>
+      </c>
+      <c r="T960" s="7">
+        <f>HYPERLINK("#'"&amp;R960&amp;"'!"&amp;S960,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" s="4" t="n"/>
+      <c r="B961" s="4" t="n"/>
+      <c r="C961" s="4" t="n"/>
+      <c r="D961" s="4" t="n"/>
+      <c r="E961" s="4" t="n"/>
+      <c r="F961" s="4" t="n"/>
+      <c r="G961" s="4" t="n"/>
+      <c r="H961" s="4" t="n"/>
+      <c r="I961" s="4" t="n"/>
+      <c r="J961" s="4" t="n"/>
+      <c r="K961" s="4" t="n"/>
+      <c r="L961" s="4" t="n"/>
+      <c r="M961" s="4" t="n"/>
+      <c r="N961" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O961" s="6" t="inlineStr">
+        <is>
+          <t>FROM FHMI JOIN PLPO ON FHMI.PLNKN = PLPO.PLNKN</t>
+        </is>
+      </c>
+      <c r="P961" s="4" t="inlineStr">
+        <is>
+          <t>שיוך כלי עזר ייצור (PRT) לפעולה</t>
+        </is>
+      </c>
+      <c r="Q961" s="4" t="inlineStr"/>
+      <c r="R961" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S961" s="4" t="inlineStr">
+        <is>
+          <t>A32</t>
+        </is>
+      </c>
+      <c r="T961" s="7">
+        <f>HYPERLINK("#'"&amp;R961&amp;"'!"&amp;S961,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" s="4" t="n"/>
+      <c r="B962" s="4" t="n"/>
+      <c r="C962" s="4" t="n"/>
+      <c r="D962" s="4" t="n"/>
+      <c r="E962" s="4" t="n"/>
+      <c r="F962" s="4" t="n"/>
+      <c r="G962" s="4" t="n"/>
+      <c r="H962" s="4" t="n"/>
+      <c r="I962" s="4" t="n"/>
+      <c r="J962" s="4" t="n"/>
+      <c r="K962" s="4" t="n"/>
+      <c r="L962" s="4" t="n"/>
+      <c r="M962" s="4" t="n"/>
+      <c r="N962" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O962" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLZU JOIN PLKO ON PLZU.PLNNR = PLKO.PLNNR</t>
+        </is>
+      </c>
+      <c r="P962" s="4" t="inlineStr">
+        <is>
+          <t>קישור היסטוריית רשימת פעולות</t>
+        </is>
+      </c>
+      <c r="Q962" s="4" t="inlineStr"/>
+      <c r="R962" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S962" s="4" t="inlineStr">
+        <is>
+          <t>A33</t>
+        </is>
+      </c>
+      <c r="T962" s="7">
+        <f>HYPERLINK("#'"&amp;R962&amp;"'!"&amp;S962,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" s="4" t="n"/>
+      <c r="B963" s="4" t="n"/>
+      <c r="C963" s="4" t="n"/>
+      <c r="D963" s="4" t="n"/>
+      <c r="E963" s="4" t="n"/>
+      <c r="F963" s="4" t="n"/>
+      <c r="G963" s="4" t="n"/>
+      <c r="H963" s="4" t="n"/>
+      <c r="I963" s="4" t="n"/>
+      <c r="J963" s="4" t="n"/>
+      <c r="K963" s="4" t="n"/>
+      <c r="L963" s="4" t="n"/>
+      <c r="M963" s="4" t="n"/>
+      <c r="N963" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O963" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLPO JOIN TC60 ON PLPO.STEUS = TC60.STEUS</t>
+        </is>
+      </c>
+      <c r="P963" s="4" t="inlineStr">
+        <is>
+          <t>מאפייני הוראות תהליך (PI)</t>
+        </is>
+      </c>
+      <c r="Q963" s="4" t="inlineStr"/>
+      <c r="R963" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S963" s="4" t="inlineStr">
+        <is>
+          <t>A34</t>
+        </is>
+      </c>
+      <c r="T963" s="7">
+        <f>HYPERLINK("#'"&amp;R963&amp;"'!"&amp;S963,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" s="4" t="n"/>
+      <c r="B964" s="4" t="n"/>
+      <c r="C964" s="4" t="n"/>
+      <c r="D964" s="4" t="n"/>
+      <c r="E964" s="4" t="n"/>
+      <c r="F964" s="4" t="n"/>
+      <c r="G964" s="4" t="n"/>
+      <c r="H964" s="4" t="n"/>
+      <c r="I964" s="4" t="n"/>
+      <c r="J964" s="4" t="n"/>
+      <c r="K964" s="4" t="n"/>
+      <c r="L964" s="4" t="n"/>
+      <c r="M964" s="4" t="n"/>
+      <c r="N964" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O964" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLKO JOIN TCA01 ON PLKO.PROFIDNETZ = TCA01.PROFIDNETZ</t>
+        </is>
+      </c>
+      <c r="P964" s="4" t="inlineStr">
+        <is>
+          <t>פרופיל רשימת פעולות (Customizing)</t>
+        </is>
+      </c>
+      <c r="Q964" s="4" t="inlineStr"/>
+      <c r="R964" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S964" s="4" t="inlineStr">
+        <is>
+          <t>A35</t>
+        </is>
+      </c>
+      <c r="T964" s="7">
+        <f>HYPERLINK("#'"&amp;R964&amp;"'!"&amp;S964,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" s="4" t="n"/>
+      <c r="B965" s="4" t="n"/>
+      <c r="C965" s="4" t="n"/>
+      <c r="D965" s="4" t="n"/>
+      <c r="E965" s="4" t="n"/>
+      <c r="F965" s="4" t="n"/>
+      <c r="G965" s="4" t="n"/>
+      <c r="H965" s="4" t="n"/>
+      <c r="I965" s="4" t="n"/>
+      <c r="J965" s="4" t="n"/>
+      <c r="K965" s="4" t="n"/>
+      <c r="L965" s="4" t="n"/>
+      <c r="M965" s="4" t="n"/>
+      <c r="N965" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O965" s="6" t="inlineStr">
+        <is>
+          <t>FROM MKAL JOIN MARC ON MKAL.MATNR = MARC.MATNR AND MKAL.WERKS = MARC.WERKS</t>
+        </is>
+      </c>
+      <c r="P965" s="4" t="inlineStr">
+        <is>
+          <t>גרסאות ייצור לחומר</t>
+        </is>
+      </c>
+      <c r="Q965" s="4" t="inlineStr"/>
+      <c r="R965" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S965" s="4" t="inlineStr">
+        <is>
+          <t>A36</t>
+        </is>
+      </c>
+      <c r="T965" s="7">
+        <f>HYPERLINK("#'"&amp;R965&amp;"'!"&amp;S965,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" s="4" t="n"/>
+      <c r="B966" s="4" t="n"/>
+      <c r="C966" s="4" t="n"/>
+      <c r="D966" s="4" t="n"/>
+      <c r="E966" s="4" t="n"/>
+      <c r="F966" s="4" t="n"/>
+      <c r="G966" s="4" t="n"/>
+      <c r="H966" s="4" t="n"/>
+      <c r="I966" s="4" t="n"/>
+      <c r="J966" s="4" t="n"/>
+      <c r="K966" s="4" t="n"/>
+      <c r="L966" s="4" t="n"/>
+      <c r="M966" s="4" t="n"/>
+      <c r="N966" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O966" s="6" t="inlineStr">
+        <is>
+          <t>FROM CRTX JOIN CRHD ON CRTX.OBJID = CRHD.OBJID AND CRTX.OBJTY = CRHD.OBJTY</t>
+        </is>
+      </c>
+      <c r="P966" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים של משאב</t>
+        </is>
+      </c>
+      <c r="Q966" s="4" t="inlineStr"/>
+      <c r="R966" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S966" s="4" t="inlineStr">
+        <is>
+          <t>A37</t>
+        </is>
+      </c>
+      <c r="T966" s="7">
+        <f>HYPERLINK("#'"&amp;R966&amp;"'!"&amp;S966,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" s="4" t="n"/>
+      <c r="B967" s="4" t="n"/>
+      <c r="C967" s="4" t="n"/>
+      <c r="D967" s="4" t="n"/>
+      <c r="E967" s="4" t="n"/>
+      <c r="F967" s="4" t="n"/>
+      <c r="G967" s="4" t="n"/>
+      <c r="H967" s="4" t="n"/>
+      <c r="I967" s="4" t="n"/>
+      <c r="J967" s="4" t="n"/>
+      <c r="K967" s="4" t="n"/>
+      <c r="L967" s="4" t="n"/>
+      <c r="M967" s="4" t="n"/>
+      <c r="N967" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O967" s="6" t="inlineStr">
+        <is>
+          <t>FROM CRCO JOIN CRHD ON CRCO.OBJID = CRHD.OBJID AND CRCO.OBJTY = CRHD.OBJTY</t>
+        </is>
+      </c>
+      <c r="P967" s="4" t="inlineStr">
+        <is>
+          <t>שיוך משאב למרכז עלות</t>
+        </is>
+      </c>
+      <c r="Q967" s="4" t="inlineStr"/>
+      <c r="R967" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S967" s="4" t="inlineStr">
+        <is>
+          <t>A38</t>
+        </is>
+      </c>
+      <c r="T967" s="7">
+        <f>HYPERLINK("#'"&amp;R967&amp;"'!"&amp;S967,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" s="4" t="n"/>
+      <c r="B968" s="4" t="n"/>
+      <c r="C968" s="4" t="n"/>
+      <c r="D968" s="4" t="n"/>
+      <c r="E968" s="4" t="n"/>
+      <c r="F968" s="4" t="n"/>
+      <c r="G968" s="4" t="n"/>
+      <c r="H968" s="4" t="n"/>
+      <c r="I968" s="4" t="n"/>
+      <c r="J968" s="4" t="n"/>
+      <c r="K968" s="4" t="n"/>
+      <c r="L968" s="4" t="n"/>
+      <c r="M968" s="4" t="n"/>
+      <c r="N968" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O968" s="6" t="inlineStr">
+        <is>
+          <t>FROM CRCA JOIN CRHD ON CRCA.OBJID = CRHD.OBJID AND CRCA.OBJTY = CRHD.OBJTY</t>
+        </is>
+      </c>
+      <c r="P968" s="4" t="inlineStr">
+        <is>
+          <t>הקצאת קיבולת למשאב</t>
+        </is>
+      </c>
+      <c r="Q968" s="4" t="inlineStr"/>
+      <c r="R968" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S968" s="4" t="inlineStr">
+        <is>
+          <t>A39</t>
+        </is>
+      </c>
+      <c r="T968" s="7">
+        <f>HYPERLINK("#'"&amp;R968&amp;"'!"&amp;S968,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" s="4" t="n"/>
+      <c r="B969" s="4" t="n"/>
+      <c r="C969" s="4" t="n"/>
+      <c r="D969" s="4" t="n"/>
+      <c r="E969" s="4" t="n"/>
+      <c r="F969" s="4" t="n"/>
+      <c r="G969" s="4" t="n"/>
+      <c r="H969" s="4" t="n"/>
+      <c r="I969" s="4" t="n"/>
+      <c r="J969" s="4" t="n"/>
+      <c r="K969" s="4" t="n"/>
+      <c r="L969" s="4" t="n"/>
+      <c r="M969" s="4" t="n"/>
+      <c r="N969" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O969" s="6" t="inlineStr">
+        <is>
+          <t>FROM KAKO JOIN CRCA ON KAKO.KAPID = CRCA.KAPID</t>
+        </is>
+      </c>
+      <c r="P969" s="4" t="inlineStr">
+        <is>
+          <t>כותרת קיבולת</t>
+        </is>
+      </c>
+      <c r="Q969" s="4" t="inlineStr"/>
+      <c r="R969" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S969" s="4" t="inlineStr">
+        <is>
+          <t>A40</t>
+        </is>
+      </c>
+      <c r="T969" s="7">
+        <f>HYPERLINK("#'"&amp;R969&amp;"'!"&amp;S969,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="970">
+      <c r="A970" s="4" t="n"/>
+      <c r="B970" s="4" t="n"/>
+      <c r="C970" s="4" t="n"/>
+      <c r="D970" s="4" t="n"/>
+      <c r="E970" s="4" t="n"/>
+      <c r="F970" s="4" t="n"/>
+      <c r="G970" s="4" t="n"/>
+      <c r="H970" s="4" t="n"/>
+      <c r="I970" s="4" t="n"/>
+      <c r="J970" s="4" t="n"/>
+      <c r="K970" s="4" t="n"/>
+      <c r="L970" s="4" t="n"/>
+      <c r="M970" s="4" t="n"/>
+      <c r="N970" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O970" s="6" t="inlineStr">
+        <is>
+          <t>FROM FHMI JOIN CRFH ON FHMI.FHMNR = CRFH.FHMNR</t>
+        </is>
+      </c>
+      <c r="P970" s="4" t="inlineStr">
+        <is>
+          <t>אב כלי עזר ייצור (PRT)</t>
+        </is>
+      </c>
+      <c r="Q970" s="4" t="inlineStr"/>
+      <c r="R970" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S970" s="4" t="inlineStr">
+        <is>
+          <t>A41</t>
+        </is>
+      </c>
+      <c r="T970" s="7">
+        <f>HYPERLINK("#'"&amp;R970&amp;"'!"&amp;S970,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="971">
+      <c r="A971" s="4" t="n"/>
+      <c r="B971" s="4" t="n"/>
+      <c r="C971" s="4" t="n"/>
+      <c r="D971" s="4" t="n"/>
+      <c r="E971" s="4" t="n"/>
+      <c r="F971" s="4" t="n"/>
+      <c r="G971" s="4" t="n"/>
+      <c r="H971" s="4" t="n"/>
+      <c r="I971" s="4" t="n"/>
+      <c r="J971" s="4" t="n"/>
+      <c r="K971" s="4" t="n"/>
+      <c r="L971" s="4" t="n"/>
+      <c r="M971" s="4" t="n"/>
+      <c r="N971" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O971" s="6" t="inlineStr">
+        <is>
+          <t>FROM CRVD_A JOIN CRHD ON CRVD_A.OBJID = CRHD.OBJID</t>
+        </is>
+      </c>
+      <c r="P971" s="4" t="inlineStr">
+        <is>
+          <t>ברירות מחדל למשאב (PI)</t>
+        </is>
+      </c>
+      <c r="Q971" s="4" t="inlineStr"/>
+      <c r="R971" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S971" s="4" t="inlineStr">
+        <is>
+          <t>A42</t>
+        </is>
+      </c>
+      <c r="T971" s="7">
+        <f>HYPERLINK("#'"&amp;R971&amp;"'!"&amp;S971,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="972">
+      <c r="A972" s="4" t="n"/>
+      <c r="B972" s="4" t="n"/>
+      <c r="C972" s="4" t="n"/>
+      <c r="D972" s="4" t="n"/>
+      <c r="E972" s="4" t="n"/>
+      <c r="F972" s="4" t="n"/>
+      <c r="G972" s="4" t="n"/>
+      <c r="H972" s="4" t="n"/>
+      <c r="I972" s="4" t="n"/>
+      <c r="J972" s="4" t="n"/>
+      <c r="K972" s="4" t="n"/>
+      <c r="L972" s="4" t="n"/>
+      <c r="M972" s="4" t="n"/>
+      <c r="N972" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O972" s="6" t="inlineStr">
+        <is>
+          <t>FROM CSLA JOIN CRCO ON CSLA.LSTAR = CRCO.LSTAR</t>
+        </is>
+      </c>
+      <c r="P972" s="4" t="inlineStr">
+        <is>
+          <t>סוגי פעילות למרכז עבודה</t>
+        </is>
+      </c>
+      <c r="Q972" s="4" t="inlineStr"/>
+      <c r="R972" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S972" s="4" t="inlineStr">
+        <is>
+          <t>A43</t>
+        </is>
+      </c>
+      <c r="T972" s="7">
+        <f>HYPERLINK("#'"&amp;R972&amp;"'!"&amp;S972,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="973">
+      <c r="A973" s="4" t="n"/>
+      <c r="B973" s="4" t="n"/>
+      <c r="C973" s="4" t="n"/>
+      <c r="D973" s="4" t="n"/>
+      <c r="E973" s="4" t="n"/>
+      <c r="F973" s="4" t="n"/>
+      <c r="G973" s="4" t="n"/>
+      <c r="H973" s="4" t="n"/>
+      <c r="I973" s="4" t="n"/>
+      <c r="J973" s="4" t="n"/>
+      <c r="K973" s="4" t="n"/>
+      <c r="L973" s="4" t="n"/>
+      <c r="M973" s="4" t="n"/>
+      <c r="N973" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O973" s="6" t="inlineStr">
+        <is>
+          <t>FROM KAZT JOIN KAKO ON KAZT.KAPID = KAKO.KAPID</t>
+        </is>
+      </c>
+      <c r="P973" s="4" t="inlineStr">
+        <is>
+          <t>מרווחי קיבולת זמינה</t>
+        </is>
+      </c>
+      <c r="Q973" s="4" t="inlineStr"/>
+      <c r="R973" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S973" s="4" t="inlineStr">
+        <is>
+          <t>A44</t>
+        </is>
+      </c>
+      <c r="T973" s="7">
+        <f>HYPERLINK("#'"&amp;R973&amp;"'!"&amp;S973,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" s="4" t="n"/>
+      <c r="B974" s="4" t="n"/>
+      <c r="C974" s="4" t="n"/>
+      <c r="D974" s="4" t="n"/>
+      <c r="E974" s="4" t="n"/>
+      <c r="F974" s="4" t="n"/>
+      <c r="G974" s="4" t="n"/>
+      <c r="H974" s="4" t="n"/>
+      <c r="I974" s="4" t="n"/>
+      <c r="J974" s="4" t="n"/>
+      <c r="K974" s="4" t="n"/>
+      <c r="L974" s="4" t="n"/>
+      <c r="M974" s="4" t="n"/>
+      <c r="N974" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O974" s="6" t="inlineStr">
+        <is>
+          <t>FROM AFKO JOIN AUFK ON AFKO.AUFNR = AUFK.AUFNR</t>
+        </is>
+      </c>
+      <c r="P974" s="4" t="inlineStr">
+        <is>
+          <t>כותרת פקודת ייצור</t>
+        </is>
+      </c>
+      <c r="Q974" s="4" t="inlineStr"/>
+      <c r="R974" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S974" s="4" t="inlineStr">
+        <is>
+          <t>A45</t>
+        </is>
+      </c>
+      <c r="T974" s="7">
+        <f>HYPERLINK("#'"&amp;R974&amp;"'!"&amp;S974,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" s="4" t="n"/>
+      <c r="B975" s="4" t="n"/>
+      <c r="C975" s="4" t="n"/>
+      <c r="D975" s="4" t="n"/>
+      <c r="E975" s="4" t="n"/>
+      <c r="F975" s="4" t="n"/>
+      <c r="G975" s="4" t="n"/>
+      <c r="H975" s="4" t="n"/>
+      <c r="I975" s="4" t="n"/>
+      <c r="J975" s="4" t="n"/>
+      <c r="K975" s="4" t="n"/>
+      <c r="L975" s="4" t="n"/>
+      <c r="M975" s="4" t="n"/>
+      <c r="N975" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O975" s="6" t="inlineStr">
+        <is>
+          <t>FROM AFPO JOIN AFKO ON AFPO.AUFNR = AFKO.AUFNR</t>
+        </is>
+      </c>
+      <c r="P975" s="4" t="inlineStr">
+        <is>
+          <t>פריט פקודת ייצור</t>
+        </is>
+      </c>
+      <c r="Q975" s="4" t="inlineStr"/>
+      <c r="R975" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S975" s="4" t="inlineStr">
+        <is>
+          <t>A46</t>
+        </is>
+      </c>
+      <c r="T975" s="7">
+        <f>HYPERLINK("#'"&amp;R975&amp;"'!"&amp;S975,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" s="4" t="n"/>
+      <c r="B976" s="4" t="n"/>
+      <c r="C976" s="4" t="n"/>
+      <c r="D976" s="4" t="n"/>
+      <c r="E976" s="4" t="n"/>
+      <c r="F976" s="4" t="n"/>
+      <c r="G976" s="4" t="n"/>
+      <c r="H976" s="4" t="n"/>
+      <c r="I976" s="4" t="n"/>
+      <c r="J976" s="4" t="n"/>
+      <c r="K976" s="4" t="n"/>
+      <c r="L976" s="4" t="n"/>
+      <c r="M976" s="4" t="n"/>
+      <c r="N976" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O976" s="6" t="inlineStr">
+        <is>
+          <t>FROM AFVC JOIN AFKO ON AFVC.AUFPL = AFKO.AUFPL</t>
+        </is>
+      </c>
+      <c r="P976" s="4" t="inlineStr">
+        <is>
+          <t>פעולות פקודת הייצור</t>
+        </is>
+      </c>
+      <c r="Q976" s="4" t="inlineStr"/>
+      <c r="R976" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S976" s="4" t="inlineStr">
+        <is>
+          <t>A47</t>
+        </is>
+      </c>
+      <c r="T976" s="7">
+        <f>HYPERLINK("#'"&amp;R976&amp;"'!"&amp;S976,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" s="4" t="n"/>
+      <c r="B977" s="4" t="n"/>
+      <c r="C977" s="4" t="n"/>
+      <c r="D977" s="4" t="n"/>
+      <c r="E977" s="4" t="n"/>
+      <c r="F977" s="4" t="n"/>
+      <c r="G977" s="4" t="n"/>
+      <c r="H977" s="4" t="n"/>
+      <c r="I977" s="4" t="n"/>
+      <c r="J977" s="4" t="n"/>
+      <c r="K977" s="4" t="n"/>
+      <c r="L977" s="4" t="n"/>
+      <c r="M977" s="4" t="n"/>
+      <c r="N977" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O977" s="6" t="inlineStr">
+        <is>
+          <t>FROM RESB JOIN AFKO ON RESB.AUFNR = AFKO.AUFNR</t>
+        </is>
+      </c>
+      <c r="P977" s="4" t="inlineStr">
+        <is>
+          <t>הזמנת רכיבים לפק"ע</t>
+        </is>
+      </c>
+      <c r="Q977" s="4" t="inlineStr"/>
+      <c r="R977" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S977" s="4" t="inlineStr">
+        <is>
+          <t>A48</t>
+        </is>
+      </c>
+      <c r="T977" s="7">
+        <f>HYPERLINK("#'"&amp;R977&amp;"'!"&amp;S977,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="978">
+      <c r="A978" s="4" t="n"/>
+      <c r="B978" s="4" t="n"/>
+      <c r="C978" s="4" t="n"/>
+      <c r="D978" s="4" t="n"/>
+      <c r="E978" s="4" t="n"/>
+      <c r="F978" s="4" t="n"/>
+      <c r="G978" s="4" t="n"/>
+      <c r="H978" s="4" t="n"/>
+      <c r="I978" s="4" t="n"/>
+      <c r="J978" s="4" t="n"/>
+      <c r="K978" s="4" t="n"/>
+      <c r="L978" s="4" t="n"/>
+      <c r="M978" s="4" t="n"/>
+      <c r="N978" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O978" s="6" t="inlineStr">
+        <is>
+          <t>FROM AFRU JOIN AFKO ON AFRU.AUFNR = AFKO.AUFNR</t>
+        </is>
+      </c>
+      <c r="P978" s="4" t="inlineStr">
+        <is>
+          <t>דיווחי ביצוע פק"ע</t>
+        </is>
+      </c>
+      <c r="Q978" s="4" t="inlineStr"/>
+      <c r="R978" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S978" s="4" t="inlineStr">
+        <is>
+          <t>A49</t>
+        </is>
+      </c>
+      <c r="T978" s="7">
+        <f>HYPERLINK("#'"&amp;R978&amp;"'!"&amp;S978,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" s="4" t="n"/>
+      <c r="B979" s="4" t="n"/>
+      <c r="C979" s="4" t="n"/>
+      <c r="D979" s="4" t="n"/>
+      <c r="E979" s="4" t="n"/>
+      <c r="F979" s="4" t="n"/>
+      <c r="G979" s="4" t="n"/>
+      <c r="H979" s="4" t="n"/>
+      <c r="I979" s="4" t="n"/>
+      <c r="J979" s="4" t="n"/>
+      <c r="K979" s="4" t="n"/>
+      <c r="L979" s="4" t="n"/>
+      <c r="M979" s="4" t="n"/>
+      <c r="N979" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O979" s="6" t="inlineStr">
+        <is>
+          <t>FROM AFFH JOIN AFKO ON AFFH.AUFPL = AFKO.AUFPL</t>
+        </is>
+      </c>
+      <c r="P979" s="4" t="inlineStr">
+        <is>
+          <t>שיוך PRT לפק"ע</t>
+        </is>
+      </c>
+      <c r="Q979" s="4" t="inlineStr"/>
+      <c r="R979" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S979" s="4" t="inlineStr">
+        <is>
+          <t>A50</t>
+        </is>
+      </c>
+      <c r="T979" s="7">
+        <f>HYPERLINK("#'"&amp;R979&amp;"'!"&amp;S979,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="980">
+      <c r="A980" s="4" t="n"/>
+      <c r="B980" s="4" t="n"/>
+      <c r="C980" s="4" t="n"/>
+      <c r="D980" s="4" t="n"/>
+      <c r="E980" s="4" t="n"/>
+      <c r="F980" s="4" t="n"/>
+      <c r="G980" s="4" t="n"/>
+      <c r="H980" s="4" t="n"/>
+      <c r="I980" s="4" t="n"/>
+      <c r="J980" s="4" t="n"/>
+      <c r="K980" s="4" t="n"/>
+      <c r="L980" s="4" t="n"/>
+      <c r="M980" s="4" t="n"/>
+      <c r="N980" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O980" s="6" t="inlineStr">
+        <is>
+          <t>FROM AFFL JOIN AFKO ON AFFL.AUFPL = AFKO.AUFPL</t>
+        </is>
+      </c>
+      <c r="P980" s="4" t="inlineStr">
+        <is>
+          <t>רצפי פעולות בפק"ע</t>
+        </is>
+      </c>
+      <c r="Q980" s="4" t="inlineStr"/>
+      <c r="R980" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S980" s="4" t="inlineStr">
+        <is>
+          <t>A51</t>
+        </is>
+      </c>
+      <c r="T980" s="7">
+        <f>HYPERLINK("#'"&amp;R980&amp;"'!"&amp;S980,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" s="4" t="n"/>
+      <c r="B981" s="4" t="n"/>
+      <c r="C981" s="4" t="n"/>
+      <c r="D981" s="4" t="n"/>
+      <c r="E981" s="4" t="n"/>
+      <c r="F981" s="4" t="n"/>
+      <c r="G981" s="4" t="n"/>
+      <c r="H981" s="4" t="n"/>
+      <c r="I981" s="4" t="n"/>
+      <c r="J981" s="4" t="n"/>
+      <c r="K981" s="4" t="n"/>
+      <c r="L981" s="4" t="n"/>
+      <c r="M981" s="4" t="n"/>
+      <c r="N981" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O981" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARA JOIN T134 ON MARA.MTART = T134.MTART</t>
+        </is>
+      </c>
+      <c r="P981" s="4" t="inlineStr">
+        <is>
+          <t>סוגי חומר (Customizing)</t>
+        </is>
+      </c>
+      <c r="Q981" s="4" t="inlineStr"/>
+      <c r="R981" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S981" s="4" t="inlineStr">
+        <is>
+          <t>A52</t>
+        </is>
+      </c>
+      <c r="T981" s="7">
+        <f>HYPERLINK("#'"&amp;R981&amp;"'!"&amp;S981,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="982">
+      <c r="A982" s="4" t="n"/>
+      <c r="B982" s="4" t="n"/>
+      <c r="C982" s="4" t="n"/>
+      <c r="D982" s="4" t="n"/>
+      <c r="E982" s="4" t="n"/>
+      <c r="F982" s="4" t="n"/>
+      <c r="G982" s="4" t="n"/>
+      <c r="H982" s="4" t="n"/>
+      <c r="I982" s="4" t="n"/>
+      <c r="J982" s="4" t="n"/>
+      <c r="K982" s="4" t="n"/>
+      <c r="L982" s="4" t="n"/>
+      <c r="M982" s="4" t="n"/>
+      <c r="N982" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O982" s="6" t="inlineStr">
+        <is>
+          <t>FROM T134T JOIN T134 ON T134T.MTART = T134.MTART</t>
+        </is>
+      </c>
+      <c r="P982" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים לסוגי חומר</t>
+        </is>
+      </c>
+      <c r="Q982" s="4" t="inlineStr"/>
+      <c r="R982" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S982" s="4" t="inlineStr">
+        <is>
+          <t>A53</t>
+        </is>
+      </c>
+      <c r="T982" s="7">
+        <f>HYPERLINK("#'"&amp;R982&amp;"'!"&amp;S982,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="983">
+      <c r="A983" s="4" t="n"/>
+      <c r="B983" s="4" t="n"/>
+      <c r="C983" s="4" t="n"/>
+      <c r="D983" s="4" t="n"/>
+      <c r="E983" s="4" t="n"/>
+      <c r="F983" s="4" t="n"/>
+      <c r="G983" s="4" t="n"/>
+      <c r="H983" s="4" t="n"/>
+      <c r="I983" s="4" t="n"/>
+      <c r="J983" s="4" t="n"/>
+      <c r="K983" s="4" t="n"/>
+      <c r="L983" s="4" t="n"/>
+      <c r="M983" s="4" t="n"/>
+      <c r="N983" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O983" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARA JOIN T023 ON MARA.MATKL = T023.MATKL</t>
+        </is>
+      </c>
+      <c r="P983" s="4" t="inlineStr">
+        <is>
+          <t>קבוצות חומר (Customizing)</t>
+        </is>
+      </c>
+      <c r="Q983" s="4" t="inlineStr"/>
+      <c r="R983" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S983" s="4" t="inlineStr">
+        <is>
+          <t>A54</t>
+        </is>
+      </c>
+      <c r="T983" s="7">
+        <f>HYPERLINK("#'"&amp;R983&amp;"'!"&amp;S983,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" s="4" t="n"/>
+      <c r="B984" s="4" t="n"/>
+      <c r="C984" s="4" t="n"/>
+      <c r="D984" s="4" t="n"/>
+      <c r="E984" s="4" t="n"/>
+      <c r="F984" s="4" t="n"/>
+      <c r="G984" s="4" t="n"/>
+      <c r="H984" s="4" t="n"/>
+      <c r="I984" s="4" t="n"/>
+      <c r="J984" s="4" t="n"/>
+      <c r="K984" s="4" t="n"/>
+      <c r="L984" s="4" t="n"/>
+      <c r="M984" s="4" t="n"/>
+      <c r="N984" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O984" s="6" t="inlineStr">
+        <is>
+          <t>FROM T023T JOIN T023 ON T023T.MATKL = T023.MATKL</t>
+        </is>
+      </c>
+      <c r="P984" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים לקבוצות חומר</t>
+        </is>
+      </c>
+      <c r="Q984" s="4" t="inlineStr"/>
+      <c r="R984" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S984" s="4" t="inlineStr">
+        <is>
+          <t>A55</t>
+        </is>
+      </c>
+      <c r="T984" s="7">
+        <f>HYPERLINK("#'"&amp;R984&amp;"'!"&amp;S984,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="985">
+      <c r="A985" s="4" t="n"/>
+      <c r="B985" s="4" t="n"/>
+      <c r="C985" s="4" t="n"/>
+      <c r="D985" s="4" t="n"/>
+      <c r="E985" s="4" t="n"/>
+      <c r="F985" s="4" t="n"/>
+      <c r="G985" s="4" t="n"/>
+      <c r="H985" s="4" t="n"/>
+      <c r="I985" s="4" t="n"/>
+      <c r="J985" s="4" t="n"/>
+      <c r="K985" s="4" t="n"/>
+      <c r="L985" s="4" t="n"/>
+      <c r="M985" s="4" t="n"/>
+      <c r="N985" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O985" s="6" t="inlineStr">
+        <is>
+          <t>FROM AUFK JOIN T399X ON AUFK.WERKS = T399X.WERKS AND AUFK.AUART = T399X.AUART</t>
+        </is>
+      </c>
+      <c r="P985" s="4" t="inlineStr">
+        <is>
+          <t>פרמטרי בקרת ייצור למפעל</t>
+        </is>
+      </c>
+      <c r="Q985" s="4" t="inlineStr"/>
+      <c r="R985" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S985" s="4" t="inlineStr">
+        <is>
+          <t>A56</t>
+        </is>
+      </c>
+      <c r="T985" s="7">
+        <f>HYPERLINK("#'"&amp;R985&amp;"'!"&amp;S985,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="986">
+      <c r="A986" s="4" t="n"/>
+      <c r="B986" s="4" t="n"/>
+      <c r="C986" s="4" t="n"/>
+      <c r="D986" s="4" t="n"/>
+      <c r="E986" s="4" t="n"/>
+      <c r="F986" s="4" t="n"/>
+      <c r="G986" s="4" t="n"/>
+      <c r="H986" s="4" t="n"/>
+      <c r="I986" s="4" t="n"/>
+      <c r="J986" s="4" t="n"/>
+      <c r="K986" s="4" t="n"/>
+      <c r="L986" s="4" t="n"/>
+      <c r="M986" s="4" t="n"/>
+      <c r="N986" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O986" s="6" t="inlineStr">
+        <is>
+          <t>FROM T399X JOIN TCK03 ON T399X.KLVARP = TCK03.KLVAR</t>
+        </is>
+      </c>
+      <c r="P986" s="4" t="inlineStr">
+        <is>
+          <t>וריאנט תמחיר (Costing Variant)</t>
+        </is>
+      </c>
+      <c r="Q986" s="4" t="inlineStr"/>
+      <c r="R986" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S986" s="4" t="inlineStr">
+        <is>
+          <t>A57</t>
+        </is>
+      </c>
+      <c r="T986" s="7">
+        <f>HYPERLINK("#'"&amp;R986&amp;"'!"&amp;S986,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="987">
+      <c r="A987" s="4" t="n"/>
+      <c r="B987" s="4" t="n"/>
+      <c r="C987" s="4" t="n"/>
+      <c r="D987" s="4" t="n"/>
+      <c r="E987" s="4" t="n"/>
+      <c r="F987" s="4" t="n"/>
+      <c r="G987" s="4" t="n"/>
+      <c r="H987" s="4" t="n"/>
+      <c r="I987" s="4" t="n"/>
+      <c r="J987" s="4" t="n"/>
+      <c r="K987" s="4" t="n"/>
+      <c r="L987" s="4" t="n"/>
+      <c r="M987" s="4" t="n"/>
+      <c r="N987" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O987" s="6" t="inlineStr">
+        <is>
+          <t>FROM MARC JOIN T438M ON MARC.DISMM = T438M.DISMM</t>
+        </is>
+      </c>
+      <c r="P987" s="4" t="inlineStr">
+        <is>
+          <t>פרמטרי MRP לחומר/מפעל</t>
+        </is>
+      </c>
+      <c r="Q987" s="4" t="inlineStr"/>
+      <c r="R987" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S987" s="4" t="inlineStr">
+        <is>
+          <t>A58</t>
+        </is>
+      </c>
+      <c r="T987" s="7">
+        <f>HYPERLINK("#'"&amp;R987&amp;"'!"&amp;S987,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="988">
+      <c r="A988" s="4" t="n"/>
+      <c r="B988" s="4" t="n"/>
+      <c r="C988" s="4" t="n"/>
+      <c r="D988" s="4" t="n"/>
+      <c r="E988" s="4" t="n"/>
+      <c r="F988" s="4" t="n"/>
+      <c r="G988" s="4" t="n"/>
+      <c r="H988" s="4" t="n"/>
+      <c r="I988" s="4" t="n"/>
+      <c r="J988" s="4" t="n"/>
+      <c r="K988" s="4" t="n"/>
+      <c r="L988" s="4" t="n"/>
+      <c r="M988" s="4" t="n"/>
+      <c r="N988" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O988" s="6" t="inlineStr">
+        <is>
+          <t>FROM AUFK JOIN T003O ON AUFK.AUART = T003O.AUART</t>
+        </is>
+      </c>
+      <c r="P988" s="4" t="inlineStr">
+        <is>
+          <t>סוגי פקודת ייצור (Process Order Types)</t>
+        </is>
+      </c>
+      <c r="Q988" s="4" t="inlineStr"/>
+      <c r="R988" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S988" s="4" t="inlineStr">
+        <is>
+          <t>A59</t>
+        </is>
+      </c>
+      <c r="T988" s="7">
+        <f>HYPERLINK("#'"&amp;R988&amp;"'!"&amp;S988,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="989">
+      <c r="A989" s="4" t="n"/>
+      <c r="B989" s="4" t="n"/>
+      <c r="C989" s="4" t="n"/>
+      <c r="D989" s="4" t="n"/>
+      <c r="E989" s="4" t="n"/>
+      <c r="F989" s="4" t="n"/>
+      <c r="G989" s="4" t="n"/>
+      <c r="H989" s="4" t="n"/>
+      <c r="I989" s="4" t="n"/>
+      <c r="J989" s="4" t="n"/>
+      <c r="K989" s="4" t="n"/>
+      <c r="L989" s="4" t="n"/>
+      <c r="M989" s="4" t="n"/>
+      <c r="N989" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O989" s="6" t="inlineStr">
+        <is>
+          <t>FROM TCO01 JOIN T003O ON TCO01.AUART = T003O.AUART</t>
+        </is>
+      </c>
+      <c r="P989" s="4" t="inlineStr">
+        <is>
+          <t>פרמטרים תלויי סוג פק"ע (Order Profile)</t>
+        </is>
+      </c>
+      <c r="Q989" s="4" t="inlineStr"/>
+      <c r="R989" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S989" s="4" t="inlineStr">
+        <is>
+          <t>A60</t>
+        </is>
+      </c>
+      <c r="T989" s="7">
+        <f>HYPERLINK("#'"&amp;R989&amp;"'!"&amp;S989,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="990">
+      <c r="A990" s="4" t="n"/>
+      <c r="B990" s="4" t="n"/>
+      <c r="C990" s="4" t="n"/>
+      <c r="D990" s="4" t="n"/>
+      <c r="E990" s="4" t="n"/>
+      <c r="F990" s="4" t="n"/>
+      <c r="G990" s="4" t="n"/>
+      <c r="H990" s="4" t="n"/>
+      <c r="I990" s="4" t="n"/>
+      <c r="J990" s="4" t="n"/>
+      <c r="K990" s="4" t="n"/>
+      <c r="L990" s="4" t="n"/>
+      <c r="M990" s="4" t="n"/>
+      <c r="N990" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O990" s="6" t="inlineStr">
+        <is>
+          <t>FROM JEST JOIN TJ30 ON JEST.STAT = TJ30.ESTAT</t>
+        </is>
+      </c>
+      <c r="P990" s="4" t="inlineStr">
+        <is>
+          <t>סטטוסי משתמש בפרופיל (User Status)</t>
+        </is>
+      </c>
+      <c r="Q990" s="4" t="inlineStr"/>
+      <c r="R990" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S990" s="4" t="inlineStr">
+        <is>
+          <t>A61</t>
+        </is>
+      </c>
+      <c r="T990" s="7">
+        <f>HYPERLINK("#'"&amp;R990&amp;"'!"&amp;S990,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="991">
+      <c r="A991" s="4" t="n"/>
+      <c r="B991" s="4" t="n"/>
+      <c r="C991" s="4" t="n"/>
+      <c r="D991" s="4" t="n"/>
+      <c r="E991" s="4" t="n"/>
+      <c r="F991" s="4" t="n"/>
+      <c r="G991" s="4" t="n"/>
+      <c r="H991" s="4" t="n"/>
+      <c r="I991" s="4" t="n"/>
+      <c r="J991" s="4" t="n"/>
+      <c r="K991" s="4" t="n"/>
+      <c r="L991" s="4" t="n"/>
+      <c r="M991" s="4" t="n"/>
+      <c r="N991" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O991" s="6" t="inlineStr">
+        <is>
+          <t>FROM TJ30T JOIN TJ30 ON TJ30T.STSMA = TJ30.STSMA AND TJ30T.ESTAT = TJ30.ESTAT</t>
+        </is>
+      </c>
+      <c r="P991" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים לסטטוסי משתמש</t>
+        </is>
+      </c>
+      <c r="Q991" s="4" t="inlineStr"/>
+      <c r="R991" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S991" s="4" t="inlineStr">
+        <is>
+          <t>A62</t>
+        </is>
+      </c>
+      <c r="T991" s="7">
+        <f>HYPERLINK("#'"&amp;R991&amp;"'!"&amp;S991,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" s="4" t="n"/>
+      <c r="B992" s="4" t="n"/>
+      <c r="C992" s="4" t="n"/>
+      <c r="D992" s="4" t="n"/>
+      <c r="E992" s="4" t="n"/>
+      <c r="F992" s="4" t="n"/>
+      <c r="G992" s="4" t="n"/>
+      <c r="H992" s="4" t="n"/>
+      <c r="I992" s="4" t="n"/>
+      <c r="J992" s="4" t="n"/>
+      <c r="K992" s="4" t="n"/>
+      <c r="L992" s="4" t="n"/>
+      <c r="M992" s="4" t="n"/>
+      <c r="N992" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O992" s="6" t="inlineStr">
+        <is>
+          <t>FROM EKKO JOIN BUT000 ON EKKO.LIFNR = BUT000.PARTNER</t>
+        </is>
+      </c>
+      <c r="P992" s="4" t="inlineStr">
+        <is>
+          <t>שותף עסקי (BP - השפעת מעבר S/4)</t>
+        </is>
+      </c>
+      <c r="Q992" s="4" t="inlineStr"/>
+      <c r="R992" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S992" s="4" t="inlineStr">
+        <is>
+          <t>A63</t>
+        </is>
+      </c>
+      <c r="T992" s="7">
+        <f>HYPERLINK("#'"&amp;R992&amp;"'!"&amp;S992,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="993">
+      <c r="A993" s="4" t="n"/>
+      <c r="B993" s="4" t="n"/>
+      <c r="C993" s="4" t="n"/>
+      <c r="D993" s="4" t="n"/>
+      <c r="E993" s="4" t="n"/>
+      <c r="F993" s="4" t="n"/>
+      <c r="G993" s="4" t="n"/>
+      <c r="H993" s="4" t="n"/>
+      <c r="I993" s="4" t="n"/>
+      <c r="J993" s="4" t="n"/>
+      <c r="K993" s="4" t="n"/>
+      <c r="L993" s="4" t="n"/>
+      <c r="M993" s="4" t="n"/>
+      <c r="N993" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O993" s="6" t="inlineStr">
+        <is>
+          <t>FROM PLPO JOIN TC22 ON PLPO.STEUS = TC22.STEUS</t>
+        </is>
+      </c>
+      <c r="P993" s="4" t="inlineStr">
+        <is>
+          <t>מפתחות בקרת תהליך/פעולה (PI Control)</t>
+        </is>
+      </c>
+      <c r="Q993" s="4" t="inlineStr"/>
+      <c r="R993" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S993" s="4" t="inlineStr">
+        <is>
+          <t>A64</t>
+        </is>
+      </c>
+      <c r="T993" s="7">
+        <f>HYPERLINK("#'"&amp;R993&amp;"'!"&amp;S993,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" s="4" t="n"/>
+      <c r="B994" s="4" t="n"/>
+      <c r="C994" s="4" t="n"/>
+      <c r="D994" s="4" t="n"/>
+      <c r="E994" s="4" t="n"/>
+      <c r="F994" s="4" t="n"/>
+      <c r="G994" s="4" t="n"/>
+      <c r="H994" s="4" t="n"/>
+      <c r="I994" s="4" t="n"/>
+      <c r="J994" s="4" t="n"/>
+      <c r="K994" s="4" t="n"/>
+      <c r="L994" s="4" t="n"/>
+      <c r="M994" s="4" t="n"/>
+      <c r="N994" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O994" s="6" t="inlineStr">
+        <is>
+          <t>FROM JEST JOIN AUFK ON JEST.OBJNR = AUFK.OBJNR</t>
+        </is>
+      </c>
+      <c r="P994" s="4" t="inlineStr">
+        <is>
+          <t>סטטוס אובייקט - מכונת מצבים של הפק"ע</t>
+        </is>
+      </c>
+      <c r="Q994" s="4" t="inlineStr"/>
+      <c r="R994" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S994" s="4" t="inlineStr">
+        <is>
+          <t>A65</t>
+        </is>
+      </c>
+      <c r="T994" s="7">
+        <f>HYPERLINK("#'"&amp;R994&amp;"'!"&amp;S994,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" s="4" t="n"/>
+      <c r="B995" s="4" t="n"/>
+      <c r="C995" s="4" t="n"/>
+      <c r="D995" s="4" t="n"/>
+      <c r="E995" s="4" t="n"/>
+      <c r="F995" s="4" t="n"/>
+      <c r="G995" s="4" t="n"/>
+      <c r="H995" s="4" t="n"/>
+      <c r="I995" s="4" t="n"/>
+      <c r="J995" s="4" t="n"/>
+      <c r="K995" s="4" t="n"/>
+      <c r="L995" s="4" t="n"/>
+      <c r="M995" s="4" t="n"/>
+      <c r="N995" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O995" s="6" t="inlineStr">
+        <is>
+          <t>FROM JSTO JOIN AUFK ON JSTO.OBJNR = AUFK.OBJNR</t>
+        </is>
+      </c>
+      <c r="P995" s="4" t="inlineStr">
+        <is>
+          <t>כותרת אובייקט סטטוס + פרופיל</t>
+        </is>
+      </c>
+      <c r="Q995" s="4" t="inlineStr"/>
+      <c r="R995" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S995" s="4" t="inlineStr">
+        <is>
+          <t>A66</t>
+        </is>
+      </c>
+      <c r="T995" s="7">
+        <f>HYPERLINK("#'"&amp;R995&amp;"'!"&amp;S995,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="996">
+      <c r="A996" s="4" t="n"/>
+      <c r="B996" s="4" t="n"/>
+      <c r="C996" s="4" t="n"/>
+      <c r="D996" s="4" t="n"/>
+      <c r="E996" s="4" t="n"/>
+      <c r="F996" s="4" t="n"/>
+      <c r="G996" s="4" t="n"/>
+      <c r="H996" s="4" t="n"/>
+      <c r="I996" s="4" t="n"/>
+      <c r="J996" s="4" t="n"/>
+      <c r="K996" s="4" t="n"/>
+      <c r="L996" s="4" t="n"/>
+      <c r="M996" s="4" t="n"/>
+      <c r="N996" s="4" t="inlineStr">
+        <is>
+          <t>Join</t>
+        </is>
+      </c>
+      <c r="O996" s="6" t="inlineStr">
+        <is>
+          <t>FROM JEST JOIN TJ02T ON JEST.STAT = TJ02T.ISTAT</t>
+        </is>
+      </c>
+      <c r="P996" s="4" t="inlineStr">
+        <is>
+          <t>טקסטים של סטטוסי מערכת (CRTE/REL/CNF/TECO)</t>
+        </is>
+      </c>
+      <c r="Q996" s="4" t="inlineStr"/>
+      <c r="R996" s="4" t="inlineStr">
+        <is>
+          <t>ER - Join Map</t>
+        </is>
+      </c>
+      <c r="S996" s="4" t="inlineStr">
+        <is>
+          <t>A67</t>
+        </is>
+      </c>
+      <c r="T996" s="7">
+        <f>HYPERLINK("#'"&amp;R996&amp;"'!"&amp;S996,"➜ פתח")</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="20">
+    <mergeCell ref="B9:H9"/>
+    <mergeCell ref="B56:H59"/>
+    <mergeCell ref="F16:F17"/>
+    <mergeCell ref="B5:H5"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="D16:D17"/>
+    <mergeCell ref="B10:B11"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="F13:F14"/>
+    <mergeCell ref="H13:H14"/>
+    <mergeCell ref="H16:H17"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="C25:F25"/>
     <mergeCell ref="J2:M3"/>
     <mergeCell ref="D10:D11"/>
-    <mergeCell ref="H13:H14"/>
-    <mergeCell ref="B9:H9"/>
     <mergeCell ref="B24:F24"/>
+    <mergeCell ref="B16:B17"/>
     <mergeCell ref="F10:F11"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="B56:H59"/>
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="D16:D17"/>
-    <mergeCell ref="B16:B17"/>
-    <mergeCell ref="C25:F25"/>
-    <mergeCell ref="B10:B11"/>
-    <mergeCell ref="B3:H3"/>
-    <mergeCell ref="B5:H5"/>
     <mergeCell ref="H10:H11"/>
   </mergeCells>
   <hyperlinks>
@@ -46189,6 +49689,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B16" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="D16" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F16" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId12"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
@@ -46203,6 +49705,1686 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00D62027"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+    <col width="40" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>◄ חזרה למסך הראשי</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="n"/>
+      <c r="C1" s="34" t="inlineStr">
+        <is>
+          <t>Production Transactions &amp; Reports Directory - מדריך טרנזקציות ודוחות ייצור  ·  CBC NEO</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+      <c r="G1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="75" t="inlineStr">
+        <is>
+          <t>מס' (#)</t>
+        </is>
+      </c>
+      <c r="B2" s="75" t="inlineStr">
+        <is>
+          <t>Legacy ECC T-Code</t>
+        </is>
+      </c>
+      <c r="C2" s="75" t="inlineStr">
+        <is>
+          <t>מודול (Scope)</t>
+        </is>
+      </c>
+      <c r="D2" s="75" t="inlineStr">
+        <is>
+          <t>הסבר פונקציונלי בעברית</t>
+        </is>
+      </c>
+      <c r="E2" s="75" t="inlineStr">
+        <is>
+          <t>שינוי מבני S/4HANA</t>
+        </is>
+      </c>
+      <c r="F2" s="75" t="inlineStr">
+        <is>
+          <t>Fiori App + ID</t>
+        </is>
+      </c>
+      <c r="G2" s="75" t="inlineStr">
+        <is>
+          <t>נוף Fiori מורחב (Hebrew)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="66" customHeight="1">
+      <c r="A3" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="87" t="inlineStr">
+        <is>
+          <t>CS01 / CS02 / CS03</t>
+        </is>
+      </c>
+      <c r="C3" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D3" s="79" t="inlineStr">
+        <is>
+          <t>יצירה / שינוי / תצוגה של עץ מוצר חומר (Material BOM). הליבה להגדרת מבנה הרכיבים של כל מוצר CBC - תרכיז, סוכר, CO2, חומרי אריזה - כולל כמויות, יחידות ופחת רכיב (1%). מקור הפיצוץ לכל פק"ע.</t>
+        </is>
+      </c>
+      <c r="E3" s="79" t="inlineStr">
+        <is>
+          <t>ללא שינוי מבני; MATNR מורחב ל-40 תווים משפיע על IDNRK והממשקים.</t>
+        </is>
+      </c>
+      <c r="F3" s="88" t="inlineStr">
+        <is>
+          <t>Maintain Bill of Material / Manage Material BOMs  (F1743 / F1813)</t>
+        </is>
+      </c>
+      <c r="G3" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori פוצל לאפליקציות נפרדות: 'Maintain Bill of Material' (תחזוקה) ו-'Manage Material BOMs' (סקירה וניהול). יש גם Object Page לכל BOM עם היסטוריית שינויים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="66" customHeight="1">
+      <c r="A4" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="90" t="inlineStr">
+        <is>
+          <t>CS11</t>
+        </is>
+      </c>
+      <c r="C4" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D4" s="84" t="inlineStr">
+        <is>
+          <t>פיצוץ עץ מוצר רב-רמתי (Multilevel BOM Explosion) - מציג את כל רמות ההיררכיה של הרכיבים מהמוצר המוגמר ועד חומרי הגלם. כלי ניתוח מרכזי לתכנון חומרים ולבדיקת עלות מוצר ב-CBC.</t>
+        </is>
+      </c>
+      <c r="E4" s="84" t="inlineStr">
+        <is>
+          <t>הפיצוץ עובר ל-HANA-optimized; ב-S/4 התצוגה דרך Fiori עם CDS Views במקום הרצת דוח כבדה.</t>
+        </is>
+      </c>
+      <c r="F4" s="91" t="inlineStr">
+        <is>
+          <t>Display Bill of Material (multilevel)  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G4" s="84" t="inlineStr">
+        <is>
+          <t>הפיצוץ הרב-רמתי מוצג כעץ אינטראקטיבי ב-Fiori; ניתן לקפוץ מכל רכיב ל-Object Page שלו (drill-down) במקום מסך SAPGUI סטטי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="66" customHeight="1">
+      <c r="A5" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>CS12</t>
+        </is>
+      </c>
+      <c r="C5" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D5" s="79" t="inlineStr">
+        <is>
+          <t>פיצוץ עץ מוצר רב-רמתי מלא (כל הרמות בו-זמנית) עם כמויות מצטברות. משמש להפקת רשימת חומרים מלאה (Total BOM) לתמחיר ולרכש מרוכז.</t>
+        </is>
+      </c>
+      <c r="E5" s="79" t="inlineStr">
+        <is>
+          <t>מבוסס HANA; חישוב הכמויות המצטברות מהיר יותר משמעותית.</t>
+        </is>
+      </c>
+      <c r="F5" s="92" t="inlineStr">
+        <is>
+          <t>Display Bill of Material (multilevel)  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G5" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori הנתונים זמינים גם כ-Analytical tile עם ייצוא ל-Excel/BI לצורך ניתוח עלות חומרים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="66" customHeight="1">
+      <c r="A6" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="90" t="inlineStr">
+        <is>
+          <t>CS13</t>
+        </is>
+      </c>
+      <c r="C6" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D6" s="84" t="inlineStr">
+        <is>
+          <t>פיצוץ עץ מוצר מסוכם (Summarized BOM) - מאחד רכיבים זהים החוזרים במספר רמות לשורה אחת עם כמות כוללת. חיוני לרכש ולתכנון חומר גלם משותף (סוכר/CO2) בין מוצרים.</t>
+        </is>
+      </c>
+      <c r="E6" s="84" t="inlineStr">
+        <is>
+          <t>ללא שינוי לוגי; ביצוע מהיר על HANA.</t>
+        </is>
+      </c>
+      <c r="F6" s="91" t="inlineStr">
+        <is>
+          <t>Display Bill of Material (multilevel)  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G6" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori הסיכום זמין כ-View אנליטי עם סינון לפי קבוצת חומר.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="66" customHeight="1">
+      <c r="A7" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>CS14</t>
+        </is>
+      </c>
+      <c r="C7" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D7" s="79" t="inlineStr">
+        <is>
+          <t>השוואת עצי מוצר (BOM Comparison) - משווה שני עצי מוצר (או שתי חלופות/גרסאות) ומסמן הבדלים ברכיבים ובכמויות. קריטי לאימות שינויי מתכון מאושרים ב-CBC לפני העברה לייצור.</t>
+        </is>
+      </c>
+      <c r="E7" s="79" t="inlineStr">
+        <is>
+          <t>ללא שינוי; ב-S/4 ניתן להשוות גם דרך Engineering/Change Records.</t>
+        </is>
+      </c>
+      <c r="F7" s="92" t="inlineStr">
+        <is>
+          <t>Compare Bill of Materials  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G7" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori ההשוואה ויזואלית (side-by-side) עם הדגשת דלתות; משולב בתהליך ניהול שינויים הנדסיים (ECM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>CS15</t>
+        </is>
+      </c>
+      <c r="C8" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D8" s="84" t="inlineStr">
+        <is>
+          <t>רשימת 'היכן בשימוש' (Where-Used List) - מציג בכל אילו עצי מוצר/מוצרים משמש רכיב נתון. חיוני לניתוח השפעה (Impact Analysis) בעת החלפת חומר גלם/ספק או ריקול אצווה.</t>
+        </is>
+      </c>
+      <c r="E8" s="84" t="inlineStr">
+        <is>
+          <t>ללא שינוי; ב-S/4 מהיר יותר ומשולב ב-Object Page של החומר.</t>
+        </is>
+      </c>
+      <c r="F8" s="91" t="inlineStr">
+        <is>
+          <t>Where-Used List - Material  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G8" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori ה-Where-Used נגיש ישירות מ-Object Page של החומר כלשונית, ללא הרצת דוח נפרד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="66" customHeight="1">
+      <c r="A9" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="87" t="inlineStr">
+        <is>
+          <t>CO24</t>
+        </is>
+      </c>
+      <c r="C9" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D9" s="79" t="inlineStr">
+        <is>
+          <t>מידע חוסרים (Missing Parts Info System) - מציג רכיבים חסרים לפק"ע שלא ניתן לפלוט (מלאי לא מספיק). כלי תפעולי לזיהוי עיכובי ייצור בקו ב-CBC לפני שחרור.</t>
+        </is>
+      </c>
+      <c r="E9" s="79" t="inlineStr">
+        <is>
+          <t>ב-S/4 משולב ב-MRP Live וב-Fiori Material Coverage; בדיקת זמינות בזמן אמת.</t>
+        </is>
+      </c>
+      <c r="F9" s="88" t="inlineStr">
+        <is>
+          <t>Monitor Material Coverage - Net Segments  (F0251)</t>
+        </is>
+      </c>
+      <c r="G9" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori זה הופך ל-Monitor Material Coverage עם MRP cockpit מבוסס תפקיד; כל חוסר מציג פעולות מוצעות (Solve) ישירות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="66" customHeight="1">
+      <c r="A10" s="89" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="90" t="inlineStr">
+        <is>
+          <t>CO46</t>
+        </is>
+      </c>
+      <c r="C10" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D10" s="84" t="inlineStr">
+        <is>
+          <t>דוח התקדמות פק"ע (Order Progress Report) - מציג את מצב הפק"ע, הפעולות, הרכיבים והדיווחים במבט אחד. כלי מעקב לתפעול לבקרת קצב ייצור והשלמת אצוות.</t>
+        </is>
+      </c>
+      <c r="E10" s="84" t="inlineStr">
+        <is>
+          <t>מוחלף בדוחות Fiori אנליטיים ולוחות מעקב מבוססי תפקיד.</t>
+        </is>
+      </c>
+      <c r="F10" s="91" t="inlineStr">
+        <is>
+          <t>Production Order/Process Order Progress  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G10" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori המעקב הופך ל-Overview Page / Analytical tiles עם KPIs (פק"ע פתוחות, פיגורים) במקום דוח טקסטואלי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="66" customHeight="1">
+      <c r="A11" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="87" t="inlineStr">
+        <is>
+          <t>COOIS</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="D11" s="79" t="inlineStr">
+        <is>
+          <t>מערכת מידע פקודות ייצור (Production Order Information System) - דוח מרכזי לסינון, צפייה ועיבוד המוני של פקודות ייצור בדידות (Discrete) לפי סטטוס, חומר, מועד ועוד.</t>
+        </is>
+      </c>
+      <c r="E11" s="79" t="inlineStr">
+        <is>
+          <t>נתמך; אסטרטגית מוחלף ב-Manage Production Orders ובדוחות אנליטיים.</t>
+        </is>
+      </c>
+      <c r="F11" s="92" t="inlineStr">
+        <is>
+          <t>Manage Production Orders  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G11" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori פוצל ל-List Report עם פילטרים חכמים + Analytical tiles; עיבוד המוני דרך פעולות מרובות-בחירה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="66" customHeight="1">
+      <c r="A12" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="90" t="inlineStr">
+        <is>
+          <t>COOISPI</t>
+        </is>
+      </c>
+      <c r="C12" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D12" s="84" t="inlineStr">
+        <is>
+          <t>מערכת מידע פקודות תהליך (Process Order Information System) - המקבילה של COOIS לפק"ע תהליכיות (Process Orders). הדוח התפעולי המרכזי של CBC לסינון ועיבוד המוני של פק"ע ייצור משקאות.</t>
+        </is>
+      </c>
+      <c r="E12" s="84" t="inlineStr">
+        <is>
+          <t>נתמך; מוחלף ב-Manage Process Orders ובלוחות מעקב.</t>
+        </is>
+      </c>
+      <c r="F12" s="88" t="inlineStr">
+        <is>
+          <t>Manage Process Orders  (F4512)</t>
+        </is>
+      </c>
+      <c r="G12" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Manage Process Orders' (F4512) הוא ה-List Report הראשי; משולב עם Process Order Object Page ועם דיווח (Confirm).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="66" customHeight="1">
+      <c r="A13" s="86" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="87" t="inlineStr">
+        <is>
+          <t>COIO</t>
+        </is>
+      </c>
+      <c r="C13" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D13" s="79" t="inlineStr">
+        <is>
+          <t>לוח מעקב פקודות (Order Tracking Cockpit / Process Order Cockpit) - מסך תפעולי מאוחד למעקב אחר פק"ע התהליך, סטטוסים, חומרים ודיווחים. לב המעקב התפעולי של מנהל הקו ב-CBC.</t>
+        </is>
+      </c>
+      <c r="E13" s="79" t="inlineStr">
+        <is>
+          <t>מוחלף בלוחות Fiori מבוססי תפקיד (Production Operator / Supervisor).</t>
+        </is>
+      </c>
+      <c r="F13" s="92" t="inlineStr">
+        <is>
+          <t>Process Order Cockpit / Operator Dashboard  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G13" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori המעקב מתפצל לדאשבורדים לפי תפקיד: מפעיל קו (Confirm), מתכנן (Schedule), ומנהל (KPIs) - launchpad מבוסס תפקיד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
+      <c r="A14" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="90" t="inlineStr">
+        <is>
+          <t>COR1 / COR2 / COR3</t>
+        </is>
+      </c>
+      <c r="C14" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D14" s="84" t="inlineStr">
+        <is>
+          <t>יצירה / שינוי / תצוגה של פקודת ייצור תהליכית (Process Order) - ליבת ביצוע הייצור ב-CBC. שחרור הפק"ע (REL) מייצר Control Recipe ושולח הוראות תהליך (IDoc LOIPRO) לקו/MES.</t>
+        </is>
+      </c>
+      <c r="E14" s="84" t="inlineStr">
+        <is>
+          <t>מודל מותאם; עלויות ל-ACDOCA; שחרור/Control Recipe נשמרים.</t>
+        </is>
+      </c>
+      <c r="F14" s="88" t="inlineStr">
+        <is>
+          <t>Create / Manage Process Orders  (F4512)</t>
+        </is>
+      </c>
+      <c r="G14" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori יצירה/שינוי דרך 'Manage Process Orders' + Object Page; פעולות ייעודיות (Release, Confirm, Print) כ-tiles נפרדים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="66" customHeight="1">
+      <c r="A15" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="87" t="inlineStr">
+        <is>
+          <t>CO01 / CO02 / CO03</t>
+        </is>
+      </c>
+      <c r="C15" s="63" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="D15" s="79" t="inlineStr">
+        <is>
+          <t>יצירה / שינוי / תצוגה של פקודת ייצור בדידה (Discrete Production Order). משמש בייצור בדיד (לא משקאות) - מובא כאן לצורך הבחנה מ-PP-PI; ב-CBC הליבה היא Process Orders.</t>
+        </is>
+      </c>
+      <c r="E15" s="79" t="inlineStr">
+        <is>
+          <t>מודל מותאם; דומה ל-Process Order ב-S/4.</t>
+        </is>
+      </c>
+      <c r="F15" s="92" t="inlineStr">
+        <is>
+          <t>Create / Manage Production Orders  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G15" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori מקביל ל-Manage Production Orders; בייצור משקאות לא בשימוש (PP-PI מוביל).</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="66" customHeight="1">
+      <c r="A16" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="90" t="inlineStr">
+        <is>
+          <t>C201 / C202 / C203</t>
+        </is>
+      </c>
+      <c r="C16" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D16" s="84" t="inlineStr">
+        <is>
+          <t>יצירה / שינוי / תצוגה של מתכון ייצור (Master Recipe) - הגדרת הנוסחה, הפאזות, ההוראות וערכי התקן. כל משקה ב-CBC מיוצר לפי מתכון מאושר; שינוי דורש ניהול שינויים הנדסי (ECM).</t>
+        </is>
+      </c>
+      <c r="E16" s="84" t="inlineStr">
+        <is>
+          <t>ללא שינוי מבני; Fiori 'Manage Master Recipes'.</t>
+        </is>
+      </c>
+      <c r="F16" s="91" t="inlineStr">
+        <is>
+          <t>Manage Master Recipes  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G16" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Manage Master Recipes' עם Object Page לכל מתכון; שילוב עם Manage Process Instructions ו-PI characteristics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="66" customHeight="1">
+      <c r="A17" s="86" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="87" t="inlineStr">
+        <is>
+          <t>CA01 / CA02 / CA03</t>
+        </is>
+      </c>
+      <c r="C17" s="63" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="D17" s="79" t="inlineStr">
+        <is>
+          <t>יצירה / שינוי / תצוגה של רשימת פעולות (Routing) לייצור בדיד. המקבילה הבדידה של מתכון ה-PP-PI; מובא להבחנה - ב-CBC משתמשים ב-Master Recipe ולא ב-Routing.</t>
+        </is>
+      </c>
+      <c r="E17" s="79" t="inlineStr">
+        <is>
+          <t>ללא שינוי; Fiori 'Manage Routings'.</t>
+        </is>
+      </c>
+      <c r="F17" s="92" t="inlineStr">
+        <is>
+          <t>Manage Routings  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G17" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Manage Routings'; אינו בשימוש בייצור משקאות תהליכי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="66" customHeight="1">
+      <c r="A18" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="90" t="inlineStr">
+        <is>
+          <t>C223</t>
+        </is>
+      </c>
+      <c r="C18" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D18" s="84" t="inlineStr">
+        <is>
+          <t>ניהול גרסאות ייצור (Production Versions) - מקשר חומר -&gt; עץ מוצר חלופי + מתכון + קו ייצור. ב-S/4HANA חובה מוחלטת לכל ביצוע ייצור; ב-CBC כל שילוב מוצר/קו = גרסה.</t>
+        </is>
+      </c>
+      <c r="E18" s="84" t="inlineStr">
+        <is>
+          <t>גרסת ייצור (VERID) חובה 100% ב-S/4; הרץ בדיקת עקביות לפני ההמרה (RCC22300).</t>
+        </is>
+      </c>
+      <c r="F18" s="88" t="inlineStr">
+        <is>
+          <t>Manage Production Versions  (F2703)</t>
+        </is>
+      </c>
+      <c r="G18" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Manage Production Versions' (F2703) מרכז את כל הגרסאות עם בדיקת תקינות (consistency) ויזואלית - חיוני ל-Pre-check המיגרציה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="66" customHeight="1">
+      <c r="A19" s="86" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>CO11N</t>
+        </is>
+      </c>
+      <c r="C19" s="63" t="inlineStr">
+        <is>
+          <t>PP</t>
+        </is>
+      </c>
+      <c r="D19" s="79" t="inlineStr">
+        <is>
+          <t>דיווח ביצוע לפעולה בייצור בדיד (Time Ticket Confirmation). מובא להבחנה; ב-CBC הדיווח התהליכי מתבצע דרך COR6N/CORK והודעות תהליך מהקו.</t>
+        </is>
+      </c>
+      <c r="E19" s="79" t="inlineStr">
+        <is>
+          <t>מוחלף ב-Fiori 'Confirm Production Operation'.</t>
+        </is>
+      </c>
+      <c r="F19" s="88" t="inlineStr">
+        <is>
+          <t>Confirm Production Operation  (F3372)</t>
+        </is>
+      </c>
+      <c r="G19" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Confirm Production Operation' (F3372) - דיווח מהיר מבוסס תפקיד מפעיל, מותאם למסך מגע בקו.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="90" t="inlineStr">
+        <is>
+          <t>COR6N</t>
+        </is>
+      </c>
+      <c r="C20" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D20" s="84" t="inlineStr">
+        <is>
+          <t>דיווח ביצוע לפאזת פק"ע תהליכית (Process Order Phase Confirmation) - דיווח כמות שיוצרה, פחת וזמני מכונה/אדם לפאזה. מקור הנתונים מהקו (PI Sheet/MES) ובסיס לעלות ולניתוח פחת מול 1% היעד.</t>
+        </is>
+      </c>
+      <c r="E20" s="84" t="inlineStr">
+        <is>
+          <t>ללא שינוי; Fiori Confirmation מבוסס תפקיד.</t>
+        </is>
+      </c>
+      <c r="F20" s="88" t="inlineStr">
+        <is>
+          <t>Confirm Process Order / Operation  (F3372)</t>
+        </is>
+      </c>
+      <c r="G20" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori הדיווח התהליכי מאוחד עם ה-Confirm app; אוטומציה דרך הודעות תהליך (PPCC1) מ-MES ל-SAP.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="86" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="87" t="inlineStr">
+        <is>
+          <t>MD04</t>
+        </is>
+      </c>
+      <c r="C21" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D21" s="79" t="inlineStr">
+        <is>
+          <t>רשימת מלאי/דרישות (Stock / Requirements List) - המסך התפעולי המרכזי לתכנון: מציג מלאי, דרישות, פק"ע, הזמנות רכש וגרעונות לחומר. מנהל החומר ב-CBC עובד מולו יומית.</t>
+        </is>
+      </c>
+      <c r="E21" s="79" t="inlineStr">
+        <is>
+          <t>ב-S/4 נשען על MRP Live; הצגה דרך Fiori Material Coverage עם נתוני זמן אמת מ-HANA.</t>
+        </is>
+      </c>
+      <c r="F21" s="88" t="inlineStr">
+        <is>
+          <t>Monitor Material Coverage - Net Segments  (F0251)</t>
+        </is>
+      </c>
+      <c r="G21" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Monitor Material Coverage' (F0251) מחליף את MD04 עם MRP cockpit מבוסס תפקיד, אזורי כיסוי (segments) ופעולות פתרון מוצעות.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="89" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="90" t="inlineStr">
+        <is>
+          <t>MD01 / MD01N</t>
+        </is>
+      </c>
+      <c r="C22" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D22" s="84" t="inlineStr">
+        <is>
+          <t>הרצת תכנון חומרים (MRP / MRP Live). MD01N היא הגרסה החדשה הרצה ישירות על HANA (MRP Live) - מתכננת חומרי גלם, מוצרי ביניים וייצור ומייצרת פק"ע/הזמנות רכש מתוכננות.</t>
+        </is>
+      </c>
+      <c r="E22" s="84" t="inlineStr">
+        <is>
+          <t>MD01N (MRP Live) מחליף את MD01 הקלאסי; ריצה in-memory מהירה משמעותית, ללא טבלאות ביניים.</t>
+        </is>
+      </c>
+      <c r="F22" s="88" t="inlineStr">
+        <is>
+          <t>Schedule MRP Runs / Monitor Material Requirements  (F2101)</t>
+        </is>
+      </c>
+      <c r="G22" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori התכנון מנוהל דרך 'Schedule MRP Runs' + 'Monitor Material Coverage'; MRP Live רץ ברקע על HANA והתוצאות נצפות בלוחות מבוססי תפקיד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="86" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="87" t="inlineStr">
+        <is>
+          <t>COGI</t>
+        </is>
+      </c>
+      <c r="C23" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D23" s="79" t="inlineStr">
+        <is>
+          <t>עיבוד תנועות מלאי שגויות (Postprocessing of Faulty Goods Movements) - מטפל בפליטות/קליטות אוטומטיות שנכשלו (Backflush). קריטי בייצור משקאות: כשל בפליטת חומר גלם אוטומטית מהקו חייב טיפול מיידי כדי לא לעצור דיווח.</t>
+        </is>
+      </c>
+      <c r="E23" s="79" t="inlineStr">
+        <is>
+          <t>נתמך; ב-S/4 מומלץ לצמצם שגיאות דרך בדיקת זמינות ו-MATDOC.</t>
+        </is>
+      </c>
+      <c r="F23" s="92" t="inlineStr">
+        <is>
+          <t>Manage Material Documents / Clear Faulty Movements  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G23" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori הטיפול בתנועות שגויות נגיש דרך 'Manage Material Documents' ולוחות חריגים; התראות אוטומטיות על כשלי Backflush.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="66" customHeight="1">
+      <c r="A24" s="89" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="90" t="inlineStr">
+        <is>
+          <t>CM01 / CM07</t>
+        </is>
+      </c>
+      <c r="C24" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D24" s="84" t="inlineStr">
+        <is>
+          <t>הערכת עומסי קיבולת (Capacity Load / Evaluation) - מציג את העומס מול הזמינות של קווי הייצור/המשאבים. כלי לזיהוי צווארי בקבוק ולתזמון ייצור משקאות יעיל ב-CBC.</t>
+        </is>
+      </c>
+      <c r="E24" s="84" t="inlineStr">
+        <is>
+          <t>ללא שינוי לוגי; ב-S/4 לוח תזמון גרפי (Scheduling Board) מודרני.</t>
+        </is>
+      </c>
+      <c r="F24" s="91" t="inlineStr">
+        <is>
+          <t>Capacity Scheduling Board / Monitor Capacity Utilisation  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G24" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Capacity Scheduling Board' מספק תזמון גרירה-ושחרור (drag&amp;drop) ויזואלי במקום דוחות הטקסט של CM01/CM07.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="66" customHeight="1">
+      <c r="A25" s="86" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="87" t="inlineStr">
+        <is>
+          <t>COHV / COHVPI</t>
+        </is>
+      </c>
+      <c r="C25" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D25" s="79" t="inlineStr">
+        <is>
+          <t>עיבוד המוני של פקודות (Mass Processing) - מאפשר שחרור, הדפסה, דיווח או ביטול של מאות פק"ע בו-זמנית. חיוני לתפעול יומי של עשרות פק"ע ייצור ב-CBC.</t>
+        </is>
+      </c>
+      <c r="E25" s="79" t="inlineStr">
+        <is>
+          <t>נתמך; משולב עם רקע (Application Jobs) ב-S/4.</t>
+        </is>
+      </c>
+      <c r="F25" s="92" t="inlineStr">
+        <is>
+          <t>Mass Processing - Orders  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G25" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori העיבוד ההמוני נגיש דרך List Report עם בחירה מרובה + תזמון Application Jobs לרקע.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="66" customHeight="1">
+      <c r="A26" s="89" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="90" t="inlineStr">
+        <is>
+          <t>CORK / CORT</t>
+        </is>
+      </c>
+      <c r="C26" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D26" s="84" t="inlineStr">
+        <is>
+          <t>השלמה ובקרה של פק"ע תהליך: CORK = דיווח השלמת פק"ע; CORT = מוניטור מתכוני בקרה (Control Recipe Monitor). CORT מנהל את שליחת הוראות התהליך לקו/MES ומעקב סטטוס המסירה (Zetes/Daymax).</t>
+        </is>
+      </c>
+      <c r="E26" s="84" t="inlineStr">
+        <is>
+          <t>ללא שינוי; הודעות תהליך נשמרות.</t>
+        </is>
+      </c>
+      <c r="F26" s="91" t="inlineStr">
+        <is>
+          <t>Confirm Process Order / Control Recipe Monitor  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G26" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori המעקב אחר Control Recipes משולב בלוחות התפעול; סטטוס המסירה ל-MES מוצג כ-KPI.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="66" customHeight="1">
+      <c r="A27" s="86" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="87" t="inlineStr">
+        <is>
+          <t>CO53</t>
+        </is>
+      </c>
+      <c r="C27" s="93" t="inlineStr">
+        <is>
+          <t>PP-PI</t>
+        </is>
+      </c>
+      <c r="D27" s="79" t="inlineStr">
+        <is>
+          <t>רשימת עבודה למתכוני בקרה / גיליון PI (Control Recipe / PI Sheet Worklist) - מציג למפעיל הקו את הוראות התהליך לביצוע ולתיעוד (ערכים נמדדים, אישורים). הממשק הישיר בין SAP לאוטומציית הקו ב-CBC.</t>
+        </is>
+      </c>
+      <c r="E27" s="79" t="inlineStr">
+        <is>
+          <t>ב-S/4 מומלץ Manufacturing Execution / Digital Manufacturing במקום PI Sheet קלאסי.</t>
+        </is>
+      </c>
+      <c r="F27" s="92" t="inlineStr">
+        <is>
+          <t>Process Operator Dashboard / Digital Mfg  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G27" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori גיליון ה-PI הופך לדאשבורד מפעיל מבוסס תפקיד (Process Operator) עם קליטת ערכים ואישורים בזמן אמת מהמסך.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="66" customHeight="1">
+      <c r="A28" s="89" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="90" t="inlineStr">
+        <is>
+          <t>MB1A / MIGO</t>
+        </is>
+      </c>
+      <c r="C28" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D28" s="84" t="inlineStr">
+        <is>
+          <t>תנועות מלאי: MB1A = פליטת חומר (261) לפק"ע; MIGO = תנועת מלאי כללית (פליטה/קליטה). פליטת חומרי גלם וקליטת מוצר מוגמר ב-CBC, מסונכרן עם מסופי Zetes.</t>
+        </is>
+      </c>
+      <c r="E28" s="84" t="inlineStr">
+        <is>
+          <t>תנועות מנוהלות ב-MATDOC; MIGO נתמך; Fiori 'Post Goods Movement'.</t>
+        </is>
+      </c>
+      <c r="F28" s="91" t="inlineStr">
+        <is>
+          <t>Post Goods Movement  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G28" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Post Goods Movement' מאוחד; קליטות/פליטות מהקו מבוצעות גם דרך מסופים ניידים (Zetes) המחוברים ל-OData.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="66" customHeight="1">
+      <c r="A29" s="86" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="87" t="inlineStr">
+        <is>
+          <t>MB31</t>
+        </is>
+      </c>
+      <c r="C29" s="68" t="inlineStr">
+        <is>
+          <t>Both</t>
+        </is>
+      </c>
+      <c r="D29" s="79" t="inlineStr">
+        <is>
+          <t>קליטת סחורה לפק"ע (Goods Receipt for Order, תנועה 101) - קליטת המוצר המוגמר/ביניים שיוצר למלאי, כולל אצווה ותאריך תפוגה. נקודת סיום הייצור והעברה ללוגיסטיקה.</t>
+        </is>
+      </c>
+      <c r="E29" s="79" t="inlineStr">
+        <is>
+          <t>מנוהל ב-MATDOC; נתמך.</t>
+        </is>
+      </c>
+      <c r="F29" s="92" t="inlineStr">
+        <is>
+          <t>Post Goods Receipt for Production  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="G29" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori קליטת המוצר המוגמר דרך 'Post Goods Receipt' או אוטומטית בדיווח הפק"ע (auto-GR).</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:G1"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F9" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F12" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F14" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F18" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F19" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F20" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F21" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F22" r:id="rId10"/>
+  </hyperlinks>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;8&amp;K6B7280CBC NEO - PP/PP-PI T-codes - Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="001E1E24"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="58" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>◄ חזרה למסך הראשי</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="n"/>
+      <c r="C1" s="34" t="inlineStr">
+        <is>
+          <t>General Implementer &amp; Basis Toolkit - ערכת כלי המיישם וה-Basis  ·  CBC NEO</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="n"/>
+      <c r="E1" s="4" t="n"/>
+      <c r="F1" s="4" t="n"/>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="75" t="inlineStr">
+        <is>
+          <t>מס' (#)</t>
+        </is>
+      </c>
+      <c r="B2" s="75" t="inlineStr">
+        <is>
+          <t>כלי (T-Code)</t>
+        </is>
+      </c>
+      <c r="C2" s="75" t="inlineStr">
+        <is>
+          <t>יכולות וסקופ טכני (Hebrew)</t>
+        </is>
+      </c>
+      <c r="D2" s="75" t="inlineStr">
+        <is>
+          <t>השפעת S/4HANA</t>
+        </is>
+      </c>
+      <c r="E2" s="75" t="inlineStr">
+        <is>
+          <t>Fiori App + ID</t>
+        </is>
+      </c>
+      <c r="F2" s="75" t="inlineStr">
+        <is>
+          <t>נוף Launchpad (Hebrew)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="70" customHeight="1">
+      <c r="A3" s="86" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="87" t="inlineStr">
+        <is>
+          <t>SPRO</t>
+        </is>
+      </c>
+      <c r="C3" s="79" t="inlineStr">
+        <is>
+          <t>מרכז ה-Customizing (IMG) - הגדרת כל הקונפיגורציה של SAP: מבנה ארגוני, סוגי פק"ע, פרופילי סטטוס, פרמטרי MRP, ממשקים ועוד. כלי העבודה המרכזי של המיישם ב-Project NEO.</t>
+        </is>
+      </c>
+      <c r="D3" s="79" t="inlineStr">
+        <is>
+          <t>נשמר ב-S/4 (Customizing עדיין דרך SPRO ב-Backend); חלק מההגדרות נגישות גם דרך 'Manage Your Solution'.</t>
+        </is>
+      </c>
+      <c r="E3" s="92" t="inlineStr">
+        <is>
+          <t>Manage Your Solution / Configure Your Solution  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F3" s="79" t="inlineStr">
+        <is>
+          <t>ב-S/4 Cloud הקונפיגורציה עוברת ל-SSCUI (Self-Service Configuration UIs) מבוססי תפקיד; On-Premise עדיין SPRO + SSCUI נבחרים.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="70" customHeight="1">
+      <c r="A4" s="89" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="90" t="inlineStr">
+        <is>
+          <t>SU01</t>
+        </is>
+      </c>
+      <c r="C4" s="84" t="inlineStr">
+        <is>
+          <t>תחזוקת משתמשים - יצירה/שינוי/נעילה של משתמשי SAP, הקצאת תפקידים, פרופילים, פרמטרים וסיסמאות. בסיס לאבטחת המערכת ולהרשאות בפרויקט.</t>
+        </is>
+      </c>
+      <c r="D4" s="84" t="inlineStr">
+        <is>
+          <t>נשמר; ב-S/4 ניהול זהויות מומלץ דרך Identity Authentication/Provisioning (IAS/IPS) בענן.</t>
+        </is>
+      </c>
+      <c r="E4" s="91" t="inlineStr">
+        <is>
+          <t>Maintain Business Users / Import Users  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F4" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori ניהול המשתמשים עובר ל-'Maintain Business Users' ו-launchpad ניהולי; שילוב עם IAS לניהול זהויות מרכזי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="70" customHeight="1">
+      <c r="A5" s="86" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="87" t="inlineStr">
+        <is>
+          <t>PFCG</t>
+        </is>
+      </c>
+      <c r="C5" s="79" t="inlineStr">
+        <is>
+          <t>תחזוקת תפקידים והרשאות (Role Maintenance) - בניית תפקידים (Roles), אובייקטי הרשאה, תפריטים והקצאת אפליקציות. הליבה לאבטחת הגישה לטרנזקציות ולאפליקציות Fiori.</t>
+        </is>
+      </c>
+      <c r="D5" s="79" t="inlineStr">
+        <is>
+          <t>נשמר; ב-S/4 תפקידים כוללים גם קטלוגי Fiori (Catalogs/Groups/Spaces) - 'Business Roles'.</t>
+        </is>
+      </c>
+      <c r="E5" s="88" t="inlineStr">
+        <is>
+          <t>Maintain Business Roles  (F1491)</t>
+        </is>
+      </c>
+      <c r="F5" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Maintain Business Roles' (F1491) מנהל תפקידים עסקיים הכוללים הרשאות backend + הקצאת אפליקציות/Spaces ל-Launchpad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="70" customHeight="1">
+      <c r="A6" s="89" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="90" t="inlineStr">
+        <is>
+          <t>SE37</t>
+        </is>
+      </c>
+      <c r="C6" s="84" t="inlineStr">
+        <is>
+          <t>Function Builder - יצירה ובדיקה של מודולי פונקציה ו-BAPIs. כלי הליבה של ABAP לבדיקת ממשקים (BAPI_MATERIAL_SAVEDATA, BAPI_PROCORD_CREATE) ולפיתוח אינטגרציות.</t>
+        </is>
+      </c>
+      <c r="D6" s="84" t="inlineStr">
+        <is>
+          <t>נשמר (פיתוח); ב-S/4 מומלץ פיתוח מודרני דרך ADT (Eclipse) ו-RAP.</t>
+        </is>
+      </c>
+      <c r="E6" s="91" t="inlineStr">
+        <is>
+          <t>(Developer tool - אין Fiori ייעודי)  (-)</t>
+        </is>
+      </c>
+      <c r="F6" s="84" t="inlineStr">
+        <is>
+          <t>פיתוח ב-S/4 עובר ל-ABAP Development Tools (Eclipse/ADT); SE37 נשאר זמין ב-Backend לבדיקות ולתחזוקה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="70" customHeight="1">
+      <c r="A7" s="86" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="87" t="inlineStr">
+        <is>
+          <t>SE38 / SA38</t>
+        </is>
+      </c>
+      <c r="C7" s="79" t="inlineStr">
+        <is>
+          <t>ABAP Editor (SE38) והרצת דוחות (SA38) - כתיבה, עריכה והרצה של תוכניות ABAP ודוחות סטנדרטיים (RMMG2000, RCC22300). כלי מרכזי לדיווח ולתחזוקה.</t>
+        </is>
+      </c>
+      <c r="D7" s="79" t="inlineStr">
+        <is>
+          <t>נשמר; פיתוח חדש דרך ADT; הרצת דוחות גם דרך Fiori 'Application Jobs'.</t>
+        </is>
+      </c>
+      <c r="E7" s="92" t="inlineStr">
+        <is>
+          <t>(Developer / reporting - אין Fiori ייעודי)  (-)</t>
+        </is>
+      </c>
+      <c r="F7" s="79" t="inlineStr">
+        <is>
+          <t>הרצת דוחות ברקע עוברת ל-'Application Jobs' (Fiori); פיתוח קוד ל-ADT. SE38/SA38 נשמרים ב-Backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="70" customHeight="1">
+      <c r="A8" s="89" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="90" t="inlineStr">
+        <is>
+          <t>SE11 / SE16 / SE16N</t>
+        </is>
+      </c>
+      <c r="C8" s="84" t="inlineStr">
+        <is>
+          <t>מילון הנתונים (Data Dictionary) ועיון בתוכן טבלאות. SE11 = הגדרת טבלאות/Views/Structures; SE16/SE16N = דפדפן תוכן הטבלאות (MARA, MKAL, AFKO). חיוני לבדיקת מבנה ונתונים בפרויקט.</t>
+        </is>
+      </c>
+      <c r="D8" s="84" t="inlineStr">
+        <is>
+          <t>מותאם: ב-S/4 רבות מהטבלאות הקלאסיות הן Compatibility Views; SE16N קורא גם CDS Views. בדוק MATDOC/ACDOCA במקום MSEG/COEP.</t>
+        </is>
+      </c>
+      <c r="E8" s="88" t="inlineStr">
+        <is>
+          <t>View Browser / Custom Fields and Logic  (F2170 / F1433)</t>
+        </is>
+      </c>
+      <c r="F8" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'View Browser' (F2170) לעיון ב-CDS Views; 'Custom Fields and Logic' (F1433) להרחבות שדות. SE16N נשמר ב-Backend ותומך בקריאת CDS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="70" customHeight="1">
+      <c r="A9" s="86" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="87" t="inlineStr">
+        <is>
+          <t>SM30 / SM31</t>
+        </is>
+      </c>
+      <c r="C9" s="79" t="inlineStr">
+        <is>
+          <t>תחזוקת תצוגות טבלה (Table View Maintenance) - עדכון ידני של טבלאות קונפיגורציה (T003O, TCO01, T399X) ללא SPRO. כלי מהיר למיישם לעדכון פרמטרים.</t>
+        </is>
+      </c>
+      <c r="D9" s="79" t="inlineStr">
+        <is>
+          <t>נשמר; שינויי קונפיגורציה נרשמים ל-Transport.</t>
+        </is>
+      </c>
+      <c r="E9" s="92" t="inlineStr">
+        <is>
+          <t>(Config - דרך SSCUI/Manage Your Solution)  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F9" s="79" t="inlineStr">
+        <is>
+          <t>חלק מטבלאות הקונפיגורציה נגישות דרך SSCUI ב-Fiori; SM30 נשמר ב-Backend לטבלאות ללא ממשק ייעודי.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="70" customHeight="1">
+      <c r="A10" s="89" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="90" t="inlineStr">
+        <is>
+          <t>SM37</t>
+        </is>
+      </c>
+      <c r="C10" s="84" t="inlineStr">
+        <is>
+          <t>מוניטור משימות רקע (Background Job Monitor) - מעקב, תזמון וניתוח של ג'obs ברקע (הרצות MRP, יצירת IDocs, עיבוד המוני). חיוני לתפעול אצוות לילה ב-CBC.</t>
+        </is>
+      </c>
+      <c r="D10" s="84" t="inlineStr">
+        <is>
+          <t>נשמר; ב-S/4 ניהול ותזמון דרך Fiori 'Application Jobs'.</t>
+        </is>
+      </c>
+      <c r="E10" s="88" t="inlineStr">
+        <is>
+          <t>Application Jobs / Job Scheduling Monitor  (F1239)</t>
+        </is>
+      </c>
+      <c r="F10" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Application Jobs' (F1239) מנהל תזמון, ניטור והתראות על ג'obs מבוסס תפקיד; SM37 נשמר ב-Backend.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="70" customHeight="1">
+      <c r="A11" s="86" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="87" t="inlineStr">
+        <is>
+          <t>ST22</t>
+        </is>
+      </c>
+      <c r="C11" s="79" t="inlineStr">
+        <is>
+          <t>ניתוח קריסות ABAP (Dump Analysis) - מציג שגיאות ריצה (Short Dumps) עם stack trace וניתוח שורש. כלי הדיבוג הראשון לכל תקלת תוכנית או ממשק.</t>
+        </is>
+      </c>
+      <c r="D11" s="79" t="inlineStr">
+        <is>
+          <t>נשמר; ב-S/4 משולב גם ב-Fiori monitoring וב-Focused Run.</t>
+        </is>
+      </c>
+      <c r="E11" s="92" t="inlineStr">
+        <is>
+          <t>ABAP Dump Analysis (monitoring)  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F11" s="79" t="inlineStr">
+        <is>
+          <t>ב-S/4/Focused Run ניתוח ה-Dumps זמין בלוחות ניטור מרכזיים; ST22 נשמר ב-Backend לניתוח מפורט.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="70" customHeight="1">
+      <c r="A12" s="89" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="90" t="inlineStr">
+        <is>
+          <t>SM04 / AL08</t>
+        </is>
+      </c>
+      <c r="C12" s="84" t="inlineStr">
+        <is>
+          <t>מוניטור משתמשים מחוברים (User Monitor) - SM04 = משתמשים בשרת נוכחי; AL08 = כל המשתמשים בכל השרתים. לבקרת עומס, ניתוק תהליכים ופתרון נעילות.</t>
+        </is>
+      </c>
+      <c r="D12" s="84" t="inlineStr">
+        <is>
+          <t>נשמר; ניטור מרכזי דרך Fiori/Focused Run.</t>
+        </is>
+      </c>
+      <c r="E12" s="91" t="inlineStr">
+        <is>
+          <t>(System monitoring - Focused Run)  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F12" s="84" t="inlineStr">
+        <is>
+          <t>ב-S/4 ניטור המשתמשים והעומסים עובר ללוחות Fiori מרכזיים (Focused Run / Cloud ALM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="70" customHeight="1">
+      <c r="A13" s="86" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="87" t="inlineStr">
+        <is>
+          <t>WE02 / WE05 / WE19</t>
+        </is>
+      </c>
+      <c r="C13" s="79" t="inlineStr">
+        <is>
+          <t>מוניטור IDocs - WE02/WE05 = צפייה וניתוח IDocs נכנסים/יוצאים (MATMAS, LOIPRO) וסטטוסים; WE19 = כלי בדיקה (test tool). הליבה לפתרון תקלות בממשקים ל-Zetes ו-Daymax.</t>
+        </is>
+      </c>
+      <c r="D13" s="79" t="inlineStr">
+        <is>
+          <t>נשמר; ב-S/4 ניטור הודעות מומלץ דרך 'Message Monitoring' (AIF/Fiori).</t>
+        </is>
+      </c>
+      <c r="E13" s="92" t="inlineStr">
+        <is>
+          <t>Monitor IDocs / Message Dashboard  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F13" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori ניטור ה-IDocs/ממשקים עובר ל-'Message Monitoring' ולוחות AIF מבוססי תפקיד עם התראות על כשלים בממשקי הלוגיסטיקה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="70" customHeight="1">
+      <c r="A14" s="89" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="90" t="inlineStr">
+        <is>
+          <t>WE20 / WE21</t>
+        </is>
+      </c>
+      <c r="C14" s="84" t="inlineStr">
+        <is>
+          <t>פרופילי שותפים ויציאות (Partner Profiles &amp; Ports) - WE20 = הגדרת פרופיל שותף (אילו IDocs נשלחים/מתקבלים לכל שותף); WE21 = הגדרת פורטים (tRFC/File). מגדיר את צינור התקשורת ל-Zetes/Daymax.</t>
+        </is>
+      </c>
+      <c r="D14" s="84" t="inlineStr">
+        <is>
+          <t>נשמר; הגדרות הממשק זהות, מומלץ AIF לניטור.</t>
+        </is>
+      </c>
+      <c r="E14" s="91" t="inlineStr">
+        <is>
+          <t>(Interface config - Communication Mgmt)  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F14" s="84" t="inlineStr">
+        <is>
+          <t>ב-S/4 Cloud ההגדרות עוברות ל-'Communication Arrangements/Systems'; On-Premise נשמר WE20/WE21 + AIF.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="70" customHeight="1">
+      <c r="A15" s="86" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="87" t="inlineStr">
+        <is>
+          <t>BD64</t>
+        </is>
+      </c>
+      <c r="C15" s="79" t="inlineStr">
+        <is>
+          <t>מודל הפצה (Distribution Model / ALE) - הגדרת אילו הודעות (Message Types) מופצות בין מערכות SAP/חיצוניות. בסיס ה-ALE לתשתית ה-IDoc של המפעל.</t>
+        </is>
+      </c>
+      <c r="D15" s="79" t="inlineStr">
+        <is>
+          <t>נשמר; תשתית ALE/IDoc זהה ב-S/4.</t>
+        </is>
+      </c>
+      <c r="E15" s="92" t="inlineStr">
+        <is>
+          <t>(ALE config - Backend)  (-)</t>
+        </is>
+      </c>
+      <c r="F15" s="79" t="inlineStr">
+        <is>
+          <t>מודל ההפצה נשמר ב-Backend; ניטור ההפצה משולב ב-Message Monitoring.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="70" customHeight="1">
+      <c r="A16" s="89" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="90" t="inlineStr">
+        <is>
+          <t>SMQ1 / SMQ2</t>
+        </is>
+      </c>
+      <c r="C16" s="84" t="inlineStr">
+        <is>
+          <t>מוניטור תורים (qRFC Queues) - SMQ1 = תור יוצא (outbound); SMQ2 = תור נכנס (inbound). מעקב וטיפול בהודעות תקועות בתקשורת אסינכרונית בין SAP למערכות (CIF/MES).</t>
+        </is>
+      </c>
+      <c r="D16" s="84" t="inlineStr">
+        <is>
+          <t>נשמר; ניטור התורים גם דרך Fiori/Focused Run.</t>
+        </is>
+      </c>
+      <c r="E16" s="91" t="inlineStr">
+        <is>
+          <t>Monitor Outbound/Inbound Queues  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F16" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori ניטור התורים זמין בלוחות מרכזיים; טיפול בהודעות תקועות (requeue/delete) מבוסס תפקיד.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="70" customHeight="1">
+      <c r="A17" s="86" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="87" t="inlineStr">
+        <is>
+          <t>STMS / SE09 / SE10</t>
+        </is>
+      </c>
+      <c r="C17" s="79" t="inlineStr">
+        <is>
+          <t>ניהול תעבורה (Transport Management) - STMS = נוף התעבורה והעברת בקשות בין סביבות (DEV-&gt;QA-&gt;PRD); SE09/SE10 = ארגון בקשות התעבורה. ליבת ה-Change Management של הפרויקט.</t>
+        </is>
+      </c>
+      <c r="D17" s="79" t="inlineStr">
+        <is>
+          <t>נשמר On-Premise; ב-S/4 Cloud דרך 'Manage Software Collection' / Cloud Transport Management (BTP).</t>
+        </is>
+      </c>
+      <c r="E17" s="92" t="inlineStr">
+        <is>
+          <t>Export/Import Software Collection / cTMS  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F17" s="79" t="inlineStr">
+        <is>
+          <t>ב-S/4 Cloud התעבורה עוברת ל-Cloud Transport Management (BTP) ולכלי Fiori; On-Premise נשמר STMS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="70" customHeight="1">
+      <c r="A18" s="89" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="90" t="inlineStr">
+        <is>
+          <t>ST05 / SAT</t>
+        </is>
+      </c>
+      <c r="C18" s="84" t="inlineStr">
+        <is>
+          <t>כלי Trace וביצועים - ST05 = SQL/RFC/Buffer trace לניתוח ביצועי שאילתות וממשקים; SAT = ניתוח זמן ריצה (Runtime Analysis). חיוני לאופטימיזציה של דוחות וממשקים כבדים.</t>
+        </is>
+      </c>
+      <c r="D18" s="84" t="inlineStr">
+        <is>
+          <t>נשמר; ב-S/4 דגש על ביצועי HANA - בדוק שאילתות מול CDS/Code Pushdown.</t>
+        </is>
+      </c>
+      <c r="E18" s="91" t="inlineStr">
+        <is>
+          <t>(Performance - Backend/ADT)  (-)</t>
+        </is>
+      </c>
+      <c r="F18" s="84" t="inlineStr">
+        <is>
+          <t>ב-S/4 ניתוח הביצועים משולב ב-ADT וב-HANA tooling; ST05/SAT נשמרים ב-Backend לניתוח עמוק.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="70" customHeight="1">
+      <c r="A19" s="86" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>SLG1</t>
+        </is>
+      </c>
+      <c r="C19" s="79" t="inlineStr">
+        <is>
+          <t>יומן יישום (Application Log) - מציג הודעות, אזהרות ושגיאות שתוכניות/ממשקים רשמו (לדוגמה כשלי המרת BP, שגיאות MRP). כלי מעקב מרכזי לאבחון תהליכים ברקע.</t>
+        </is>
+      </c>
+      <c r="D19" s="79" t="inlineStr">
+        <is>
+          <t>נשמר; חלק מהלוגים נגישים גם דרך Fiori 'Application Logs'.</t>
+        </is>
+      </c>
+      <c r="E19" s="92" t="inlineStr">
+        <is>
+          <t>Display Application Logs  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F19" s="79" t="inlineStr">
+        <is>
+          <t>ב-Fiori 'Application Logs' מרכז את יומני היישום מבוסס תפקיד עם סינון לפי אובייקט/חומרת הודעה.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="70" customHeight="1">
+      <c r="A20" s="89" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="90" t="inlineStr">
+        <is>
+          <t>BP</t>
+        </is>
+      </c>
+      <c r="C20" s="84" t="inlineStr">
+        <is>
+          <t>שותף עסקי (Business Partner) - נקודת הכניסה היחידה לניהול לקוחות/ספקים ב-S/4HANA (מחליף XK01/MK01/XD01). ניהול תפקידים (Roles), קבוצות וכתובות. קריטי לספקי חומרי הגלם של CBC.</t>
+        </is>
+      </c>
+      <c r="D20" s="84" t="inlineStr">
+        <is>
+          <t>מחליף - ב-S/4 BP חובה; נדרש CVI להמרת LFA1/KNA1 ל-BUT000 (SAP Note 2265093).</t>
+        </is>
+      </c>
+      <c r="E20" s="91" t="inlineStr">
+        <is>
+          <t>Manage Business Partner Master Data  ((אמת ID))</t>
+        </is>
+      </c>
+      <c r="F20" s="84" t="inlineStr">
+        <is>
+          <t>ב-Fiori ניהול ה-BP מבוסס תפקיד עם Object Page לכל שותף; תפקידי ספק/לקוח מנוהלים כ-BP Roles באותה רשומה.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E8" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E10" r:id="rId4"/>
+  </hyperlinks>
+  <printOptions gridLines="0"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;"Segoe UI"&amp;8&amp;K6B7280CBC NEO - Implementer Toolkit - Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D62027"/>
@@ -46259,12 +51441,12 @@
       <c r="H2" s="4" t="n"/>
       <c r="I2" s="4" t="n"/>
       <c r="J2" s="4" t="n"/>
-      <c r="K2" s="86" t="inlineStr">
+      <c r="K2" s="94" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="L2" s="86" t="inlineStr">
+      <c r="L2" s="94" t="inlineStr">
         <is>
           <t>Count</t>
         </is>
@@ -46299,44 +51481,44 @@
       <c r="H3" s="4" t="n"/>
       <c r="I3" s="4" t="n"/>
       <c r="J3" s="4" t="n"/>
-      <c r="K3" s="87" t="inlineStr">
+      <c r="K3" s="95" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="L3" s="88">
+      <c r="L3" s="96">
         <f>COUNTIF($D$8:$D$75,$K3)</f>
         <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="n"/>
-      <c r="B4" s="89" t="inlineStr">
+      <c r="B4" s="97" t="inlineStr">
         <is>
           <t>סה"כ</t>
         </is>
       </c>
-      <c r="C4" s="90" t="inlineStr">
+      <c r="C4" s="98" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="D4" s="91" t="inlineStr">
+      <c r="D4" s="99" t="inlineStr">
         <is>
           <t>Tested</t>
         </is>
       </c>
-      <c r="E4" s="92" t="inlineStr">
+      <c r="E4" s="100" t="inlineStr">
         <is>
           <t>In Progress</t>
         </is>
       </c>
-      <c r="F4" s="93" t="inlineStr">
+      <c r="F4" s="101" t="inlineStr">
         <is>
           <t>Open</t>
         </is>
       </c>
-      <c r="G4" s="94" t="inlineStr">
+      <c r="G4" s="102" t="inlineStr">
         <is>
           <t>% Done</t>
         </is>
@@ -46344,12 +51526,12 @@
       <c r="H4" s="4" t="n"/>
       <c r="I4" s="4" t="n"/>
       <c r="J4" s="4" t="n"/>
-      <c r="K4" s="95" t="inlineStr">
+      <c r="K4" s="103" t="inlineStr">
         <is>
           <t>In analysis</t>
         </is>
       </c>
-      <c r="L4" s="88">
+      <c r="L4" s="96">
         <f>COUNTIF($D$8:$D$75,$K4)</f>
         <v/>
       </c>
@@ -46365,12 +51547,12 @@
       <c r="H5" s="4" t="n"/>
       <c r="I5" s="4" t="n"/>
       <c r="J5" s="4" t="n"/>
-      <c r="K5" s="96" t="inlineStr">
+      <c r="K5" s="104" t="inlineStr">
         <is>
           <t>In conversion</t>
         </is>
       </c>
-      <c r="L5" s="88">
+      <c r="L5" s="96">
         <f>COUNTIF($D$8:$D$75,$K5)</f>
         <v/>
       </c>
@@ -46386,12 +51568,12 @@
       <c r="H6" s="4" t="n"/>
       <c r="I6" s="4" t="n"/>
       <c r="J6" s="4" t="n"/>
-      <c r="K6" s="97" t="inlineStr">
+      <c r="K6" s="105" t="inlineStr">
         <is>
           <t>Tested</t>
         </is>
       </c>
-      <c r="L6" s="88">
+      <c r="L6" s="96">
         <f>COUNTIF($D$8:$D$75,$K6)</f>
         <v/>
       </c>
@@ -46431,12 +51613,12 @@
       <c r="H7" s="4" t="n"/>
       <c r="I7" s="4" t="n"/>
       <c r="J7" s="4" t="n"/>
-      <c r="K7" s="98" t="inlineStr">
+      <c r="K7" s="106" t="inlineStr">
         <is>
           <t>Done</t>
         </is>
       </c>
-      <c r="L7" s="88">
+      <c r="L7" s="96">
         <f>COUNTIF($D$8:$D$75,$K7)</f>
         <v/>
       </c>
@@ -46460,7 +51642,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E8" s="99">
+      <c r="E8" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A22","➜ פתח")</f>
         <v/>
       </c>
@@ -46495,7 +51677,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E9" s="100">
+      <c r="E9" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A32","➜ פתח")</f>
         <v/>
       </c>
@@ -46530,7 +51712,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E10" s="99">
+      <c r="E10" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A38","➜ פתח")</f>
         <v/>
       </c>
@@ -46565,7 +51747,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E11" s="100">
+      <c r="E11" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A48","➜ פתח")</f>
         <v/>
       </c>
@@ -46600,7 +51782,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E12" s="99">
+      <c r="E12" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A55","➜ פתח")</f>
         <v/>
       </c>
@@ -46635,7 +51817,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E13" s="100">
+      <c r="E13" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A63","➜ פתח")</f>
         <v/>
       </c>
@@ -46670,7 +51852,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E14" s="99">
+      <c r="E14" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A70","➜ פתח")</f>
         <v/>
       </c>
@@ -46705,7 +51887,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E15" s="100">
+      <c r="E15" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A78","➜ פתח")</f>
         <v/>
       </c>
@@ -46740,7 +51922,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E16" s="99">
+      <c r="E16" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A84","➜ פתח")</f>
         <v/>
       </c>
@@ -46775,7 +51957,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E17" s="100">
+      <c r="E17" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A89","➜ פתח")</f>
         <v/>
       </c>
@@ -46810,7 +51992,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E18" s="99">
+      <c r="E18" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A95","➜ פתח")</f>
         <v/>
       </c>
@@ -46845,7 +52027,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E19" s="100">
+      <c r="E19" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A101","➜ פתח")</f>
         <v/>
       </c>
@@ -46880,7 +52062,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E20" s="99">
+      <c r="E20" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A107","➜ פתח")</f>
         <v/>
       </c>
@@ -46915,7 +52097,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E21" s="100">
+      <c r="E21" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A113","➜ פתח")</f>
         <v/>
       </c>
@@ -46950,7 +52132,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E22" s="99">
+      <c r="E22" s="107">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A122","➜ פתח")</f>
         <v/>
       </c>
@@ -46985,7 +52167,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E23" s="100">
+      <c r="E23" s="108">
         <f>HYPERLINK("#'"&amp;"1. נתוני אב חומר ויחידות מידה ("&amp;"'!A128","➜ פתח")</f>
         <v/>
       </c>
@@ -47020,7 +52202,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E24" s="99">
+      <c r="E24" s="107">
         <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A21","➜ פתח")</f>
         <v/>
       </c>
@@ -47055,7 +52237,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E25" s="100">
+      <c r="E25" s="108">
         <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A28","➜ פתח")</f>
         <v/>
       </c>
@@ -47090,7 +52272,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E26" s="99">
+      <c r="E26" s="107">
         <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A36","➜ פתח")</f>
         <v/>
       </c>
@@ -47125,7 +52307,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E27" s="100">
+      <c r="E27" s="108">
         <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A47","➜ פתח")</f>
         <v/>
       </c>
@@ -47160,7 +52342,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E28" s="99">
+      <c r="E28" s="107">
         <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A54","➜ פתח")</f>
         <v/>
       </c>
@@ -47195,7 +52377,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E29" s="100">
+      <c r="E29" s="108">
         <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A60","➜ פתח")</f>
         <v/>
       </c>
@@ -47230,7 +52412,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E30" s="99">
+      <c r="E30" s="107">
         <f>HYPERLINK("#'"&amp;"2. עץ מוצר (BOM)"&amp;"'!A65","➜ פתח")</f>
         <v/>
       </c>
@@ -47265,7 +52447,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E31" s="100">
+      <c r="E31" s="108">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A21","➜ פתח")</f>
         <v/>
       </c>
@@ -47300,7 +52482,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E32" s="99">
+      <c r="E32" s="107">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A30","➜ פתח")</f>
         <v/>
       </c>
@@ -47335,7 +52517,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E33" s="100">
+      <c r="E33" s="108">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A41","➜ פתח")</f>
         <v/>
       </c>
@@ -47370,7 +52552,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E34" s="99">
+      <c r="E34" s="107">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A49","➜ פתח")</f>
         <v/>
       </c>
@@ -47405,7 +52587,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E35" s="100">
+      <c r="E35" s="108">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A55","➜ פתח")</f>
         <v/>
       </c>
@@ -47440,7 +52622,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E36" s="99">
+      <c r="E36" s="107">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A62","➜ פתח")</f>
         <v/>
       </c>
@@ -47475,7 +52657,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E37" s="100">
+      <c r="E37" s="108">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A70","➜ פתח")</f>
         <v/>
       </c>
@@ -47510,7 +52692,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E38" s="99">
+      <c r="E38" s="107">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A77","➜ פתח")</f>
         <v/>
       </c>
@@ -47545,7 +52727,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E39" s="100">
+      <c r="E39" s="108">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A83","➜ פתח")</f>
         <v/>
       </c>
@@ -47580,7 +52762,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E40" s="99">
+      <c r="E40" s="107">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A88","➜ פתח")</f>
         <v/>
       </c>
@@ -47615,7 +52797,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E41" s="100">
+      <c r="E41" s="108">
         <f>HYPERLINK("#'"&amp;"3. מתכון ייצור ופעולות (Master "&amp;"'!A93","➜ פתח")</f>
         <v/>
       </c>
@@ -47650,7 +52832,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E42" s="99">
+      <c r="E42" s="107">
         <f>HYPERLINK("#'"&amp;"4. גרסאות ייצור (Production Ver"&amp;"'!A19","➜ פתח")</f>
         <v/>
       </c>
@@ -47685,7 +52867,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E43" s="100">
+      <c r="E43" s="108">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A20","➜ פתח")</f>
         <v/>
       </c>
@@ -47720,7 +52902,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E44" s="99">
+      <c r="E44" s="107">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A29","➜ פתח")</f>
         <v/>
       </c>
@@ -47755,7 +52937,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E45" s="100">
+      <c r="E45" s="108">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A35","➜ פתח")</f>
         <v/>
       </c>
@@ -47790,7 +52972,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E46" s="99">
+      <c r="E46" s="107">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A43","➜ פתח")</f>
         <v/>
       </c>
@@ -47825,7 +53007,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E47" s="100">
+      <c r="E47" s="108">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A49","➜ פתח")</f>
         <v/>
       </c>
@@ -47860,7 +53042,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E48" s="99">
+      <c r="E48" s="107">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A55","➜ פתח")</f>
         <v/>
       </c>
@@ -47895,7 +53077,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E49" s="100">
+      <c r="E49" s="108">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A61","➜ פתח")</f>
         <v/>
       </c>
@@ -47930,7 +53112,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E50" s="99">
+      <c r="E50" s="107">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A66","➜ פתח")</f>
         <v/>
       </c>
@@ -47965,7 +53147,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E51" s="100">
+      <c r="E51" s="108">
         <f>HYPERLINK("#'"&amp;"5. משאבים  מרכזי עבודה (Resourc"&amp;"'!A71","➜ פתח")</f>
         <v/>
       </c>
@@ -48000,7 +53182,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E52" s="99">
+      <c r="E52" s="107">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A22","➜ פתח")</f>
         <v/>
       </c>
@@ -48035,7 +53217,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E53" s="100">
+      <c r="E53" s="108">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A29","➜ פתח")</f>
         <v/>
       </c>
@@ -48070,7 +53252,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E54" s="99">
+      <c r="E54" s="107">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A37","➜ פתח")</f>
         <v/>
       </c>
@@ -48105,7 +53287,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E55" s="100">
+      <c r="E55" s="108">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A44","➜ פתח")</f>
         <v/>
       </c>
@@ -48140,7 +53322,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E56" s="99">
+      <c r="E56" s="107">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A52","➜ פתח")</f>
         <v/>
       </c>
@@ -48175,7 +53357,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E57" s="100">
+      <c r="E57" s="108">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A60","➜ פתח")</f>
         <v/>
       </c>
@@ -48210,7 +53392,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E58" s="99">
+      <c r="E58" s="107">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A67","➜ פתח")</f>
         <v/>
       </c>
@@ -48245,7 +53427,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E59" s="100">
+      <c r="E59" s="108">
         <f>HYPERLINK("#'"&amp;"6. פק"ע ייצור ומתכון בקרה (Proc"&amp;"'!A72","➜ פתח")</f>
         <v/>
       </c>
@@ -48280,7 +53462,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E60" s="99">
+      <c r="E60" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A22","➜ פתח")</f>
         <v/>
       </c>
@@ -48315,7 +53497,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E61" s="100">
+      <c r="E61" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A27","➜ פתח")</f>
         <v/>
       </c>
@@ -48350,7 +53532,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E62" s="99">
+      <c r="E62" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A32","➜ פתח")</f>
         <v/>
       </c>
@@ -48385,7 +53567,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E63" s="100">
+      <c r="E63" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A36","➜ פתח")</f>
         <v/>
       </c>
@@ -48420,7 +53602,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E64" s="99">
+      <c r="E64" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A41","➜ פתח")</f>
         <v/>
       </c>
@@ -48455,7 +53637,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E65" s="100">
+      <c r="E65" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A47","➜ פתח")</f>
         <v/>
       </c>
@@ -48490,7 +53672,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E66" s="99">
+      <c r="E66" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A52","➜ פתח")</f>
         <v/>
       </c>
@@ -48525,7 +53707,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E67" s="100">
+      <c r="E67" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A56","➜ פתח")</f>
         <v/>
       </c>
@@ -48560,7 +53742,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E68" s="99">
+      <c r="E68" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A62","➜ פתח")</f>
         <v/>
       </c>
@@ -48595,7 +53777,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E69" s="100">
+      <c r="E69" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A68","➜ פתח")</f>
         <v/>
       </c>
@@ -48630,7 +53812,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E70" s="99">
+      <c r="E70" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A74","➜ פתח")</f>
         <v/>
       </c>
@@ -48665,7 +53847,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E71" s="100">
+      <c r="E71" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A81","➜ פתח")</f>
         <v/>
       </c>
@@ -48700,7 +53882,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E72" s="99">
+      <c r="E72" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A88","➜ פתח")</f>
         <v/>
       </c>
@@ -48735,7 +53917,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E73" s="100">
+      <c r="E73" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A94","➜ פתח")</f>
         <v/>
       </c>
@@ -48770,7 +53952,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E74" s="99">
+      <c r="E74" s="107">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A100","➜ פתח")</f>
         <v/>
       </c>
@@ -48805,7 +53987,7 @@
           <t>Not started</t>
         </is>
       </c>
-      <c r="E75" s="100">
+      <c r="E75" s="108">
         <f>HYPERLINK("#'"&amp;"7. קונפיגורציה (Customizing)"&amp;"'!A106","➜ פתח")</f>
         <v/>
       </c>
@@ -48856,7 +54038,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00D62027"/>
@@ -48912,12 +54094,12 @@
       <c r="A3" s="47" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="101" t="inlineStr">
+      <c r="B3" s="109" t="inlineStr">
         <is>
           <t>MAKT</t>
         </is>
       </c>
-      <c r="C3" s="102" t="inlineStr">
+      <c r="C3" s="110" t="inlineStr">
         <is>
           <t>FROM MAKT JOIN MARA ON MAKT.MATNR = MARA.MATNR</t>
         </is>
@@ -48932,12 +54114,12 @@
       <c r="A4" s="59" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="103" t="inlineStr">
+      <c r="B4" s="111" t="inlineStr">
         <is>
           <t>MARC</t>
         </is>
       </c>
-      <c r="C4" s="104" t="inlineStr">
+      <c r="C4" s="112" t="inlineStr">
         <is>
           <t>FROM MARC JOIN MARA ON MARC.MATNR = MARA.MATNR</t>
         </is>
@@ -48952,12 +54134,12 @@
       <c r="A5" s="47" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="101" t="inlineStr">
+      <c r="B5" s="109" t="inlineStr">
         <is>
           <t>MARD</t>
         </is>
       </c>
-      <c r="C5" s="102" t="inlineStr">
+      <c r="C5" s="110" t="inlineStr">
         <is>
           <t>FROM MARD JOIN MARC ON MARD.MATNR = MARC.MATNR AND MARD.WERKS = MARC.WERKS</t>
         </is>
@@ -48972,12 +54154,12 @@
       <c r="A6" s="59" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="103" t="inlineStr">
+      <c r="B6" s="111" t="inlineStr">
         <is>
           <t>MARM</t>
         </is>
       </c>
-      <c r="C6" s="104" t="inlineStr">
+      <c r="C6" s="112" t="inlineStr">
         <is>
           <t>FROM MARM JOIN MARA ON MARM.MATNR = MARA.MATNR</t>
         </is>
@@ -48992,12 +54174,12 @@
       <c r="A7" s="47" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="101" t="inlineStr">
+      <c r="B7" s="109" t="inlineStr">
         <is>
           <t>MEAN</t>
         </is>
       </c>
-      <c r="C7" s="102" t="inlineStr">
+      <c r="C7" s="110" t="inlineStr">
         <is>
           <t>FROM MEAN JOIN MARA ON MEAN.MATNR = MARA.MATNR</t>
         </is>
@@ -49012,12 +54194,12 @@
       <c r="A8" s="59" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="103" t="inlineStr">
+      <c r="B8" s="111" t="inlineStr">
         <is>
           <t>MBEW</t>
         </is>
       </c>
-      <c r="C8" s="104" t="inlineStr">
+      <c r="C8" s="112" t="inlineStr">
         <is>
           <t>FROM MBEW JOIN MARA ON MBEW.MATNR = MARA.MATNR</t>
         </is>
@@ -49032,12 +54214,12 @@
       <c r="A9" s="47" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="101" t="inlineStr">
+      <c r="B9" s="109" t="inlineStr">
         <is>
           <t>MVKE</t>
         </is>
       </c>
-      <c r="C9" s="102" t="inlineStr">
+      <c r="C9" s="110" t="inlineStr">
         <is>
           <t>FROM MVKE JOIN MARA ON MVKE.MATNR = MARA.MATNR</t>
         </is>
@@ -49052,12 +54234,12 @@
       <c r="A10" s="59" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="103" t="inlineStr">
+      <c r="B10" s="111" t="inlineStr">
         <is>
           <t>MLAN</t>
         </is>
       </c>
-      <c r="C10" s="104" t="inlineStr">
+      <c r="C10" s="112" t="inlineStr">
         <is>
           <t>FROM MLAN JOIN MARA ON MLAN.MATNR = MARA.MATNR</t>
         </is>
@@ -49072,12 +54254,12 @@
       <c r="A11" s="47" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="101" t="inlineStr">
+      <c r="B11" s="109" t="inlineStr">
         <is>
           <t>MLGN</t>
         </is>
       </c>
-      <c r="C11" s="102" t="inlineStr">
+      <c r="C11" s="110" t="inlineStr">
         <is>
           <t>FROM MLGN JOIN MARA ON MLGN.MATNR = MARA.MATNR</t>
         </is>
@@ -49092,12 +54274,12 @@
       <c r="A12" s="59" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="103" t="inlineStr">
+      <c r="B12" s="111" t="inlineStr">
         <is>
           <t>MLGT</t>
         </is>
       </c>
-      <c r="C12" s="104" t="inlineStr">
+      <c r="C12" s="112" t="inlineStr">
         <is>
           <t>FROM MLGT JOIN MLGN ON MLGT.MATNR = MLGN.MATNR AND MLGT.LGNUM = MLGN.LGNUM</t>
         </is>
@@ -49112,12 +54294,12 @@
       <c r="A13" s="47" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="101" t="inlineStr">
+      <c r="B13" s="109" t="inlineStr">
         <is>
           <t>MDMA</t>
         </is>
       </c>
-      <c r="C13" s="102" t="inlineStr">
+      <c r="C13" s="110" t="inlineStr">
         <is>
           <t>FROM MDMA JOIN MARC ON MDMA.MATNR = MARC.MATNR AND MDMA.WERKS = MARC.WERKS</t>
         </is>
@@ -49132,12 +54314,12 @@
       <c r="A14" s="59" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="103" t="inlineStr">
+      <c r="B14" s="111" t="inlineStr">
         <is>
           <t>QMAT</t>
         </is>
       </c>
-      <c r="C14" s="104" t="inlineStr">
+      <c r="C14" s="112" t="inlineStr">
         <is>
           <t>FROM QMAT JOIN MARC ON QMAT.MATNR = MARC.MATNR AND QMAT.WERKS = MARC.WERKS</t>
         </is>
@@ -49152,12 +54334,12 @@
       <c r="A15" s="47" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="101" t="inlineStr">
+      <c r="B15" s="109" t="inlineStr">
         <is>
           <t>MCH1</t>
         </is>
       </c>
-      <c r="C15" s="102" t="inlineStr">
+      <c r="C15" s="110" t="inlineStr">
         <is>
           <t>FROM MCH1 JOIN MARA ON MCH1.MATNR = MARA.MATNR</t>
         </is>
@@ -49172,12 +54354,12 @@
       <c r="A16" s="59" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="103" t="inlineStr">
+      <c r="B16" s="111" t="inlineStr">
         <is>
           <t>MCHA</t>
         </is>
       </c>
-      <c r="C16" s="104" t="inlineStr">
+      <c r="C16" s="112" t="inlineStr">
         <is>
           <t>FROM MCHA JOIN MCH1 ON MCHA.MATNR = MCH1.MATNR AND MCHA.CHARG = MCH1.CHARG</t>
         </is>
@@ -49192,12 +54374,12 @@
       <c r="A17" s="47" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="101" t="inlineStr">
+      <c r="B17" s="109" t="inlineStr">
         <is>
           <t>T006</t>
         </is>
       </c>
-      <c r="C17" s="102" t="inlineStr">
+      <c r="C17" s="110" t="inlineStr">
         <is>
           <t>FROM MARM JOIN T006 ON MARM.MEINH = T006.MSEHI</t>
         </is>
@@ -49212,12 +54394,12 @@
       <c r="A18" s="59" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="103" t="inlineStr">
+      <c r="B18" s="111" t="inlineStr">
         <is>
           <t>MAST</t>
         </is>
       </c>
-      <c r="C18" s="104" t="inlineStr">
+      <c r="C18" s="112" t="inlineStr">
         <is>
           <t>FROM MAST JOIN MARA ON MAST.MATNR = MARA.MATNR</t>
         </is>
@@ -49232,12 +54414,12 @@
       <c r="A19" s="47" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="101" t="inlineStr">
+      <c r="B19" s="109" t="inlineStr">
         <is>
           <t>STKO</t>
         </is>
       </c>
-      <c r="C19" s="102" t="inlineStr">
+      <c r="C19" s="110" t="inlineStr">
         <is>
           <t>FROM STKO JOIN MAST ON STKO.STLNR = MAST.STLNR</t>
         </is>
@@ -49252,12 +54434,12 @@
       <c r="A20" s="59" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="103" t="inlineStr">
+      <c r="B20" s="111" t="inlineStr">
         <is>
           <t>STPO</t>
         </is>
       </c>
-      <c r="C20" s="104" t="inlineStr">
+      <c r="C20" s="112" t="inlineStr">
         <is>
           <t>FROM STPO JOIN STKO ON STPO.STLNR = STKO.STLNR AND STPO.STLTY = STKO.STLTY</t>
         </is>
@@ -49272,12 +54454,12 @@
       <c r="A21" s="47" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="101" t="inlineStr">
+      <c r="B21" s="109" t="inlineStr">
         <is>
           <t>STAS</t>
         </is>
       </c>
-      <c r="C21" s="102" t="inlineStr">
+      <c r="C21" s="110" t="inlineStr">
         <is>
           <t>FROM STAS JOIN STKO ON STAS.STLNR = STKO.STLNR</t>
         </is>
@@ -49292,12 +54474,12 @@
       <c r="A22" s="59" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="103" t="inlineStr">
+      <c r="B22" s="111" t="inlineStr">
         <is>
           <t>STZU</t>
         </is>
       </c>
-      <c r="C22" s="104" t="inlineStr">
+      <c r="C22" s="112" t="inlineStr">
         <is>
           <t>FROM STZU JOIN STKO ON STZU.STLNR = STKO.STLNR</t>
         </is>
@@ -49312,12 +54494,12 @@
       <c r="A23" s="47" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="101" t="inlineStr">
+      <c r="B23" s="109" t="inlineStr">
         <is>
           <t>STPU</t>
         </is>
       </c>
-      <c r="C23" s="102" t="inlineStr">
+      <c r="C23" s="110" t="inlineStr">
         <is>
           <t>FROM STPU JOIN STPO ON STPU.STLKN = STPO.STLKN</t>
         </is>
@@ -49332,12 +54514,12 @@
       <c r="A24" s="59" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="103" t="inlineStr">
+      <c r="B24" s="111" t="inlineStr">
         <is>
           <t>KDST</t>
         </is>
       </c>
-      <c r="C24" s="104" t="inlineStr">
+      <c r="C24" s="112" t="inlineStr">
         <is>
           <t>FROM KDST JOIN MAST ON KDST.MATNR = MAST.MATNR</t>
         </is>
@@ -49352,12 +54534,12 @@
       <c r="A25" s="47" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="101" t="inlineStr">
+      <c r="B25" s="109" t="inlineStr">
         <is>
           <t>PLKO</t>
         </is>
       </c>
-      <c r="C25" s="102" t="inlineStr">
+      <c r="C25" s="110" t="inlineStr">
         <is>
           <t>FROM PLKO JOIN MAPL ON PLKO.PLNTY = MAPL.PLNTY AND PLKO.PLNNR = MAPL.PLNNR</t>
         </is>
@@ -49372,12 +54554,12 @@
       <c r="A26" s="59" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="103" t="inlineStr">
+      <c r="B26" s="111" t="inlineStr">
         <is>
           <t>PLPO</t>
         </is>
       </c>
-      <c r="C26" s="104" t="inlineStr">
+      <c r="C26" s="112" t="inlineStr">
         <is>
           <t>FROM PLPO JOIN PLAS ON PLPO.PLNTY = PLAS.PLNTY AND PLPO.PLNNR = PLAS.PLNNR AND PLPO.PLNKN = PLAS.PLNKN</t>
         </is>
@@ -49392,12 +54574,12 @@
       <c r="A27" s="47" t="n">
         <v>25</v>
       </c>
-      <c r="B27" s="101" t="inlineStr">
+      <c r="B27" s="109" t="inlineStr">
         <is>
           <t>PLAS</t>
         </is>
       </c>
-      <c r="C27" s="102" t="inlineStr">
+      <c r="C27" s="110" t="inlineStr">
         <is>
           <t>FROM PLAS JOIN PLKO ON PLAS.PLNTY = PLKO.PLNTY AND PLAS.PLNNR = PLKO.PLNNR</t>
         </is>
@@ -49412,12 +54594,12 @@
       <c r="A28" s="59" t="n">
         <v>26</v>
       </c>
-      <c r="B28" s="103" t="inlineStr">
+      <c r="B28" s="111" t="inlineStr">
         <is>
           <t>PLFL</t>
         </is>
       </c>
-      <c r="C28" s="104" t="inlineStr">
+      <c r="C28" s="112" t="inlineStr">
         <is>
           <t>FROM PLFL JOIN PLKO ON PLFL.PLNNR = PLKO.PLNNR</t>
         </is>
@@ -49432,12 +54614,12 @@
       <c r="A29" s="47" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="101" t="inlineStr">
+      <c r="B29" s="109" t="inlineStr">
         <is>
           <t>PLMZ</t>
         </is>
       </c>
-      <c r="C29" s="102" t="inlineStr">
+      <c r="C29" s="110" t="inlineStr">
         <is>
           <t>FROM PLMZ JOIN PLPO ON PLMZ.PLNKN = PLPO.PLNKN</t>
         </is>
@@ -49452,12 +54634,12 @@
       <c r="A30" s="59" t="n">
         <v>28</v>
       </c>
-      <c r="B30" s="103" t="inlineStr">
+      <c r="B30" s="111" t="inlineStr">
         <is>
           <t>PLMK</t>
         </is>
       </c>
-      <c r="C30" s="104" t="inlineStr">
+      <c r="C30" s="112" t="inlineStr">
         <is>
           <t>FROM PLMK JOIN PLPO ON PLMK.PLNKN = PLPO.PLNKN</t>
         </is>
@@ -49472,12 +54654,12 @@
       <c r="A31" s="47" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="101" t="inlineStr">
+      <c r="B31" s="109" t="inlineStr">
         <is>
           <t>MAPL</t>
         </is>
       </c>
-      <c r="C31" s="102" t="inlineStr">
+      <c r="C31" s="110" t="inlineStr">
         <is>
           <t>FROM MAPL JOIN MARC ON MAPL.MATNR = MARC.MATNR AND MAPL.WERKS = MARC.WERKS</t>
         </is>
@@ -49492,12 +54674,12 @@
       <c r="A32" s="59" t="n">
         <v>30</v>
       </c>
-      <c r="B32" s="103" t="inlineStr">
+      <c r="B32" s="111" t="inlineStr">
         <is>
           <t>FHMI</t>
         </is>
       </c>
-      <c r="C32" s="104" t="inlineStr">
+      <c r="C32" s="112" t="inlineStr">
         <is>
           <t>FROM FHMI JOIN PLPO ON FHMI.PLNKN = PLPO.PLNKN</t>
         </is>
@@ -49512,12 +54694,12 @@
       <c r="A33" s="47" t="n">
         <v>31</v>
       </c>
-      <c r="B33" s="101" t="inlineStr">
+      <c r="B33" s="109" t="inlineStr">
         <is>
           <t>PLZU</t>
         </is>
       </c>
-      <c r="C33" s="102" t="inlineStr">
+      <c r="C33" s="110" t="inlineStr">
         <is>
           <t>FROM PLZU JOIN PLKO ON PLZU.PLNNR = PLKO.PLNNR</t>
         </is>
@@ -49532,12 +54714,12 @@
       <c r="A34" s="59" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="103" t="inlineStr">
+      <c r="B34" s="111" t="inlineStr">
         <is>
           <t>TC60</t>
         </is>
       </c>
-      <c r="C34" s="104" t="inlineStr">
+      <c r="C34" s="112" t="inlineStr">
         <is>
           <t>FROM PLPO JOIN TC60 ON PLPO.STEUS = TC60.STEUS</t>
         </is>
@@ -49552,12 +54734,12 @@
       <c r="A35" s="47" t="n">
         <v>33</v>
       </c>
-      <c r="B35" s="101" t="inlineStr">
+      <c r="B35" s="109" t="inlineStr">
         <is>
           <t>TCA01</t>
         </is>
       </c>
-      <c r="C35" s="102" t="inlineStr">
+      <c r="C35" s="110" t="inlineStr">
         <is>
           <t>FROM PLKO JOIN TCA01 ON PLKO.PROFIDNETZ = TCA01.PROFIDNETZ</t>
         </is>
@@ -49572,12 +54754,12 @@
       <c r="A36" s="59" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="103" t="inlineStr">
+      <c r="B36" s="111" t="inlineStr">
         <is>
           <t>MKAL</t>
         </is>
       </c>
-      <c r="C36" s="104" t="inlineStr">
+      <c r="C36" s="112" t="inlineStr">
         <is>
           <t>FROM MKAL JOIN MARC ON MKAL.MATNR = MARC.MATNR AND MKAL.WERKS = MARC.WERKS</t>
         </is>
@@ -49592,12 +54774,12 @@
       <c r="A37" s="47" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="101" t="inlineStr">
+      <c r="B37" s="109" t="inlineStr">
         <is>
           <t>CRTX</t>
         </is>
       </c>
-      <c r="C37" s="102" t="inlineStr">
+      <c r="C37" s="110" t="inlineStr">
         <is>
           <t>FROM CRTX JOIN CRHD ON CRTX.OBJID = CRHD.OBJID AND CRTX.OBJTY = CRHD.OBJTY</t>
         </is>
@@ -49612,12 +54794,12 @@
       <c r="A38" s="59" t="n">
         <v>36</v>
       </c>
-      <c r="B38" s="103" t="inlineStr">
+      <c r="B38" s="111" t="inlineStr">
         <is>
           <t>CRCO</t>
         </is>
       </c>
-      <c r="C38" s="104" t="inlineStr">
+      <c r="C38" s="112" t="inlineStr">
         <is>
           <t>FROM CRCO JOIN CRHD ON CRCO.OBJID = CRHD.OBJID AND CRCO.OBJTY = CRHD.OBJTY</t>
         </is>
@@ -49632,12 +54814,12 @@
       <c r="A39" s="47" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="101" t="inlineStr">
+      <c r="B39" s="109" t="inlineStr">
         <is>
           <t>CRCA</t>
         </is>
       </c>
-      <c r="C39" s="102" t="inlineStr">
+      <c r="C39" s="110" t="inlineStr">
         <is>
           <t>FROM CRCA JOIN CRHD ON CRCA.OBJID = CRHD.OBJID AND CRCA.OBJTY = CRHD.OBJTY</t>
         </is>
@@ -49652,12 +54834,12 @@
       <c r="A40" s="59" t="n">
         <v>38</v>
       </c>
-      <c r="B40" s="103" t="inlineStr">
+      <c r="B40" s="111" t="inlineStr">
         <is>
           <t>KAKO</t>
         </is>
       </c>
-      <c r="C40" s="104" t="inlineStr">
+      <c r="C40" s="112" t="inlineStr">
         <is>
           <t>FROM KAKO JOIN CRCA ON KAKO.KAPID = CRCA.KAPID</t>
         </is>
@@ -49672,12 +54854,12 @@
       <c r="A41" s="47" t="n">
         <v>39</v>
       </c>
-      <c r="B41" s="101" t="inlineStr">
+      <c r="B41" s="109" t="inlineStr">
         <is>
           <t>CRFH</t>
         </is>
       </c>
-      <c r="C41" s="102" t="inlineStr">
+      <c r="C41" s="110" t="inlineStr">
         <is>
           <t>FROM FHMI JOIN CRFH ON FHMI.FHMNR = CRFH.FHMNR</t>
         </is>
@@ -49692,12 +54874,12 @@
       <c r="A42" s="59" t="n">
         <v>40</v>
       </c>
-      <c r="B42" s="103" t="inlineStr">
+      <c r="B42" s="111" t="inlineStr">
         <is>
           <t>CRVD_A</t>
         </is>
       </c>
-      <c r="C42" s="104" t="inlineStr">
+      <c r="C42" s="112" t="inlineStr">
         <is>
           <t>FROM CRVD_A JOIN CRHD ON CRVD_A.OBJID = CRHD.OBJID</t>
         </is>
@@ -49712,12 +54894,12 @@
       <c r="A43" s="47" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="101" t="inlineStr">
+      <c r="B43" s="109" t="inlineStr">
         <is>
           <t>CSLA</t>
         </is>
       </c>
-      <c r="C43" s="102" t="inlineStr">
+      <c r="C43" s="110" t="inlineStr">
         <is>
           <t>FROM CSLA JOIN CRCO ON CSLA.LSTAR = CRCO.LSTAR</t>
         </is>
@@ -49732,12 +54914,12 @@
       <c r="A44" s="59" t="n">
         <v>42</v>
       </c>
-      <c r="B44" s="103" t="inlineStr">
+      <c r="B44" s="111" t="inlineStr">
         <is>
           <t>KAZT</t>
         </is>
       </c>
-      <c r="C44" s="104" t="inlineStr">
+      <c r="C44" s="112" t="inlineStr">
         <is>
           <t>FROM KAZT JOIN KAKO ON KAZT.KAPID = KAKO.KAPID</t>
         </is>
@@ -49752,12 +54934,12 @@
       <c r="A45" s="47" t="n">
         <v>43</v>
       </c>
-      <c r="B45" s="101" t="inlineStr">
+      <c r="B45" s="109" t="inlineStr">
         <is>
           <t>AFKO</t>
         </is>
       </c>
-      <c r="C45" s="102" t="inlineStr">
+      <c r="C45" s="110" t="inlineStr">
         <is>
           <t>FROM AFKO JOIN AUFK ON AFKO.AUFNR = AUFK.AUFNR</t>
         </is>
@@ -49772,12 +54954,12 @@
       <c r="A46" s="59" t="n">
         <v>44</v>
       </c>
-      <c r="B46" s="103" t="inlineStr">
+      <c r="B46" s="111" t="inlineStr">
         <is>
           <t>AFPO</t>
         </is>
       </c>
-      <c r="C46" s="104" t="inlineStr">
+      <c r="C46" s="112" t="inlineStr">
         <is>
           <t>FROM AFPO JOIN AFKO ON AFPO.AUFNR = AFKO.AUFNR</t>
         </is>
@@ -49792,12 +54974,12 @@
       <c r="A47" s="47" t="n">
         <v>45</v>
       </c>
-      <c r="B47" s="101" t="inlineStr">
+      <c r="B47" s="109" t="inlineStr">
         <is>
           <t>AFVC</t>
         </is>
       </c>
-      <c r="C47" s="102" t="inlineStr">
+      <c r="C47" s="110" t="inlineStr">
         <is>
           <t>FROM AFVC JOIN AFKO ON AFVC.AUFPL = AFKO.AUFPL</t>
         </is>
@@ -49812,12 +54994,12 @@
       <c r="A48" s="59" t="n">
         <v>46</v>
       </c>
-      <c r="B48" s="103" t="inlineStr">
+      <c r="B48" s="111" t="inlineStr">
         <is>
           <t>RESB</t>
         </is>
       </c>
-      <c r="C48" s="104" t="inlineStr">
+      <c r="C48" s="112" t="inlineStr">
         <is>
           <t>FROM RESB JOIN AFKO ON RESB.AUFNR = AFKO.AUFNR</t>
         </is>
@@ -49832,12 +55014,12 @@
       <c r="A49" s="47" t="n">
         <v>47</v>
       </c>
-      <c r="B49" s="101" t="inlineStr">
+      <c r="B49" s="109" t="inlineStr">
         <is>
           <t>AFRU</t>
         </is>
       </c>
-      <c r="C49" s="102" t="inlineStr">
+      <c r="C49" s="110" t="inlineStr">
         <is>
           <t>FROM AFRU JOIN AFKO ON AFRU.AUFNR = AFKO.AUFNR</t>
         </is>
@@ -49852,12 +55034,12 @@
       <c r="A50" s="59" t="n">
         <v>48</v>
       </c>
-      <c r="B50" s="103" t="inlineStr">
+      <c r="B50" s="111" t="inlineStr">
         <is>
           <t>AFFH</t>
         </is>
       </c>
-      <c r="C50" s="104" t="inlineStr">
+      <c r="C50" s="112" t="inlineStr">
         <is>
           <t>FROM AFFH JOIN AFKO ON AFFH.AUFPL = AFKO.AUFPL</t>
         </is>
@@ -49872,12 +55054,12 @@
       <c r="A51" s="47" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="101" t="inlineStr">
+      <c r="B51" s="109" t="inlineStr">
         <is>
           <t>AFFL</t>
         </is>
       </c>
-      <c r="C51" s="102" t="inlineStr">
+      <c r="C51" s="110" t="inlineStr">
         <is>
           <t>FROM AFFL JOIN AFKO ON AFFL.AUFPL = AFKO.AUFPL</t>
         </is>
@@ -49892,12 +55074,12 @@
       <c r="A52" s="59" t="n">
         <v>50</v>
       </c>
-      <c r="B52" s="103" t="inlineStr">
+      <c r="B52" s="111" t="inlineStr">
         <is>
           <t>T134</t>
         </is>
       </c>
-      <c r="C52" s="104" t="inlineStr">
+      <c r="C52" s="112" t="inlineStr">
         <is>
           <t>FROM MARA JOIN T134 ON MARA.MTART = T134.MTART</t>
         </is>
@@ -49912,12 +55094,12 @@
       <c r="A53" s="47" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="101" t="inlineStr">
+      <c r="B53" s="109" t="inlineStr">
         <is>
           <t>T134T</t>
         </is>
       </c>
-      <c r="C53" s="102" t="inlineStr">
+      <c r="C53" s="110" t="inlineStr">
         <is>
           <t>FROM T134T JOIN T134 ON T134T.MTART = T134.MTART</t>
         </is>
@@ -49932,12 +55114,12 @@
       <c r="A54" s="59" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="103" t="inlineStr">
+      <c r="B54" s="111" t="inlineStr">
         <is>
           <t>T023</t>
         </is>
       </c>
-      <c r="C54" s="104" t="inlineStr">
+      <c r="C54" s="112" t="inlineStr">
         <is>
           <t>FROM MARA JOIN T023 ON MARA.MATKL = T023.MATKL</t>
         </is>
@@ -49952,12 +55134,12 @@
       <c r="A55" s="47" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="101" t="inlineStr">
+      <c r="B55" s="109" t="inlineStr">
         <is>
           <t>T023T</t>
         </is>
       </c>
-      <c r="C55" s="102" t="inlineStr">
+      <c r="C55" s="110" t="inlineStr">
         <is>
           <t>FROM T023T JOIN T023 ON T023T.MATKL = T023.MATKL</t>
         </is>
@@ -49972,12 +55154,12 @@
       <c r="A56" s="59" t="n">
         <v>54</v>
       </c>
-      <c r="B56" s="103" t="inlineStr">
+      <c r="B56" s="111" t="inlineStr">
         <is>
           <t>T399X</t>
         </is>
       </c>
-      <c r="C56" s="104" t="inlineStr">
+      <c r="C56" s="112" t="inlineStr">
         <is>
           <t>FROM AUFK JOIN T399X ON AUFK.WERKS = T399X.WERKS AND AUFK.AUART = T399X.AUART</t>
         </is>
@@ -49992,12 +55174,12 @@
       <c r="A57" s="47" t="n">
         <v>55</v>
       </c>
-      <c r="B57" s="101" t="inlineStr">
+      <c r="B57" s="109" t="inlineStr">
         <is>
           <t>TCK03</t>
         </is>
       </c>
-      <c r="C57" s="102" t="inlineStr">
+      <c r="C57" s="110" t="inlineStr">
         <is>
           <t>FROM T399X JOIN TCK03 ON T399X.KLVARP = TCK03.KLVAR</t>
         </is>
@@ -50012,12 +55194,12 @@
       <c r="A58" s="59" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="103" t="inlineStr">
+      <c r="B58" s="111" t="inlineStr">
         <is>
           <t>T438M</t>
         </is>
       </c>
-      <c r="C58" s="104" t="inlineStr">
+      <c r="C58" s="112" t="inlineStr">
         <is>
           <t>FROM MARC JOIN T438M ON MARC.DISMM = T438M.DISMM</t>
         </is>
@@ -50032,12 +55214,12 @@
       <c r="A59" s="47" t="n">
         <v>57</v>
       </c>
-      <c r="B59" s="101" t="inlineStr">
+      <c r="B59" s="109" t="inlineStr">
         <is>
           <t>T003O</t>
         </is>
       </c>
-      <c r="C59" s="102" t="inlineStr">
+      <c r="C59" s="110" t="inlineStr">
         <is>
           <t>FROM AUFK JOIN T003O ON AUFK.AUART = T003O.AUART</t>
         </is>
@@ -50052,12 +55234,12 @@
       <c r="A60" s="59" t="n">
         <v>58</v>
       </c>
-      <c r="B60" s="103" t="inlineStr">
+      <c r="B60" s="111" t="inlineStr">
         <is>
           <t>TCO01</t>
         </is>
       </c>
-      <c r="C60" s="104" t="inlineStr">
+      <c r="C60" s="112" t="inlineStr">
         <is>
           <t>FROM TCO01 JOIN T003O ON TCO01.AUART = T003O.AUART</t>
         </is>
@@ -50072,12 +55254,12 @@
       <c r="A61" s="47" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="101" t="inlineStr">
+      <c r="B61" s="109" t="inlineStr">
         <is>
           <t>TJ30</t>
         </is>
       </c>
-      <c r="C61" s="102" t="inlineStr">
+      <c r="C61" s="110" t="inlineStr">
         <is>
           <t>FROM JEST JOIN TJ30 ON JEST.STAT = TJ30.ESTAT</t>
         </is>
@@ -50092,12 +55274,12 @@
       <c r="A62" s="59" t="n">
         <v>60</v>
       </c>
-      <c r="B62" s="103" t="inlineStr">
+      <c r="B62" s="111" t="inlineStr">
         <is>
           <t>TJ30T</t>
         </is>
       </c>
-      <c r="C62" s="104" t="inlineStr">
+      <c r="C62" s="112" t="inlineStr">
         <is>
           <t>FROM TJ30T JOIN TJ30 ON TJ30T.STSMA = TJ30.STSMA AND TJ30T.ESTAT = TJ30.ESTAT</t>
         </is>
@@ -50112,12 +55294,12 @@
       <c r="A63" s="47" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="101" t="inlineStr">
+      <c r="B63" s="109" t="inlineStr">
         <is>
           <t>BUT000</t>
         </is>
       </c>
-      <c r="C63" s="102" t="inlineStr">
+      <c r="C63" s="110" t="inlineStr">
         <is>
           <t>FROM EKKO JOIN BUT000 ON EKKO.LIFNR = BUT000.PARTNER</t>
         </is>
@@ -50132,12 +55314,12 @@
       <c r="A64" s="59" t="n">
         <v>62</v>
       </c>
-      <c r="B64" s="103" t="inlineStr">
+      <c r="B64" s="111" t="inlineStr">
         <is>
           <t>TC22</t>
         </is>
       </c>
-      <c r="C64" s="104" t="inlineStr">
+      <c r="C64" s="112" t="inlineStr">
         <is>
           <t>FROM PLPO JOIN TC22 ON PLPO.STEUS = TC22.STEUS</t>
         </is>
@@ -50152,12 +55334,12 @@
       <c r="A65" s="47" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="101" t="inlineStr">
+      <c r="B65" s="109" t="inlineStr">
         <is>
           <t>JEST</t>
         </is>
       </c>
-      <c r="C65" s="102" t="inlineStr">
+      <c r="C65" s="110" t="inlineStr">
         <is>
           <t>FROM JEST JOIN AUFK ON JEST.OBJNR = AUFK.OBJNR</t>
         </is>
@@ -50172,12 +55354,12 @@
       <c r="A66" s="59" t="n">
         <v>64</v>
       </c>
-      <c r="B66" s="103" t="inlineStr">
+      <c r="B66" s="111" t="inlineStr">
         <is>
           <t>JSTO</t>
         </is>
       </c>
-      <c r="C66" s="104" t="inlineStr">
+      <c r="C66" s="112" t="inlineStr">
         <is>
           <t>FROM JSTO JOIN AUFK ON JSTO.OBJNR = AUFK.OBJNR</t>
         </is>
@@ -50192,12 +55374,12 @@
       <c r="A67" s="47" t="n">
         <v>65</v>
       </c>
-      <c r="B67" s="101" t="inlineStr">
+      <c r="B67" s="109" t="inlineStr">
         <is>
           <t>TJ02T</t>
         </is>
       </c>
-      <c r="C67" s="102" t="inlineStr">
+      <c r="C67" s="110" t="inlineStr">
         <is>
           <t>FROM JEST JOIN TJ02T ON JEST.STAT = TJ02T.ISTAT</t>
         </is>
